--- a/BSI.IT.6.C7.3-Evidences/BSI.IT.6.C7.3_E00_Workpaper_DR_DIV_INTEGRATED_APPLICATION_Evidence.xlsx
+++ b/BSI.IT.6.C7.3-Evidences/BSI.IT.6.C7.3_E00_Workpaper_DR_DIV_INTEGRATED_APPLICATION_Evidence.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BSI.IT.6.C7.3 Evidence Index" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'BSI.IT.6.C7.3 Evidence Index'!$A$2:$K$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'BSI.IT.6.C7.3 Evidence Index'!$A$2:$K$44</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="F16" s="51" t="inlineStr">
         <is>
-          <t>BLA01–BLA06 (BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email); DMA01–DMA12 (BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals); E09; E12; E03 approval fields</t>
+          <t>BLA01–BLA06 (BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email); DMA01–DMA12 (BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals); E09; E03 approval fields</t>
         </is>
       </c>
       <c r="G16" s="53" t="inlineStr">
@@ -2404,7 +2404,7 @@
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 3 – Exercise Date 12/11/25, 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 47 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – row 48 – Business Data Validation Date 11/15/2025
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml – request email states DR exercises conducted 11/15/2025 and 02/21/2026 (failover Miami-Telefonica → DR site)
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted Cesar Vidal request 08/17/2026 states DR exercises conducted 11/15/2025 and 02/21/2026 (failover Miami-Telefonica → DR site)
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – script header DATE: 11/15/2025</t>
         </is>
       </c>
@@ -2414,7 +2414,7 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 3 – 2025 DR Test Scope = True, Exercise Date 12/11/2025
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 47 – Business Data Validation Date 11/15/2025
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 Background: 'the IT DR team facilitates, on an annual basis, data integrity validation testing'</t>
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 Background: 'the IT DR team facilitates, on an annual basis, data integrity validation testing'</t>
         </is>
       </c>
       <c r="D5" s="45" t="inlineStr">
@@ -2506,8 +2506,8 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 3 – Exercise Date 12/11/2025 / 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 47 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml – DR exercises 11/15/2025 and 02/21/2026
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – dated 11/15/2025</t>
         </is>
       </c>
@@ -2517,7 +2517,7 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review 09/15/2025
 • E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – follow-up 09/18/2025
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg – IT DR (Elizabeth Noda) issued test script, collected evidence and requested approval
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 47 – Y/N Format, Headers, Content = Y</t>
@@ -2532,7 +2532,7 @@
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
 • E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – BIA results &amp; applications list review
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg – scope table: application → Client Back Office → Claudia Romero</t>
         </is>
       </c>
@@ -2554,7 +2554,7 @@
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 47
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – row 48
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – BCiC report screen (record on a later page of the 66-item report)
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="Q5" s="49" t="inlineStr">
@@ -2574,6 +2574,8 @@
 [03 DIV Manager Attestation Email Approvals]
 DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
 DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
+DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
+DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 [04 Data Integrity &amp; Email Testing Evidence]
 E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx
 E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg
@@ -2582,8 +2584,6 @@
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
 E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml
 E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml
-E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
         </is>
       </c>
@@ -2651,7 +2651,7 @@
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 19 – Exercise Date 12/11/25, 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 9 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – row 9 – Business Data Validation Date 11/15/2025
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml – request email states DR exercises conducted 11/15/2025 and 02/21/2026 (failover Miami-Telefonica → DR site)
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted Cesar Vidal request 08/17/2026 states DR exercises conducted 11/15/2025 and 02/21/2026 (failover Miami-Telefonica → DR site)
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – script header DATE: 11/15/2025</t>
         </is>
       </c>
@@ -2661,7 +2661,7 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 19 – 2025 DR Test Scope = True, Exercise Date 12/11/2025
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 9 – Business Data Validation Date 11/15/2025
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 Background: 'the IT DR team facilitates, on an annual basis, data integrity validation testing'</t>
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 Background: 'the IT DR team facilitates, on an annual basis, data integrity validation testing'</t>
         </is>
       </c>
       <c r="D6" s="45" t="inlineStr">
@@ -2757,8 +2757,8 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 19 – Exercise Date 12/11/2025 / 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 9 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml – DR exercises 11/15/2025 and 02/21/2026
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – dated 11/15/2025</t>
         </is>
       </c>
@@ -2768,7 +2768,7 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review 09/15/2025
 • E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – follow-up 09/18/2025
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg – IT DR (Elizabeth Noda) issued test script, collected evidence and requested approval
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 9 – Y/N Format, Headers, Content = Y</t>
@@ -2783,7 +2783,7 @@
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
 • E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – BIA results &amp; applications list review
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg – scope table: application → Client Back Office → Claudia Romero</t>
         </is>
       </c>
@@ -2805,7 +2805,7 @@
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 9
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – row 9
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – record(s) visible on screen
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="Q6" s="49" t="inlineStr">
@@ -2825,6 +2825,8 @@
 [03 DIV Manager Attestation Email Approvals]
 DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
 DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
+DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
+DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 [04 Data Integrity &amp; Email Testing Evidence]
 E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx
 E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg
@@ -2833,8 +2835,6 @@
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
 E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml
 E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml
-E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
         </is>
       </c>
@@ -2902,7 +2902,7 @@
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 20 – Exercise Date 12/11/25, 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 10 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – row 10 – Business Data Validation Date 11/15/2025
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml – request email states DR exercises conducted 11/15/2025 and 02/21/2026 (failover Miami-Telefonica → DR site)
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted Cesar Vidal request 08/17/2026 states DR exercises conducted 11/15/2025 and 02/21/2026 (failover Miami-Telefonica → DR site)
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – script header DATE: 11/15/2025</t>
         </is>
       </c>
@@ -2912,7 +2912,7 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 20 – 2025 DR Test Scope = True, Exercise Date 12/11/2025
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 10 – Business Data Validation Date 11/15/2025
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 Background: 'the IT DR team facilitates, on an annual basis, data integrity validation testing'</t>
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 Background: 'the IT DR team facilitates, on an annual basis, data integrity validation testing'</t>
         </is>
       </c>
       <c r="D7" s="45" t="inlineStr">
@@ -3008,8 +3008,8 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 20 – Exercise Date 12/11/2025 / 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 10 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml – DR exercises 11/15/2025 and 02/21/2026
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – dated 11/15/2025</t>
         </is>
       </c>
@@ -3019,7 +3019,7 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review 09/15/2025
 • E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – follow-up 09/18/2025
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg – IT DR (Elizabeth Noda) issued test script, collected evidence and requested approval
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 10 – Y/N Format, Headers, Content = Y</t>
@@ -3034,7 +3034,7 @@
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
 • E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – BIA results &amp; applications list review
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg – scope table: application → Client Back Office → Claudia Romero</t>
         </is>
       </c>
@@ -3056,7 +3056,7 @@
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 10
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – row 10
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – record(s) visible on screen
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="Q7" s="49" t="inlineStr">
@@ -3075,6 +3075,8 @@
 [03 DIV Manager Attestation Email Approvals]
 DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
 DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
+DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
+DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 [04 Data Integrity &amp; Email Testing Evidence]
 E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx
 E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg
@@ -3083,8 +3085,6 @@
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
 E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml
 E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml
-E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
         </is>
       </c>
@@ -3152,7 +3152,7 @@
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 24 – Exercise Date 11/15/25, 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 5, 11, 13, 51, 53, 57 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – rows 5, 11, 13, 52, 54, 58 – Business Data Validation Date 11/15/2025
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml – request email states DR exercises conducted 11/15/2025 and 02/21/2026 (failover Miami-Telefonica → DR site)
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted Cesar Vidal request 08/17/2026 states DR exercises conducted 11/15/2025 and 02/21/2026 (failover Miami-Telefonica → DR site)
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – script header DATE: 11/15/2025
 • BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf – script header DATE: 11/15/2025</t>
         </is>
@@ -3163,7 +3163,7 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 24 – 2025 DR Test Scope = True, Exercise Date 11/15/2025
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 5, 11, 13, 51, 53, 57 – Business Data Validation Date 11/15/2025
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 Background: 'the IT DR team facilitates, on an annual basis, data integrity validation testing'</t>
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 Background: 'the IT DR team facilitates, on an annual basis, data integrity validation testing'</t>
         </is>
       </c>
       <c r="D8" s="45" t="inlineStr">
@@ -3236,16 +3236,12 @@
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – Department Manager Approval Date column
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
 • DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
 • DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
 • DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
 • DMA11 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
 • DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-• DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf
-• E16 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 2 (1).msg.eml
-• E16a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16a_Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+• DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
         </is>
       </c>
       <c r="I8" s="45" t="inlineStr">
@@ -3267,23 +3263,19 @@
       <c r="J8" s="45" t="inlineStr">
         <is>
           <t>Yes – application-specific business line manager approval evidence obtained for every DIV record:
-David Marquez: DMA02/E14 email + DMA02a/E14a signed attestation 08/19/2026
+David Marquez: DMA02 email + DMA02a signed attestation 08/19/2026
 Claudia Romero: E09 email "Approved." 05/05/2026 (Client Back Office results); DMA01/DMA01a signed attestation 08/18/2026
 Miguel Orozco: DMA11 email "I approve the integrity validation…" 09/09/2026
-Maria del Cerro Hontanilla: DMA05/E16 email + DMA05a/E16a signed attestation 08/19/2026
+Maria del Cerro Hontanilla: DMA05 email + DMA05a signed attestation 08/19/2026
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
 • DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
 • DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
 • DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
 • DMA11 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
 • DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-• DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf
-• E16 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 2 (1).msg.eml
-• E16a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16a_Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+• DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
         </is>
       </c>
       <c r="K8" s="46" t="inlineStr">
@@ -3304,8 +3296,8 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 24 – Exercise Date 11/15/2025 / 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 5, 11, 13, 51, 53, 57 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml – DR exercises 11/15/2025 and 02/21/2026
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – dated 11/15/2025
 • BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf – dated 11/15/2025</t>
         </is>
@@ -3316,7 +3308,7 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review 09/15/2025
 • E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – follow-up 09/18/2025
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg – IT DR (Elizabeth Noda) issued test script, collected evidence and requested approval
@@ -3332,7 +3324,7 @@
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
 • E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – BIA results &amp; applications list review
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg – scope table: application → Client Back Office → Claudia Romero</t>
         </is>
       </c>
@@ -3344,16 +3336,12 @@
 • BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf – business line DIV results document – 11/15/2025 – BSA/AML/OFAC Compliance (operator David Marquez)
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
 • DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
 • DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
 • DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
 • DMA11 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
 • DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
 • DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf
-• E16 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 2 (1).msg.eml
-• E16a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16a_Data_Integrity_Attestation_Santander-BCiC.pdf
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 5, 11, 13, 51, 53, 57 – Department Manager / Approval Date / Attestation fields</t>
         </is>
       </c>
@@ -3364,17 +3352,17 @@
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 5, 11, 13, 51, 53, 57
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – rows 5, 11, 13, 52, 54, 58
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – record(s) visible on screen
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="Q8" s="49" t="inlineStr">
         <is>
           <t>PASS – all five control attributes satisfied (Annual Testing Executed, DIV Performed by IT DR Team, Applications in Scope Identified, Business Line Approval of Results, Results Documented in BCMS).
 Observations (do not change the attribute conclusions – reviewer to confirm):
-1. Timing – Miguel Orozco: 1 record(s), BCiC approval 09/09/2026; Maria del Cerro Hontanilla: 2 record(s), BCiC approval 08/19/2026 – business line approval obtained after the review period end (06/01/2026) through retrospective management attestation (E14a §3.6 commits to contemporaneous approval going forward).
+1. Timing – Miguel Orozco: 1 record(s), BCiC approval 09/09/2026; Maria del Cerro Hontanilla: 2 record(s), BCiC approval 08/19/2026 – business line approval obtained after the review period end (06/01/2026) through retrospective management attestation (DMA02a §3.6 commits to contemporaneous approval going forward).
 2. Approval evidence – David Marquez: 1 record(s), BCiC approval 11/15/2025 (in period) confirmed by signed attestation 08/19/2026 – no contemporaneous approval email for the BCiC approval date is in the package; approval is confirmed retrospectively.
 3. Segregation – business tester and approving manager are the same person for: David Marquez, Miguel Orozco.
-4. Results document – BLA02 (BSA/AML/OFAC) DIV Yes/No boxes are blank; mitigated by BLA02 production vs test-day screenshots, BCiC Y/Y/Y (E03) and David Marquez signed attestation (E14a).</t>
+4. Results document – BLA02 (BSA/AML/OFAC) DIV Yes/No boxes are blank; mitigated by BLA02 production vs test-day screenshots, BCiC Y/Y/Y (E03) and David Marquez signed attestation (DMA02a).</t>
         </is>
       </c>
       <c r="R8" s="43" t="inlineStr">
@@ -3400,10 +3388,6 @@
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
 E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml
 E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml
-E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
-E16 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 2 (1).msg.eml
-E16a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16a_Data_Integrity_Attestation_Santander-BCiC.pdf
 E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
         </is>
       </c>
@@ -3460,7 +3444,7 @@
       <c r="BM8" s="58" t="n"/>
       <c r="BN8" s="58" t="n"/>
     </row>
-    <row r="9" ht="404" customFormat="1" customHeight="1" s="39">
+    <row r="9" ht="356" customFormat="1" customHeight="1" s="39">
       <c r="A9" s="45" t="n">
         <v>4052</v>
       </c>
@@ -3471,7 +3455,7 @@
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 25 – Exercise Date 11/15/25, 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 61 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – row 62 – Business Data Validation Date 11/15/2025
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml – request email states DR exercises conducted 11/15/2025 and 02/21/2026 (failover Miami-Telefonica → DR site)
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted Cesar Vidal request 08/17/2026 states DR exercises conducted 11/15/2025 and 02/21/2026 (failover Miami-Telefonica → DR site)
 • BLA04 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx – script header DATE: 11/15/2025</t>
         </is>
       </c>
@@ -3481,7 +3465,7 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 25 – 2025 DR Test Scope = True, Exercise Date 11/15/2025
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 61 – Business Data Validation Date 11/15/2025
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 Background: 'the IT DR team facilitates, on an annual basis, data integrity validation testing'</t>
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 Background: 'the IT DR team facilitates, on an annual basis, data integrity validation testing'</t>
         </is>
       </c>
       <c r="D9" s="45" t="inlineStr">
@@ -3530,9 +3514,7 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 61 – 'Department Manager Approval Date' and 'Attestation Date' columns
 • DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-• DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf
-• E15 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 1 (1).msg.eml
-• E15a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15a_Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+• DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
         </is>
       </c>
       <c r="I9" s="45" t="inlineStr">
@@ -3548,12 +3530,10 @@
       <c r="J9" s="45" t="inlineStr">
         <is>
           <t>Yes – application-specific business line manager approval evidence obtained for every DIV record:
-Michelle Oropesa: DMA04/E15 email + DMA04a/E15a signed attestation 08/17/2026
+Michelle Oropesa: DMA04 email + DMA04a signed attestation 08/17/2026
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-• DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf
-• E15 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 1 (1).msg.eml
-• E15a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15a_Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+• DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
         </is>
       </c>
       <c r="K9" s="46" t="inlineStr">
@@ -3574,8 +3554,8 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 25 – Exercise Date 11/15/2025 / 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 61 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml – DR exercises 11/15/2025 and 02/21/2026
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
 • BLA04 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx – dated 11/15/2025</t>
         </is>
       </c>
@@ -3585,7 +3565,7 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review 09/15/2025
 • E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – follow-up 09/18/2025
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
 • BLA04 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx – IT DR test script completed by the business-line tester
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 61 – Y/N Format, Headers, Content = Y</t>
         </is>
@@ -3599,7 +3579,7 @@
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
 • E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – BIA results &amp; applications list review
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data</t>
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data</t>
         </is>
       </c>
       <c r="O9" s="69" t="inlineStr">
@@ -3609,8 +3589,6 @@
 • BLA04 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx – business line DIV results document – 11/15/2025 – Investment Operations (operator Michelle Oropesa)
 • DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
 • DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf
-• E15 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 1 (1).msg.eml
-• E15a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15a_Data_Integrity_Attestation_Santander-BCiC.pdf
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 61 – Department Manager / Approval Date / Attestation fields</t>
         </is>
       </c>
@@ -3621,14 +3599,14 @@
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 61
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – row 62
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – BCiC report screen (record on a later page of the 66-item report)
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="Q9" s="49" t="inlineStr">
         <is>
           <t>PASS – all five control attributes satisfied (Annual Testing Executed, DIV Performed by IT DR Team, Applications in Scope Identified, Business Line Approval of Results, Results Documented in BCMS).
 Observations (do not change the attribute conclusions – reviewer to confirm):
-1. Timing – Michelle Oropesa: 1 record(s), BCiC approval 08/17/2026 – business line approval obtained after the review period end (06/01/2026) through retrospective management attestation (E14a §3.6 commits to contemporaneous approval going forward).
+1. Timing – Michelle Oropesa: 1 record(s), BCiC approval 08/17/2026 – business line approval obtained after the review period end (06/01/2026) through retrospective management attestation (DMA02a §3.6 commits to contemporaneous approval going forward).
 2. Segregation – business tester and approving manager are the same person for: Michelle Oropesa.
 3. Scope wording – BLA04 names "Swift Interface Monitor – BSI" / "Swift Interface – BSI" rather than "Interface Monitor"; BCiC full name of 1936 is "Interface Monitor::Swift Interface - BSI" (MA01). DIV record: E03 row 61.</t>
         </is>
@@ -3640,6 +3618,8 @@
 [02 Business Line Approval Results – Email]
 BLA04 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx
 [03 DIV Manager Attestation Email Approvals]
+DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
+DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
 DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf
 [04 Data Integrity &amp; Email Testing Evidence]
@@ -3649,10 +3629,6 @@
 E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
 E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml
-E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml
-E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
-E15 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 1 (1).msg.eml
-E15a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15a_Data_Integrity_Attestation_Santander-BCiC.pdf
 E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
         </is>
       </c>
@@ -3709,7 +3685,7 @@
       <c r="BM9" s="58" t="n"/>
       <c r="BN9" s="58" t="n"/>
     </row>
-    <row r="10" ht="409" customFormat="1" customHeight="1" s="39">
+    <row r="10" ht="404" customFormat="1" customHeight="1" s="39">
       <c r="A10" s="45" t="n">
         <v>3301</v>
       </c>
@@ -3720,7 +3696,7 @@
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 31 – Exercise Date 11/15/25, 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 25, 29 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – rows 25, 29 – Business Data Validation Date 11/15/2025
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml – request email states DR exercises conducted 11/15/2025 and 02/21/2026 (failover Miami-Telefonica → DR site)
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted Cesar Vidal request 08/17/2026 states DR exercises conducted 11/15/2025 and 02/21/2026 (failover Miami-Telefonica → DR site)
 • BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – script header DATE: 11/15/2025</t>
         </is>
       </c>
@@ -3730,7 +3706,7 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 31 – 2025 DR Test Scope = True, Exercise Date 11/15/2025
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 25, 29 – Business Data Validation Date 11/15/2025
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 Background: 'the IT DR team facilitates, on an annual basis, data integrity validation testing'</t>
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 Background: 'the IT DR team facilitates, on an annual basis, data integrity validation testing'</t>
         </is>
       </c>
       <c r="D10" s="45" t="inlineStr">
@@ -3781,10 +3757,7 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 25, 29 – 'Department Manager Approval Date' and 'Attestation Date' columns
 • DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-• DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf
-• E17 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 3 (1).msg.eml
-• E17a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17a_4069_001.pdf
-• MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg</t>
+• DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf</t>
         </is>
       </c>
       <c r="I10" s="45" t="inlineStr">
@@ -3801,13 +3774,10 @@
       <c r="J10" s="45" t="inlineStr">
         <is>
           <t>Yes – application-specific business line manager approval evidence obtained for every DIV record:
-Franklin Puentes: DMA03/E17/MA02 email + DMA03a/E17a signed attestation 08/18/2026
+Franklin Puentes: DMA03 email + DMA03a signed attestation 08/18/2026
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-• DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf
-• E17 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 3 (1).msg.eml
-• E17a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17a_4069_001.pdf
-• MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg</t>
+• DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf</t>
         </is>
       </c>
       <c r="K10" s="46" t="inlineStr">
@@ -3828,8 +3798,8 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 31 – Exercise Date 11/15/2025 / 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 25, 29 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml – DR exercises 11/15/2025 and 02/21/2026
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
 • BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – dated 11/15/2025</t>
         </is>
       </c>
@@ -3839,7 +3809,7 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review 09/15/2025
 • E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – follow-up 09/18/2025
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
 • BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • E08 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg – business-line DIV comparison files sent to IT DR (Elizabeth Noda) on 11/15/2025
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 25, 29 – Y/N Format, Headers, Content = Y</t>
@@ -3854,7 +3824,7 @@
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
 • E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – BIA results &amp; applications list review
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data</t>
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data</t>
         </is>
       </c>
       <c r="O10" s="69" t="inlineStr">
@@ -3864,9 +3834,6 @@
 • BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – business line DIV results document – 11/15/2025 – Payments &amp; Position Management (operators Frank Puentes / Gustavo Bucaro)
 • DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
 • DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf
-• E17 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 3 (1).msg.eml
-• E17a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17a_4069_001.pdf
-• MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 25, 29 – Department Manager / Approval Date / Attestation fields</t>
         </is>
       </c>
@@ -3877,7 +3844,7 @@
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 25, 29
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – rows 25, 29
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – BCiC report screen (record on a later page of the 66-item report)
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="Q10" s="49" t="inlineStr">
@@ -3892,10 +3859,11 @@
         <is>
           <t>[01 Management Attestation / In-Scope Applications]
 MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
-MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg
 [02 Business Line Approval Results – Email]
 BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf
 [03 DIV Manager Attestation Email Approvals]
+DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
+DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
 DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf
 [04 Data Integrity &amp; Email Testing Evidence]
@@ -3907,11 +3875,7 @@
 E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml
 E07 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg
 E08 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg
-E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml
-E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
-E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx
-E17 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 3 (1).msg.eml
-E17a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17a_4069_001.pdf</t>
+E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
         </is>
       </c>
       <c r="S10" s="42" t="inlineStr">
@@ -3978,7 +3942,7 @@
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 34 – Exercise Date 11/15/25, 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 6, 26, 30, 34, 58 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – rows 6, 26, 30, 34, 59 – Business Data Validation Date 11/15/2025
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml – request email states DR exercises conducted 11/15/2025 and 02/21/2026 (failover Miami-Telefonica → DR site)
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted Cesar Vidal request 08/17/2026 states DR exercises conducted 11/15/2025 and 02/21/2026 (failover Miami-Telefonica → DR site)
 • BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf – script header DATE: 11/15/2025
 • BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – script header DATE: 11/15/2025</t>
         </is>
@@ -3989,7 +3953,7 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 34 – 2025 DR Test Scope = True, Exercise Date 11/15/2025
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 6, 26, 30, 34, 58 – Business Data Validation Date 11/15/2025
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 Background: 'the IT DR team facilitates, on an annual basis, data integrity validation testing'</t>
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 Background: 'the IT DR team facilitates, on an annual basis, data integrity validation testing'</t>
         </is>
       </c>
       <c r="D11" s="45" t="inlineStr">
@@ -4057,17 +4021,10 @@
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – Department Manager Approval Date column
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
 • DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
 • DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf
-• E17 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 3 (1).msg.eml
-• E17a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17a_4069_001.pdf
-• MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg
 • DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-• DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf
-• E16 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 2 (1).msg.eml
-• E16a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16a_Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+• DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
         </is>
       </c>
       <c r="I11" s="40" t="inlineStr">
@@ -4088,23 +4045,16 @@
       <c r="J11" s="40" t="inlineStr">
         <is>
           <t>Yes – application-specific business line manager approval evidence obtained for every DIV record:
-David Marquez: DMA02/E14 email + DMA02a/E14a signed attestation 08/19/2026
-Franklin Puentes: DMA03/E17/MA02 email + DMA03a/E17a signed attestation 08/18/2026
-Maria del Cerro Hontanilla: DMA05/E16 email + DMA05a/E16a signed attestation 08/19/2026
+David Marquez: DMA02 email + DMA02a signed attestation 08/19/2026
+Franklin Puentes: DMA03 email + DMA03a signed attestation 08/18/2026
+Maria del Cerro Hontanilla: DMA05 email + DMA05a signed attestation 08/19/2026
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
 • DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
 • DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf
-• E17 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 3 (1).msg.eml
-• E17a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17a_4069_001.pdf
-• MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg
 • DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-• DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf
-• E16 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 2 (1).msg.eml
-• E16a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16a_Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+• DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
         </is>
       </c>
       <c r="K11" s="41" t="inlineStr">
@@ -4125,8 +4075,8 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 34 – Exercise Date 11/15/2025 / 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 6, 26, 30, 34, 58 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml – DR exercises 11/15/2025 and 02/21/2026
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
 • BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf – dated 11/15/2025
 • BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – dated 11/15/2025</t>
         </is>
@@ -4137,7 +4087,7 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review 09/15/2025
 • E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – follow-up 09/18/2025
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
 • BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • E08 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg – business-line DIV comparison files sent to IT DR (Elizabeth Noda) on 11/15/2025
@@ -4153,7 +4103,7 @@
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
 • E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – BIA results &amp; applications list review
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data</t>
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data</t>
         </is>
       </c>
       <c r="O11" s="69" t="inlineStr">
@@ -4164,17 +4114,10 @@
 • BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – business line DIV results document – 11/15/2025 – Payments &amp; Position Management (operators Frank Puentes / Gustavo Bucaro)
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
 • DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
 • DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf
-• E17 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 3 (1).msg.eml
-• E17a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17a_4069_001.pdf
-• MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg
 • DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
 • DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf
-• E16 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 2 (1).msg.eml
-• E16a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16a_Data_Integrity_Attestation_Santander-BCiC.pdf
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 6, 26, 30, 34, 58 – Department Manager / Approval Date / Attestation fields</t>
         </is>
       </c>
@@ -4185,24 +4128,23 @@
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 6, 26, 30, 34, 58
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – rows 6, 26, 30, 34, 59
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – record(s) visible on screen
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="Q11" s="49" t="inlineStr">
         <is>
           <t>PASS – all five control attributes satisfied (Annual Testing Executed, DIV Performed by IT DR Team, Applications in Scope Identified, Business Line Approval of Results, Results Documented in BCMS).
 Observations (do not change the attribute conclusions – reviewer to confirm):
-1. Timing – Maria del Cerro Hontanilla: 1 record(s), BCiC approval 08/19/2026 – business line approval obtained after the review period end (06/01/2026) through retrospective management attestation (E14a §3.6 commits to contemporaneous approval going forward).
+1. Timing – Maria del Cerro Hontanilla: 1 record(s), BCiC approval 08/19/2026 – business line approval obtained after the review period end (06/01/2026) through retrospective management attestation (DMA02a §3.6 commits to contemporaneous approval going forward).
 2. Approval evidence – David Marquez: 1 record(s), BCiC approval 11/15/2025 (in period) confirmed by signed attestation 08/19/2026; Franklin Puentes: 3 record(s), BCiC approval 12/18/2025 (in period) confirmed by signed attestation 08/18/2026 – no contemporaneous approval email for the BCiC approval date is in the package; approval is confirmed retrospectively.
 3. Segregation – business tester and approving manager are the same person for: David Marquez, Franklin Puentes.
-4. Results document – BLA02 (BSA/AML/OFAC) DIV Yes/No boxes are blank; mitigated by BLA02 production vs test-day screenshots, BCiC Y/Y/Y (E03) and David Marquez signed attestation (E14a).</t>
+4. Results document – BLA02 (BSA/AML/OFAC) DIV Yes/No boxes are blank; mitigated by BLA02 production vs test-day screenshots, BCiC Y/Y/Y (E03) and David Marquez signed attestation (DMA02a).</t>
         </is>
       </c>
       <c r="R11" s="40" t="inlineStr">
         <is>
           <t>[01 Management Attestation / In-Scope Applications]
 MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
-MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg
 [02 Business Line Approval Results – Email]
 BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf
 BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf
@@ -4222,13 +4164,7 @@
 E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml
 E07 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg
 E08 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg
-E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml
-E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
-E16 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 2 (1).msg.eml
-E16a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16a_Data_Integrity_Attestation_Santander-BCiC.pdf
-E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx
-E17 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 3 (1).msg.eml
-E17a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17a_4069_001.pdf</t>
+E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
         </is>
       </c>
       <c r="S11" s="42" t="inlineStr">
@@ -4284,7 +4220,7 @@
       <c r="BM11" s="58" t="n"/>
       <c r="BN11" s="58" t="n"/>
     </row>
-    <row r="12" ht="392" customFormat="1" customHeight="1" s="39">
+    <row r="12" ht="356" customFormat="1" customHeight="1" s="39">
       <c r="A12" s="45" t="n">
         <v>1917</v>
       </c>
@@ -4295,7 +4231,7 @@
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 36 – Exercise Date 11/15/25, 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 17 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – row 17 – Business Data Validation Date 11/15/2025
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml – request email states DR exercises conducted 11/15/2025 and 02/21/2026 (failover Miami-Telefonica → DR site)
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted Cesar Vidal request 08/17/2026 states DR exercises conducted 11/15/2025 and 02/21/2026 (failover Miami-Telefonica → DR site)
 • BLA05 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf – script header DATE: 11/15/2025</t>
         </is>
       </c>
@@ -4305,7 +4241,7 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 36 – 2025 DR Test Scope = True, Exercise Date 11/15/2025
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 17 – Business Data Validation Date 11/15/2025
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 Background: 'the IT DR team facilitates, on an annual basis, data integrity validation testing'</t>
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 Background: 'the IT DR team facilitates, on an annual basis, data integrity validation testing'</t>
         </is>
       </c>
       <c r="D12" s="45" t="inlineStr">
@@ -4344,8 +4280,7 @@
           <t>Sadis Alvarenga Hernandez (Financial Analysis and Control) – E03 row 17
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 17 – 'Department Manager' column
-• BLA06 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg
-• E12 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E12_RE_ Testing enviroment Financial Analysis manager approval.msg</t>
+• BLA06 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg</t>
         </is>
       </c>
       <c r="H12" s="45" t="inlineStr">
@@ -4353,8 +4288,7 @@
           <t>Sadis Alvarenga Hernandez: BCiC approval 01/26/2026; approval evidence 01/26/2026
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 17 – 'Department Manager Approval Date' and 'Attestation Date' columns
-• BLA06 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg
-• E12 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E12_RE_ Testing enviroment Financial Analysis manager approval.msg</t>
+• BLA06 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg</t>
         </is>
       </c>
       <c r="I12" s="45" t="inlineStr">
@@ -4370,10 +4304,9 @@
       <c r="J12" s="45" t="inlineStr">
         <is>
           <t>Yes – application-specific business line manager approval evidence obtained for every DIV record:
-Sadis Alvarenga Hernandez: BLA06/E12 email "Approved." 12/31/2025 &amp; 01/26/2026 (supplemental: E10/E11 Finance approval, Lina Acuna 03/09/2026)
+Sadis Alvarenga Hernandez: BLA06 email "Approved." 12/31/2025 &amp; 01/26/2026 (supplemental: E10 Finance approval, Lina Acuna 03/09/2026)
 Evidence location (BSI.IT.6.C7.3-Evidences):
-• BLA06 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg
-• E12 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E12_RE_ Testing enviroment Financial Analysis manager approval.msg</t>
+• BLA06 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg</t>
         </is>
       </c>
       <c r="K12" s="44" t="inlineStr">
@@ -4394,8 +4327,8 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 36 – Exercise Date 11/15/2025 / 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 17 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml – DR exercises 11/15/2025 and 02/21/2026
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
 • BLA05 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf – dated 11/15/2025</t>
         </is>
       </c>
@@ -4405,10 +4338,9 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review 09/15/2025
 • E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – follow-up 09/18/2025
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
 • BLA05 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • E10 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg – IT DR (Elizabeth Noda) Finance DIV chart and approval request
-• E11 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E11_BSI.IT.6.C7.3 Manager Approval.msg – same Finance thread (separate save) – Lina Acuna approval 03/09/2026
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 17 – Y/N Format, Headers, Content = Y</t>
         </is>
       </c>
@@ -4421,7 +4353,7 @@
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
 • E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – BIA results &amp; applications list review
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data</t>
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data</t>
         </is>
       </c>
       <c r="O12" s="69" t="inlineStr">
@@ -4430,7 +4362,6 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • BLA05 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf – business line DIV results document – 11/15/2025 – Finance &amp; Accounting Reporting (operator Dunia Gonzalez Collado)
 • BLA06 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg
-• E12 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E12_RE_ Testing enviroment Financial Analysis manager approval.msg
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 17 – Department Manager / Approval Date / Attestation fields</t>
         </is>
       </c>
@@ -4441,7 +4372,7 @@
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 17
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – row 17
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – BCiC report screen (record on a later page of the 66-item report)
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="Q12" s="49" t="inlineStr">
@@ -4449,7 +4380,7 @@
           <t>PASS – all five control attributes satisfied (Annual Testing Executed, DIV Performed by IT DR Team, Applications in Scope Identified, Business Line Approval of Results, Results Documented in BCMS).
 Observations (do not change the attribute conclusions – reviewer to confirm):
 1. Segregation – business tester and approving manager are the same person for: Sadis Alvarenga Hernandez.
-2. Approval linkage – BLA06/E12 thread references approval of "the backup testing on 12/03/2025" test script; the 01/26/2026 approval date agrees to the BCiC Department Manager Approval Date (E03 row 17). Supplemental Finance approval E10/E11 (Lina Acuna 03/09/2026).</t>
+2. Approval linkage – BLA06 thread references approval of "the backup testing on 12/03/2025" test script; the 01/26/2026 approval date agrees to the BCiC Department Manager Approval Date (E03 row 17). Supplemental Finance approval E10 (Lina Acuna 03/09/2026).</t>
         </is>
       </c>
       <c r="R12" s="43" t="inlineStr">
@@ -4459,6 +4390,9 @@
 [02 Business Line Approval Results – Email]
 BLA05 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf
 BLA06 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg
+[03 DIV Manager Attestation Email Approvals]
+DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
+DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 [04 Data Integrity &amp; Email Testing Evidence]
 E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx
 E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg
@@ -4467,10 +4401,6 @@
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
 E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml
 E10 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg
-E11 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E11_BSI.IT.6.C7.3 Manager Approval.msg
-E12 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E12_RE_ Testing enviroment Financial Analysis manager approval.msg
-E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml
-E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
         </is>
       </c>
@@ -4538,7 +4468,7 @@
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 42 – Exercise Date 11/15/25, 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 7, 60 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – rows 7, 61 – Business Data Validation Date 11/15/2025
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml – request email states DR exercises conducted 11/15/2025 and 02/21/2026 (failover Miami-Telefonica → DR site)
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted Cesar Vidal request 08/17/2026 states DR exercises conducted 11/15/2025 and 02/21/2026 (failover Miami-Telefonica → DR site)
 • BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – script header DATE: 11/15/2025
 • BLA04 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx – script header DATE: 11/15/2025</t>
         </is>
@@ -4549,7 +4479,7 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 42 – 2025 DR Test Scope = True, Exercise Date 11/15/2025
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 7, 60 – Business Data Validation Date 11/15/2025
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 Background: 'the IT DR team facilitates, on an annual basis, data integrity validation testing'</t>
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 Background: 'the IT DR team facilitates, on an annual basis, data integrity validation testing'</t>
         </is>
       </c>
       <c r="D13" s="45" t="inlineStr">
@@ -4612,12 +4542,8 @@
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – Department Manager Approval Date column
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
 • DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-• DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf
-• E15 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 1 (1).msg.eml
-• E15a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15a_Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+• DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
         </is>
       </c>
       <c r="I13" s="40" t="inlineStr">
@@ -4635,17 +4561,13 @@
       <c r="J13" s="40" t="inlineStr">
         <is>
           <t>Yes – application-specific business line manager approval evidence obtained for every DIV record:
-David Marquez: DMA02/E14 email + DMA02a/E14a signed attestation 08/19/2026
-Michelle Oropesa: DMA04/E15 email + DMA04a/E15a signed attestation 08/17/2026
+David Marquez: DMA02 email + DMA02a signed attestation 08/19/2026
+Michelle Oropesa: DMA04 email + DMA04a signed attestation 08/17/2026
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
 • DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-• DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf
-• E15 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 1 (1).msg.eml
-• E15a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15a_Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+• DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
         </is>
       </c>
       <c r="K13" s="41" t="inlineStr">
@@ -4666,8 +4588,8 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 42 – Exercise Date 11/15/2025 / 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 7, 60 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml – DR exercises 11/15/2025 and 02/21/2026
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
 • BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – dated 11/15/2025
 • BLA04 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx – dated 11/15/2025</t>
         </is>
@@ -4678,7 +4600,7 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review 09/15/2025
 • E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – follow-up 09/18/2025
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
 • BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • BLA04 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx – IT DR test script completed by the business-line tester
 • E08 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg – business-line DIV comparison files sent to IT DR (Elizabeth Noda) on 11/15/2025
@@ -4694,7 +4616,7 @@
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
 • E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – BIA results &amp; applications list review
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data</t>
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data</t>
         </is>
       </c>
       <c r="O13" s="69" t="inlineStr">
@@ -4705,12 +4627,8 @@
 • BLA04 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx – business line DIV results document – 11/15/2025 – Investment Operations (operator Michelle Oropesa)
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
 • DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
 • DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf
-• E15 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 1 (1).msg.eml
-• E15a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15a_Data_Integrity_Attestation_Santander-BCiC.pdf
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 7, 60 – Department Manager / Approval Date / Attestation fields</t>
         </is>
       </c>
@@ -4721,17 +4639,17 @@
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 7, 60
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – rows 7, 61
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – record(s) visible on screen
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="Q13" s="49" t="inlineStr">
         <is>
           <t>PASS – all five control attributes satisfied (Annual Testing Executed, DIV Performed by IT DR Team, Applications in Scope Identified, Business Line Approval of Results, Results Documented in BCMS).
 Observations (do not change the attribute conclusions – reviewer to confirm):
-1. Timing – Michelle Oropesa: 1 record(s), BCiC approval 08/17/2026 – business line approval obtained after the review period end (06/01/2026) through retrospective management attestation (E14a §3.6 commits to contemporaneous approval going forward).
+1. Timing – Michelle Oropesa: 1 record(s), BCiC approval 08/17/2026 – business line approval obtained after the review period end (06/01/2026) through retrospective management attestation (DMA02a §3.6 commits to contemporaneous approval going forward).
 2. Approval evidence – David Marquez: 1 record(s), BCiC approval 11/15/2025 (in period) confirmed by signed attestation 08/19/2026 – no contemporaneous approval email for the BCiC approval date is in the package; approval is confirmed retrospectively.
 3. Segregation – business tester and approving manager are the same person for: David Marquez, Michelle Oropesa.
-4. Results document – BLA02 (BSA/AML/OFAC) DIV Yes/No boxes are blank; mitigated by BLA02 production vs test-day screenshots, BCiC Y/Y/Y (E03) and David Marquez signed attestation (E14a).</t>
+4. Results document – BLA02 (BSA/AML/OFAC) DIV Yes/No boxes are blank; mitigated by BLA02 production vs test-day screenshots, BCiC Y/Y/Y (E03) and David Marquez signed attestation (DMA02a).</t>
         </is>
       </c>
       <c r="R13" s="40" t="inlineStr">
@@ -4755,10 +4673,6 @@
 E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml
 E07 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg
 E08 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg
-E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml
-E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
-E15 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 1 (1).msg.eml
-E15a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15a_Data_Integrity_Attestation_Santander-BCiC.pdf
 E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
         </is>
       </c>
@@ -4826,7 +4740,7 @@
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 43 – Exercise Date 11/15/25, 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 47, 49, 50, 51, 53, 55, 56, 57, 60, 63, 64 – Business Data Validation Date 11/15/2025
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml – request email states DR exercises conducted 11/15/2025 and 02/21/2026 (failover Miami-Telefonica → DR site)
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted Cesar Vidal request 08/17/2026 states DR exercises conducted 11/15/2025 and 02/21/2026 (failover Miami-Telefonica → DR site)
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – script header DATE: 11/15/2025
 • BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf – script header DATE: 11/15/2025
 • BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – script header DATE: 11/15/2025
@@ -4840,7 +4754,7 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 43 – 2025 DR Test Scope = True, Exercise Date 11/15/2025
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63 – Business Data Validation Date 11/15/2025
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 Background: 'the IT DR team facilitates, on an annual basis, data integrity validation testing'</t>
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 Background: 'the IT DR team facilitates, on an annual basis, data integrity validation testing'</t>
         </is>
       </c>
       <c r="D14" s="43" t="inlineStr">
@@ -4928,7 +4842,6 @@
 • DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
 • DMA11 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
 • BLA06 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg
-• E12 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E12_RE_ Testing enviroment Financial Analysis manager approval.msg
 • DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
 • DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf
 • DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
@@ -4966,27 +4879,17 @@
 • DMA06a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA06a_Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Data_Integrity_Attestation_Santander-BCiC_signed.pdf
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
 • DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
 • DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
 • DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
 • DMA11 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
 • BLA06 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg
-• E12 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E12_RE_ Testing enviroment Financial Analysis manager approval.msg
 • DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
 • DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf
-• E16 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 2 (1).msg.eml
-• E16a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16a_Data_Integrity_Attestation_Santander-BCiC.pdf
 • DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
 • DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf
-• E15 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 1 (1).msg.eml
-• E15a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15a_Data_Integrity_Attestation_Santander-BCiC.pdf
 • DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
 • DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf
-• E17 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 3 (1).msg.eml
-• E17a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17a_4069_001.pdf
-• MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg
 • DMA07 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg
 • DMA07a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA07a_Treasury &amp; Capital Planning - Data_Integrity_Attestation_Santander-BCiC.pdf
 • DMA12 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml
@@ -5021,13 +4924,13 @@
         <is>
           <t>Yes – application-specific business line manager approval evidence obtained for every DIV record:
 Ricardo Garcia: DMA06 email + DMA06a e-signed attestation 08/18/2026
-David Marquez: DMA02/E14 email + DMA02a/E14a signed attestation 08/19/2026
+David Marquez: DMA02 email + DMA02a signed attestation 08/19/2026
 Claudia Romero: E09 email "Approved." 05/05/2026 (Client Back Office results); DMA01/DMA01a signed attestation 08/18/2026
 Miguel Orozco: DMA11 email "I approve the integrity validation…" 09/09/2026
-Sadis Alvarenga Hernandez: BLA06/E12 email "Approved." 12/31/2025 &amp; 01/26/2026 (supplemental: E10/E11 Finance approval, Lina Acuna 03/09/2026)
-Maria del Cerro Hontanilla: DMA05/E16 email + DMA05a/E16a signed attestation 08/19/2026
-Michelle Oropesa: DMA04/E15 email + DMA04a/E15a signed attestation 08/17/2026
-Franklin Puentes: DMA03/E17/MA02 email + DMA03a/E17a signed attestation 08/18/2026
+Sadis Alvarenga Hernandez: BLA06 email "Approved." 12/31/2025 &amp; 01/26/2026 (supplemental: E10 Finance approval, Lina Acuna 03/09/2026)
+Maria del Cerro Hontanilla: DMA05 email + DMA05a signed attestation 08/19/2026
+Michelle Oropesa: DMA04 email + DMA04a signed attestation 08/17/2026
+Franklin Puentes: DMA03 email + DMA03a signed attestation 08/18/2026
 Martha Sullivan: DMA07 email + DMA07a signed attestation 08/18/2026
 Liliana Vizhnay: DMA12 email "I approve." 09/09/2026
 Victoria Fernandez: DMA10 email "Approved" 08/21/2026
@@ -5038,27 +4941,17 @@
 • DMA06a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA06a_Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Data_Integrity_Attestation_Santander-BCiC_signed.pdf
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
 • DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
 • DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
 • DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
 • DMA11 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
 • BLA06 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg
-• E12 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E12_RE_ Testing enviroment Financial Analysis manager approval.msg
 • DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
 • DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf
-• E16 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 2 (1).msg.eml
-• E16a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16a_Data_Integrity_Attestation_Santander-BCiC.pdf
 • DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
 • DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf
-• E15 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 1 (1).msg.eml
-• E15a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15a_Data_Integrity_Attestation_Santander-BCiC.pdf
 • DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
 • DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf
-• E17 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 3 (1).msg.eml
-• E17a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17a_4069_001.pdf
-• MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg
 • DMA07 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg
 • DMA07a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA07a_Treasury &amp; Capital Planning - Data_Integrity_Attestation_Santander-BCiC.pdf
 • DMA12 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml
@@ -5086,8 +4979,8 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 43 – Exercise Date 11/15/2025 / 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml – DR exercises 11/15/2025 and 02/21/2026
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – dated 11/15/2025
 • BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf – dated 11/15/2025
 • BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – dated 11/15/2025
@@ -5101,7 +4994,7 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review 09/15/2025
 • E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – follow-up 09/18/2025
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
@@ -5109,7 +5002,6 @@
 • BLA05 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • E08 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg – business-line DIV comparison files sent to IT DR (Elizabeth Noda) on 11/15/2025
 • E10 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg – IT DR (Elizabeth Noda) Finance DIV chart and approval request
-• E11 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E11_BSI.IT.6.C7.3 Manager Approval.msg – same Finance thread (separate save) – Lina Acuna approval 03/09/2026
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63 – Y/N Format, Headers, Content = Y</t>
         </is>
       </c>
@@ -5122,7 +5014,7 @@
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
 • E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – BIA results &amp; applications list review
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data</t>
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data</t>
         </is>
       </c>
       <c r="O14" s="69" t="inlineStr">
@@ -5138,27 +5030,17 @@
 • DMA06a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA06a_Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Data_Integrity_Attestation_Santander-BCiC_signed.pdf
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
 • DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
 • DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
 • DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
 • DMA11 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
 • BLA06 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg
-• E12 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E12_RE_ Testing enviroment Financial Analysis manager approval.msg
 • DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
 • DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf
-• E16 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 2 (1).msg.eml
-• E16a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16a_Data_Integrity_Attestation_Santander-BCiC.pdf
 • DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
 • DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf
-• E15 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 1 (1).msg.eml
-• E15a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15a_Data_Integrity_Attestation_Santander-BCiC.pdf
 • DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
 • DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf
-• E17 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 3 (1).msg.eml
-• E17a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17a_4069_001.pdf
-• MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg
 • DMA07 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg
 • DMA07a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA07a_Treasury &amp; Capital Planning - Data_Integrity_Attestation_Santander-BCiC.pdf
 • DMA12 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml
@@ -5176,25 +5058,24 @@
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 47, 49, 50, 51, 53, 55, 56, 57, 60, 63, 64
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – record(s) visible on screen
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="Q14" s="49" t="inlineStr">
         <is>
           <t>PASS – all five control attributes satisfied (Annual Testing Executed, DIV Performed by IT DR Team, Applications in Scope Identified, Business Line Approval of Results, Results Documented in BCMS).
 Observations (do not change the attribute conclusions – reviewer to confirm):
-1. Timing – Ricardo Garcia: 8 record(s), BCiC approval 08/18/2026; Miguel Orozco: 2 record(s), BCiC approval 09/09/2026; Maria del Cerro Hontanilla: 3 record(s), BCiC approval 08/19/2026; Michelle Oropesa: 3 record(s), BCiC approval 08/17/2026; Martha Sullivan: 6 record(s), BCiC approval 08/18/2026; Liliana Vizhnay: 1 record(s), BCiC approval 09/09/2026; Victoria Fernandez: 1 record(s), BCiC approval 08/21/2026; Xavier Caisapanta: 2 record(s), BCiC approval 08/18/2026; Clara De Castro: 1 record(s), BCiC approval 08/18/2026 – business line approval obtained after the review period end (06/01/2026) through retrospective management attestation (E14a §3.6 commits to contemporaneous approval going forward).
+1. Timing – Ricardo Garcia: 8 record(s), BCiC approval 08/18/2026; Miguel Orozco: 2 record(s), BCiC approval 09/09/2026; Maria del Cerro Hontanilla: 3 record(s), BCiC approval 08/19/2026; Michelle Oropesa: 3 record(s), BCiC approval 08/17/2026; Martha Sullivan: 6 record(s), BCiC approval 08/18/2026; Liliana Vizhnay: 1 record(s), BCiC approval 09/09/2026; Victoria Fernandez: 1 record(s), BCiC approval 08/21/2026; Xavier Caisapanta: 2 record(s), BCiC approval 08/18/2026; Clara De Castro: 1 record(s), BCiC approval 08/18/2026 – business line approval obtained after the review period end (06/01/2026) through retrospective management attestation (DMA02a §3.6 commits to contemporaneous approval going forward).
 2. Approval evidence – David Marquez: 1 record(s), BCiC approval 11/15/2025 (in period) confirmed by signed attestation 08/19/2026; Franklin Puentes: 4 record(s), BCiC approval 12/18/2025 (in period) confirmed by signed attestation 08/18/2026 – no contemporaneous approval email for the BCiC approval date is in the package; approval is confirmed retrospectively.
 3. Segregation – business tester and approving manager are the same person for: David Marquez, Miguel Orozco, Sadis Alvarenga Hernandez, Michelle Oropesa, Franklin Puentes, Martha Sullivan, Liliana Vizhnay, Victoria Fernandez.
-4. Results document – BLA02 (BSA/AML/OFAC) DIV Yes/No boxes are blank; mitigated by BLA02 production vs test-day screenshots, BCiC Y/Y/Y (E03) and David Marquez signed attestation (E14a).
-5. Data – E03 row 8 (BSA T24) Attestation Date 08/29/2026 vs signed attestation 8/19/2026 (E14a); Financial Risk manager recorded as "Xavier Caisapanta" in BCiC while approval email is from Ivan Caisapanta (DMA08); E16b contains one additional Treasury T24 row (row 45, blank department) vs E03.</t>
+4. Results document – BLA02 (BSA/AML/OFAC) DIV Yes/No boxes are blank; mitigated by BLA02 production vs test-day screenshots, BCiC Y/Y/Y (E03) and David Marquez signed attestation (DMA02a).
+5. Data – E03 row 8 (BSA T24) Attestation Date 08/29/2026 vs signed attestation 8/19/2026 (DMA02a); Financial Risk manager recorded as "Xavier Caisapanta" in BCiC while approval email is from Ivan Caisapanta (DMA08); E16b contains one additional Treasury T24 row (row 45, blank department) vs E03.</t>
         </is>
       </c>
       <c r="R14" s="43" t="inlineStr">
         <is>
           <t>[01 Management Attestation / In-Scope Applications]
 MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
-MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg
 [02 Business Line Approval Results – Email]
 BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf
 BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf
@@ -5234,17 +5115,7 @@
 E08 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg
 E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
 E10 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg
-E11 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E11_BSI.IT.6.C7.3 Manager Approval.msg
-E12 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E12_RE_ Testing enviroment Financial Analysis manager approval.msg
-E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml
-E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
-E15 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 1 (1).msg.eml
-E15a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15a_Data_Integrity_Attestation_Santander-BCiC.pdf
-E16 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 2 (1).msg.eml
-E16a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16a_Data_Integrity_Attestation_Santander-BCiC.pdf
-E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx
-E17 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 3 (1).msg.eml
-E17a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17a_4069_001.pdf</t>
+E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
         </is>
       </c>
       <c r="S14" s="42" t="inlineStr">
@@ -5303,7 +5174,7 @@
     <row r="15" ht="33.65" customHeight="1" s="71">
       <c r="A15" s="72" t="inlineStr">
         <is>
-          <t>Assessment rule applied: a control sample is rated PASS when (1) annual DIV testing was executed during the DR exercise, (2) the DIV was facilitated by IT DR and performed by business-line testers, (3) the application is identified in scope (MA01 / E01), (4) business line management approved the results (Business Line Approval Results folder 02 + application-specific approvals in folder 03 / E09 / E12), and (5) results are documented in BCMS/BCiC. Every evidence reference points to its location in the BSI.IT.6.C7.3-Evidences repository (folders 01–04). Observations are listed in column Q and in the Observations section below.</t>
+          <t>Assessment rule applied: a control sample is rated PASS when (1) annual DIV testing was executed during the DR exercise, (2) the DIV was facilitated by IT DR and performed by business-line testers, (3) the application is identified in scope (MA01 / E01), (4) business line management approved the results (Business Line Approval Results folder 02 + application-specific approvals in folder 03 / E09), and (5) results are documented in BCMS/BCiC. Every evidence reference points to its location in the BSI.IT.6.C7.3-Evidences repository (folders 01–04). Observations are listed in column Q and in the Observations section below.</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5277,7 @@
       </c>
       <c r="J19" s="59" t="inlineStr">
         <is>
-          <t>Observation only – blank BCiC attestation fields are covered by the approval emails / signed attestations in folder 03 (DMA11, DMA12) and BLA06 / E12.</t>
+          <t>Observation only – blank BCiC attestation fields are covered by the approval emails / signed attestations in folder 03 (DMA11, DMA12) and BLA06.</t>
         </is>
       </c>
     </row>
@@ -5445,7 +5316,7 @@
       </c>
       <c r="J20" s="59" t="inlineStr">
         <is>
-          <t>Observation only – blank BCiC attestation fields are covered by the approval emails / signed attestations in folder 03 (DMA11, DMA12) and BLA06 / E12.</t>
+          <t>Observation only – blank BCiC attestation fields are covered by the approval emails / signed attestations in folder 03 (DMA11, DMA12) and BLA06.</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5475,7 @@
       </c>
       <c r="J25" s="29" t="inlineStr">
         <is>
-          <t>Observation – 33 of 56 records: BCiC approval dated 08/17/2026 – 09/09/2026 via retrospective management attestation (folder 03). 13 of 56 records: in-period BCiC approval (BSA 11/15/2025, Payments 12/18/2025) confirmed only by 08/2026 signed attestations. 10 of 56 records: in-period approval email (Claudia Romero 05/05/2026 – E09; Sadis Alvarenga 01/26/2026 – BLA06/E12).</t>
+          <t>Observation – 33 of 56 records: BCiC approval dated 08/17/2026 – 09/09/2026 via retrospective management attestation (folder 03). 13 of 56 records: in-period BCiC approval (BSA 11/15/2025, Payments 12/18/2025) confirmed only by 08/2026 signed attestations. 10 of 56 records: in-period approval email (Claudia Romero 05/05/2026 – E09; Sadis Alvarenga 01/26/2026 – BLA06).</t>
         </is>
       </c>
     </row>
@@ -5992,7 +5863,7 @@
       </c>
       <c r="E35" s="86" t="inlineStr">
         <is>
-          <t>Sadis Alvarenga (Financial Analysis &amp; Control manager) replies "Approved." on 12/31/2025 and again on 01/26/2026 to Elizabeth Noda's request to approve the submitted test script. Same message as E12.</t>
+          <t>Sadis Alvarenga (Financial Analysis &amp; Control manager) replies "Approved." on 12/31/2025 and again on 01/26/2026 to Elizabeth Noda's request to approve the submitted test script.</t>
         </is>
       </c>
       <c r="F35" s="86" t="inlineStr">
@@ -6207,12 +6078,12 @@
       </c>
       <c r="E41" s="86" t="inlineStr">
         <is>
-          <t>David Marquez (OFAC Manager) returns signed attestation. Same message as E14.</t>
+          <t>Cesar Vidal request to Department Managers (08/17/2026; DR exercises 11/15/2025 and 02/21/2026; BCiC export attached) and David Marquez (OFAC Manager) reply returning the signed attestation.</t>
         </is>
       </c>
       <c r="F41" s="86" t="inlineStr">
         <is>
-          <t>Approval evidence for 4 DIV record(s) – approval evidence dated after 06/01/2026 (BCiC approval 11/15/2025) – samples 3299, 1903, 1936, 1937</t>
+          <t>Approval evidence for 4 DIV record(s) – approval evidence dated after 06/01/2026 (BCiC approval 11/15/2025) – samples 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
         </is>
       </c>
       <c r="G41" s="82" t="n"/>
@@ -6229,7 +6100,7 @@
       <c r="R41" s="82" t="n"/>
       <c r="S41" s="82" t="n"/>
     </row>
-    <row r="42" ht="42" customHeight="1" s="71">
+    <row r="42" ht="54" customHeight="1" s="71">
       <c r="A42" s="86" t="inlineStr">
         <is>
           <t>DMA02a</t>
@@ -6252,12 +6123,12 @@
       </c>
       <c r="E42" s="86" t="inlineStr">
         <is>
-          <t>Signed attestation – OFAC Manager, VP, BSA/AML-OFAC Compliance, dated 8/19/2026.</t>
+          <t>Signed attestation – OFAC Manager, VP, BSA/AML-OFAC Compliance, dated 8/19/2026. §1 states the IT DR team facilitates DIV annually; §2 lists 63 entries / 13 applications, all Y/Y/Y; §3.5 retention in BCMS/BCiC; §3.6 contemporaneous approval going forward.</t>
         </is>
       </c>
       <c r="F42" s="86" t="inlineStr">
         <is>
-          <t>Signed attachment extracted from DMA02 – samples 3299, 1903, 1936, 1937</t>
+          <t>Signed attachment extracted from DMA02 – samples 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
         </is>
       </c>
       <c r="G42" s="82" t="n"/>
@@ -6297,7 +6168,7 @@
       </c>
       <c r="E43" s="86" t="inlineStr">
         <is>
-          <t>Frank Puentes returns signed attestation. Same message as E17 / MA02.</t>
+          <t>Frank Puentes returns signed attestation (DMA03a).</t>
         </is>
       </c>
       <c r="F43" s="86" t="inlineStr">
@@ -6387,7 +6258,7 @@
       </c>
       <c r="E45" s="86" t="inlineStr">
         <is>
-          <t>Michelle Oropesa (Investment Operations Director) returns signed attestation. Same message as E15.</t>
+          <t>Michelle Oropesa (Investment Operations Director) returns signed attestation (DMA04a).</t>
         </is>
       </c>
       <c r="F45" s="86" t="inlineStr">
@@ -6477,7 +6348,7 @@
       </c>
       <c r="E47" s="86" t="inlineStr">
         <is>
-          <t>Signed attestation + BCiC export returned by Senior Director of Operations. Same message as E16.</t>
+          <t>Signed attestation + BCiC export (E16b) returned by Senior Director of Operations.</t>
         </is>
       </c>
       <c r="F47" s="86" t="inlineStr">
@@ -6547,32 +6418,32 @@
     <row r="49" ht="42" customHeight="1" s="71">
       <c r="A49" s="86" t="inlineStr">
         <is>
-          <t>DMA05b</t>
+          <t>DMA06</t>
         </is>
       </c>
       <c r="B49" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05b_Operations (Governance &amp; Static Data, Multi-Family Office) - All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg</t>
         </is>
       </c>
       <c r="C49" s="86" t="inlineStr">
         <is>
-          <t>08/19/2026 – attached by M. T. Del Cerro</t>
+          <t>08/18/2026 – Ricardo Garcia-Marques</t>
         </is>
       </c>
       <c r="D49" s="86" t="inlineStr">
         <is>
-          <t>T24 (rows 18, 54, 59); Imaging101 (rows 53, 57); OFAC - BSI (row 58)</t>
+          <t>T24 (rows 3, 35, 36, 37, 38, 39, 40, 63)</t>
         </is>
       </c>
       <c r="E49" s="86" t="inlineStr">
         <is>
-          <t>BCiC DIV export reviewed with the attestation (identical to E16b).</t>
+          <t>Attestation and approval from Trading &amp; Capital Markets (covers BCiC records approved by Ricardo Garcia).</t>
         </is>
       </c>
       <c r="F49" s="86" t="inlineStr">
         <is>
-          <t>Signed attachment extracted from DMA05 – samples —</t>
+          <t>Approval evidence for 8 DIV record(s) – approval evidence dated after 06/01/2026 (BCiC approval 08/18/2026) – samples 1937</t>
         </is>
       </c>
       <c r="G49" s="82" t="n"/>
@@ -6592,17 +6463,17 @@
     <row r="50" ht="42" customHeight="1" s="71">
       <c r="A50" s="86" t="inlineStr">
         <is>
-          <t>DMA06</t>
+          <t>DMA06a</t>
         </is>
       </c>
       <c r="B50" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA06a_Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Data_Integrity_Attestation_Santander-BCiC_signed.pdf</t>
         </is>
       </c>
       <c r="C50" s="86" t="inlineStr">
         <is>
-          <t>08/18/2026 – Ricardo Garcia-Marques</t>
+          <t>08/18/2026 11:45 AM EDT – Ricardo Garcia Marques</t>
         </is>
       </c>
       <c r="D50" s="86" t="inlineStr">
@@ -6612,12 +6483,12 @@
       </c>
       <c r="E50" s="86" t="inlineStr">
         <is>
-          <t>Attestation and approval from Trading &amp; Capital Markets (covers BCiC records approved by Ricardo Garcia).</t>
+          <t>e-signed attestation – MD, Head of Trading &amp; Capital Markets.</t>
         </is>
       </c>
       <c r="F50" s="86" t="inlineStr">
         <is>
-          <t>Approval evidence for 8 DIV record(s) – approval evidence dated after 06/01/2026 (BCiC approval 08/18/2026) – samples 1937</t>
+          <t>Signed attachment extracted from DMA06 – samples 1937</t>
         </is>
       </c>
       <c r="G50" s="82" t="n"/>
@@ -6637,32 +6508,32 @@
     <row r="51" ht="42" customHeight="1" s="71">
       <c r="A51" s="86" t="inlineStr">
         <is>
-          <t>DMA06a</t>
+          <t>DMA07</t>
         </is>
       </c>
       <c r="B51" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA06a_Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Data_Integrity_Attestation_Santander-BCiC_signed.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg</t>
         </is>
       </c>
       <c r="C51" s="86" t="inlineStr">
         <is>
-          <t>08/18/2026 11:45 AM EDT – Ricardo Garcia Marques</t>
+          <t>08/18/2026 – Martha Sullivan</t>
         </is>
       </c>
       <c r="D51" s="86" t="inlineStr">
         <is>
-          <t>T24 (rows 3, 35, 36, 37, 38, 39, 40, 63)</t>
+          <t>T24 (rows 41, 42, 43, 44, 45, 46)</t>
         </is>
       </c>
       <c r="E51" s="86" t="inlineStr">
         <is>
-          <t>e-signed attestation – MD, Head of Trading &amp; Capital Markets.</t>
+          <t>Martha Sullivan returns signed attestation (DMA07a).</t>
         </is>
       </c>
       <c r="F51" s="86" t="inlineStr">
         <is>
-          <t>Signed attachment extracted from DMA06 – samples 1937</t>
+          <t>Approval evidence for 6 DIV record(s) – approval evidence dated after 06/01/2026 (BCiC approval 08/18/2026) – samples 1937</t>
         </is>
       </c>
       <c r="G51" s="82" t="n"/>
@@ -6682,12 +6553,12 @@
     <row r="52" ht="42" customHeight="1" s="71">
       <c r="A52" s="86" t="inlineStr">
         <is>
-          <t>DMA07</t>
+          <t>DMA07a</t>
         </is>
       </c>
       <c r="B52" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA07a_Treasury &amp; Capital Planning - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
         </is>
       </c>
       <c r="C52" s="86" t="inlineStr">
@@ -6702,12 +6573,12 @@
       </c>
       <c r="E52" s="86" t="inlineStr">
         <is>
-          <t>Martha Sullivan returns signed attestation (DMA07a).</t>
+          <t>Signed attestation – Balance Sheet Manager, Treasury.</t>
         </is>
       </c>
       <c r="F52" s="86" t="inlineStr">
         <is>
-          <t>Approval evidence for 6 DIV record(s) – approval evidence dated after 06/01/2026 (BCiC approval 08/18/2026) – samples 1937</t>
+          <t>Signed attachment extracted from DMA07 – samples 1937</t>
         </is>
       </c>
       <c r="G52" s="82" t="n"/>
@@ -6727,32 +6598,32 @@
     <row r="53" ht="42" customHeight="1" s="71">
       <c r="A53" s="86" t="inlineStr">
         <is>
-          <t>DMA07a</t>
+          <t>DMA08</t>
         </is>
       </c>
       <c r="B53" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA07a_Treasury &amp; Capital Planning - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg</t>
         </is>
       </c>
       <c r="C53" s="86" t="inlineStr">
         <is>
-          <t>08/18/2026 – Martha Sullivan</t>
+          <t>08/18/2026 – Ivan Caisapanta</t>
         </is>
       </c>
       <c r="D53" s="86" t="inlineStr">
         <is>
-          <t>T24 (rows 41, 42, 43, 44, 45, 46)</t>
+          <t>T24 (rows 55, 56)</t>
         </is>
       </c>
       <c r="E53" s="86" t="inlineStr">
         <is>
-          <t>Signed attestation – Balance Sheet Manager, Treasury.</t>
+          <t>"Hi Elizabeth, You have my approval" – Financial Risk (BCiC Department Manager recorded as Xavier Caisapanta).</t>
         </is>
       </c>
       <c r="F53" s="86" t="inlineStr">
         <is>
-          <t>Signed attachment extracted from DMA07 – samples 1937</t>
+          <t>Approval evidence for 2 DIV record(s) – approval evidence dated after 06/01/2026 (BCiC approval 08/18/2026) – samples 1937</t>
         </is>
       </c>
       <c r="G53" s="82" t="n"/>
@@ -6772,32 +6643,32 @@
     <row r="54" ht="42" customHeight="1" s="71">
       <c r="A54" s="86" t="inlineStr">
         <is>
-          <t>DMA08</t>
+          <t>DMA09</t>
         </is>
       </c>
       <c r="B54" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg</t>
         </is>
       </c>
       <c r="C54" s="86" t="inlineStr">
         <is>
-          <t>08/18/2026 – Ivan Caisapanta</t>
+          <t>08/18/2026 – Clara G. De Castro</t>
         </is>
       </c>
       <c r="D54" s="86" t="inlineStr">
         <is>
-          <t>T24 (rows 55, 56)</t>
+          <t>T24 (row 62)</t>
         </is>
       </c>
       <c r="E54" s="86" t="inlineStr">
         <is>
-          <t>"Hi Elizabeth, You have my approval" – Financial Risk (BCiC Department Manager recorded as Xavier Caisapanta).</t>
+          <t>Clara De Castro (Director, General Services &amp; Facilities) returns signed attestation (DMA09a).</t>
         </is>
       </c>
       <c r="F54" s="86" t="inlineStr">
         <is>
-          <t>Approval evidence for 2 DIV record(s) – approval evidence dated after 06/01/2026 (BCiC approval 08/18/2026) – samples 1937</t>
+          <t>Approval evidence for 1 DIV record(s) – approval evidence dated after 06/01/2026 (BCiC approval 08/18/2026) – samples 1937</t>
         </is>
       </c>
       <c r="G54" s="82" t="n"/>
@@ -6817,12 +6688,12 @@
     <row r="55" ht="42" customHeight="1" s="71">
       <c r="A55" s="86" t="inlineStr">
         <is>
-          <t>DMA09</t>
+          <t>DMA09a</t>
         </is>
       </c>
       <c r="B55" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA09a_General Services (Marketing &amp; General Services) - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
         </is>
       </c>
       <c r="C55" s="86" t="inlineStr">
@@ -6837,12 +6708,12 @@
       </c>
       <c r="E55" s="86" t="inlineStr">
         <is>
-          <t>Clara De Castro (Director, General Services &amp; Facilities) returns signed attestation (DMA09a).</t>
+          <t>Signed attestation – General Services.</t>
         </is>
       </c>
       <c r="F55" s="86" t="inlineStr">
         <is>
-          <t>Approval evidence for 1 DIV record(s) – approval evidence dated after 06/01/2026 (BCiC approval 08/18/2026) – samples 1937</t>
+          <t>Signed attachment extracted from DMA09 – samples 1937</t>
         </is>
       </c>
       <c r="G55" s="82" t="n"/>
@@ -6862,32 +6733,32 @@
     <row r="56" ht="42" customHeight="1" s="71">
       <c r="A56" s="86" t="inlineStr">
         <is>
-          <t>DMA09a</t>
+          <t>DMA10</t>
         </is>
       </c>
       <c r="B56" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA09a_General Services (Marketing &amp; General Services) - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml</t>
         </is>
       </c>
       <c r="C56" s="86" t="inlineStr">
         <is>
-          <t>08/18/2026 – Clara G. De Castro</t>
+          <t>08/21/2026 – Victoria Fernandez</t>
         </is>
       </c>
       <c r="D56" s="86" t="inlineStr">
         <is>
-          <t>T24 (row 62)</t>
+          <t>T24 (row 52)</t>
         </is>
       </c>
       <c r="E56" s="86" t="inlineStr">
         <is>
-          <t>Signed attestation – General Services.</t>
+          <t>"Approved" – Digital Wealth.</t>
         </is>
       </c>
       <c r="F56" s="86" t="inlineStr">
         <is>
-          <t>Signed attachment extracted from DMA09 – samples 1937</t>
+          <t>Approval evidence for 1 DIV record(s) – approval evidence dated after 06/01/2026 (BCiC approval 08/21/2026) – samples 1937</t>
         </is>
       </c>
       <c r="G56" s="82" t="n"/>
@@ -6907,32 +6778,32 @@
     <row r="57" ht="42" customHeight="1" s="71">
       <c r="A57" s="86" t="inlineStr">
         <is>
-          <t>DMA10</t>
+          <t>DMA11</t>
         </is>
       </c>
       <c r="B57" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml</t>
         </is>
       </c>
       <c r="C57" s="86" t="inlineStr">
         <is>
-          <t>08/21/2026 – Victoria Fernandez</t>
+          <t>09/09/2026 – Miguel Orozco</t>
         </is>
       </c>
       <c r="D57" s="86" t="inlineStr">
         <is>
-          <t>T24 (row 52)</t>
+          <t>T24 (rows 15, 50); Imaging101 (row 51)</t>
         </is>
       </c>
       <c r="E57" s="86" t="inlineStr">
         <is>
-          <t>"Approved" – Digital Wealth.</t>
+          <t>"I approve the integrity validation for the testing performed by the Commercial Middle Office."</t>
         </is>
       </c>
       <c r="F57" s="86" t="inlineStr">
         <is>
-          <t>Approval evidence for 1 DIV record(s) – approval evidence dated after 06/01/2026 (BCiC approval 08/21/2026) – samples 1937</t>
+          <t>Approval evidence for 3 DIV record(s) – approval evidence dated after 06/01/2026 (BCiC approval 09/09/2026) – samples 3299, 1937</t>
         </is>
       </c>
       <c r="G57" s="82" t="n"/>
@@ -6952,32 +6823,32 @@
     <row r="58" ht="42" customHeight="1" s="71">
       <c r="A58" s="86" t="inlineStr">
         <is>
-          <t>DMA11</t>
+          <t>DMA12</t>
         </is>
       </c>
       <c r="B58" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml</t>
         </is>
       </c>
       <c r="C58" s="86" t="inlineStr">
         <is>
-          <t>09/09/2026 – Miguel Orozco</t>
+          <t>09/09/2026 – Liliana Vizhnay</t>
         </is>
       </c>
       <c r="D58" s="86" t="inlineStr">
         <is>
-          <t>T24 (rows 15, 50); Imaging101 (row 51)</t>
+          <t>T24 (row 49)</t>
         </is>
       </c>
       <c r="E58" s="86" t="inlineStr">
         <is>
-          <t>"I approve the integrity validation for the testing performed by the Commercial Middle Office."</t>
+          <t>"I approve." – Client Servicing Unit.</t>
         </is>
       </c>
       <c r="F58" s="86" t="inlineStr">
         <is>
-          <t>Approval evidence for 3 DIV record(s) – approval evidence dated after 06/01/2026 (BCiC approval 09/09/2026) – samples 3299, 1937</t>
+          <t>Approval evidence for 1 DIV record(s) – approval evidence dated after 06/01/2026 (BCiC approval 09/09/2026) – samples 1937</t>
         </is>
       </c>
       <c r="G58" s="82" t="n"/>
@@ -6997,32 +6868,32 @@
     <row r="59" ht="42" customHeight="1" s="71">
       <c r="A59" s="86" t="inlineStr">
         <is>
-          <t>DMA12</t>
+          <t>DMA13</t>
         </is>
       </c>
       <c r="B59" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml</t>
         </is>
       </c>
       <c r="C59" s="86" t="inlineStr">
         <is>
-          <t>09/09/2026 – Liliana Vizhnay</t>
+          <t>09/09/2026 – Elizabeth Noda</t>
         </is>
       </c>
       <c r="D59" s="86" t="inlineStr">
         <is>
-          <t>T24 (row 49)</t>
+          <t>Cisco Call Manager – not one of the 10 tested applications</t>
         </is>
       </c>
       <c r="E59" s="86" t="inlineStr">
         <is>
-          <t>"I approve." – Client Servicing Unit.</t>
+          <t>"approve" – Cisco Call Manager (IT). Cisco Call Manager is NOT one of the 10 tested applications – retained for completeness only.</t>
         </is>
       </c>
       <c r="F59" s="86" t="inlineStr">
         <is>
-          <t>Approval evidence for 1 DIV record(s) – approval evidence dated after 06/01/2026 (BCiC approval 09/09/2026) – samples 1937</t>
+          <t>Out of scope – retained for completeness – samples —</t>
         </is>
       </c>
       <c r="G59" s="82" t="n"/>
@@ -7039,37 +6910,13 @@
       <c r="R59" s="82" t="n"/>
       <c r="S59" s="82" t="n"/>
     </row>
-    <row r="60" ht="42" customHeight="1" s="71">
-      <c r="A60" s="86" t="inlineStr">
-        <is>
-          <t>DMA13</t>
-        </is>
-      </c>
-      <c r="B60" s="86" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml</t>
-        </is>
-      </c>
-      <c r="C60" s="86" t="inlineStr">
-        <is>
-          <t>09/09/2026 – Elizabeth Noda</t>
-        </is>
-      </c>
-      <c r="D60" s="86" t="inlineStr">
-        <is>
-          <t>Cisco Call Manager – not one of the 10 tested applications</t>
-        </is>
-      </c>
-      <c r="E60" s="86" t="inlineStr">
-        <is>
-          <t>"approve" – Cisco Call Manager (IT). Cisco Call Manager is NOT one of the 10 tested applications – retained for completeness only.</t>
-        </is>
-      </c>
-      <c r="F60" s="86" t="inlineStr">
-        <is>
-          <t>Out of scope – retained for completeness – samples —</t>
-        </is>
-      </c>
+    <row r="60" s="71">
+      <c r="A60" s="82" t="n"/>
+      <c r="B60" s="82" t="n"/>
+      <c r="C60" s="82" t="n"/>
+      <c r="D60" s="82" t="n"/>
+      <c r="E60" s="82" t="n"/>
+      <c r="F60" s="82" t="n"/>
       <c r="G60" s="82" t="n"/>
       <c r="H60" s="82" t="n"/>
       <c r="I60" s="82" t="n"/>
@@ -7084,19 +6931,12 @@
       <c r="R60" s="82" t="n"/>
       <c r="S60" s="82" t="n"/>
     </row>
-    <row r="61" s="71">
-      <c r="A61" s="82" t="n"/>
-      <c r="B61" s="82" t="n"/>
-      <c r="C61" s="82" t="n"/>
-      <c r="D61" s="82" t="n"/>
-      <c r="E61" s="82" t="n"/>
-      <c r="F61" s="82" t="n"/>
-      <c r="G61" s="82" t="n"/>
-      <c r="H61" s="82" t="n"/>
-      <c r="I61" s="82" t="n"/>
-      <c r="J61" s="82" t="n"/>
-      <c r="K61" s="82" t="n"/>
-      <c r="L61" s="82" t="n"/>
+    <row r="61" ht="22" customHeight="1" s="71">
+      <c r="A61" s="73" t="inlineStr">
+        <is>
+          <t>Management Attestation / In-Scope Applications (folder 01) and Data Integrity &amp; Email Testing Evidence (folder 04) – Review</t>
+        </is>
+      </c>
       <c r="M61" s="82" t="n"/>
       <c r="N61" s="82" t="n"/>
       <c r="O61" s="82" t="n"/>
@@ -7105,12 +6945,43 @@
       <c r="R61" s="82" t="n"/>
       <c r="S61" s="82" t="n"/>
     </row>
-    <row r="62" ht="22" customHeight="1" s="71">
-      <c r="A62" s="73" t="inlineStr">
-        <is>
-          <t>Management Attestation / In-Scope Applications (folder 01) and Data Integrity &amp; Email Testing Evidence (folder 04) – Review</t>
-        </is>
-      </c>
+    <row r="62" ht="30" customHeight="1" s="71">
+      <c r="A62" s="85" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="B62" s="85" t="inlineStr">
+        <is>
+          <t>Evidence file (repository location)</t>
+        </is>
+      </c>
+      <c r="C62" s="85" t="inlineStr">
+        <is>
+          <t>Date / owner</t>
+        </is>
+      </c>
+      <c r="D62" s="85" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E62" s="85" t="inlineStr">
+        <is>
+          <t>Content reviewed</t>
+        </is>
+      </c>
+      <c r="F62" s="85" t="inlineStr">
+        <is>
+          <t>Samples / workpaper columns supported</t>
+        </is>
+      </c>
+      <c r="G62" s="82" t="n"/>
+      <c r="H62" s="82" t="n"/>
+      <c r="I62" s="82" t="n"/>
+      <c r="J62" s="82" t="n"/>
+      <c r="K62" s="82" t="n"/>
+      <c r="L62" s="82" t="n"/>
       <c r="M62" s="82" t="n"/>
       <c r="N62" s="82" t="n"/>
       <c r="O62" s="82" t="n"/>
@@ -7119,35 +6990,35 @@
       <c r="R62" s="82" t="n"/>
       <c r="S62" s="82" t="n"/>
     </row>
-    <row r="63" ht="30" customHeight="1" s="71">
-      <c r="A63" s="85" t="inlineStr">
-        <is>
-          <t>Ref</t>
-        </is>
-      </c>
-      <c r="B63" s="85" t="inlineStr">
-        <is>
-          <t>Evidence file (repository location)</t>
-        </is>
-      </c>
-      <c r="C63" s="85" t="inlineStr">
-        <is>
-          <t>Date / owner</t>
-        </is>
-      </c>
-      <c r="D63" s="85" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="E63" s="85" t="inlineStr">
-        <is>
-          <t>Content reviewed</t>
-        </is>
-      </c>
-      <c r="F63" s="85" t="inlineStr">
-        <is>
-          <t>Samples / workpaper columns supported</t>
+    <row r="63" ht="66" customHeight="1" s="71">
+      <c r="A63" s="86" t="inlineStr">
+        <is>
+          <t>MA01</t>
+        </is>
+      </c>
+      <c r="B63" s="86" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png</t>
+        </is>
+      </c>
+      <c r="C63" s="86" t="inlineStr">
+        <is>
+          <t>09/23/2026 – Cesar Vidal (BCiC walkthrough)</t>
+        </is>
+      </c>
+      <c r="D63" s="86" t="inlineStr">
+        <is>
+          <t>BCiC screenshot</t>
+        </is>
+      </c>
+      <c r="E63" s="86" t="inlineStr">
+        <is>
+          <t>BC in the Cloud 'Applications In Scope for DR Test BSI' view (filter Scope Entity = BSI; 43 items). The 10 tested applications are selected (1822, 1867, 1868, 1903, 1917, 1937, 1936, 3301, 3299, 4052) and each shows 2025 DR Test Scope = True, 2025 Backup/Restore Test Scope = True and 2025 Backup/Restore DIV Scope = True.</t>
+        </is>
+      </c>
+      <c r="F63" s="86" t="inlineStr">
+        <is>
+          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: D, K, N</t>
         </is>
       </c>
       <c r="G63" s="82" t="n"/>
@@ -7164,35 +7035,35 @@
       <c r="R63" s="82" t="n"/>
       <c r="S63" s="82" t="n"/>
     </row>
-    <row r="64" ht="66" customHeight="1" s="71">
+    <row r="64" ht="30" customHeight="1" s="71">
       <c r="A64" s="86" t="inlineStr">
         <is>
-          <t>MA01</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="B64" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
         </is>
       </c>
       <c r="C64" s="86" t="inlineStr">
         <is>
-          <t>09/23/2026 – Cesar Vidal (BCiC walkthrough)</t>
+          <t>BCiC – Applications In Scope for DR Test BSI</t>
         </is>
       </c>
       <c r="D64" s="86" t="inlineStr">
         <is>
-          <t>BCiC screenshot</t>
+          <t>BCiC export</t>
         </is>
       </c>
       <c r="E64" s="86" t="inlineStr">
         <is>
-          <t>BC in the Cloud 'Applications In Scope for DR Test BSI' view (filter Scope Entity = BSI; 43 items). The 10 tested applications are selected (1822, 1867, 1868, 1903, 1917, 1937, 1936, 3301, 3299, 4052) and each shows 2025 DR Test Scope = True, 2025 Backup/Restore Test Scope = True and 2025 Backup/Restore DIV Scope = True.</t>
+          <t>BCiC export of the BSI DR-scope population (43 applications) with Exercise Date and 2025 DR / Backup-Restore / DIV scope flags.</t>
         </is>
       </c>
       <c r="F64" s="86" t="inlineStr">
         <is>
-          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: D, K, N</t>
+          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: B, C, D, K, L, N</t>
         </is>
       </c>
       <c r="G64" s="82" t="n"/>
@@ -7209,35 +7080,35 @@
       <c r="R64" s="82" t="n"/>
       <c r="S64" s="82" t="n"/>
     </row>
-    <row r="65" ht="42" customHeight="1" s="71">
+    <row r="65" ht="30" customHeight="1" s="71">
       <c r="A65" s="86" t="inlineStr">
         <is>
-          <t>MA02</t>
+          <t>E02</t>
         </is>
       </c>
       <c r="B65" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg</t>
         </is>
       </c>
       <c r="C65" s="86" t="inlineStr">
         <is>
-          <t>08/18/2026 – Frank Puentes</t>
+          <t>09/10/2026 – Cesar Vidal</t>
         </is>
       </c>
       <c r="D65" s="86" t="inlineStr">
         <is>
-          <t>Email attestation</t>
+          <t>BCiC screenshot</t>
         </is>
       </c>
       <c r="E65" s="86" t="inlineStr">
         <is>
-          <t>Frank Puentes returns signed Management Attestation (4069_001.pdf) to Cesar Vidal. Same message as DMA03 / E17.</t>
+          <t>BCiC Applications screen with view 'Applications In Scope for DR Test BSI' selected (1–20 of 43 items).</t>
         </is>
       </c>
       <c r="F65" s="86" t="inlineStr">
         <is>
-          <t>Samples: 3301, 1903, 1937; columns: H, J, O</t>
+          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: D, K, N</t>
         </is>
       </c>
       <c r="G65" s="82" t="n"/>
@@ -7254,20 +7125,20 @@
       <c r="R65" s="82" t="n"/>
       <c r="S65" s="82" t="n"/>
     </row>
-    <row r="66" ht="30" customHeight="1" s="71">
+    <row r="66" ht="42" customHeight="1" s="71">
       <c r="A66" s="86" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>E03</t>
         </is>
       </c>
       <c r="B66" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
         </is>
       </c>
       <c r="C66" s="86" t="inlineStr">
         <is>
-          <t>BCiC – Applications In Scope for DR Test BSI</t>
+          <t>BCiC – Data Integrity Validation Testing (62 records)</t>
         </is>
       </c>
       <c r="D66" s="86" t="inlineStr">
@@ -7277,12 +7148,12 @@
       </c>
       <c r="E66" s="86" t="inlineStr">
         <is>
-          <t>BCiC export of the BSI DR-scope population (43 applications) with Exercise Date and 2025 DR / Backup-Restore / DIV scope flags.</t>
+          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Y/N Format/Headers/Content, Attestation Date / Provided By. Row numbers quoted are Excel rows.</t>
         </is>
       </c>
       <c r="F66" s="86" t="inlineStr">
         <is>
-          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: B, C, D, K, L, N</t>
+          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: B, C, D, E, F, G, H, I, K, L, M, O, P</t>
         </is>
       </c>
       <c r="G66" s="82" t="n"/>
@@ -7299,15 +7170,15 @@
       <c r="R66" s="82" t="n"/>
       <c r="S66" s="82" t="n"/>
     </row>
-    <row r="67" ht="30" customHeight="1" s="71">
+    <row r="67" ht="42" customHeight="1" s="71">
       <c r="A67" s="86" t="inlineStr">
         <is>
-          <t>E02</t>
+          <t>E04</t>
         </is>
       </c>
       <c r="B67" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg</t>
         </is>
       </c>
       <c r="C67" s="86" t="inlineStr">
@@ -7322,12 +7193,12 @@
       </c>
       <c r="E67" s="86" t="inlineStr">
         <is>
-          <t>BCiC Applications screen with view 'Applications In Scope for DR Test BSI' selected (1–20 of 43 items).</t>
+          <t>BCiC 'Data Integrity Validation Testing' screen (1–20 of 66 items) showing tester, validation date, manager, approval date, Y/N results and attestation fields.</t>
         </is>
       </c>
       <c r="F67" s="86" t="inlineStr">
         <is>
-          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: D, K, N</t>
+          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: D, E, F, G, H, K, P</t>
         </is>
       </c>
       <c r="G67" s="82" t="n"/>
@@ -7344,35 +7215,35 @@
       <c r="R67" s="82" t="n"/>
       <c r="S67" s="82" t="n"/>
     </row>
-    <row r="68" ht="42" customHeight="1" s="71">
+    <row r="68" ht="30" customHeight="1" s="71">
       <c r="A68" s="86" t="inlineStr">
         <is>
-          <t>E03</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="B68" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg</t>
         </is>
       </c>
       <c r="C68" s="86" t="inlineStr">
         <is>
-          <t>BCiC – Data Integrity Validation Testing (62 records)</t>
+          <t>09/15/2025 – Elizabeth Noda</t>
         </is>
       </c>
       <c r="D68" s="86" t="inlineStr">
         <is>
-          <t>BCiC export</t>
+          <t>Meeting invite</t>
         </is>
       </c>
       <c r="E68" s="86" t="inlineStr">
         <is>
-          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Y/N Format/Headers/Content, Attestation Date / Provided By. Row numbers quoted are Excel rows.</t>
+          <t>IT DR meeting to review the 2025 BIA results and applications list ahead of the DR exercise.</t>
         </is>
       </c>
       <c r="F68" s="86" t="inlineStr">
         <is>
-          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: B, C, D, E, F, G, H, I, K, L, M, O, P</t>
+          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: M, N</t>
         </is>
       </c>
       <c r="G68" s="82" t="n"/>
@@ -7389,35 +7260,35 @@
       <c r="R68" s="82" t="n"/>
       <c r="S68" s="82" t="n"/>
     </row>
-    <row r="69" ht="42" customHeight="1" s="71">
+    <row r="69" ht="30" customHeight="1" s="71">
       <c r="A69" s="86" t="inlineStr">
         <is>
-          <t>E04</t>
+          <t>E06</t>
         </is>
       </c>
       <c r="B69" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml</t>
         </is>
       </c>
       <c r="C69" s="86" t="inlineStr">
         <is>
-          <t>09/10/2026 – Cesar Vidal</t>
+          <t>09/18/2025 – Elizabeth Noda</t>
         </is>
       </c>
       <c r="D69" s="86" t="inlineStr">
         <is>
-          <t>BCiC screenshot</t>
+          <t>Meeting invite</t>
         </is>
       </c>
       <c r="E69" s="86" t="inlineStr">
         <is>
-          <t>BCiC 'Data Integrity Validation Testing' screen (1–20 of 66 items) showing tester, validation date, manager, approval date, Y/N results and attestation fields.</t>
+          <t>Follow-up IT BIA results / DR preparation meeting (applications list review).</t>
         </is>
       </c>
       <c r="F69" s="86" t="inlineStr">
         <is>
-          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: D, E, F, G, H, K, P</t>
+          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: M, N</t>
         </is>
       </c>
       <c r="G69" s="82" t="n"/>
@@ -7434,35 +7305,35 @@
       <c r="R69" s="82" t="n"/>
       <c r="S69" s="82" t="n"/>
     </row>
-    <row r="70" ht="30" customHeight="1" s="71">
+    <row r="70" ht="42" customHeight="1" s="71">
       <c r="A70" s="86" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>E07</t>
         </is>
       </c>
       <c r="B70" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg</t>
         </is>
       </c>
       <c r="C70" s="86" t="inlineStr">
         <is>
-          <t>09/15/2025 – Elizabeth Noda</t>
+          <t>11/15/2025 – Frank Puentes</t>
         </is>
       </c>
       <c r="D70" s="86" t="inlineStr">
         <is>
-          <t>Meeting invite</t>
+          <t>Email + 13 attachments</t>
         </is>
       </c>
       <c r="E70" s="86" t="inlineStr">
         <is>
-          <t>IT DR meeting to review the 2025 BIA results and applications list ahead of the DR exercise.</t>
+          <t>Pre-DR (11/14/2025) source reports: Fedlink, OFAC ACH/FED/SWIFT, Payment Monitor, SWIFT Interface Monitor, outgoing Fedwire/SWIFT. Attachments extracted to E07_Attachments_extracted.</t>
         </is>
       </c>
       <c r="F70" s="86" t="inlineStr">
         <is>
-          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: M, N</t>
+          <t>Samples: 3301, 1903, 1936, 1937; columns: F</t>
         </is>
       </c>
       <c r="G70" s="82" t="n"/>
@@ -7482,32 +7353,32 @@
     <row r="71" ht="30" customHeight="1" s="71">
       <c r="A71" s="86" t="inlineStr">
         <is>
-          <t>E06</t>
+          <t>E08</t>
         </is>
       </c>
       <c r="B71" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg</t>
         </is>
       </c>
       <c r="C71" s="86" t="inlineStr">
         <is>
-          <t>09/18/2025 – Elizabeth Noda</t>
+          <t>11/15/2025 – Frank Puentes</t>
         </is>
       </c>
       <c r="D71" s="86" t="inlineStr">
         <is>
-          <t>Meeting invite</t>
+          <t>Email + 13 attachments</t>
         </is>
       </c>
       <c r="E71" s="86" t="inlineStr">
         <is>
-          <t>Follow-up IT BIA results / DR preparation meeting (applications list review).</t>
+          <t>DR test-day (11/15/2025) re-run of the same reports for comparison with 11/14/2025 source. Attachments extracted to E08_Attachments_extracted.</t>
         </is>
       </c>
       <c r="F71" s="86" t="inlineStr">
         <is>
-          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: M, N</t>
+          <t>Samples: 3301, 1903, 1936, 1937; columns: F, M</t>
         </is>
       </c>
       <c r="G71" s="82" t="n"/>
@@ -7524,35 +7395,35 @@
       <c r="R71" s="82" t="n"/>
       <c r="S71" s="82" t="n"/>
     </row>
-    <row r="72" ht="42" customHeight="1" s="71">
+    <row r="72" ht="54" customHeight="1" s="71">
       <c r="A72" s="86" t="inlineStr">
         <is>
-          <t>E07</t>
+          <t>E09</t>
         </is>
       </c>
       <c r="B72" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg</t>
         </is>
       </c>
       <c r="C72" s="86" t="inlineStr">
         <is>
-          <t>11/15/2025 – Frank Puentes</t>
+          <t>03/03/2026 – 05/05/2026 – Claudia Romero</t>
         </is>
       </c>
       <c r="D72" s="86" t="inlineStr">
         <is>
-          <t>Email + 13 attachments</t>
+          <t>Email approval</t>
         </is>
       </c>
       <c r="E72" s="86" t="inlineStr">
         <is>
-          <t>Pre-DR (11/14/2025) source reports: Fedlink, OFAC ACH/FED/SWIFT, Payment Monitor, SWIFT Interface Monitor, outgoing Fedwire/SWIFT. Attachments extracted to E07_Attachments_extracted.</t>
+          <t>Client Back Office test evidence (Mariorly Morales, Ilumel Rodriguez, Rolando Bonilla) and Claudia Romero "Approved." 05/05/2026. Thread maps ACH Express, FedExport, FedImport, Imaging101 to Client Back Office / Claudia Romero.</t>
         </is>
       </c>
       <c r="F72" s="86" t="inlineStr">
         <is>
-          <t>Samples: 3301, 1903, 1936, 1937; columns: F</t>
+          <t>Samples: 1822, 1867, 1868, 3299, 1937; columns: E, G, H, J, M, N, O</t>
         </is>
       </c>
       <c r="G72" s="82" t="n"/>
@@ -7569,35 +7440,35 @@
       <c r="R72" s="82" t="n"/>
       <c r="S72" s="82" t="n"/>
     </row>
-    <row r="73" ht="30" customHeight="1" s="71">
+    <row r="73" ht="42" customHeight="1" s="71">
       <c r="A73" s="86" t="inlineStr">
         <is>
-          <t>E08</t>
+          <t>E10</t>
         </is>
       </c>
       <c r="B73" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg</t>
         </is>
       </c>
       <c r="C73" s="86" t="inlineStr">
         <is>
-          <t>11/15/2025 – Frank Puentes</t>
+          <t>03/09/2026 – Lina Acuna</t>
         </is>
       </c>
       <c r="D73" s="86" t="inlineStr">
         <is>
-          <t>Email + 13 attachments</t>
+          <t>Email approval</t>
         </is>
       </c>
       <c r="E73" s="86" t="inlineStr">
         <is>
-          <t>DR test-day (11/15/2025) re-run of the same reports for comparison with 11/14/2025 source. Attachments extracted to E08_Attachments_extracted.</t>
+          <t>Finance DIV results chart (Jose Acero) and Lina Acuna "Approved" 03/09/2026 (T24 / ReconXpert backup-restore).</t>
         </is>
       </c>
       <c r="F73" s="86" t="inlineStr">
         <is>
-          <t>Samples: 3301, 1903, 1936, 1937; columns: F, M</t>
+          <t>Samples: 1917, 1937; columns: M</t>
         </is>
       </c>
       <c r="G73" s="82" t="n"/>
@@ -7614,35 +7485,35 @@
       <c r="R73" s="82" t="n"/>
       <c r="S73" s="82" t="n"/>
     </row>
-    <row r="74" ht="54" customHeight="1" s="71">
+    <row r="74" ht="42" customHeight="1" s="71">
       <c r="A74" s="86" t="inlineStr">
         <is>
-          <t>E09</t>
+          <t>E13</t>
         </is>
       </c>
       <c r="B74" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg</t>
         </is>
       </c>
       <c r="C74" s="86" t="inlineStr">
         <is>
-          <t>03/03/2026 – 05/05/2026 – Claudia Romero</t>
+          <t>11/13/2024 – T24 backup user</t>
         </is>
       </c>
       <c r="D74" s="86" t="inlineStr">
         <is>
-          <t>Email approval</t>
+          <t>System email</t>
         </is>
       </c>
       <c r="E74" s="86" t="inlineStr">
         <is>
-          <t>Client Back Office test evidence (Mariorly Morales, Ilumel Rodriguez, Rolando Bonilla) and Claudia Romero "Approved." 05/05/2026. Thread maps ACH Express, FedExport, FedImport, Imaging101 to Client Back Office / Claudia Romero.</t>
+          <t>T24 environment refresh log – prior period (outside review period); supplemental only.</t>
         </is>
       </c>
       <c r="F74" s="86" t="inlineStr">
         <is>
-          <t>Samples: 1822, 1867, 1868, 3299, 1937; columns: E, G, H, J, M, N, O</t>
+          <t>Samples: —; columns: — (supplemental)</t>
         </is>
       </c>
       <c r="G74" s="82" t="n"/>
@@ -7662,32 +7533,32 @@
     <row r="75" ht="42" customHeight="1" s="71">
       <c r="A75" s="86" t="inlineStr">
         <is>
-          <t>E10</t>
+          <t>E16b</t>
         </is>
       </c>
       <c r="B75" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
         </is>
       </c>
       <c r="C75" s="86" t="inlineStr">
         <is>
-          <t>03/09/2026 – Lina Acuna</t>
+          <t>08/2026 – BCiC export sent with attestation request</t>
         </is>
       </c>
       <c r="D75" s="86" t="inlineStr">
         <is>
-          <t>Email approval</t>
+          <t>BCiC export</t>
         </is>
       </c>
       <c r="E75" s="86" t="inlineStr">
         <is>
-          <t>Finance DIV results chart (Jose Acero) and Lina Acuna "Approved" 03/09/2026 (T24 / ReconXpert backup-restore).</t>
+          <t>BCiC DIV export 2025-26 (64 rows; no manager columns) sent to managers with the attestation request and returned by M. T. Del Cerro (DMA05). Row numbers are Excel rows.</t>
         </is>
       </c>
       <c r="F75" s="86" t="inlineStr">
         <is>
-          <t>Samples: 1917, 1937; columns: M</t>
+          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: B, D, E, F, I, K, P</t>
         </is>
       </c>
       <c r="G75" s="82" t="n"/>
@@ -7704,37 +7575,13 @@
       <c r="R75" s="82" t="n"/>
       <c r="S75" s="82" t="n"/>
     </row>
-    <row r="76" ht="30" customHeight="1" s="71">
-      <c r="A76" s="86" t="inlineStr">
-        <is>
-          <t>E11</t>
-        </is>
-      </c>
-      <c r="B76" s="86" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E11_BSI.IT.6.C7.3 Manager Approval.msg</t>
-        </is>
-      </c>
-      <c r="C76" s="86" t="inlineStr">
-        <is>
-          <t>03/09/2026 – Lina Acuna</t>
-        </is>
-      </c>
-      <c r="D76" s="86" t="inlineStr">
-        <is>
-          <t>Email approval</t>
-        </is>
-      </c>
-      <c r="E76" s="86" t="inlineStr">
-        <is>
-          <t>Same Finance approval thread as E10 (separate save).</t>
-        </is>
-      </c>
-      <c r="F76" s="86" t="inlineStr">
-        <is>
-          <t>Samples: 1917, 1937; columns: M</t>
-        </is>
-      </c>
+    <row r="76" s="71">
+      <c r="A76" s="82" t="n"/>
+      <c r="B76" s="82" t="n"/>
+      <c r="C76" s="82" t="n"/>
+      <c r="D76" s="82" t="n"/>
+      <c r="E76" s="82" t="n"/>
+      <c r="F76" s="82" t="n"/>
       <c r="G76" s="82" t="n"/>
       <c r="H76" s="82" t="n"/>
       <c r="I76" s="82" t="n"/>
@@ -7749,43 +7596,12 @@
       <c r="R76" s="82" t="n"/>
       <c r="S76" s="82" t="n"/>
     </row>
-    <row r="77" ht="30" customHeight="1" s="71">
-      <c r="A77" s="86" t="inlineStr">
-        <is>
-          <t>E12</t>
-        </is>
-      </c>
-      <c r="B77" s="86" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E12_RE_ Testing enviroment Financial Analysis manager approval.msg</t>
-        </is>
-      </c>
-      <c r="C77" s="86" t="inlineStr">
-        <is>
-          <t>12/31/2025 &amp; 01/26/2026 – Sadis Alvarenga</t>
-        </is>
-      </c>
-      <c r="D77" s="86" t="inlineStr">
-        <is>
-          <t>Email approval</t>
-        </is>
-      </c>
-      <c r="E77" s="86" t="inlineStr">
-        <is>
-          <t>Same message as BLA06 – Sadis Alvarenga "Approved."</t>
-        </is>
-      </c>
-      <c r="F77" s="86" t="inlineStr">
-        <is>
-          <t>Samples: 1917, 1937; columns: G, H, J, O</t>
-        </is>
-      </c>
-      <c r="G77" s="82" t="n"/>
-      <c r="H77" s="82" t="n"/>
-      <c r="I77" s="82" t="n"/>
-      <c r="J77" s="82" t="n"/>
-      <c r="K77" s="82" t="n"/>
-      <c r="L77" s="82" t="n"/>
+    <row r="77" ht="22" customHeight="1" s="71">
+      <c r="A77" s="73" t="inlineStr">
+        <is>
+          <t>Observations for reviewer consideration (do not change the PASS conclusions unless the reviewer determines otherwise)</t>
+        </is>
+      </c>
       <c r="M77" s="82" t="n"/>
       <c r="N77" s="82" t="n"/>
       <c r="O77" s="82" t="n"/>
@@ -7794,37 +7610,33 @@
       <c r="R77" s="82" t="n"/>
       <c r="S77" s="82" t="n"/>
     </row>
-    <row r="78" ht="42" customHeight="1" s="71">
-      <c r="A78" s="86" t="inlineStr">
-        <is>
-          <t>E13</t>
-        </is>
-      </c>
-      <c r="B78" s="86" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg</t>
-        </is>
-      </c>
-      <c r="C78" s="86" t="inlineStr">
-        <is>
-          <t>11/13/2024 – T24 backup user</t>
-        </is>
-      </c>
-      <c r="D78" s="86" t="inlineStr">
-        <is>
-          <t>System email</t>
-        </is>
-      </c>
-      <c r="E78" s="86" t="inlineStr">
-        <is>
-          <t>T24 environment refresh log – prior period (outside review period); supplemental only.</t>
-        </is>
-      </c>
-      <c r="F78" s="86" t="inlineStr">
-        <is>
-          <t>Samples: —; columns: — (supplemental)</t>
-        </is>
-      </c>
+    <row r="78" ht="30" customHeight="1" s="71">
+      <c r="A78" s="85" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B78" s="85" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="C78" s="85" t="inlineStr">
+        <is>
+          <t>Samples affected</t>
+        </is>
+      </c>
+      <c r="D78" s="85" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="E78" s="85" t="inlineStr">
+        <is>
+          <t>Impact / reviewer consideration</t>
+        </is>
+      </c>
+      <c r="F78" s="85" t="inlineStr"/>
       <c r="G78" s="82" t="n"/>
       <c r="H78" s="82" t="n"/>
       <c r="I78" s="82" t="n"/>
@@ -7839,37 +7651,31 @@
       <c r="R78" s="82" t="n"/>
       <c r="S78" s="82" t="n"/>
     </row>
-    <row r="79" ht="42" customHeight="1" s="71">
-      <c r="A79" s="86" t="inlineStr">
-        <is>
-          <t>E14</t>
-        </is>
-      </c>
-      <c r="B79" s="86" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml</t>
-        </is>
-      </c>
-      <c r="C79" s="86" t="inlineStr">
-        <is>
-          <t>08/17/2026 request / 08/19/2026 reply – David Marquez</t>
-        </is>
-      </c>
-      <c r="D79" s="86" t="inlineStr">
-        <is>
-          <t>Email attestation</t>
-        </is>
-      </c>
-      <c r="E79" s="86" t="inlineStr">
-        <is>
-          <t>Cesar Vidal request to Department Managers (DR exercises 11/15/2025 and 02/21/2026; BCiC export attached) and David Marquez's signed reply.</t>
-        </is>
-      </c>
-      <c r="F79" s="86" t="inlineStr">
-        <is>
-          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: B, H, J, L, O</t>
-        </is>
-      </c>
+    <row r="79" ht="90" customHeight="1" s="71">
+      <c r="A79" s="87" t="n">
+        <v>1</v>
+      </c>
+      <c r="B79" s="87" t="inlineStr">
+        <is>
+          <t>Business line approvals for 33 of 56 in-scope DIV records were obtained through retrospective management attestations dated 08/17/2026 – 09/09/2026, i.e. after the review period end (06/01/2026) and ~9-10 months after the 11/15/2025 DIV testing. A further 13 records (BSA/AML/OFAC and Payments) carry in-period BCiC approval dates (11/15/2025, 12/18/2025) supported only by 08/2026 signed attestations. 10 records have in-period approval emails (E09, BLA06).</t>
+        </is>
+      </c>
+      <c r="C79" s="87" t="inlineStr">
+        <is>
+          <t>3299, 4052, 3301, 1903, 1936, 1937</t>
+        </is>
+      </c>
+      <c r="D79" s="87" t="inlineStr">
+        <is>
+          <t>Folder 03 (DMA01–DMA12); E03 approval dates</t>
+        </is>
+      </c>
+      <c r="E79" s="87" t="inlineStr">
+        <is>
+          <t>Approval is evidenced for 100% of records; timing is an observation. The attestation (DMA02a §3.6) commits to contemporaneous approval going forward. Reviewer to conclude whether retrospective approval satisfies the control for the period.</t>
+        </is>
+      </c>
+      <c r="F79" s="87" t="inlineStr"/>
       <c r="G79" s="82" t="n"/>
       <c r="H79" s="82" t="n"/>
       <c r="I79" s="82" t="n"/>
@@ -7884,37 +7690,31 @@
       <c r="R79" s="82" t="n"/>
       <c r="S79" s="82" t="n"/>
     </row>
-    <row r="80" ht="42" customHeight="1" s="71">
-      <c r="A80" s="86" t="inlineStr">
-        <is>
-          <t>E14a</t>
-        </is>
-      </c>
-      <c r="B80" s="86" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf</t>
-        </is>
-      </c>
-      <c r="C80" s="86" t="inlineStr">
-        <is>
-          <t>08/19/2026 – David Marquez</t>
-        </is>
-      </c>
-      <c r="D80" s="86" t="inlineStr">
-        <is>
-          <t>Signed attestation</t>
-        </is>
-      </c>
-      <c r="E80" s="86" t="inlineStr">
-        <is>
-          <t>Signed attestation – OFAC Manager, BSA/AML-OFAC Compliance. States IT DR team facilitates DIV annually; 63 entries / 13 applications, all Y/Y/Y.</t>
-        </is>
-      </c>
-      <c r="F80" s="86" t="inlineStr">
-        <is>
-          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: C, H, J, L, M, N, O, P</t>
-        </is>
-      </c>
+    <row r="80" ht="78" customHeight="1" s="71">
+      <c r="A80" s="87" t="n">
+        <v>2</v>
+      </c>
+      <c r="B80" s="87" t="inlineStr">
+        <is>
+          <t>Self-approval: the business tester and the approving Department Manager are the same person for BSA/AML/OFAC (David Marquez), Payments (Franklin Puentes), Investment Operations (Michelle Oropesa), Treasury (Martha Sullivan), Digital Wealth (Victoria Fernandez), Client Servicing Unit (Liliana Vizhnay), Commercial Middle Office (Miguel Orozco – Imaging101 / T24 row 15, 51) and Financial Analysis (Sadis Alvarenga).</t>
+        </is>
+      </c>
+      <c r="C80" s="87" t="inlineStr">
+        <is>
+          <t>3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
+        </is>
+      </c>
+      <c r="D80" s="87" t="inlineStr">
+        <is>
+          <t>E03 tester vs manager columns</t>
+        </is>
+      </c>
+      <c r="E80" s="87" t="inlineStr">
+        <is>
+          <t>Segregation-of-duties observation; the approvers are the business line heads for those areas.</t>
+        </is>
+      </c>
+      <c r="F80" s="87" t="inlineStr"/>
       <c r="G80" s="82" t="n"/>
       <c r="H80" s="82" t="n"/>
       <c r="I80" s="82" t="n"/>
@@ -7929,37 +7729,31 @@
       <c r="R80" s="82" t="n"/>
       <c r="S80" s="82" t="n"/>
     </row>
-    <row r="81" ht="42" customHeight="1" s="71">
-      <c r="A81" s="86" t="inlineStr">
-        <is>
-          <t>E15</t>
-        </is>
-      </c>
-      <c r="B81" s="86" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 1 (1).msg.eml</t>
-        </is>
-      </c>
-      <c r="C81" s="86" t="inlineStr">
-        <is>
-          <t>08/17/2026 – Michelle Oropesa</t>
-        </is>
-      </c>
-      <c r="D81" s="86" t="inlineStr">
-        <is>
-          <t>Email attestation</t>
-        </is>
-      </c>
-      <c r="E81" s="86" t="inlineStr">
-        <is>
-          <t>Michelle Oropesa returns signed attestation.</t>
-        </is>
-      </c>
-      <c r="F81" s="86" t="inlineStr">
-        <is>
-          <t>Samples: 4052, 1936, 1937; columns: H, J, O</t>
-        </is>
-      </c>
+    <row r="81" ht="30" customHeight="1" s="71">
+      <c r="A81" s="87" t="n">
+        <v>3</v>
+      </c>
+      <c r="B81" s="87" t="inlineStr">
+        <is>
+          <t>FedExport – BCiC Department Manager Approval Date 06/05/2026 (E03 row 9, E04) vs Claudia Romero "Approved." 05/05/2026 (E09).</t>
+        </is>
+      </c>
+      <c r="C81" s="87" t="inlineStr">
+        <is>
+          <t>1867</t>
+        </is>
+      </c>
+      <c r="D81" s="87" t="inlineStr">
+        <is>
+          <t>E03, E04, E09</t>
+        </is>
+      </c>
+      <c r="E81" s="87" t="inlineStr">
+        <is>
+          <t>Likely BCiC data-entry error; recommend management correct the BCiC record.</t>
+        </is>
+      </c>
+      <c r="F81" s="87" t="inlineStr"/>
       <c r="G81" s="82" t="n"/>
       <c r="H81" s="82" t="n"/>
       <c r="I81" s="82" t="n"/>
@@ -7975,36 +7769,30 @@
       <c r="S81" s="82" t="n"/>
     </row>
     <row r="82" ht="30" customHeight="1" s="71">
-      <c r="A82" s="86" t="inlineStr">
-        <is>
-          <t>E15a</t>
-        </is>
-      </c>
-      <c r="B82" s="86" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15a_Data_Integrity_Attestation_Santander-BCiC.pdf</t>
-        </is>
-      </c>
-      <c r="C82" s="86" t="inlineStr">
-        <is>
-          <t>08/17/2026 – Michelle Oropesa</t>
-        </is>
-      </c>
-      <c r="D82" s="86" t="inlineStr">
-        <is>
-          <t>Signed attestation</t>
-        </is>
-      </c>
-      <c r="E82" s="86" t="inlineStr">
-        <is>
-          <t>Signed attestation – Investment Operations.</t>
-        </is>
-      </c>
-      <c r="F82" s="86" t="inlineStr">
-        <is>
-          <t>Samples: 4052, 1936, 1937; columns: H, J, O</t>
-        </is>
-      </c>
+      <c r="A82" s="87" t="n">
+        <v>4</v>
+      </c>
+      <c r="B82" s="87" t="inlineStr">
+        <is>
+          <t>BLA02 (BSA/AML/OFAC) test script – DIV Yes/No answer boxes are blank.</t>
+        </is>
+      </c>
+      <c r="C82" s="87" t="inlineStr">
+        <is>
+          <t>3299, 1903, 1936, 1937</t>
+        </is>
+      </c>
+      <c r="D82" s="87" t="inlineStr">
+        <is>
+          <t>BLA02 p.1</t>
+        </is>
+      </c>
+      <c r="E82" s="87" t="inlineStr">
+        <is>
+          <t>Mitigated by production vs test-day screenshots in BLA02, BCiC Y/Y/Y (E03) and signed attestation (DMA02a).</t>
+        </is>
+      </c>
+      <c r="F82" s="87" t="inlineStr"/>
       <c r="G82" s="82" t="n"/>
       <c r="H82" s="82" t="n"/>
       <c r="I82" s="82" t="n"/>
@@ -8020,36 +7808,30 @@
       <c r="S82" s="82" t="n"/>
     </row>
     <row r="83" ht="42" customHeight="1" s="71">
-      <c r="A83" s="86" t="inlineStr">
-        <is>
-          <t>E16</t>
-        </is>
-      </c>
-      <c r="B83" s="86" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 2 (1).msg.eml</t>
-        </is>
-      </c>
-      <c r="C83" s="86" t="inlineStr">
-        <is>
-          <t>08/19/2026 – Maria Teresa Del Cerro</t>
-        </is>
-      </c>
-      <c r="D83" s="86" t="inlineStr">
-        <is>
-          <t>Email attestation</t>
-        </is>
-      </c>
-      <c r="E83" s="86" t="inlineStr">
-        <is>
-          <t>Signed attestation and BCiC export returned.</t>
-        </is>
-      </c>
-      <c r="F83" s="86" t="inlineStr">
-        <is>
-          <t>Samples: 3299, 1903, 1937; columns: H, J, O</t>
-        </is>
-      </c>
+      <c r="A83" s="87" t="n">
+        <v>5</v>
+      </c>
+      <c r="B83" s="87" t="inlineStr">
+        <is>
+          <t>BSA T24 record (E03 row 8) Attestation Date 08/29/2026 vs signed attestation 8/19/2026 (DMA02a); Financial Risk manager recorded as "Xavier Caisapanta" in BCiC while the approval email is from Ivan Caisapanta (DMA08).</t>
+        </is>
+      </c>
+      <c r="C83" s="87" t="inlineStr">
+        <is>
+          <t>1937</t>
+        </is>
+      </c>
+      <c r="D83" s="87" t="inlineStr">
+        <is>
+          <t>E03, DMA02a, DMA08</t>
+        </is>
+      </c>
+      <c r="E83" s="87" t="inlineStr">
+        <is>
+          <t>BCiC data-entry / naming consistency; confirm identity of Financial Risk approver.</t>
+        </is>
+      </c>
+      <c r="F83" s="87" t="inlineStr"/>
       <c r="G83" s="82" t="n"/>
       <c r="H83" s="82" t="n"/>
       <c r="I83" s="82" t="n"/>
@@ -8064,37 +7846,31 @@
       <c r="R83" s="82" t="n"/>
       <c r="S83" s="82" t="n"/>
     </row>
-    <row r="84" ht="30" customHeight="1" s="71">
-      <c r="A84" s="86" t="inlineStr">
-        <is>
-          <t>E16a</t>
-        </is>
-      </c>
-      <c r="B84" s="86" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16a_Data_Integrity_Attestation_Santander-BCiC.pdf</t>
-        </is>
-      </c>
-      <c r="C84" s="86" t="inlineStr">
-        <is>
-          <t>08/19/2026 – Maria Teresa Del Cerro Hontanilla</t>
-        </is>
-      </c>
-      <c r="D84" s="86" t="inlineStr">
-        <is>
-          <t>Signed attestation</t>
-        </is>
-      </c>
-      <c r="E84" s="86" t="inlineStr">
-        <is>
-          <t>Signed attestation – Operations.</t>
-        </is>
-      </c>
-      <c r="F84" s="86" t="inlineStr">
-        <is>
-          <t>Samples: 3299, 1903, 1937; columns: H, J, O</t>
-        </is>
-      </c>
+    <row r="84" ht="42" customHeight="1" s="71">
+      <c r="A84" s="87" t="n">
+        <v>6</v>
+      </c>
+      <c r="B84" s="87" t="inlineStr">
+        <is>
+          <t>ACH Express and Interface Monitor are not named verbatim in the DIV "Application In-scope" lines of BLA01 / BLA04; BLA01 operator (Raimy Ayala) differs from BCiC tester (Andreina De Stefano).</t>
+        </is>
+      </c>
+      <c r="C84" s="87" t="inlineStr">
+        <is>
+          <t>1822, 4052, 1867, 1868</t>
+        </is>
+      </c>
+      <c r="D84" s="87" t="inlineStr">
+        <is>
+          <t>BLA01, BLA04, E03, MA01</t>
+        </is>
+      </c>
+      <c r="E84" s="87" t="inlineStr">
+        <is>
+          <t>Application-level DIV records exist in BCiC (E03 rows 47 and 61) with Y/Y/Y results and manager approval.</t>
+        </is>
+      </c>
+      <c r="F84" s="87" t="inlineStr"/>
       <c r="G84" s="82" t="n"/>
       <c r="H84" s="82" t="n"/>
       <c r="I84" s="82" t="n"/>
@@ -8109,37 +7885,31 @@
       <c r="R84" s="82" t="n"/>
       <c r="S84" s="82" t="n"/>
     </row>
-    <row r="85" ht="30" customHeight="1" s="71">
-      <c r="A85" s="86" t="inlineStr">
-        <is>
-          <t>E16b</t>
-        </is>
-      </c>
-      <c r="B85" s="86" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
-        </is>
-      </c>
-      <c r="C85" s="86" t="inlineStr">
-        <is>
-          <t>08/2026 – BCiC export sent with attestation request</t>
-        </is>
-      </c>
-      <c r="D85" s="86" t="inlineStr">
-        <is>
-          <t>BCiC export</t>
-        </is>
-      </c>
-      <c r="E85" s="86" t="inlineStr">
-        <is>
-          <t>BCiC DIV export 2025-26 (64 rows; no manager columns) reviewed by managers with the attestation. Row numbers are Excel rows.</t>
-        </is>
-      </c>
-      <c r="F85" s="86" t="inlineStr">
-        <is>
-          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: B, D, E, F, I, K, P</t>
-        </is>
-      </c>
+    <row r="85" ht="54" customHeight="1" s="71">
+      <c r="A85" s="87" t="n">
+        <v>7</v>
+      </c>
+      <c r="B85" s="87" t="inlineStr">
+        <is>
+          <t>Count reconciliation – E03 contains 62 DIV records (56 for the 10 tested applications); E16b contains 64 rows (one additional Treasury T24 row with blank department, row 45); the attestation states 63 entries / 13 applications.</t>
+        </is>
+      </c>
+      <c r="C85" s="87" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D85" s="87" t="inlineStr">
+        <is>
+          <t>E03, E16b, DMA02a</t>
+        </is>
+      </c>
+      <c r="E85" s="87" t="inlineStr">
+        <is>
+          <t>Testing performed on E03 (the export containing the manager approval fields).</t>
+        </is>
+      </c>
+      <c r="F85" s="87" t="inlineStr"/>
       <c r="G85" s="82" t="n"/>
       <c r="H85" s="82" t="n"/>
       <c r="I85" s="82" t="n"/>
@@ -8154,37 +7924,31 @@
       <c r="R85" s="82" t="n"/>
       <c r="S85" s="82" t="n"/>
     </row>
-    <row r="86" ht="42" customHeight="1" s="71">
-      <c r="A86" s="86" t="inlineStr">
-        <is>
-          <t>E17</t>
-        </is>
-      </c>
-      <c r="B86" s="86" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 3 (1).msg.eml</t>
-        </is>
-      </c>
-      <c r="C86" s="86" t="inlineStr">
-        <is>
-          <t>08/18/2026 – Frank Puentes</t>
-        </is>
-      </c>
-      <c r="D86" s="86" t="inlineStr">
-        <is>
-          <t>Email attestation</t>
-        </is>
-      </c>
-      <c r="E86" s="86" t="inlineStr">
-        <is>
-          <t>Frank Puentes returns signed attestation.</t>
-        </is>
-      </c>
-      <c r="F86" s="86" t="inlineStr">
-        <is>
-          <t>Samples: 3301, 1903, 1937; columns: H, J, O</t>
-        </is>
-      </c>
+    <row r="86" ht="30" customHeight="1" s="71">
+      <c r="A86" s="87" t="n">
+        <v>8</v>
+      </c>
+      <c r="B86" s="87" t="inlineStr">
+        <is>
+          <t>Annual interval – prior DR exercise 10/19/2024 to 11/15/2025 = 392 days; one exercise per annual DR cycle (2024, 2025) and within the review period.</t>
+        </is>
+      </c>
+      <c r="C86" s="87" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D86" s="87" t="inlineStr">
+        <is>
+          <t>Tab 'DR 2024 Testing Results'; E01; E03</t>
+        </is>
+      </c>
+      <c r="E86" s="87" t="inlineStr">
+        <is>
+          <t>Annual requirement assessed per DR cycle.</t>
+        </is>
+      </c>
+      <c r="F86" s="87" t="inlineStr"/>
       <c r="G86" s="82" t="n"/>
       <c r="H86" s="82" t="n"/>
       <c r="I86" s="82" t="n"/>
@@ -8199,37 +7963,31 @@
       <c r="R86" s="82" t="n"/>
       <c r="S86" s="82" t="n"/>
     </row>
-    <row r="87" ht="30" customHeight="1" s="71">
-      <c r="A87" s="86" t="inlineStr">
-        <is>
-          <t>E17a</t>
-        </is>
-      </c>
-      <c r="B87" s="86" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17a_4069_001.pdf</t>
-        </is>
-      </c>
-      <c r="C87" s="86" t="inlineStr">
-        <is>
-          <t>08/18/2026 – Frank Puentes</t>
-        </is>
-      </c>
-      <c r="D87" s="86" t="inlineStr">
-        <is>
-          <t>Signed attestation (scan)</t>
-        </is>
-      </c>
-      <c r="E87" s="86" t="inlineStr">
-        <is>
-          <t>Scanned signed attestation – Executive Director, Payments &amp; Cash Management.</t>
-        </is>
-      </c>
-      <c r="F87" s="86" t="inlineStr">
-        <is>
-          <t>Samples: 3301, 1903, 1937; columns: H, J, O</t>
-        </is>
-      </c>
+    <row r="87" ht="66" customHeight="1" s="71">
+      <c r="A87" s="87" t="n">
+        <v>9</v>
+      </c>
+      <c r="B87" s="87" t="inlineStr">
+        <is>
+          <t>Duplicate evidence removed: 12 files that were byte-identical copies or the same email message saved twice (E11, E12, E14, E14a, E15, E15a, E16, E16a, E17, E17a, MA02, DMA05b) were removed; one copy of each is retained (see Evidence Index – Duplicate files removed). E13 (11/13/2024) is prior period – supplemental only. DMA13 (Cisco Call Manager) is out of scope.</t>
+        </is>
+      </c>
+      <c r="C87" s="87" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D87" s="87" t="inlineStr">
+        <is>
+          <t>Evidence Index tab</t>
+        </is>
+      </c>
+      <c r="E87" s="87" t="inlineStr">
+        <is>
+          <t>No impact – retained copy carries identical content.</t>
+        </is>
+      </c>
+      <c r="F87" s="87" t="inlineStr"/>
       <c r="G87" s="82" t="n"/>
       <c r="H87" s="82" t="n"/>
       <c r="I87" s="82" t="n"/>
@@ -8268,7 +8026,7 @@
     <row r="89" ht="22" customHeight="1" s="71">
       <c r="A89" s="73" t="inlineStr">
         <is>
-          <t>Observations for reviewer consideration (do not change the PASS conclusions unless the reviewer determines otherwise)</t>
+          <t>Reviewer Note</t>
         </is>
       </c>
       <c r="M89" s="82" t="n"/>
@@ -8279,39 +8037,12 @@
       <c r="R89" s="82" t="n"/>
       <c r="S89" s="82" t="n"/>
     </row>
-    <row r="90" ht="30" customHeight="1" s="71">
-      <c r="A90" s="85" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B90" s="85" t="inlineStr">
-        <is>
-          <t>Observation</t>
-        </is>
-      </c>
-      <c r="C90" s="85" t="inlineStr">
-        <is>
-          <t>Samples affected</t>
-        </is>
-      </c>
-      <c r="D90" s="85" t="inlineStr">
-        <is>
-          <t>Evidence</t>
-        </is>
-      </c>
-      <c r="E90" s="85" t="inlineStr">
-        <is>
-          <t>Impact / reviewer consideration</t>
-        </is>
-      </c>
-      <c r="F90" s="85" t="inlineStr"/>
-      <c r="G90" s="82" t="n"/>
-      <c r="H90" s="82" t="n"/>
-      <c r="I90" s="82" t="n"/>
-      <c r="J90" s="82" t="n"/>
-      <c r="K90" s="82" t="n"/>
-      <c r="L90" s="82" t="n"/>
+    <row r="90" ht="75" customHeight="1" s="71">
+      <c r="A90" s="88" t="inlineStr">
+        <is>
+          <t>All requested attributes (IT DR exercise name, annual execution, application, tester, business data validation, manager name/approval dates, DIV procedures, approval emails, BCiC evidence, Annual Testing Executed, DIV Performed by IT DR Team, Applications in Scope Identified, Business Line Approval of Results, Results Documented in BCMS, overall assessment, supporting evidence and sample result) are completed for the 10 in-scope applications (56 DIV records) and every conclusion is linked to its evidence file and folder location in BSI.IT.6.C7.3-Evidences. Applications in Scope Identified is based on MA01 (BSI In-Scope Applications-2026). Business Line Approval of Results is based on the Business Line Approval Results – Email folder (BLA01–BLA06) together with the application-specific approval emails / signed attestations (folder 03, E09).</t>
+        </is>
+      </c>
       <c r="M90" s="82" t="n"/>
       <c r="N90" s="82" t="n"/>
       <c r="O90" s="82" t="n"/>
@@ -8320,31 +8051,13 @@
       <c r="R90" s="82" t="n"/>
       <c r="S90" s="82" t="n"/>
     </row>
-    <row r="91" ht="90" customHeight="1" s="71">
-      <c r="A91" s="87" t="n">
-        <v>1</v>
-      </c>
-      <c r="B91" s="87" t="inlineStr">
-        <is>
-          <t>Business line approvals for 33 of 56 in-scope DIV records were obtained through retrospective management attestations dated 08/17/2026 – 09/09/2026, i.e. after the review period end (06/01/2026) and ~9-10 months after the 11/15/2025 DIV testing. A further 13 records (BSA/AML/OFAC and Payments) carry in-period BCiC approval dates (11/15/2025, 12/18/2025) supported only by 08/2026 signed attestations. 10 records have in-period approval emails (E09, BLA06/E12).</t>
-        </is>
-      </c>
-      <c r="C91" s="87" t="inlineStr">
-        <is>
-          <t>3299, 4052, 3301, 1903, 1936, 1937</t>
-        </is>
-      </c>
-      <c r="D91" s="87" t="inlineStr">
-        <is>
-          <t>Folder 03 (DMA01–DMA12); E14–E17a; E03 approval dates</t>
-        </is>
-      </c>
-      <c r="E91" s="87" t="inlineStr">
-        <is>
-          <t>Approval is evidenced for 100% of records; timing is an observation. The attestation (E14a §3.6) commits to contemporaneous approval going forward. Reviewer to conclude whether retrospective approval satisfies the control for the period.</t>
-        </is>
-      </c>
-      <c r="F91" s="87" t="inlineStr"/>
+    <row r="91" s="71">
+      <c r="A91" s="82" t="n"/>
+      <c r="B91" s="82" t="n"/>
+      <c r="C91" s="82" t="n"/>
+      <c r="D91" s="82" t="n"/>
+      <c r="E91" s="82" t="n"/>
+      <c r="F91" s="82" t="n"/>
       <c r="G91" s="82" t="n"/>
       <c r="H91" s="82" t="n"/>
       <c r="I91" s="82" t="n"/>
@@ -8359,31 +8072,13 @@
       <c r="R91" s="82" t="n"/>
       <c r="S91" s="82" t="n"/>
     </row>
-    <row r="92" ht="78" customHeight="1" s="71">
-      <c r="A92" s="87" t="n">
-        <v>2</v>
-      </c>
-      <c r="B92" s="87" t="inlineStr">
-        <is>
-          <t>Self-approval: the business tester and the approving Department Manager are the same person for BSA/AML/OFAC (David Marquez), Payments (Franklin Puentes), Investment Operations (Michelle Oropesa), Treasury (Martha Sullivan), Digital Wealth (Victoria Fernandez), Client Servicing Unit (Liliana Vizhnay), Commercial Middle Office (Miguel Orozco – Imaging101 / T24 row 15, 51) and Financial Analysis (Sadis Alvarenga).</t>
-        </is>
-      </c>
-      <c r="C92" s="87" t="inlineStr">
-        <is>
-          <t>3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
-        </is>
-      </c>
-      <c r="D92" s="87" t="inlineStr">
-        <is>
-          <t>E03 tester vs manager columns</t>
-        </is>
-      </c>
-      <c r="E92" s="87" t="inlineStr">
-        <is>
-          <t>Segregation-of-duties observation; the approvers are the business line heads for those areas.</t>
-        </is>
-      </c>
-      <c r="F92" s="87" t="inlineStr"/>
+    <row r="92" s="71">
+      <c r="A92" s="82" t="n"/>
+      <c r="B92" s="82" t="n"/>
+      <c r="C92" s="82" t="n"/>
+      <c r="D92" s="82" t="n"/>
+      <c r="E92" s="82" t="n"/>
+      <c r="F92" s="82" t="n"/>
       <c r="G92" s="82" t="n"/>
       <c r="H92" s="82" t="n"/>
       <c r="I92" s="82" t="n"/>
@@ -8398,31 +8093,13 @@
       <c r="R92" s="82" t="n"/>
       <c r="S92" s="82" t="n"/>
     </row>
-    <row r="93" ht="30" customHeight="1" s="71">
-      <c r="A93" s="87" t="n">
-        <v>3</v>
-      </c>
-      <c r="B93" s="87" t="inlineStr">
-        <is>
-          <t>FedExport – BCiC Department Manager Approval Date 06/05/2026 (E03 row 9, E04) vs Claudia Romero "Approved." 05/05/2026 (E09).</t>
-        </is>
-      </c>
-      <c r="C93" s="87" t="inlineStr">
-        <is>
-          <t>1867</t>
-        </is>
-      </c>
-      <c r="D93" s="87" t="inlineStr">
-        <is>
-          <t>E03, E04, E09</t>
-        </is>
-      </c>
-      <c r="E93" s="87" t="inlineStr">
-        <is>
-          <t>Likely BCiC data-entry error; recommend management correct the BCiC record.</t>
-        </is>
-      </c>
-      <c r="F93" s="87" t="inlineStr"/>
+    <row r="93" s="71">
+      <c r="A93" s="82" t="n"/>
+      <c r="B93" s="82" t="n"/>
+      <c r="C93" s="82" t="n"/>
+      <c r="D93" s="82" t="n"/>
+      <c r="E93" s="82" t="n"/>
+      <c r="F93" s="82" t="n"/>
       <c r="G93" s="82" t="n"/>
       <c r="H93" s="82" t="n"/>
       <c r="I93" s="82" t="n"/>
@@ -8437,31 +8114,13 @@
       <c r="R93" s="82" t="n"/>
       <c r="S93" s="82" t="n"/>
     </row>
-    <row r="94" ht="30" customHeight="1" s="71">
-      <c r="A94" s="87" t="n">
-        <v>4</v>
-      </c>
-      <c r="B94" s="87" t="inlineStr">
-        <is>
-          <t>BLA02 (BSA/AML/OFAC) test script – DIV Yes/No answer boxes are blank.</t>
-        </is>
-      </c>
-      <c r="C94" s="87" t="inlineStr">
-        <is>
-          <t>3299, 1903, 1936, 1937</t>
-        </is>
-      </c>
-      <c r="D94" s="87" t="inlineStr">
-        <is>
-          <t>BLA02 p.1</t>
-        </is>
-      </c>
-      <c r="E94" s="87" t="inlineStr">
-        <is>
-          <t>Mitigated by production vs test-day screenshots in BLA02, BCiC Y/Y/Y (E03) and signed attestation (E14a / DMA02a).</t>
-        </is>
-      </c>
-      <c r="F94" s="87" t="inlineStr"/>
+    <row r="94" s="71">
+      <c r="A94" s="82" t="n"/>
+      <c r="B94" s="82" t="n"/>
+      <c r="C94" s="82" t="n"/>
+      <c r="D94" s="82" t="n"/>
+      <c r="E94" s="82" t="n"/>
+      <c r="F94" s="82" t="n"/>
       <c r="G94" s="82" t="n"/>
       <c r="H94" s="82" t="n"/>
       <c r="I94" s="82" t="n"/>
@@ -8476,31 +8135,13 @@
       <c r="R94" s="82" t="n"/>
       <c r="S94" s="82" t="n"/>
     </row>
-    <row r="95" ht="42" customHeight="1" s="71">
-      <c r="A95" s="87" t="n">
-        <v>5</v>
-      </c>
-      <c r="B95" s="87" t="inlineStr">
-        <is>
-          <t>BSA T24 record (E03 row 8) Attestation Date 08/29/2026 vs signed attestation 8/19/2026 (E14a); Financial Risk manager recorded as "Xavier Caisapanta" in BCiC while the approval email is from Ivan Caisapanta (DMA08).</t>
-        </is>
-      </c>
-      <c r="C95" s="87" t="inlineStr">
-        <is>
-          <t>1937</t>
-        </is>
-      </c>
-      <c r="D95" s="87" t="inlineStr">
-        <is>
-          <t>E03, E14a, DMA08</t>
-        </is>
-      </c>
-      <c r="E95" s="87" t="inlineStr">
-        <is>
-          <t>BCiC data-entry / naming consistency; confirm identity of Financial Risk approver.</t>
-        </is>
-      </c>
-      <c r="F95" s="87" t="inlineStr"/>
+    <row r="95" s="71">
+      <c r="A95" s="82" t="n"/>
+      <c r="B95" s="82" t="n"/>
+      <c r="C95" s="82" t="n"/>
+      <c r="D95" s="82" t="n"/>
+      <c r="E95" s="82" t="n"/>
+      <c r="F95" s="82" t="n"/>
       <c r="G95" s="82" t="n"/>
       <c r="H95" s="82" t="n"/>
       <c r="I95" s="82" t="n"/>
@@ -8515,31 +8156,13 @@
       <c r="R95" s="82" t="n"/>
       <c r="S95" s="82" t="n"/>
     </row>
-    <row r="96" ht="42" customHeight="1" s="71">
-      <c r="A96" s="87" t="n">
-        <v>6</v>
-      </c>
-      <c r="B96" s="87" t="inlineStr">
-        <is>
-          <t>ACH Express and Interface Monitor are not named verbatim in the DIV "Application In-scope" lines of BLA01 / BLA04; BLA01 operator (Raimy Ayala) differs from BCiC tester (Andreina De Stefano).</t>
-        </is>
-      </c>
-      <c r="C96" s="87" t="inlineStr">
-        <is>
-          <t>1822, 4052, 1867, 1868</t>
-        </is>
-      </c>
-      <c r="D96" s="87" t="inlineStr">
-        <is>
-          <t>BLA01, BLA04, E03, MA01</t>
-        </is>
-      </c>
-      <c r="E96" s="87" t="inlineStr">
-        <is>
-          <t>Application-level DIV records exist in BCiC (E03 rows 47 and 61) with Y/Y/Y results and manager approval.</t>
-        </is>
-      </c>
-      <c r="F96" s="87" t="inlineStr"/>
+    <row r="96" s="71">
+      <c r="A96" s="82" t="n"/>
+      <c r="B96" s="82" t="n"/>
+      <c r="C96" s="82" t="n"/>
+      <c r="D96" s="82" t="n"/>
+      <c r="E96" s="82" t="n"/>
+      <c r="F96" s="82" t="n"/>
       <c r="G96" s="82" t="n"/>
       <c r="H96" s="82" t="n"/>
       <c r="I96" s="82" t="n"/>
@@ -8554,31 +8177,13 @@
       <c r="R96" s="82" t="n"/>
       <c r="S96" s="82" t="n"/>
     </row>
-    <row r="97" ht="54" customHeight="1" s="71">
-      <c r="A97" s="87" t="n">
-        <v>7</v>
-      </c>
-      <c r="B97" s="87" t="inlineStr">
-        <is>
-          <t>Count reconciliation – E03 contains 62 DIV records (56 for the 10 tested applications); E16b contains 64 rows (one additional Treasury T24 row with blank department, row 45); the attestation states 63 entries / 13 applications.</t>
-        </is>
-      </c>
-      <c r="C97" s="87" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D97" s="87" t="inlineStr">
-        <is>
-          <t>E03, E16b, E14a</t>
-        </is>
-      </c>
-      <c r="E97" s="87" t="inlineStr">
-        <is>
-          <t>Testing performed on E03 (the export containing the manager approval fields).</t>
-        </is>
-      </c>
-      <c r="F97" s="87" t="inlineStr"/>
+    <row r="97" s="71">
+      <c r="A97" s="82" t="n"/>
+      <c r="B97" s="82" t="n"/>
+      <c r="C97" s="82" t="n"/>
+      <c r="D97" s="82" t="n"/>
+      <c r="E97" s="82" t="n"/>
+      <c r="F97" s="82" t="n"/>
       <c r="G97" s="82" t="n"/>
       <c r="H97" s="82" t="n"/>
       <c r="I97" s="82" t="n"/>
@@ -8593,31 +8198,13 @@
       <c r="R97" s="82" t="n"/>
       <c r="S97" s="82" t="n"/>
     </row>
-    <row r="98" ht="30" customHeight="1" s="71">
-      <c r="A98" s="87" t="n">
-        <v>8</v>
-      </c>
-      <c r="B98" s="87" t="inlineStr">
-        <is>
-          <t>Annual interval – prior DR exercise 10/19/2024 to 11/15/2025 = 392 days; one exercise per annual DR cycle (2024, 2025) and within the review period.</t>
-        </is>
-      </c>
-      <c r="C98" s="87" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D98" s="87" t="inlineStr">
-        <is>
-          <t>Tab 'DR 2024 Testing Results'; E01; E03</t>
-        </is>
-      </c>
-      <c r="E98" s="87" t="inlineStr">
-        <is>
-          <t>Annual requirement assessed per DR cycle.</t>
-        </is>
-      </c>
-      <c r="F98" s="87" t="inlineStr"/>
+    <row r="98" s="71">
+      <c r="A98" s="82" t="n"/>
+      <c r="B98" s="82" t="n"/>
+      <c r="C98" s="82" t="n"/>
+      <c r="D98" s="82" t="n"/>
+      <c r="E98" s="82" t="n"/>
+      <c r="F98" s="82" t="n"/>
       <c r="G98" s="82" t="n"/>
       <c r="H98" s="82" t="n"/>
       <c r="I98" s="82" t="n"/>
@@ -8632,31 +8219,13 @@
       <c r="R98" s="82" t="n"/>
       <c r="S98" s="82" t="n"/>
     </row>
-    <row r="99" ht="66" customHeight="1" s="71">
-      <c r="A99" s="87" t="n">
-        <v>9</v>
-      </c>
-      <c r="B99" s="87" t="inlineStr">
-        <is>
-          <t>Duplicate evidence retained for traceability: BLA06 = E12; DMA02 = E14 (DMA02a = E14a); DMA03 = E17 = MA02 (DMA03a = E17a); DMA04 = E15 (DMA04a = E15a); DMA05 = E16 (DMA05a/b = E16a/b); E11 = E10 content. E13 (11/13/2024) is prior period – supplemental only. DMA13 (Cisco Call Manager) is out of scope.</t>
-        </is>
-      </c>
-      <c r="C99" s="87" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D99" s="87" t="inlineStr">
-        <is>
-          <t>Evidence Index tab</t>
-        </is>
-      </c>
-      <c r="E99" s="87" t="inlineStr">
-        <is>
-          <t>No impact.</t>
-        </is>
-      </c>
-      <c r="F99" s="87" t="inlineStr"/>
+    <row r="99" s="71">
+      <c r="A99" s="82" t="n"/>
+      <c r="B99" s="82" t="n"/>
+      <c r="C99" s="82" t="n"/>
+      <c r="D99" s="82" t="n"/>
+      <c r="E99" s="82" t="n"/>
+      <c r="F99" s="82" t="n"/>
       <c r="G99" s="82" t="n"/>
       <c r="H99" s="82" t="n"/>
       <c r="I99" s="82" t="n"/>
@@ -8692,12 +8261,19 @@
       <c r="R100" s="82" t="n"/>
       <c r="S100" s="82" t="n"/>
     </row>
-    <row r="101" ht="22" customHeight="1" s="71">
-      <c r="A101" s="73" t="inlineStr">
-        <is>
-          <t>Reviewer Note</t>
-        </is>
-      </c>
+    <row r="101" s="71">
+      <c r="A101" s="82" t="n"/>
+      <c r="B101" s="82" t="n"/>
+      <c r="C101" s="82" t="n"/>
+      <c r="D101" s="82" t="n"/>
+      <c r="E101" s="82" t="n"/>
+      <c r="F101" s="82" t="n"/>
+      <c r="G101" s="82" t="n"/>
+      <c r="H101" s="82" t="n"/>
+      <c r="I101" s="82" t="n"/>
+      <c r="J101" s="82" t="n"/>
+      <c r="K101" s="82" t="n"/>
+      <c r="L101" s="82" t="n"/>
       <c r="M101" s="82" t="n"/>
       <c r="N101" s="82" t="n"/>
       <c r="O101" s="82" t="n"/>
@@ -8706,12 +8282,19 @@
       <c r="R101" s="82" t="n"/>
       <c r="S101" s="82" t="n"/>
     </row>
-    <row r="102" ht="75" customHeight="1" s="71">
-      <c r="A102" s="88" t="inlineStr">
-        <is>
-          <t>All requested attributes (IT DR exercise name, annual execution, application, tester, business data validation, manager name/approval dates, DIV procedures, approval emails, BCiC evidence, Annual Testing Executed, DIV Performed by IT DR Team, Applications in Scope Identified, Business Line Approval of Results, Results Documented in BCMS, overall assessment, supporting evidence and sample result) are completed for the 10 in-scope applications (56 DIV records) and every conclusion is linked to its evidence file and folder location in BSI.IT.6.C7.3-Evidences. Applications in Scope Identified is based on MA01 (BSI In-Scope Applications-2026). Business Line Approval of Results is based on the Business Line Approval Results – Email folder (BLA01–BLA06) together with the application-specific approval emails / signed attestations (folder 03, E09, E12).</t>
-        </is>
-      </c>
+    <row r="102" s="71">
+      <c r="A102" s="82" t="n"/>
+      <c r="B102" s="82" t="n"/>
+      <c r="C102" s="82" t="n"/>
+      <c r="D102" s="82" t="n"/>
+      <c r="E102" s="82" t="n"/>
+      <c r="F102" s="82" t="n"/>
+      <c r="G102" s="82" t="n"/>
+      <c r="H102" s="82" t="n"/>
+      <c r="I102" s="82" t="n"/>
+      <c r="J102" s="82" t="n"/>
+      <c r="K102" s="82" t="n"/>
+      <c r="L102" s="82" t="n"/>
       <c r="M102" s="82" t="n"/>
       <c r="N102" s="82" t="n"/>
       <c r="O102" s="82" t="n"/>
@@ -9520,14 +9103,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A101:L101"/>
     <mergeCell ref="A15:L15"/>
+    <mergeCell ref="A90:L90"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A28:L28"/>
     <mergeCell ref="A37:L37"/>
     <mergeCell ref="A89:L89"/>
-    <mergeCell ref="A102:L102"/>
-    <mergeCell ref="A62:L62"/>
+    <mergeCell ref="A61:L61"/>
+    <mergeCell ref="A77:L77"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -9683,7 +9266,7 @@
           <t>• E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 3 – Exercise Date 12/11/25, 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 47 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – row 48 – Business Data Validation Date 11/15/2025
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml – request email states DR exercises conducted 11/15/2025 and 02/21/2026 (failover Miami-Telefonica → DR site)
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted Cesar Vidal request 08/17/2026 states DR exercises conducted 11/15/2025 and 02/21/2026 (failover Miami-Telefonica → DR site)
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – script header DATE: 11/15/2025</t>
         </is>
       </c>
@@ -9755,8 +9338,8 @@
         <is>
           <t>• E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 3 – Exercise Date 12/11/2025 / 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 47 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml – DR exercises 11/15/2025 and 02/21/2026
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – dated 11/15/2025</t>
         </is>
       </c>
@@ -9764,7 +9347,7 @@
         <is>
           <t>• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review 09/15/2025
 • E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – follow-up 09/18/2025
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg – IT DR (Elizabeth Noda) issued test script, collected evidence and requested approval
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 47 – Y/N Format, Headers, Content = Y</t>
@@ -9777,7 +9360,7 @@
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
 • E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – BIA results &amp; applications list review
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg – scope table: application → Client Back Office → Claudia Romero</t>
         </is>
       </c>
@@ -9795,7 +9378,7 @@
           <t>• E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 47
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – row 48
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – BCiC report screen (record on a later page of the 66-item report)
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="P5" s="62" t="inlineStr">
@@ -9807,6 +9390,8 @@
 [03 DIV Manager Attestation Email Approvals]
 DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
 DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
+DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
+DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 [04 Data Integrity &amp; Email Testing Evidence]
 E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx
 E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg
@@ -9815,14 +9400,12 @@
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
 E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml
 E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml
-E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
         </is>
       </c>
       <c r="Q5" s="62" t="inlineStr">
         <is>
-          <t>PASS – with observations – MA01, BLA01, DMA01, DMA01a, E01, E02, E03, E04, E05, E06, E09, E14, E14a, E16b</t>
+          <t>PASS – with observations – MA01, BLA01, DMA01, DMA01a, DMA02, DMA02a, E01, E02, E03, E04, E05, E06, E09, E16b</t>
         </is>
       </c>
     </row>
@@ -9835,7 +9418,7 @@
           <t>• E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 19 – Exercise Date 12/11/25, 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 9 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – row 9 – Business Data Validation Date 11/15/2025
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml – request email states DR exercises conducted 11/15/2025 and 02/21/2026 (failover Miami-Telefonica → DR site)
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted Cesar Vidal request 08/17/2026 states DR exercises conducted 11/15/2025 and 02/21/2026 (failover Miami-Telefonica → DR site)
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – script header DATE: 11/15/2025</t>
         </is>
       </c>
@@ -9911,8 +9494,8 @@
         <is>
           <t>• E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 19 – Exercise Date 12/11/2025 / 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 9 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml – DR exercises 11/15/2025 and 02/21/2026
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – dated 11/15/2025</t>
         </is>
       </c>
@@ -9920,7 +9503,7 @@
         <is>
           <t>• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review 09/15/2025
 • E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – follow-up 09/18/2025
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg – IT DR (Elizabeth Noda) issued test script, collected evidence and requested approval
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 9 – Y/N Format, Headers, Content = Y</t>
@@ -9933,7 +9516,7 @@
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
 • E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – BIA results &amp; applications list review
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg – scope table: application → Client Back Office → Claudia Romero</t>
         </is>
       </c>
@@ -9951,7 +9534,7 @@
           <t>• E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 9
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – row 9
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – record(s) visible on screen
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="P6" s="62" t="inlineStr">
@@ -9963,6 +9546,8 @@
 [03 DIV Manager Attestation Email Approvals]
 DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
 DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
+DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
+DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 [04 Data Integrity &amp; Email Testing Evidence]
 E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx
 E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg
@@ -9971,14 +9556,12 @@
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
 E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml
 E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml
-E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
         </is>
       </c>
       <c r="Q6" s="62" t="inlineStr">
         <is>
-          <t>PASS – with observations – MA01, BLA01, DMA01, DMA01a, E01, E02, E03, E04, E05, E06, E09, E14, E14a, E16b</t>
+          <t>PASS – with observations – MA01, BLA01, DMA01, DMA01a, DMA02, DMA02a, E01, E02, E03, E04, E05, E06, E09, E16b</t>
         </is>
       </c>
     </row>
@@ -9991,7 +9574,7 @@
           <t>• E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 20 – Exercise Date 12/11/25, 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 10 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – row 10 – Business Data Validation Date 11/15/2025
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml – request email states DR exercises conducted 11/15/2025 and 02/21/2026 (failover Miami-Telefonica → DR site)
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted Cesar Vidal request 08/17/2026 states DR exercises conducted 11/15/2025 and 02/21/2026 (failover Miami-Telefonica → DR site)
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – script header DATE: 11/15/2025</t>
         </is>
       </c>
@@ -10067,8 +9650,8 @@
         <is>
           <t>• E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 20 – Exercise Date 12/11/2025 / 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 10 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml – DR exercises 11/15/2025 and 02/21/2026
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – dated 11/15/2025</t>
         </is>
       </c>
@@ -10076,7 +9659,7 @@
         <is>
           <t>• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review 09/15/2025
 • E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – follow-up 09/18/2025
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg – IT DR (Elizabeth Noda) issued test script, collected evidence and requested approval
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 10 – Y/N Format, Headers, Content = Y</t>
@@ -10089,7 +9672,7 @@
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
 • E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – BIA results &amp; applications list review
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg – scope table: application → Client Back Office → Claudia Romero</t>
         </is>
       </c>
@@ -10107,7 +9690,7 @@
           <t>• E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 10
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – row 10
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – record(s) visible on screen
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="P7" s="62" t="inlineStr">
@@ -10119,6 +9702,8 @@
 [03 DIV Manager Attestation Email Approvals]
 DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
 DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
+DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
+DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 [04 Data Integrity &amp; Email Testing Evidence]
 E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx
 E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg
@@ -10127,14 +9712,12 @@
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
 E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml
 E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml
-E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
         </is>
       </c>
       <c r="Q7" s="62" t="inlineStr">
         <is>
-          <t>PASS – with observations – MA01, BLA01, DMA01, DMA01a, E01, E02, E03, E04, E05, E06, E09, E14, E14a, E16b</t>
+          <t>PASS – with observations – MA01, BLA01, DMA01, DMA01a, DMA02, DMA02a, E01, E02, E03, E04, E05, E06, E09, E16b</t>
         </is>
       </c>
     </row>
@@ -10147,7 +9730,7 @@
           <t>• E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 24 – Exercise Date 11/15/25, 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 5, 11, 13, 51, 53, 57 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – rows 5, 11, 13, 52, 54, 58 – Business Data Validation Date 11/15/2025
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml – request email states DR exercises conducted 11/15/2025 and 02/21/2026 (failover Miami-Telefonica → DR site)
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted Cesar Vidal request 08/17/2026 states DR exercises conducted 11/15/2025 and 02/21/2026 (failover Miami-Telefonica → DR site)
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – script header DATE: 11/15/2025
 • BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf – script header DATE: 11/15/2025</t>
         </is>
@@ -10200,100 +9783,88 @@
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – Department Manager Approval Date column
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
 • DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
+• E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
+• DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
+• DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
+• DMA11 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
+• DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
+• DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+        </is>
+      </c>
+      <c r="H8" s="62" t="inlineStr">
+        <is>
+          <t>• E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 5, 11, 13, 51, 53, 57 – 'Data Integrity Validation Procedures' column
+• E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – rows 5, 11, 13, 52, 54, 58 – 'Data Integrity Validation Procedures' column
+• BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – 'Data Integrity Validation Testing' section – procedure instructions, application in-scope line and Format / Headers / Content questions
+• BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf – 'Data Integrity Validation Testing' section – procedure instructions, application in-scope line and Format / Headers / Content questions</t>
+        </is>
+      </c>
+      <c r="I8" s="62" t="inlineStr">
+        <is>
+          <t>• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
+• E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
+• DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
+• DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
+• DMA11 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
+• DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
+• DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+        </is>
+      </c>
+      <c r="J8" s="62" t="inlineStr">
+        <is>
+          <t>• E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 5, 11, 13, 51, 53, 57 – BCiC DIV export (tester, dates, manager, Y/N results, attestation)
+• E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – rows 5, 11, 13, 52, 54, 58 – BCiC DIV export 2025-26 reviewed with the attestation
+• E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – record(s) visible on screen
+• E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 24
+• E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – BCiC DR-scope view
+• MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png – App ID 3299 selected in BCiC in-scope view</t>
+        </is>
+      </c>
+      <c r="K8" s="62" t="inlineStr">
+        <is>
+          <t>• E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 24 – Exercise Date 11/15/2025 / 2025 DR Test Scope = True
+• E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 5, 11, 13, 51, 53, 57 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
+• BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – dated 11/15/2025
+• BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf – dated 11/15/2025</t>
+        </is>
+      </c>
+      <c r="L8" s="62" t="inlineStr">
+        <is>
+          <t>• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review 09/15/2025
+• E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – follow-up 09/18/2025
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
+• BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
+• BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
+• E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg – IT DR (Elizabeth Noda) issued test script, collected evidence and requested approval
+• E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 5, 11, 13, 51, 53, 57 – Y/N Format, Headers, Content = Y</t>
+        </is>
+      </c>
+      <c r="M8" s="62" t="inlineStr">
+        <is>
+          <t>• MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png – BSI In-Scope Applications-2026 – App ID 3299 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
+• E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 24 – 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
+• E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
+• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
+• E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – BIA results &amp; applications list review
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data
+• E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg – scope table: application → Client Back Office → Claudia Romero</t>
+        </is>
+      </c>
+      <c r="N8" s="62" t="inlineStr">
+        <is>
+          <t>• BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – business line DIV results document – 11/15/2025 – Client Back Office (operator Raimy Ayala)
+• BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf – business line DIV results document – 11/15/2025 – BSA/AML/OFAC Compliance (operator David Marquez)
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
 • DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
 • DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
 • DMA11 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
 • DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
 • DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf
-• E16 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 2 (1).msg.eml
-• E16a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16a_Data_Integrity_Attestation_Santander-BCiC.pdf</t>
-        </is>
-      </c>
-      <c r="H8" s="62" t="inlineStr">
-        <is>
-          <t>• E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 5, 11, 13, 51, 53, 57 – 'Data Integrity Validation Procedures' column
-• E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – rows 5, 11, 13, 52, 54, 58 – 'Data Integrity Validation Procedures' column
-• BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – 'Data Integrity Validation Testing' section – procedure instructions, application in-scope line and Format / Headers / Content questions
-• BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf – 'Data Integrity Validation Testing' section – procedure instructions, application in-scope line and Format / Headers / Content questions</t>
-        </is>
-      </c>
-      <c r="I8" s="62" t="inlineStr">
-        <is>
-          <t>• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
-• E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-• DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-• DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
-• DMA11 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
-• DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-• DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf
-• E16 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 2 (1).msg.eml
-• E16a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16a_Data_Integrity_Attestation_Santander-BCiC.pdf</t>
-        </is>
-      </c>
-      <c r="J8" s="62" t="inlineStr">
-        <is>
-          <t>• E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 5, 11, 13, 51, 53, 57 – BCiC DIV export (tester, dates, manager, Y/N results, attestation)
-• E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – rows 5, 11, 13, 52, 54, 58 – BCiC DIV export 2025-26 reviewed with the attestation
-• E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – record(s) visible on screen
-• E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 24
-• E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – BCiC DR-scope view
-• MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png – App ID 3299 selected in BCiC in-scope view</t>
-        </is>
-      </c>
-      <c r="K8" s="62" t="inlineStr">
-        <is>
-          <t>• E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 24 – Exercise Date 11/15/2025 / 2025 DR Test Scope = True
-• E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 5, 11, 13, 51, 53, 57 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml – DR exercises 11/15/2025 and 02/21/2026
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
-• BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – dated 11/15/2025
-• BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf – dated 11/15/2025</t>
-        </is>
-      </c>
-      <c r="L8" s="62" t="inlineStr">
-        <is>
-          <t>• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review 09/15/2025
-• E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – follow-up 09/18/2025
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
-• BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
-• BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
-• E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg – IT DR (Elizabeth Noda) issued test script, collected evidence and requested approval
-• E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 5, 11, 13, 51, 53, 57 – Y/N Format, Headers, Content = Y</t>
-        </is>
-      </c>
-      <c r="M8" s="62" t="inlineStr">
-        <is>
-          <t>• MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png – BSI In-Scope Applications-2026 – App ID 3299 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
-• E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 24 – 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
-• E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
-• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
-• E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – BIA results &amp; applications list review
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data
-• E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg – scope table: application → Client Back Office → Claudia Romero</t>
-        </is>
-      </c>
-      <c r="N8" s="62" t="inlineStr">
-        <is>
-          <t>• BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – business line DIV results document – 11/15/2025 – Client Back Office (operator Raimy Ayala)
-• BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf – business line DIV results document – 11/15/2025 – BSA/AML/OFAC Compliance (operator David Marquez)
-• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
-• E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-• DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-• DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
-• DMA11 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
-• DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-• DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf
-• E16 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 2 (1).msg.eml
-• E16a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16a_Data_Integrity_Attestation_Santander-BCiC.pdf
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 5, 11, 13, 51, 53, 57 – Department Manager / Approval Date / Attestation fields</t>
         </is>
       </c>
@@ -10302,7 +9873,7 @@
           <t>• E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 5, 11, 13, 51, 53, 57
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – rows 5, 11, 13, 52, 54, 58
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – record(s) visible on screen
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="P8" s="62" t="inlineStr">
@@ -10328,16 +9899,12 @@
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
 E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml
 E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml
-E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
-E16 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 2 (1).msg.eml
-E16a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16a_Data_Integrity_Attestation_Santander-BCiC.pdf
 E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
         </is>
       </c>
       <c r="Q8" s="62" t="inlineStr">
         <is>
-          <t>PASS – with observations – MA01, BLA01, BLA02, DMA01, DMA01a, DMA02, DMA02a, DMA05, DMA05a, DMA11, E01, E02, E03, E04, E05, E06, E09, E14, E14a, E16, E16a, E16b</t>
+          <t>PASS – with observations – MA01, BLA01, BLA02, DMA01, DMA01a, DMA02, DMA02a, DMA05, DMA05a, DMA11, E01, E02, E03, E04, E05, E06, E09, E16b</t>
         </is>
       </c>
     </row>
@@ -10350,7 +9917,7 @@
           <t>• E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 25 – Exercise Date 11/15/25, 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 61 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – row 62 – Business Data Validation Date 11/15/2025
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml – request email states DR exercises conducted 11/15/2025 and 02/21/2026 (failover Miami-Telefonica → DR site)
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted Cesar Vidal request 08/17/2026 states DR exercises conducted 11/15/2025 and 02/21/2026 (failover Miami-Telefonica → DR site)
 • BLA04 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx – script header DATE: 11/15/2025</t>
         </is>
       </c>
@@ -10389,9 +9956,7 @@
         <is>
           <t>• E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 61 – 'Department Manager Approval Date' and 'Attestation Date' columns
 • DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-• DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf
-• E15 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 1 (1).msg.eml
-• E15a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15a_Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+• DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
         </is>
       </c>
       <c r="H9" s="62" t="inlineStr">
@@ -10404,9 +9969,7 @@
       <c r="I9" s="62" t="inlineStr">
         <is>
           <t>• DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-• DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf
-• E15 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 1 (1).msg.eml
-• E15a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15a_Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+• DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
         </is>
       </c>
       <c r="J9" s="62" t="inlineStr">
@@ -10423,8 +9986,8 @@
         <is>
           <t>• E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 25 – Exercise Date 11/15/2025 / 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 61 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml – DR exercises 11/15/2025 and 02/21/2026
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
 • BLA04 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx – dated 11/15/2025</t>
         </is>
       </c>
@@ -10432,7 +9995,7 @@
         <is>
           <t>• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review 09/15/2025
 • E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – follow-up 09/18/2025
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
 • BLA04 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx – IT DR test script completed by the business-line tester
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 61 – Y/N Format, Headers, Content = Y</t>
         </is>
@@ -10444,7 +10007,7 @@
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
 • E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – BIA results &amp; applications list review
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data</t>
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data</t>
         </is>
       </c>
       <c r="N9" s="62" t="inlineStr">
@@ -10452,8 +10015,6 @@
           <t>• BLA04 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx – business line DIV results document – 11/15/2025 – Investment Operations (operator Michelle Oropesa)
 • DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
 • DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf
-• E15 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 1 (1).msg.eml
-• E15a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15a_Data_Integrity_Attestation_Santander-BCiC.pdf
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 61 – Department Manager / Approval Date / Attestation fields</t>
         </is>
       </c>
@@ -10462,7 +10023,7 @@
           <t>• E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 61
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – row 62
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – BCiC report screen (record on a later page of the 66-item report)
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="P9" s="62" t="inlineStr">
@@ -10472,6 +10033,8 @@
 [02 Business Line Approval Results – Email]
 BLA04 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx
 [03 DIV Manager Attestation Email Approvals]
+DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
+DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
 DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf
 [04 Data Integrity &amp; Email Testing Evidence]
@@ -10481,16 +10044,12 @@
 E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
 E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml
-E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml
-E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
-E15 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 1 (1).msg.eml
-E15a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15a_Data_Integrity_Attestation_Santander-BCiC.pdf
 E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
         </is>
       </c>
       <c r="Q9" s="62" t="inlineStr">
         <is>
-          <t>PASS – with observations – MA01, BLA04, DMA04, DMA04a, E01, E02, E03, E04, E05, E06, E14, E14a, E15, E15a, E16b</t>
+          <t>PASS – with observations – MA01, BLA04, DMA02, DMA02a, DMA04, DMA04a, E01, E02, E03, E04, E05, E06, E16b</t>
         </is>
       </c>
     </row>
@@ -10503,7 +10062,7 @@
           <t>• E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 31 – Exercise Date 11/15/25, 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 25, 29 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – rows 25, 29 – Business Data Validation Date 11/15/2025
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml – request email states DR exercises conducted 11/15/2025 and 02/21/2026 (failover Miami-Telefonica → DR site)
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted Cesar Vidal request 08/17/2026 states DR exercises conducted 11/15/2025 and 02/21/2026 (failover Miami-Telefonica → DR site)
 • BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – script header DATE: 11/15/2025</t>
         </is>
       </c>
@@ -10544,10 +10103,7 @@
         <is>
           <t>• E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 25, 29 – 'Department Manager Approval Date' and 'Attestation Date' columns
 • DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-• DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf
-• E17 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 3 (1).msg.eml
-• E17a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17a_4069_001.pdf
-• MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg</t>
+• DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf</t>
         </is>
       </c>
       <c r="H10" s="62" t="inlineStr">
@@ -10560,10 +10116,7 @@
       <c r="I10" s="62" t="inlineStr">
         <is>
           <t>• DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-• DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf
-• E17 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 3 (1).msg.eml
-• E17a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17a_4069_001.pdf
-• MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg</t>
+• DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf</t>
         </is>
       </c>
       <c r="J10" s="62" t="inlineStr">
@@ -10580,8 +10133,8 @@
         <is>
           <t>• E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 31 – Exercise Date 11/15/2025 / 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 25, 29 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml – DR exercises 11/15/2025 and 02/21/2026
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
 • BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – dated 11/15/2025</t>
         </is>
       </c>
@@ -10589,7 +10142,7 @@
         <is>
           <t>• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review 09/15/2025
 • E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – follow-up 09/18/2025
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
 • BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • E08 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg – business-line DIV comparison files sent to IT DR (Elizabeth Noda) on 11/15/2025
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 25, 29 – Y/N Format, Headers, Content = Y</t>
@@ -10602,7 +10155,7 @@
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
 • E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – BIA results &amp; applications list review
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data</t>
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data</t>
         </is>
       </c>
       <c r="N10" s="62" t="inlineStr">
@@ -10610,9 +10163,6 @@
           <t>• BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – business line DIV results document – 11/15/2025 – Payments &amp; Position Management (operators Frank Puentes / Gustavo Bucaro)
 • DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
 • DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf
-• E17 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 3 (1).msg.eml
-• E17a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17a_4069_001.pdf
-• MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 25, 29 – Department Manager / Approval Date / Attestation fields</t>
         </is>
       </c>
@@ -10621,17 +10171,18 @@
           <t>• E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 25, 29
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – rows 25, 29
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – BCiC report screen (record on a later page of the 66-item report)
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="P10" s="62" t="inlineStr">
         <is>
           <t>[01 Management Attestation / In-Scope Applications]
 MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
-MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg
 [02 Business Line Approval Results – Email]
 BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf
 [03 DIV Manager Attestation Email Approvals]
+DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
+DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
 DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf
 [04 Data Integrity &amp; Email Testing Evidence]
@@ -10643,16 +10194,12 @@
 E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml
 E07 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg
 E08 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg
-E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml
-E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
-E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx
-E17 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 3 (1).msg.eml
-E17a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17a_4069_001.pdf</t>
+E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
         </is>
       </c>
       <c r="Q10" s="62" t="inlineStr">
         <is>
-          <t>PASS – with observations – MA01, MA02, BLA03, DMA03, DMA03a, E01, E02, E03, E04, E05, E06, E07, E08, E14, E14a, E16b, E17, E17a</t>
+          <t>PASS – with observations – MA01, BLA03, DMA02, DMA02a, DMA03, DMA03a, E01, E02, E03, E04, E05, E06, E07, E08, E16b</t>
         </is>
       </c>
     </row>
@@ -10665,7 +10212,7 @@
           <t>• E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 34 – Exercise Date 11/15/25, 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 6, 26, 30, 34, 58 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – rows 6, 26, 30, 34, 59 – Business Data Validation Date 11/15/2025
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml – request email states DR exercises conducted 11/15/2025 and 02/21/2026 (failover Miami-Telefonica → DR site)
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted Cesar Vidal request 08/17/2026 states DR exercises conducted 11/15/2025 and 02/21/2026 (failover Miami-Telefonica → DR site)
 • BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf – script header DATE: 11/15/2025
 • BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – script header DATE: 11/15/2025</t>
         </is>
@@ -10718,17 +10265,10 @@
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – Department Manager Approval Date column
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
 • DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
 • DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf
-• E17 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 3 (1).msg.eml
-• E17a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17a_4069_001.pdf
-• MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg
 • DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-• DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf
-• E16 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 2 (1).msg.eml
-• E16a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16a_Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+• DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
         </is>
       </c>
       <c r="H11" s="62" t="inlineStr">
@@ -10743,17 +10283,10 @@
         <is>
           <t>• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
 • DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
 • DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf
-• E17 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 3 (1).msg.eml
-• E17a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17a_4069_001.pdf
-• MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg
 • DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-• DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf
-• E16 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 2 (1).msg.eml
-• E16a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16a_Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+• DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
         </is>
       </c>
       <c r="J11" s="62" t="inlineStr">
@@ -10770,8 +10303,8 @@
         <is>
           <t>• E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 34 – Exercise Date 11/15/2025 / 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 6, 26, 30, 34, 58 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml – DR exercises 11/15/2025 and 02/21/2026
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
 • BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf – dated 11/15/2025
 • BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – dated 11/15/2025</t>
         </is>
@@ -10780,7 +10313,7 @@
         <is>
           <t>• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review 09/15/2025
 • E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – follow-up 09/18/2025
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
 • BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • E08 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg – business-line DIV comparison files sent to IT DR (Elizabeth Noda) on 11/15/2025
@@ -10794,7 +10327,7 @@
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
 • E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – BIA results &amp; applications list review
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data</t>
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data</t>
         </is>
       </c>
       <c r="N11" s="62" t="inlineStr">
@@ -10803,17 +10336,10 @@
 • BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – business line DIV results document – 11/15/2025 – Payments &amp; Position Management (operators Frank Puentes / Gustavo Bucaro)
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
 • DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
 • DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf
-• E17 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 3 (1).msg.eml
-• E17a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17a_4069_001.pdf
-• MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg
 • DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
 • DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf
-• E16 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 2 (1).msg.eml
-• E16a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16a_Data_Integrity_Attestation_Santander-BCiC.pdf
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 6, 26, 30, 34, 58 – Department Manager / Approval Date / Attestation fields</t>
         </is>
       </c>
@@ -10822,14 +10348,13 @@
           <t>• E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 6, 26, 30, 34, 58
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – rows 6, 26, 30, 34, 59
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – record(s) visible on screen
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="P11" s="62" t="inlineStr">
         <is>
           <t>[01 Management Attestation / In-Scope Applications]
 MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
-MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg
 [02 Business Line Approval Results – Email]
 BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf
 BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf
@@ -10849,18 +10374,12 @@
 E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml
 E07 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg
 E08 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg
-E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml
-E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
-E16 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 2 (1).msg.eml
-E16a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16a_Data_Integrity_Attestation_Santander-BCiC.pdf
-E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx
-E17 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 3 (1).msg.eml
-E17a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17a_4069_001.pdf</t>
+E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
         </is>
       </c>
       <c r="Q11" s="62" t="inlineStr">
         <is>
-          <t>PASS – with observations – MA01, MA02, BLA02, BLA03, DMA02, DMA02a, DMA03, DMA03a, DMA05, DMA05a, E01, E02, E03, E04, E05, E06, E07, E08, E14, E14a, E16, E16a, E16b, E17, E17a</t>
+          <t>PASS – with observations – MA01, BLA02, BLA03, DMA02, DMA02a, DMA03, DMA03a, DMA05, DMA05a, E01, E02, E03, E04, E05, E06, E07, E08, E16b</t>
         </is>
       </c>
     </row>
@@ -10873,7 +10392,7 @@
           <t>• E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 36 – Exercise Date 11/15/25, 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 17 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – row 17 – Business Data Validation Date 11/15/2025
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml – request email states DR exercises conducted 11/15/2025 and 02/21/2026 (failover Miami-Telefonica → DR site)
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted Cesar Vidal request 08/17/2026 states DR exercises conducted 11/15/2025 and 02/21/2026 (failover Miami-Telefonica → DR site)
 • BLA05 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf – script header DATE: 11/15/2025</t>
         </is>
       </c>
@@ -10904,15 +10423,13 @@
       <c r="F12" s="62" t="inlineStr">
         <is>
           <t>• E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 17 – 'Department Manager' column
-• BLA06 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg
-• E12 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E12_RE_ Testing enviroment Financial Analysis manager approval.msg</t>
+• BLA06 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg</t>
         </is>
       </c>
       <c r="G12" s="62" t="inlineStr">
         <is>
           <t>• E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 17 – 'Department Manager Approval Date' and 'Attestation Date' columns
-• BLA06 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg
-• E12 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E12_RE_ Testing enviroment Financial Analysis manager approval.msg</t>
+• BLA06 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg</t>
         </is>
       </c>
       <c r="H12" s="62" t="inlineStr">
@@ -10924,8 +10441,7 @@
       </c>
       <c r="I12" s="62" t="inlineStr">
         <is>
-          <t>• BLA06 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg
-• E12 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E12_RE_ Testing enviroment Financial Analysis manager approval.msg</t>
+          <t>• BLA06 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg</t>
         </is>
       </c>
       <c r="J12" s="62" t="inlineStr">
@@ -10942,8 +10458,8 @@
         <is>
           <t>• E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 36 – Exercise Date 11/15/2025 / 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 17 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml – DR exercises 11/15/2025 and 02/21/2026
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
 • BLA05 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf – dated 11/15/2025</t>
         </is>
       </c>
@@ -10951,10 +10467,9 @@
         <is>
           <t>• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review 09/15/2025
 • E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – follow-up 09/18/2025
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
 • BLA05 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • E10 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg – IT DR (Elizabeth Noda) Finance DIV chart and approval request
-• E11 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E11_BSI.IT.6.C7.3 Manager Approval.msg – same Finance thread (separate save) – Lina Acuna approval 03/09/2026
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 17 – Y/N Format, Headers, Content = Y</t>
         </is>
       </c>
@@ -10965,14 +10480,13 @@
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
 • E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – BIA results &amp; applications list review
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data</t>
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data</t>
         </is>
       </c>
       <c r="N12" s="62" t="inlineStr">
         <is>
           <t>• BLA05 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf – business line DIV results document – 11/15/2025 – Finance &amp; Accounting Reporting (operator Dunia Gonzalez Collado)
 • BLA06 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg
-• E12 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E12_RE_ Testing enviroment Financial Analysis manager approval.msg
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 17 – Department Manager / Approval Date / Attestation fields</t>
         </is>
       </c>
@@ -10981,7 +10495,7 @@
           <t>• E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 17
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – row 17
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – BCiC report screen (record on a later page of the 66-item report)
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="P12" s="62" t="inlineStr">
@@ -10991,6 +10505,9 @@
 [02 Business Line Approval Results – Email]
 BLA05 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf
 BLA06 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg
+[03 DIV Manager Attestation Email Approvals]
+DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
+DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 [04 Data Integrity &amp; Email Testing Evidence]
 E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx
 E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg
@@ -10999,16 +10516,12 @@
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
 E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml
 E10 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg
-E11 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E11_BSI.IT.6.C7.3 Manager Approval.msg
-E12 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E12_RE_ Testing enviroment Financial Analysis manager approval.msg
-E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml
-E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
         </is>
       </c>
       <c r="Q12" s="62" t="inlineStr">
         <is>
-          <t>PASS – with observations – MA01, BLA05, BLA06, E01, E02, E03, E04, E05, E06, E10, E11, E12, E14, E14a, E16b</t>
+          <t>PASS – with observations – MA01, BLA05, BLA06, DMA02, DMA02a, E01, E02, E03, E04, E05, E06, E10, E16b</t>
         </is>
       </c>
     </row>
@@ -11021,7 +10534,7 @@
           <t>• E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 42 – Exercise Date 11/15/25, 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 7, 60 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – rows 7, 61 – Business Data Validation Date 11/15/2025
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml – request email states DR exercises conducted 11/15/2025 and 02/21/2026 (failover Miami-Telefonica → DR site)
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted Cesar Vidal request 08/17/2026 states DR exercises conducted 11/15/2025 and 02/21/2026 (failover Miami-Telefonica → DR site)
 • BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – script header DATE: 11/15/2025
 • BLA04 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx – script header DATE: 11/15/2025</t>
         </is>
@@ -11072,12 +10585,8 @@
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – Department Manager Approval Date column
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
 • DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-• DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf
-• E15 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 1 (1).msg.eml
-• E15a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15a_Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+• DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
         </is>
       </c>
       <c r="H13" s="62" t="inlineStr">
@@ -11092,12 +10601,8 @@
         <is>
           <t>• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
 • DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-• DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf
-• E15 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 1 (1).msg.eml
-• E15a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15a_Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+• DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
         </is>
       </c>
       <c r="J13" s="62" t="inlineStr">
@@ -11114,8 +10619,8 @@
         <is>
           <t>• E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 42 – Exercise Date 11/15/2025 / 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 7, 60 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml – DR exercises 11/15/2025 and 02/21/2026
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
 • BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – dated 11/15/2025
 • BLA04 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx – dated 11/15/2025</t>
         </is>
@@ -11124,7 +10629,7 @@
         <is>
           <t>• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review 09/15/2025
 • E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – follow-up 09/18/2025
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
 • BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • BLA04 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx – IT DR test script completed by the business-line tester
 • E08 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg – business-line DIV comparison files sent to IT DR (Elizabeth Noda) on 11/15/2025
@@ -11138,7 +10643,7 @@
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
 • E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – BIA results &amp; applications list review
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data</t>
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data</t>
         </is>
       </c>
       <c r="N13" s="62" t="inlineStr">
@@ -11147,12 +10652,8 @@
 • BLA04 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx – business line DIV results document – 11/15/2025 – Investment Operations (operator Michelle Oropesa)
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
 • DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
 • DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf
-• E15 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 1 (1).msg.eml
-• E15a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15a_Data_Integrity_Attestation_Santander-BCiC.pdf
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 7, 60 – Department Manager / Approval Date / Attestation fields</t>
         </is>
       </c>
@@ -11161,7 +10662,7 @@
           <t>• E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 7, 60
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – rows 7, 61
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – record(s) visible on screen
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="P13" s="62" t="inlineStr">
@@ -11185,16 +10686,12 @@
 E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml
 E07 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg
 E08 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg
-E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml
-E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
-E15 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 1 (1).msg.eml
-E15a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15a_Data_Integrity_Attestation_Santander-BCiC.pdf
 E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
         </is>
       </c>
       <c r="Q13" s="62" t="inlineStr">
         <is>
-          <t>PASS – with observations – MA01, BLA03, BLA04, DMA02, DMA02a, DMA04, DMA04a, E01, E02, E03, E04, E05, E06, E07, E08, E14, E14a, E15, E15a, E16b</t>
+          <t>PASS – with observations – MA01, BLA03, BLA04, DMA02, DMA02a, DMA04, DMA04a, E01, E02, E03, E04, E05, E06, E07, E08, E16b</t>
         </is>
       </c>
     </row>
@@ -11207,7 +10704,7 @@
           <t>• E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 43 – Exercise Date 11/15/25, 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 47, 49, 50, 51, 53, 55, 56, 57, 60, 63, 64 – Business Data Validation Date 11/15/2025
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml – request email states DR exercises conducted 11/15/2025 and 02/21/2026 (failover Miami-Telefonica → DR site)
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted Cesar Vidal request 08/17/2026 states DR exercises conducted 11/15/2025 and 02/21/2026 (failover Miami-Telefonica → DR site)
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – script header DATE: 11/15/2025
 • BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf – script header DATE: 11/15/2025
 • BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – script header DATE: 11/15/2025
@@ -11263,7 +10760,6 @@
 • DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
 • DMA11 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
 • BLA06 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg
-• E12 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E12_RE_ Testing enviroment Financial Analysis manager approval.msg
 • DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
 • DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf
 • DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
@@ -11287,27 +10783,17 @@
 • DMA06a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA06a_Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Data_Integrity_Attestation_Santander-BCiC_signed.pdf
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
 • DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
 • DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
 • DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
 • DMA11 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
 • BLA06 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg
-• E12 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E12_RE_ Testing enviroment Financial Analysis manager approval.msg
 • DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
 • DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf
-• E16 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 2 (1).msg.eml
-• E16a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16a_Data_Integrity_Attestation_Santander-BCiC.pdf
 • DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
 • DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf
-• E15 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 1 (1).msg.eml
-• E15a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15a_Data_Integrity_Attestation_Santander-BCiC.pdf
 • DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
 • DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf
-• E17 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 3 (1).msg.eml
-• E17a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17a_4069_001.pdf
-• MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg
 • DMA07 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg
 • DMA07a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA07a_Treasury &amp; Capital Planning - Data_Integrity_Attestation_Santander-BCiC.pdf
 • DMA12 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml
@@ -11334,27 +10820,17 @@
 • DMA06a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA06a_Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Data_Integrity_Attestation_Santander-BCiC_signed.pdf
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
 • DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
 • DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
 • DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
 • DMA11 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
 • BLA06 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg
-• E12 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E12_RE_ Testing enviroment Financial Analysis manager approval.msg
 • DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
 • DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf
-• E16 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 2 (1).msg.eml
-• E16a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16a_Data_Integrity_Attestation_Santander-BCiC.pdf
 • DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
 • DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf
-• E15 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 1 (1).msg.eml
-• E15a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15a_Data_Integrity_Attestation_Santander-BCiC.pdf
 • DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
 • DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf
-• E17 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 3 (1).msg.eml
-• E17a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17a_4069_001.pdf
-• MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg
 • DMA07 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg
 • DMA07a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA07a_Treasury &amp; Capital Planning - Data_Integrity_Attestation_Santander-BCiC.pdf
 • DMA12 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml
@@ -11378,8 +10854,8 @@
         <is>
           <t>• E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 43 – Exercise Date 11/15/2025 / 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml – DR exercises 11/15/2025 and 02/21/2026
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – dated 11/15/2025
 • BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf – dated 11/15/2025
 • BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – dated 11/15/2025
@@ -11391,7 +10867,7 @@
         <is>
           <t>• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review 09/15/2025
 • E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – follow-up 09/18/2025
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
@@ -11399,7 +10875,6 @@
 • BLA05 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • E08 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg – business-line DIV comparison files sent to IT DR (Elizabeth Noda) on 11/15/2025
 • E10 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg – IT DR (Elizabeth Noda) Finance DIV chart and approval request
-• E11 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E11_BSI.IT.6.C7.3 Manager Approval.msg – same Finance thread (separate save) – Lina Acuna approval 03/09/2026
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63 – Y/N Format, Headers, Content = Y</t>
         </is>
       </c>
@@ -11410,7 +10885,7 @@
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
 • E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – BIA results &amp; applications list review
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data</t>
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data</t>
         </is>
       </c>
       <c r="N14" s="62" t="inlineStr">
@@ -11424,27 +10899,17 @@
 • DMA06a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA06a_Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Data_Integrity_Attestation_Santander-BCiC_signed.pdf
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
 • DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
-• E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
 • DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
 • DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
 • DMA11 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
 • BLA06 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg
-• E12 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E12_RE_ Testing enviroment Financial Analysis manager approval.msg
 • DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
 • DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf
-• E16 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 2 (1).msg.eml
-• E16a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16a_Data_Integrity_Attestation_Santander-BCiC.pdf
 • DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
 • DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf
-• E15 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 1 (1).msg.eml
-• E15a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15a_Data_Integrity_Attestation_Santander-BCiC.pdf
 • DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
 • DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf
-• E17 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 3 (1).msg.eml
-• E17a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17a_4069_001.pdf
-• MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg
 • DMA07 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg
 • DMA07a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA07a_Treasury &amp; Capital Planning - Data_Integrity_Attestation_Santander-BCiC.pdf
 • DMA12 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml
@@ -11460,14 +10925,13 @@
           <t>• E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 47, 49, 50, 51, 53, 55, 56, 57, 60, 63, 64
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – record(s) visible on screen
-• E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="P14" s="62" t="inlineStr">
         <is>
           <t>[01 Management Attestation / In-Scope Applications]
 MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
-MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg
 [02 Business Line Approval Results – Email]
 BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf
 BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf
@@ -11507,22 +10971,12 @@
 E08 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg
 E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
 E10 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg
-E11 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E11_BSI.IT.6.C7.3 Manager Approval.msg
-E12 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E12_RE_ Testing enviroment Financial Analysis manager approval.msg
-E14 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml
-E14a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
-E15 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 1 (1).msg.eml
-E15a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15a_Data_Integrity_Attestation_Santander-BCiC.pdf
-E16 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 2 (1).msg.eml
-E16a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16a_Data_Integrity_Attestation_Santander-BCiC.pdf
-E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx
-E17 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 3 (1).msg.eml
-E17a – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17a_4069_001.pdf</t>
+E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
         </is>
       </c>
       <c r="Q14" s="62" t="inlineStr">
         <is>
-          <t>PASS – with observations – MA01, MA02, BLA01, BLA02, BLA03, BLA04, BLA05, BLA06, DMA01, DMA01a, DMA02, DMA02a, DMA03, DMA03a, DMA04, DMA04a, DMA05, DMA05a, DMA06, DMA06a, DMA07, DMA07a, DMA08, DMA09, DMA09a, DMA10, DMA11, DMA12, E01, E02, E03, E04, E05, E06, E07, E08, E09, E10, E11, E12, E14, E14a, E15, E15a, E16, E16a, E16b, E17, E17a</t>
+          <t>PASS – with observations – MA01, BLA01, BLA02, BLA03, BLA04, BLA05, BLA06, DMA01, DMA01a, DMA02, DMA02a, DMA03, DMA03a, DMA04, DMA04a, DMA05, DMA05a, DMA06, DMA06a, DMA07, DMA07a, DMA08, DMA09, DMA09a, DMA10, DMA11, DMA12, E01, E02, E03, E04, E05, E06, E07, E08, E09, E10, E16b</t>
         </is>
       </c>
     </row>
@@ -11539,7 +10993,7 @@
       </c>
       <c r="B17" s="81" t="inlineStr">
         <is>
-          <t>Business line approvals for 33 of 56 in-scope DIV records were obtained through retrospective management attestations dated 08/17/2026 – 09/09/2026, i.e. after the review period end (06/01/2026) and ~9-10 months after the 11/15/2025 DIV testing. A further 13 records (BSA/AML/OFAC and Payments) carry in-period BCiC approval dates (11/15/2025, 12/18/2025) supported only by 08/2026 signed attestations. 10 records have in-period approval emails (E09, BLA06/E12).</t>
+          <t>Business line approvals for 33 of 56 in-scope DIV records were obtained through retrospective management attestations dated 08/17/2026 – 09/09/2026, i.e. after the review period end (06/01/2026) and ~9-10 months after the 11/15/2025 DIV testing. A further 13 records (BSA/AML/OFAC and Payments) carry in-period BCiC approval dates (11/15/2025, 12/18/2025) supported only by 08/2026 signed attestations. 10 records have in-period approval emails (E09, BLA06).</t>
         </is>
       </c>
     </row>
@@ -11579,7 +11033,7 @@
       </c>
       <c r="B21" s="81" t="inlineStr">
         <is>
-          <t>BSA T24 record (E03 row 8) Attestation Date 08/29/2026 vs signed attestation 8/19/2026 (E14a); Financial Risk manager recorded as "Xavier Caisapanta" in BCiC while the approval email is from Ivan Caisapanta (DMA08).</t>
+          <t>BSA T24 record (E03 row 8) Attestation Date 08/29/2026 vs signed attestation 8/19/2026 (DMA02a); Financial Risk manager recorded as "Xavier Caisapanta" in BCiC while the approval email is from Ivan Caisapanta (DMA08).</t>
         </is>
       </c>
     </row>
@@ -14061,70 +13515,66 @@
     <row r="4" ht="34.5" customHeight="1" s="71">
       <c r="A4" s="64" t="inlineStr">
         <is>
-          <t>MA02</t>
+          <t>BLA01</t>
         </is>
       </c>
       <c r="B4" s="64" t="inlineStr">
         <is>
-          <t>MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg</t>
+          <t>BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf</t>
         </is>
       </c>
       <c r="C4" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications</t>
+          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email</t>
         </is>
       </c>
       <c r="D4" s="64" t="inlineStr">
         <is>
-          <t>RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 3 (2).msg</t>
+          <t>Client Back Office - FED inclearing ACH  Cash letter (1).pdf</t>
         </is>
       </c>
       <c r="E4" s="64" t="inlineStr">
         <is>
-          <t>Management_Attestation.zip</t>
+          <t>Business Line Approval Results - Email.zip</t>
         </is>
       </c>
       <c r="F4" s="64" t="inlineStr">
         <is>
-          <t>Email attestation</t>
+          <t>DR test script / DIV test results</t>
         </is>
       </c>
       <c r="G4" s="64" t="inlineStr">
         <is>
-          <t>08/18/2026 – Frank Puentes</t>
+          <t>11/15/2025 – Client Back Office (operator Raimy Ayala)</t>
         </is>
       </c>
       <c r="H4" s="64" t="inlineStr">
         <is>
-          <t>Frank Puentes returns signed Management Attestation (4069_001.pdf) to Cesar Vidal. Same message as DMA03 / E17.</t>
+          <t>DR test script with Data Integrity Validation section. Application in-scope: FedImport, FedExport, Imaging101, T24. Format / Headers / Content = Y – "No data discrepancy found". Steps include ACH Express import and Imaging101 validation screenshots (14 pages).</t>
         </is>
       </c>
       <c r="I4" s="64" t="inlineStr">
         <is>
-          <t>3301, 1903, 1937</t>
+          <t>1822, 1867, 1868, 3299, 1937</t>
         </is>
       </c>
       <c r="J4" s="64" t="inlineStr">
         <is>
-          <t>H, J, O</t>
-        </is>
-      </c>
-      <c r="K4" s="64" t="inlineStr">
-        <is>
-          <t>Same as DMA03 / E17</t>
-        </is>
-      </c>
+          <t>B, E, F, I, L, M, O</t>
+        </is>
+      </c>
+      <c r="K4" s="64" t="inlineStr"/>
       <c r="L4" s="82" t="n"/>
     </row>
     <row r="5" ht="34.5" customHeight="1" s="71">
       <c r="A5" s="64" t="inlineStr">
         <is>
-          <t>BLA01</t>
+          <t>BLA02</t>
         </is>
       </c>
       <c r="B5" s="64" t="inlineStr">
         <is>
-          <t>BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf</t>
+          <t>BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf</t>
         </is>
       </c>
       <c r="C5" s="64" t="inlineStr">
@@ -14134,7 +13584,7 @@
       </c>
       <c r="D5" s="64" t="inlineStr">
         <is>
-          <t>Client Back Office - FED inclearing ACH  Cash letter (1).pdf</t>
+          <t>BSA_AML_OFAC Compliance - DM 11.15.2025 (002) (1).pdf</t>
         </is>
       </c>
       <c r="E5" s="64" t="inlineStr">
@@ -14149,17 +13599,17 @@
       </c>
       <c r="G5" s="64" t="inlineStr">
         <is>
-          <t>11/15/2025 – Client Back Office (operator Raimy Ayala)</t>
+          <t>11/15/2025 – BSA/AML/OFAC Compliance (operator David Marquez)</t>
         </is>
       </c>
       <c r="H5" s="64" t="inlineStr">
         <is>
-          <t>DR test script with Data Integrity Validation section. Application in-scope: FedImport, FedExport, Imaging101, T24. Format / Headers / Content = Y – "No data discrepancy found". Steps include ACH Express import and Imaging101 validation screenshots (14 pages).</t>
+          <t>OFAC Verifier test script. Application in-scope: T24, Imaging101, OFAC. DIV procedure instructions listed; production-day (11/14/2025) vs test-day (11/15/2025) screenshots for T24, Imaging101/ModeloIC and OFAC Report 64. NOTE: DIV Yes/No answer boxes on p.1 are blank.</t>
         </is>
       </c>
       <c r="I5" s="64" t="inlineStr">
         <is>
-          <t>1822, 1867, 1868, 3299, 1937</t>
+          <t>3299, 1903, 1937</t>
         </is>
       </c>
       <c r="J5" s="64" t="inlineStr">
@@ -14173,12 +13623,12 @@
     <row r="6" ht="69" customHeight="1" s="71">
       <c r="A6" s="64" t="inlineStr">
         <is>
-          <t>BLA02</t>
+          <t>BLA03</t>
         </is>
       </c>
       <c r="B6" s="64" t="inlineStr">
         <is>
-          <t>BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf</t>
+          <t>BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf</t>
         </is>
       </c>
       <c r="C6" s="64" t="inlineStr">
@@ -14188,7 +13638,7 @@
       </c>
       <c r="D6" s="64" t="inlineStr">
         <is>
-          <t>BSA_AML_OFAC Compliance - DM 11.15.2025 (002) (1).pdf</t>
+          <t>PAYMENTS SCRIPT NOV 2025.pdf</t>
         </is>
       </c>
       <c r="E6" s="64" t="inlineStr">
@@ -14203,17 +13653,17 @@
       </c>
       <c r="G6" s="64" t="inlineStr">
         <is>
-          <t>11/15/2025 – BSA/AML/OFAC Compliance (operator David Marquez)</t>
+          <t>11/15/2025 – Payments &amp; Position Management (operators Frank Puentes / Gustavo Bucaro)</t>
         </is>
       </c>
       <c r="H6" s="64" t="inlineStr">
         <is>
-          <t>OFAC Verifier test script. Application in-scope: T24, Imaging101, OFAC. DIV procedure instructions listed; production-day (11/14/2025) vs test-day (11/15/2025) screenshots for T24, Imaging101/ModeloIC and OFAC Report 64. NOTE: DIV Yes/No answer boxes on p.1 are blank.</t>
+          <t>Wire Transfer / Cash Mgt / Financial Messaging script. DIV application in-scope: T24, MQ Payment Monitor, OFAC – BSI, Fedlink – BSI, Swift Interface – BSI. Format / Headers / Content = yes; data from 11/14/2025 Fed &amp; SWIFT reconciled.</t>
         </is>
       </c>
       <c r="I6" s="64" t="inlineStr">
         <is>
-          <t>3299, 1903, 1937</t>
+          <t>3301, 1903, 1936, 1937</t>
         </is>
       </c>
       <c r="J6" s="64" t="inlineStr">
@@ -14227,12 +13677,12 @@
     <row r="7" ht="46" customHeight="1" s="71">
       <c r="A7" s="64" t="inlineStr">
         <is>
-          <t>BLA03</t>
+          <t>BLA04</t>
         </is>
       </c>
       <c r="B7" s="64" t="inlineStr">
         <is>
-          <t>BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf</t>
+          <t>BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx</t>
         </is>
       </c>
       <c r="C7" s="64" t="inlineStr">
@@ -14242,7 +13692,7 @@
       </c>
       <c r="D7" s="64" t="inlineStr">
         <is>
-          <t>PAYMENTS SCRIPT NOV 2025.pdf</t>
+          <t>Investment Operations- Treasury Hub &amp; Derivatives Operations (1).docx</t>
         </is>
       </c>
       <c r="E7" s="64" t="inlineStr">
@@ -14257,17 +13707,17 @@
       </c>
       <c r="G7" s="64" t="inlineStr">
         <is>
-          <t>11/15/2025 – Payments &amp; Position Management (operators Frank Puentes / Gustavo Bucaro)</t>
+          <t>11/15/2025 – Investment Operations (operator Michelle Oropesa)</t>
         </is>
       </c>
       <c r="H7" s="64" t="inlineStr">
         <is>
-          <t>Wire Transfer / Cash Mgt / Financial Messaging script. DIV application in-scope: T24, MQ Payment Monitor, OFAC – BSI, Fedlink – BSI, Swift Interface – BSI. Format / Headers / Content = yes; data from 11/14/2025 Fed &amp; SWIFT reconciled.</t>
+          <t>Treasury Hub &amp; Derivatives Operations script. Systems accessed: Swift Interface Monitor – BSI, T24, MS Office, DTCC. DIV application in-scope: T24 &amp; Swift Interface – BSI. Incoming MT300 and FX S reports matched 11/14 vs 11/15; Format / Headers / Content = Yes.</t>
         </is>
       </c>
       <c r="I7" s="64" t="inlineStr">
         <is>
-          <t>3301, 1903, 1936, 1937</t>
+          <t>4052, 1936, 1937</t>
         </is>
       </c>
       <c r="J7" s="64" t="inlineStr">
@@ -14281,12 +13731,12 @@
     <row r="8" ht="23" customHeight="1" s="71">
       <c r="A8" s="64" t="inlineStr">
         <is>
-          <t>BLA04</t>
+          <t>BLA05</t>
         </is>
       </c>
       <c r="B8" s="64" t="inlineStr">
         <is>
-          <t>BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx</t>
+          <t>BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf</t>
         </is>
       </c>
       <c r="C8" s="64" t="inlineStr">
@@ -14296,7 +13746,7 @@
       </c>
       <c r="D8" s="64" t="inlineStr">
         <is>
-          <t>Investment Operations- Treasury Hub &amp; Derivatives Operations (1).docx</t>
+          <t>Financial Analysis and Control-GL (1).pdf</t>
         </is>
       </c>
       <c r="E8" s="64" t="inlineStr">
@@ -14311,17 +13761,17 @@
       </c>
       <c r="G8" s="64" t="inlineStr">
         <is>
-          <t>11/15/2025 – Investment Operations (operator Michelle Oropesa)</t>
+          <t>11/15/2025 – Finance &amp; Accounting Reporting (operator Dunia Gonzalez Collado)</t>
         </is>
       </c>
       <c r="H8" s="64" t="inlineStr">
         <is>
-          <t>Treasury Hub &amp; Derivatives Operations script. Systems accessed: Swift Interface Monitor – BSI, T24, MS Office, DTCC. DIV application in-scope: T24 &amp; Swift Interface – BSI. Incoming MT300 and FX S reports matched 11/14 vs 11/15; Format / Headers / Content = Yes.</t>
+          <t>General ledger review script. DIV application in-scope: T24 &amp; ReconXpert. Reconciliations passed; Format / Headers / Content = Yes, "No discrepancies found on the report".</t>
         </is>
       </c>
       <c r="I8" s="64" t="inlineStr">
         <is>
-          <t>4052, 1936, 1937</t>
+          <t>1917, 1937</t>
         </is>
       </c>
       <c r="J8" s="64" t="inlineStr">
@@ -14335,12 +13785,12 @@
     <row r="9" ht="23" customHeight="1" s="71">
       <c r="A9" s="64" t="inlineStr">
         <is>
-          <t>BLA05</t>
+          <t>BLA06</t>
         </is>
       </c>
       <c r="B9" s="64" t="inlineStr">
         <is>
-          <t>BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf</t>
+          <t>BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg</t>
         </is>
       </c>
       <c r="C9" s="64" t="inlineStr">
@@ -14350,7 +13800,7 @@
       </c>
       <c r="D9" s="64" t="inlineStr">
         <is>
-          <t>Financial Analysis and Control-GL (1).pdf</t>
+          <t>RE_ Testing enviroment.msg</t>
         </is>
       </c>
       <c r="E9" s="64" t="inlineStr">
@@ -14360,17 +13810,17 @@
       </c>
       <c r="F9" s="64" t="inlineStr">
         <is>
-          <t>DR test script / DIV test results</t>
+          <t>Email approval</t>
         </is>
       </c>
       <c r="G9" s="64" t="inlineStr">
         <is>
-          <t>11/15/2025 – Finance &amp; Accounting Reporting (operator Dunia Gonzalez Collado)</t>
+          <t>12/31/2025 &amp; 01/26/2026 – Sadis Alvarenga</t>
         </is>
       </c>
       <c r="H9" s="64" t="inlineStr">
         <is>
-          <t>General ledger review script. DIV application in-scope: T24 &amp; ReconXpert. Reconciliations passed; Format / Headers / Content = Yes, "No discrepancies found on the report".</t>
+          <t>Sadis Alvarenga (Financial Analysis &amp; Control manager) replies "Approved." on 12/31/2025 and again on 01/26/2026 to Elizabeth Noda's request to approve the submitted test script.</t>
         </is>
       </c>
       <c r="I9" s="64" t="inlineStr">
@@ -14380,7 +13830,7 @@
       </c>
       <c r="J9" s="64" t="inlineStr">
         <is>
-          <t>B, E, F, I, L, M, O</t>
+          <t>G, H, J, O</t>
         </is>
       </c>
       <c r="K9" s="64" t="inlineStr"/>
@@ -14389,47 +13839,47 @@
     <row r="10" ht="34.5" customHeight="1" s="71">
       <c r="A10" s="64" t="inlineStr">
         <is>
-          <t>BLA06</t>
+          <t>DMA01</t>
         </is>
       </c>
       <c r="B10" s="64" t="inlineStr">
         <is>
-          <t>BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg</t>
+          <t>DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
         </is>
       </c>
       <c r="C10" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
         </is>
       </c>
       <c r="D10" s="64" t="inlineStr">
         <is>
-          <t>RE_ Testing enviroment.msg</t>
+          <t>RE_ Management Attestation – DIV Client Back Office.msg</t>
         </is>
       </c>
       <c r="E10" s="64" t="inlineStr">
         <is>
-          <t>Business Line Approval Results - Email.zip</t>
+          <t>DIV Manager Attestation Email_Approvals.zip</t>
         </is>
       </c>
       <c r="F10" s="64" t="inlineStr">
         <is>
-          <t>Email approval</t>
+          <t>Email attestation</t>
         </is>
       </c>
       <c r="G10" s="64" t="inlineStr">
         <is>
-          <t>12/31/2025 &amp; 01/26/2026 – Sadis Alvarenga</t>
+          <t>08/18/2026 – Claudia Romero</t>
         </is>
       </c>
       <c r="H10" s="64" t="inlineStr">
         <is>
-          <t>Sadis Alvarenga (Financial Analysis &amp; Control manager) replies "Approved." on 12/31/2025 and again on 01/26/2026 to Elizabeth Noda's request to approve the submitted test script. Same message as E12.</t>
+          <t>Claudia Romero (Client Back Office Manager VP) returns signed attestation (DMA01a).</t>
         </is>
       </c>
       <c r="I10" s="64" t="inlineStr">
         <is>
-          <t>1917, 1937</t>
+          <t>1822, 1867, 1868, 3299, 1937</t>
         </is>
       </c>
       <c r="J10" s="64" t="inlineStr">
@@ -14437,32 +13887,28 @@
           <t>G, H, J, O</t>
         </is>
       </c>
-      <c r="K10" s="64" t="inlineStr">
-        <is>
-          <t>Same message as E12</t>
-        </is>
-      </c>
+      <c r="K10" s="64" t="inlineStr"/>
       <c r="L10" s="82" t="n"/>
     </row>
     <row r="11" ht="23" customHeight="1" s="71">
       <c r="A11" s="64" t="inlineStr">
         <is>
-          <t>DMA01</t>
+          <t>DMA01a</t>
         </is>
       </c>
       <c r="B11" s="64" t="inlineStr">
         <is>
-          <t>DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
+          <t>DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf</t>
         </is>
       </c>
       <c r="C11" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted</t>
         </is>
       </c>
       <c r="D11" s="64" t="inlineStr">
         <is>
-          <t>RE_ Management Attestation – DIV Client Back Office.msg</t>
+          <t>Data_Integrity_Attestation_Santander-BCiC (002).pdf (attachment of DMA01)</t>
         </is>
       </c>
       <c r="E11" s="64" t="inlineStr">
@@ -14472,7 +13918,7 @@
       </c>
       <c r="F11" s="64" t="inlineStr">
         <is>
-          <t>Email attestation</t>
+          <t>Signed attestation</t>
         </is>
       </c>
       <c r="G11" s="64" t="inlineStr">
@@ -14482,7 +13928,7 @@
       </c>
       <c r="H11" s="64" t="inlineStr">
         <is>
-          <t>Claudia Romero (Client Back Office Manager VP) returns signed attestation (DMA01a).</t>
+          <t>Signed Management Attestation – Client Back Office.</t>
         </is>
       </c>
       <c r="I11" s="64" t="inlineStr">
@@ -14492,7 +13938,7 @@
       </c>
       <c r="J11" s="64" t="inlineStr">
         <is>
-          <t>G, H, J, O</t>
+          <t>H, J, O</t>
         </is>
       </c>
       <c r="K11" s="64" t="inlineStr"/>
@@ -14501,22 +13947,22 @@
     <row r="12" ht="34.5" customHeight="1" s="71">
       <c r="A12" s="64" t="inlineStr">
         <is>
-          <t>DMA01a</t>
+          <t>DMA02</t>
         </is>
       </c>
       <c r="B12" s="64" t="inlineStr">
         <is>
-          <t>DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf</t>
+          <t>DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg</t>
         </is>
       </c>
       <c r="C12" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
         </is>
       </c>
       <c r="D12" s="64" t="inlineStr">
         <is>
-          <t>Data_Integrity_Attestation_Santander-BCiC (002).pdf (attachment of DMA01)</t>
+          <t>RE_ Management Attestation – OFAC.msg</t>
         </is>
       </c>
       <c r="E12" s="64" t="inlineStr">
@@ -14526,27 +13972,27 @@
       </c>
       <c r="F12" s="64" t="inlineStr">
         <is>
-          <t>Signed attestation</t>
+          <t>Email attestation</t>
         </is>
       </c>
       <c r="G12" s="64" t="inlineStr">
         <is>
-          <t>08/18/2026 – Claudia Romero</t>
+          <t>08/19/2026 – David Marquez</t>
         </is>
       </c>
       <c r="H12" s="64" t="inlineStr">
         <is>
-          <t>Signed Management Attestation – Client Back Office.</t>
+          <t>Cesar Vidal request to Department Managers (08/17/2026; DR exercises 11/15/2025 and 02/21/2026; BCiC export attached) and David Marquez (OFAC Manager) reply returning the signed attestation.</t>
         </is>
       </c>
       <c r="I12" s="64" t="inlineStr">
         <is>
-          <t>1822, 1867, 1868, 3299, 1937</t>
+          <t>1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
         </is>
       </c>
       <c r="J12" s="64" t="inlineStr">
         <is>
-          <t>H, J, O</t>
+          <t>B, G, H, J, L, O</t>
         </is>
       </c>
       <c r="K12" s="64" t="inlineStr"/>
@@ -14555,22 +14001,22 @@
     <row r="13" ht="34.5" customHeight="1" s="71">
       <c r="A13" s="64" t="inlineStr">
         <is>
-          <t>DMA02</t>
+          <t>DMA02a</t>
         </is>
       </c>
       <c r="B13" s="64" t="inlineStr">
         <is>
-          <t>DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg</t>
+          <t>DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf</t>
         </is>
       </c>
       <c r="C13" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted</t>
         </is>
       </c>
       <c r="D13" s="64" t="inlineStr">
         <is>
-          <t>RE_ Management Attestation – OFAC.msg</t>
+          <t>Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf (attachment of DMA02)</t>
         </is>
       </c>
       <c r="E13" s="64" t="inlineStr">
@@ -14580,7 +14026,7 @@
       </c>
       <c r="F13" s="64" t="inlineStr">
         <is>
-          <t>Email attestation</t>
+          <t>Signed attestation</t>
         </is>
       </c>
       <c r="G13" s="64" t="inlineStr">
@@ -14590,45 +14036,41 @@
       </c>
       <c r="H13" s="64" t="inlineStr">
         <is>
-          <t>David Marquez (OFAC Manager) returns signed attestation. Same message as E14.</t>
+          <t>Signed attestation – OFAC Manager, VP, BSA/AML-OFAC Compliance, dated 8/19/2026. §1 states the IT DR team facilitates DIV annually; §2 lists 63 entries / 13 applications, all Y/Y/Y; §3.5 retention in BCMS/BCiC; §3.6 contemporaneous approval going forward.</t>
         </is>
       </c>
       <c r="I13" s="64" t="inlineStr">
         <is>
-          <t>3299, 1903, 1936, 1937</t>
+          <t>1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
         </is>
       </c>
       <c r="J13" s="64" t="inlineStr">
         <is>
-          <t>G, H, J, O</t>
-        </is>
-      </c>
-      <c r="K13" s="64" t="inlineStr">
-        <is>
-          <t>Same as E14</t>
-        </is>
-      </c>
+          <t>C, G, H, J, L, M, N, O, P</t>
+        </is>
+      </c>
+      <c r="K13" s="64" t="inlineStr"/>
       <c r="L13" s="82" t="n"/>
     </row>
     <row r="14" ht="34.5" customHeight="1" s="71">
       <c r="A14" s="64" t="inlineStr">
         <is>
-          <t>DMA02a</t>
+          <t>DMA03</t>
         </is>
       </c>
       <c r="B14" s="64" t="inlineStr">
         <is>
-          <t>DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf</t>
+          <t>DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
         </is>
       </c>
       <c r="C14" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
         </is>
       </c>
       <c r="D14" s="64" t="inlineStr">
         <is>
-          <t>attachment of DMA02 (identical to E14a)</t>
+          <t>Management Attestation – DIV Payment &amp; Cash Management.msg</t>
         </is>
       </c>
       <c r="E14" s="64" t="inlineStr">
@@ -14638,22 +14080,22 @@
       </c>
       <c r="F14" s="64" t="inlineStr">
         <is>
-          <t>Signed attestation</t>
+          <t>Email attestation</t>
         </is>
       </c>
       <c r="G14" s="64" t="inlineStr">
         <is>
-          <t>08/19/2026 – David Marquez</t>
+          <t>08/18/2026 – Frank Puentes</t>
         </is>
       </c>
       <c r="H14" s="64" t="inlineStr">
         <is>
-          <t>Signed attestation – OFAC Manager, VP, BSA/AML-OFAC Compliance, dated 8/19/2026.</t>
+          <t>Frank Puentes returns signed attestation (DMA03a).</t>
         </is>
       </c>
       <c r="I14" s="64" t="inlineStr">
         <is>
-          <t>3299, 1903, 1936, 1937</t>
+          <t>3301, 1903, 1937</t>
         </is>
       </c>
       <c r="J14" s="64" t="inlineStr">
@@ -14661,32 +14103,28 @@
           <t>G, H, J, O</t>
         </is>
       </c>
-      <c r="K14" s="64" t="inlineStr">
-        <is>
-          <t>Identical to E14a</t>
-        </is>
-      </c>
+      <c r="K14" s="64" t="inlineStr"/>
       <c r="L14" s="82" t="n"/>
     </row>
     <row r="15" ht="34.5" customHeight="1" s="71">
       <c r="A15" s="64" t="inlineStr">
         <is>
-          <t>DMA03</t>
+          <t>DMA03a</t>
         </is>
       </c>
       <c r="B15" s="64" t="inlineStr">
         <is>
-          <t>DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
+          <t>DMA03a_Payments &amp; Cash Management - 4069_001.pdf</t>
         </is>
       </c>
       <c r="C15" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted</t>
         </is>
       </c>
       <c r="D15" s="64" t="inlineStr">
         <is>
-          <t>Management Attestation – DIV Payment &amp; Cash Management.msg</t>
+          <t>4069_001.pdf (attachment of DMA03)</t>
         </is>
       </c>
       <c r="E15" s="64" t="inlineStr">
@@ -14696,7 +14134,7 @@
       </c>
       <c r="F15" s="64" t="inlineStr">
         <is>
-          <t>Email attestation</t>
+          <t>Signed attestation (scan)</t>
         </is>
       </c>
       <c r="G15" s="64" t="inlineStr">
@@ -14706,7 +14144,7 @@
       </c>
       <c r="H15" s="64" t="inlineStr">
         <is>
-          <t>Frank Puentes returns signed attestation. Same message as E17 / MA02.</t>
+          <t>Scanned signed attestation – Executive Director, Payments &amp; Cash Management.</t>
         </is>
       </c>
       <c r="I15" s="64" t="inlineStr">
@@ -14719,32 +14157,28 @@
           <t>G, H, J, O</t>
         </is>
       </c>
-      <c r="K15" s="64" t="inlineStr">
-        <is>
-          <t>Same as E17 / MA02</t>
-        </is>
-      </c>
+      <c r="K15" s="64" t="inlineStr"/>
       <c r="L15" s="82" t="n"/>
     </row>
     <row r="16" ht="23" customHeight="1" s="71">
       <c r="A16" s="64" t="inlineStr">
         <is>
-          <t>DMA03a</t>
+          <t>DMA04</t>
         </is>
       </c>
       <c r="B16" s="64" t="inlineStr">
         <is>
-          <t>DMA03a_Payments &amp; Cash Management - 4069_001.pdf</t>
+          <t>DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
         </is>
       </c>
       <c r="C16" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
         </is>
       </c>
       <c r="D16" s="64" t="inlineStr">
         <is>
-          <t>4069_001.pdf (attachment of DMA03; identical to E17a)</t>
+          <t>RE_ Management Attestation – DIV Investment Operations.msg</t>
         </is>
       </c>
       <c r="E16" s="64" t="inlineStr">
@@ -14754,22 +14188,22 @@
       </c>
       <c r="F16" s="64" t="inlineStr">
         <is>
-          <t>Signed attestation (scan)</t>
+          <t>Email attestation</t>
         </is>
       </c>
       <c r="G16" s="64" t="inlineStr">
         <is>
-          <t>08/18/2026 – Frank Puentes</t>
+          <t>08/17/2026 – Michelle Oropesa</t>
         </is>
       </c>
       <c r="H16" s="64" t="inlineStr">
         <is>
-          <t>Scanned signed attestation – Executive Director, Payments &amp; Cash Management.</t>
+          <t>Michelle Oropesa (Investment Operations Director) returns signed attestation (DMA04a).</t>
         </is>
       </c>
       <c r="I16" s="64" t="inlineStr">
         <is>
-          <t>3301, 1903, 1937</t>
+          <t>4052, 1936, 1937</t>
         </is>
       </c>
       <c r="J16" s="64" t="inlineStr">
@@ -14777,32 +14211,28 @@
           <t>G, H, J, O</t>
         </is>
       </c>
-      <c r="K16" s="64" t="inlineStr">
-        <is>
-          <t>Identical to E17a</t>
-        </is>
-      </c>
+      <c r="K16" s="64" t="inlineStr"/>
       <c r="L16" s="82" t="n"/>
     </row>
     <row r="17" ht="23" customHeight="1" s="71">
       <c r="A17" s="64" t="inlineStr">
         <is>
-          <t>DMA04</t>
+          <t>DMA04a</t>
         </is>
       </c>
       <c r="B17" s="64" t="inlineStr">
         <is>
-          <t>DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
+          <t>DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
         </is>
       </c>
       <c r="C17" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted</t>
         </is>
       </c>
       <c r="D17" s="64" t="inlineStr">
         <is>
-          <t>RE_ Management Attestation – DIV Investment Operations.msg</t>
+          <t>Data_Integrity_Attestation_Santander-BCiC.pdf (attachment of DMA04)</t>
         </is>
       </c>
       <c r="E17" s="64" t="inlineStr">
@@ -14812,7 +14242,7 @@
       </c>
       <c r="F17" s="64" t="inlineStr">
         <is>
-          <t>Email attestation</t>
+          <t>Signed attestation</t>
         </is>
       </c>
       <c r="G17" s="64" t="inlineStr">
@@ -14822,7 +14252,7 @@
       </c>
       <c r="H17" s="64" t="inlineStr">
         <is>
-          <t>Michelle Oropesa (Investment Operations Director) returns signed attestation. Same message as E15.</t>
+          <t>Signed attestation – Investment Operations Director, VP, dated 8/17/2026.</t>
         </is>
       </c>
       <c r="I17" s="64" t="inlineStr">
@@ -14835,32 +14265,28 @@
           <t>G, H, J, O</t>
         </is>
       </c>
-      <c r="K17" s="64" t="inlineStr">
-        <is>
-          <t>Same as E15</t>
-        </is>
-      </c>
+      <c r="K17" s="64" t="inlineStr"/>
       <c r="L17" s="82" t="n"/>
     </row>
     <row r="18" ht="23" customHeight="1" s="71">
       <c r="A18" s="64" t="inlineStr">
         <is>
-          <t>DMA04a</t>
+          <t>DMA05</t>
         </is>
       </c>
       <c r="B18" s="64" t="inlineStr">
         <is>
-          <t>DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+          <t>DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
         </is>
       </c>
       <c r="C18" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
         </is>
       </c>
       <c r="D18" s="64" t="inlineStr">
         <is>
-          <t>attachment of DMA04 (identical to E15a)</t>
+          <t>RE_ Management Attestation – DIV Operations.msg</t>
         </is>
       </c>
       <c r="E18" s="64" t="inlineStr">
@@ -14870,22 +14296,22 @@
       </c>
       <c r="F18" s="64" t="inlineStr">
         <is>
-          <t>Signed attestation</t>
+          <t>Email attestation</t>
         </is>
       </c>
       <c r="G18" s="64" t="inlineStr">
         <is>
-          <t>08/17/2026 – Michelle Oropesa</t>
+          <t>08/19/2026 – Maria Teresa (Mayte) Del Cerro</t>
         </is>
       </c>
       <c r="H18" s="64" t="inlineStr">
         <is>
-          <t>Signed attestation – Investment Operations Director, VP, dated 8/17/2026.</t>
+          <t>Signed attestation + BCiC export (E16b) returned by Senior Director of Operations.</t>
         </is>
       </c>
       <c r="I18" s="64" t="inlineStr">
         <is>
-          <t>4052, 1936, 1937</t>
+          <t>3299, 1903, 1937</t>
         </is>
       </c>
       <c r="J18" s="64" t="inlineStr">
@@ -14893,32 +14319,28 @@
           <t>G, H, J, O</t>
         </is>
       </c>
-      <c r="K18" s="64" t="inlineStr">
-        <is>
-          <t>Identical to E15a</t>
-        </is>
-      </c>
+      <c r="K18" s="64" t="inlineStr"/>
       <c r="L18" s="82" t="n"/>
     </row>
     <row r="19" ht="23" customHeight="1" s="71">
       <c r="A19" s="64" t="inlineStr">
         <is>
-          <t>DMA05</t>
+          <t>DMA05a</t>
         </is>
       </c>
       <c r="B19" s="64" t="inlineStr">
         <is>
-          <t>DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
+          <t>DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
         </is>
       </c>
       <c r="C19" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted</t>
         </is>
       </c>
       <c r="D19" s="64" t="inlineStr">
         <is>
-          <t>RE_ Management Attestation – DIV Operations.msg</t>
+          <t>Data_Integrity_Attestation_Santander-BCiC.pdf (attachment of DMA05)</t>
         </is>
       </c>
       <c r="E19" s="64" t="inlineStr">
@@ -14928,17 +14350,17 @@
       </c>
       <c r="F19" s="64" t="inlineStr">
         <is>
-          <t>Email attestation</t>
+          <t>Signed attestation</t>
         </is>
       </c>
       <c r="G19" s="64" t="inlineStr">
         <is>
-          <t>08/19/2026 – Maria Teresa (Mayte) Del Cerro</t>
+          <t>08/19/2026 – Maria Teresa Del Cerro Hontanilla</t>
         </is>
       </c>
       <c r="H19" s="64" t="inlineStr">
         <is>
-          <t>Signed attestation + BCiC export returned by Senior Director of Operations. Same message as E16.</t>
+          <t>Signed attestation – Director of Operations, dated 08/19/2026.</t>
         </is>
       </c>
       <c r="I19" s="64" t="inlineStr">
@@ -14951,32 +14373,28 @@
           <t>G, H, J, O</t>
         </is>
       </c>
-      <c r="K19" s="64" t="inlineStr">
-        <is>
-          <t>Same as E16</t>
-        </is>
-      </c>
+      <c r="K19" s="64" t="inlineStr"/>
       <c r="L19" s="82" t="n"/>
     </row>
     <row r="20" ht="23" customHeight="1" s="71">
       <c r="A20" s="64" t="inlineStr">
         <is>
-          <t>DMA05a</t>
+          <t>DMA06</t>
         </is>
       </c>
       <c r="B20" s="64" t="inlineStr">
         <is>
-          <t>DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+          <t>DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg</t>
         </is>
       </c>
       <c r="C20" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
         </is>
       </c>
       <c r="D20" s="64" t="inlineStr">
         <is>
-          <t>attachment of DMA05 (identical to E16a)</t>
+          <t>RE_ Management Attestation – DIV Trading and Capital Markets.msg</t>
         </is>
       </c>
       <c r="E20" s="64" t="inlineStr">
@@ -14986,22 +14404,22 @@
       </c>
       <c r="F20" s="64" t="inlineStr">
         <is>
-          <t>Signed attestation</t>
+          <t>Email attestation</t>
         </is>
       </c>
       <c r="G20" s="64" t="inlineStr">
         <is>
-          <t>08/19/2026 – Maria Teresa Del Cerro Hontanilla</t>
+          <t>08/18/2026 – Ricardo Garcia-Marques</t>
         </is>
       </c>
       <c r="H20" s="64" t="inlineStr">
         <is>
-          <t>Signed attestation – Director of Operations, dated 08/19/2026.</t>
+          <t>Attestation and approval from Trading &amp; Capital Markets (covers BCiC records approved by Ricardo Garcia).</t>
         </is>
       </c>
       <c r="I20" s="64" t="inlineStr">
         <is>
-          <t>3299, 1903, 1937</t>
+          <t>1937</t>
         </is>
       </c>
       <c r="J20" s="64" t="inlineStr">
@@ -15009,22 +14427,18 @@
           <t>G, H, J, O</t>
         </is>
       </c>
-      <c r="K20" s="64" t="inlineStr">
-        <is>
-          <t>Identical to E16a</t>
-        </is>
-      </c>
+      <c r="K20" s="64" t="inlineStr"/>
       <c r="L20" s="82" t="n"/>
     </row>
     <row r="21" ht="23" customHeight="1" s="71">
       <c r="A21" s="64" t="inlineStr">
         <is>
-          <t>DMA05b</t>
+          <t>DMA06a</t>
         </is>
       </c>
       <c r="B21" s="64" t="inlineStr">
         <is>
-          <t>DMA05b_Operations (Governance &amp; Static Data, Multi-Family Office) - All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
+          <t>DMA06a_Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Data_Integrity_Attestation_Santander-BCiC_signed.pdf</t>
         </is>
       </c>
       <c r="C21" s="64" t="inlineStr">
@@ -15034,7 +14448,7 @@
       </c>
       <c r="D21" s="64" t="inlineStr">
         <is>
-          <t>attachment of DMA05 (identical to E16b)</t>
+          <t>Data_Integrity_Attestation_Santander-BCiC_signed.pdf (attachment of DMA06)</t>
         </is>
       </c>
       <c r="E21" s="64" t="inlineStr">
@@ -15044,45 +14458,41 @@
       </c>
       <c r="F21" s="64" t="inlineStr">
         <is>
-          <t>BCiC export</t>
+          <t>Signed attestation (e-signature)</t>
         </is>
       </c>
       <c r="G21" s="64" t="inlineStr">
         <is>
-          <t>08/19/2026 – attached by M. T. Del Cerro</t>
+          <t>08/18/2026 11:45 AM EDT – Ricardo Garcia Marques</t>
         </is>
       </c>
       <c r="H21" s="64" t="inlineStr">
         <is>
-          <t>BCiC DIV export reviewed with the attestation (identical to E16b).</t>
+          <t>e-signed attestation – MD, Head of Trading &amp; Capital Markets.</t>
         </is>
       </c>
       <c r="I21" s="64" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1937</t>
         </is>
       </c>
       <c r="J21" s="64" t="inlineStr">
         <is>
-          <t>Supplemental</t>
-        </is>
-      </c>
-      <c r="K21" s="64" t="inlineStr">
-        <is>
-          <t>Identical to E16b</t>
-        </is>
-      </c>
+          <t>G, H, J, O</t>
+        </is>
+      </c>
+      <c r="K21" s="64" t="inlineStr"/>
       <c r="L21" s="82" t="n"/>
     </row>
     <row r="22" ht="23" customHeight="1" s="71">
       <c r="A22" s="64" t="inlineStr">
         <is>
-          <t>DMA06</t>
+          <t>DMA07</t>
         </is>
       </c>
       <c r="B22" s="64" t="inlineStr">
         <is>
-          <t>DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg</t>
+          <t>DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg</t>
         </is>
       </c>
       <c r="C22" s="64" t="inlineStr">
@@ -15092,7 +14502,7 @@
       </c>
       <c r="D22" s="64" t="inlineStr">
         <is>
-          <t>RE_ Management Attestation – DIV Trading and Capital Markets.msg</t>
+          <t>RE_ Management Attestation – DIV Treasury and Capital Planning.msg</t>
         </is>
       </c>
       <c r="E22" s="64" t="inlineStr">
@@ -15107,12 +14517,12 @@
       </c>
       <c r="G22" s="64" t="inlineStr">
         <is>
-          <t>08/18/2026 – Ricardo Garcia-Marques</t>
+          <t>08/18/2026 – Martha Sullivan</t>
         </is>
       </c>
       <c r="H22" s="64" t="inlineStr">
         <is>
-          <t>Attestation and approval from Trading &amp; Capital Markets (covers BCiC records approved by Ricardo Garcia).</t>
+          <t>Martha Sullivan returns signed attestation (DMA07a).</t>
         </is>
       </c>
       <c r="I22" s="64" t="inlineStr">
@@ -15131,12 +14541,12 @@
     <row r="23" ht="23" customHeight="1" s="71">
       <c r="A23" s="64" t="inlineStr">
         <is>
-          <t>DMA06a</t>
+          <t>DMA07a</t>
         </is>
       </c>
       <c r="B23" s="64" t="inlineStr">
         <is>
-          <t>DMA06a_Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Data_Integrity_Attestation_Santander-BCiC_signed.pdf</t>
+          <t>DMA07a_Treasury &amp; Capital Planning - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
         </is>
       </c>
       <c r="C23" s="64" t="inlineStr">
@@ -15146,7 +14556,7 @@
       </c>
       <c r="D23" s="64" t="inlineStr">
         <is>
-          <t>Data_Integrity_Attestation_Santander-BCiC_signed.pdf (attachment of DMA06)</t>
+          <t>attachment of DMA07</t>
         </is>
       </c>
       <c r="E23" s="64" t="inlineStr">
@@ -15156,17 +14566,17 @@
       </c>
       <c r="F23" s="64" t="inlineStr">
         <is>
-          <t>Signed attestation (e-signature)</t>
+          <t>Signed attestation</t>
         </is>
       </c>
       <c r="G23" s="64" t="inlineStr">
         <is>
-          <t>08/18/2026 11:45 AM EDT – Ricardo Garcia Marques</t>
+          <t>08/18/2026 – Martha Sullivan</t>
         </is>
       </c>
       <c r="H23" s="64" t="inlineStr">
         <is>
-          <t>e-signed attestation – MD, Head of Trading &amp; Capital Markets.</t>
+          <t>Signed attestation – Balance Sheet Manager, Treasury.</t>
         </is>
       </c>
       <c r="I23" s="64" t="inlineStr">
@@ -15185,12 +14595,12 @@
     <row r="24" ht="23" customHeight="1" s="71">
       <c r="A24" s="64" t="inlineStr">
         <is>
-          <t>DMA07</t>
+          <t>DMA08</t>
         </is>
       </c>
       <c r="B24" s="64" t="inlineStr">
         <is>
-          <t>DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg</t>
+          <t>DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg</t>
         </is>
       </c>
       <c r="C24" s="64" t="inlineStr">
@@ -15200,7 +14610,7 @@
       </c>
       <c r="D24" s="64" t="inlineStr">
         <is>
-          <t>RE_ Management Attestation – DIV Treasury and Capital Planning.msg</t>
+          <t>RE_ Management Attestation – DIV Solvency and Market Risk.msg</t>
         </is>
       </c>
       <c r="E24" s="64" t="inlineStr">
@@ -15210,17 +14620,17 @@
       </c>
       <c r="F24" s="64" t="inlineStr">
         <is>
-          <t>Email attestation</t>
+          <t>Email approval</t>
         </is>
       </c>
       <c r="G24" s="64" t="inlineStr">
         <is>
-          <t>08/18/2026 – Martha Sullivan</t>
+          <t>08/18/2026 – Ivan Caisapanta</t>
         </is>
       </c>
       <c r="H24" s="64" t="inlineStr">
         <is>
-          <t>Martha Sullivan returns signed attestation (DMA07a).</t>
+          <t>"Hi Elizabeth, You have my approval" – Financial Risk (BCiC Department Manager recorded as Xavier Caisapanta).</t>
         </is>
       </c>
       <c r="I24" s="64" t="inlineStr">
@@ -15239,22 +14649,22 @@
     <row r="25" ht="23" customHeight="1" s="71">
       <c r="A25" s="64" t="inlineStr">
         <is>
-          <t>DMA07a</t>
+          <t>DMA09</t>
         </is>
       </c>
       <c r="B25" s="64" t="inlineStr">
         <is>
-          <t>DMA07a_Treasury &amp; Capital Planning - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+          <t>DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg</t>
         </is>
       </c>
       <c r="C25" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
         </is>
       </c>
       <c r="D25" s="64" t="inlineStr">
         <is>
-          <t>attachment of DMA07</t>
+          <t>RE_ Management Attestation – DIV General Services.msg</t>
         </is>
       </c>
       <c r="E25" s="64" t="inlineStr">
@@ -15264,17 +14674,17 @@
       </c>
       <c r="F25" s="64" t="inlineStr">
         <is>
-          <t>Signed attestation</t>
+          <t>Email attestation</t>
         </is>
       </c>
       <c r="G25" s="64" t="inlineStr">
         <is>
-          <t>08/18/2026 – Martha Sullivan</t>
+          <t>08/18/2026 – Clara G. De Castro</t>
         </is>
       </c>
       <c r="H25" s="64" t="inlineStr">
         <is>
-          <t>Signed attestation – Balance Sheet Manager, Treasury.</t>
+          <t>Clara De Castro (Director, General Services &amp; Facilities) returns signed attestation (DMA09a).</t>
         </is>
       </c>
       <c r="I25" s="64" t="inlineStr">
@@ -15293,22 +14703,22 @@
     <row r="26">
       <c r="A26" s="64" t="inlineStr">
         <is>
-          <t>DMA08</t>
+          <t>DMA09a</t>
         </is>
       </c>
       <c r="B26" s="64" t="inlineStr">
         <is>
-          <t>DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg</t>
+          <t>DMA09a_General Services (Marketing &amp; General Services) - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
         </is>
       </c>
       <c r="C26" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted</t>
         </is>
       </c>
       <c r="D26" s="64" t="inlineStr">
         <is>
-          <t>RE_ Management Attestation – DIV Solvency and Market Risk.msg</t>
+          <t>attachment of DMA09</t>
         </is>
       </c>
       <c r="E26" s="64" t="inlineStr">
@@ -15318,17 +14728,17 @@
       </c>
       <c r="F26" s="64" t="inlineStr">
         <is>
-          <t>Email approval</t>
+          <t>Signed attestation</t>
         </is>
       </c>
       <c r="G26" s="64" t="inlineStr">
         <is>
-          <t>08/18/2026 – Ivan Caisapanta</t>
+          <t>08/18/2026 – Clara G. De Castro</t>
         </is>
       </c>
       <c r="H26" s="64" t="inlineStr">
         <is>
-          <t>"Hi Elizabeth, You have my approval" – Financial Risk (BCiC Department Manager recorded as Xavier Caisapanta).</t>
+          <t>Signed attestation – General Services.</t>
         </is>
       </c>
       <c r="I26" s="64" t="inlineStr">
@@ -15347,12 +14757,12 @@
     <row r="27">
       <c r="A27" s="64" t="inlineStr">
         <is>
-          <t>DMA09</t>
+          <t>DMA10</t>
         </is>
       </c>
       <c r="B27" s="64" t="inlineStr">
         <is>
-          <t>DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg</t>
+          <t>DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml</t>
         </is>
       </c>
       <c r="C27" s="64" t="inlineStr">
@@ -15362,7 +14772,7 @@
       </c>
       <c r="D27" s="64" t="inlineStr">
         <is>
-          <t>RE_ Management Attestation – DIV General Services.msg</t>
+          <t>RE Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises).eml</t>
         </is>
       </c>
       <c r="E27" s="64" t="inlineStr">
@@ -15372,17 +14782,17 @@
       </c>
       <c r="F27" s="64" t="inlineStr">
         <is>
-          <t>Email attestation</t>
+          <t>Email approval</t>
         </is>
       </c>
       <c r="G27" s="64" t="inlineStr">
         <is>
-          <t>08/18/2026 – Clara G. De Castro</t>
+          <t>08/21/2026 – Victoria Fernandez</t>
         </is>
       </c>
       <c r="H27" s="64" t="inlineStr">
         <is>
-          <t>Clara De Castro (Director, General Services &amp; Facilities) returns signed attestation (DMA09a).</t>
+          <t>"Approved" – Digital Wealth.</t>
         </is>
       </c>
       <c r="I27" s="64" t="inlineStr">
@@ -15401,22 +14811,22 @@
     <row r="28">
       <c r="A28" s="64" t="inlineStr">
         <is>
-          <t>DMA09a</t>
+          <t>DMA11</t>
         </is>
       </c>
       <c r="B28" s="64" t="inlineStr">
         <is>
-          <t>DMA09a_General Services (Marketing &amp; General Services) - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+          <t>DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml</t>
         </is>
       </c>
       <c r="C28" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
         </is>
       </c>
       <c r="D28" s="64" t="inlineStr">
         <is>
-          <t>attachment of DMA09</t>
+          <t>RE Management Attestation – DIV Commercial Middle Office.eml</t>
         </is>
       </c>
       <c r="E28" s="64" t="inlineStr">
@@ -15426,22 +14836,22 @@
       </c>
       <c r="F28" s="64" t="inlineStr">
         <is>
-          <t>Signed attestation</t>
+          <t>Email approval</t>
         </is>
       </c>
       <c r="G28" s="64" t="inlineStr">
         <is>
-          <t>08/18/2026 – Clara G. De Castro</t>
+          <t>09/09/2026 – Miguel Orozco</t>
         </is>
       </c>
       <c r="H28" s="64" t="inlineStr">
         <is>
-          <t>Signed attestation – General Services.</t>
+          <t>"I approve the integrity validation for the testing performed by the Commercial Middle Office."</t>
         </is>
       </c>
       <c r="I28" s="64" t="inlineStr">
         <is>
-          <t>1937</t>
+          <t>3299, 1937</t>
         </is>
       </c>
       <c r="J28" s="64" t="inlineStr">
@@ -15455,12 +14865,12 @@
     <row r="29">
       <c r="A29" s="64" t="inlineStr">
         <is>
-          <t>DMA10</t>
+          <t>DMA12</t>
         </is>
       </c>
       <c r="B29" s="64" t="inlineStr">
         <is>
-          <t>DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml</t>
+          <t>DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml</t>
         </is>
       </c>
       <c r="C29" s="64" t="inlineStr">
@@ -15470,7 +14880,7 @@
       </c>
       <c r="D29" s="64" t="inlineStr">
         <is>
-          <t>RE Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises).eml</t>
+          <t>RE Management Attestation – DIV Client Servicing Unit.eml</t>
         </is>
       </c>
       <c r="E29" s="64" t="inlineStr">
@@ -15485,12 +14895,12 @@
       </c>
       <c r="G29" s="64" t="inlineStr">
         <is>
-          <t>08/21/2026 – Victoria Fernandez</t>
+          <t>09/09/2026 – Liliana Vizhnay</t>
         </is>
       </c>
       <c r="H29" s="64" t="inlineStr">
         <is>
-          <t>"Approved" – Digital Wealth.</t>
+          <t>"I approve." – Client Servicing Unit.</t>
         </is>
       </c>
       <c r="I29" s="64" t="inlineStr">
@@ -15509,12 +14919,12 @@
     <row r="30">
       <c r="A30" s="64" t="inlineStr">
         <is>
-          <t>DMA11</t>
+          <t>DMA13</t>
         </is>
       </c>
       <c r="B30" s="64" t="inlineStr">
         <is>
-          <t>DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml</t>
+          <t>DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml</t>
         </is>
       </c>
       <c r="C30" s="64" t="inlineStr">
@@ -15524,7 +14934,7 @@
       </c>
       <c r="D30" s="64" t="inlineStr">
         <is>
-          <t>RE Management Attestation – DIV Commercial Middle Office.eml</t>
+          <t>RE Management Attestation – DIV Unified Communication - Cisco Call Manager.eml</t>
         </is>
       </c>
       <c r="E30" s="64" t="inlineStr">
@@ -15539,22 +14949,22 @@
       </c>
       <c r="G30" s="64" t="inlineStr">
         <is>
-          <t>09/09/2026 – Miguel Orozco</t>
+          <t>09/09/2026 – Elizabeth Noda</t>
         </is>
       </c>
       <c r="H30" s="64" t="inlineStr">
         <is>
-          <t>"I approve the integrity validation for the testing performed by the Commercial Middle Office."</t>
+          <t>"approve" – Cisco Call Manager (IT). Cisco Call Manager is NOT one of the 10 tested applications – retained for completeness only.</t>
         </is>
       </c>
       <c r="I30" s="64" t="inlineStr">
         <is>
-          <t>3299, 1937</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J30" s="64" t="inlineStr">
         <is>
-          <t>G, H, J, O</t>
+          <t>Supplemental</t>
         </is>
       </c>
       <c r="K30" s="64" t="inlineStr"/>
@@ -15563,52 +14973,52 @@
     <row r="31">
       <c r="A31" s="64" t="inlineStr">
         <is>
-          <t>DMA12</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="B31" s="64" t="inlineStr">
         <is>
-          <t>DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml</t>
+          <t>BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
         </is>
       </c>
       <c r="C31" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
         </is>
       </c>
       <c r="D31" s="64" t="inlineStr">
         <is>
-          <t>RE Management Attestation – DIV Client Servicing Unit.eml</t>
+          <t>Applications In Scope for DR Test BSI (13).xlsx</t>
         </is>
       </c>
       <c r="E31" s="64" t="inlineStr">
         <is>
-          <t>DIV Manager Attestation Email_Approvals.zip</t>
+          <t>Data Integrity &amp; Email Testing Evidence.zip</t>
         </is>
       </c>
       <c r="F31" s="64" t="inlineStr">
         <is>
-          <t>Email approval</t>
+          <t>BCiC export</t>
         </is>
       </c>
       <c r="G31" s="64" t="inlineStr">
         <is>
-          <t>09/09/2026 – Liliana Vizhnay</t>
+          <t>BCiC – Applications In Scope for DR Test BSI</t>
         </is>
       </c>
       <c r="H31" s="64" t="inlineStr">
         <is>
-          <t>"I approve." – Client Servicing Unit.</t>
+          <t>BCiC export of the BSI DR-scope population (43 applications) with Exercise Date and 2025 DR / Backup-Restore / DIV scope flags.</t>
         </is>
       </c>
       <c r="I31" s="64" t="inlineStr">
         <is>
-          <t>1937</t>
+          <t>1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
         </is>
       </c>
       <c r="J31" s="64" t="inlineStr">
         <is>
-          <t>G, H, J, O</t>
+          <t>B, C, D, K, L, N</t>
         </is>
       </c>
       <c r="K31" s="64" t="inlineStr"/>
@@ -15617,52 +15027,52 @@
     <row r="32">
       <c r="A32" s="64" t="inlineStr">
         <is>
-          <t>DMA13</t>
+          <t>E02</t>
         </is>
       </c>
       <c r="B32" s="64" t="inlineStr">
         <is>
-          <t>DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml</t>
+          <t>BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg</t>
         </is>
       </c>
       <c r="C32" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
         </is>
       </c>
       <c r="D32" s="64" t="inlineStr">
         <is>
-          <t>RE Management Attestation – DIV Unified Communication - Cisco Call Manager.eml</t>
+          <t>screenshot BCiC apps in scope for DR Testing.jpg</t>
         </is>
       </c>
       <c r="E32" s="64" t="inlineStr">
         <is>
-          <t>DIV Manager Attestation Email_Approvals.zip</t>
+          <t>Data Integrity &amp; Email Testing Evidence.zip</t>
         </is>
       </c>
       <c r="F32" s="64" t="inlineStr">
         <is>
-          <t>Email approval</t>
+          <t>BCiC screenshot</t>
         </is>
       </c>
       <c r="G32" s="64" t="inlineStr">
         <is>
-          <t>09/09/2026 – Elizabeth Noda</t>
+          <t>09/10/2026 – Cesar Vidal</t>
         </is>
       </c>
       <c r="H32" s="64" t="inlineStr">
         <is>
-          <t>"approve" – Cisco Call Manager (IT). Cisco Call Manager is NOT one of the 10 tested applications – retained for completeness only.</t>
+          <t>BCiC Applications screen with view 'Applications In Scope for DR Test BSI' selected (1–20 of 43 items).</t>
         </is>
       </c>
       <c r="I32" s="64" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
         </is>
       </c>
       <c r="J32" s="64" t="inlineStr">
         <is>
-          <t>Supplemental</t>
+          <t>D, K, N</t>
         </is>
       </c>
       <c r="K32" s="64" t="inlineStr"/>
@@ -15671,12 +15081,12 @@
     <row r="33">
       <c r="A33" s="64" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>E03</t>
         </is>
       </c>
       <c r="B33" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
+          <t>BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
         </is>
       </c>
       <c r="C33" s="64" t="inlineStr">
@@ -15686,7 +15096,7 @@
       </c>
       <c r="D33" s="64" t="inlineStr">
         <is>
-          <t>Applications In Scope for DR Test BSI (13).xlsx</t>
+          <t>All Data Integrity Validation Testing_FV.xls</t>
         </is>
       </c>
       <c r="E33" s="64" t="inlineStr">
@@ -15701,12 +15111,12 @@
       </c>
       <c r="G33" s="64" t="inlineStr">
         <is>
-          <t>BCiC – Applications In Scope for DR Test BSI</t>
+          <t>BCiC – Data Integrity Validation Testing (62 records)</t>
         </is>
       </c>
       <c r="H33" s="64" t="inlineStr">
         <is>
-          <t>BCiC export of the BSI DR-scope population (43 applications) with Exercise Date and 2025 DR / Backup-Restore / DIV scope flags.</t>
+          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Y/N Format/Headers/Content, Attestation Date / Provided By. Row numbers quoted are Excel rows.</t>
         </is>
       </c>
       <c r="I33" s="64" t="inlineStr">
@@ -15716,7 +15126,7 @@
       </c>
       <c r="J33" s="64" t="inlineStr">
         <is>
-          <t>B, C, D, K, L, N</t>
+          <t>B, C, D, E, F, G, H, I, K, L, M, O, P</t>
         </is>
       </c>
       <c r="K33" s="64" t="inlineStr"/>
@@ -15725,12 +15135,12 @@
     <row r="34">
       <c r="A34" s="64" t="inlineStr">
         <is>
-          <t>E02</t>
+          <t>E04</t>
         </is>
       </c>
       <c r="B34" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg</t>
+          <t>BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg</t>
         </is>
       </c>
       <c r="C34" s="64" t="inlineStr">
@@ -15740,7 +15150,7 @@
       </c>
       <c r="D34" s="64" t="inlineStr">
         <is>
-          <t>screenshot BCiC apps in scope for DR Testing.jpg</t>
+          <t>BCiC_Screenshot for Data Integrity Validation report.jpg</t>
         </is>
       </c>
       <c r="E34" s="64" t="inlineStr">
@@ -15760,7 +15170,7 @@
       </c>
       <c r="H34" s="64" t="inlineStr">
         <is>
-          <t>BCiC Applications screen with view 'Applications In Scope for DR Test BSI' selected (1–20 of 43 items).</t>
+          <t>BCiC 'Data Integrity Validation Testing' screen (1–20 of 66 items) showing tester, validation date, manager, approval date, Y/N results and attestation fields.</t>
         </is>
       </c>
       <c r="I34" s="64" t="inlineStr">
@@ -15770,7 +15180,7 @@
       </c>
       <c r="J34" s="64" t="inlineStr">
         <is>
-          <t>D, K, N</t>
+          <t>D, E, F, G, H, K, P</t>
         </is>
       </c>
       <c r="K34" s="64" t="inlineStr"/>
@@ -15779,12 +15189,12 @@
     <row r="35">
       <c r="A35" s="64" t="inlineStr">
         <is>
-          <t>E03</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="B35" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+          <t>BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg</t>
         </is>
       </c>
       <c r="C35" s="64" t="inlineStr">
@@ -15794,7 +15204,7 @@
       </c>
       <c r="D35" s="64" t="inlineStr">
         <is>
-          <t>All Data Integrity Validation Testing_FV.xls</t>
+          <t>IT BIA Results Review and preparation for DR .msg</t>
         </is>
       </c>
       <c r="E35" s="64" t="inlineStr">
@@ -15804,17 +15214,17 @@
       </c>
       <c r="F35" s="64" t="inlineStr">
         <is>
-          <t>BCiC export</t>
+          <t>Meeting invite</t>
         </is>
       </c>
       <c r="G35" s="64" t="inlineStr">
         <is>
-          <t>BCiC – Data Integrity Validation Testing (62 records)</t>
+          <t>09/15/2025 – Elizabeth Noda</t>
         </is>
       </c>
       <c r="H35" s="64" t="inlineStr">
         <is>
-          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Y/N Format/Headers/Content, Attestation Date / Provided By. Row numbers quoted are Excel rows.</t>
+          <t>IT DR meeting to review the 2025 BIA results and applications list ahead of the DR exercise.</t>
         </is>
       </c>
       <c r="I35" s="64" t="inlineStr">
@@ -15824,7 +15234,7 @@
       </c>
       <c r="J35" s="64" t="inlineStr">
         <is>
-          <t>B, C, D, E, F, G, H, I, K, L, M, O, P</t>
+          <t>M, N</t>
         </is>
       </c>
       <c r="K35" s="64" t="inlineStr"/>
@@ -15833,12 +15243,12 @@
     <row r="36">
       <c r="A36" s="64" t="inlineStr">
         <is>
-          <t>E04</t>
+          <t>E06</t>
         </is>
       </c>
       <c r="B36" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg</t>
+          <t>BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml</t>
         </is>
       </c>
       <c r="C36" s="64" t="inlineStr">
@@ -15848,7 +15258,7 @@
       </c>
       <c r="D36" s="64" t="inlineStr">
         <is>
-          <t>BCiC_Screenshot for Data Integrity Validation report.jpg</t>
+          <t>IT BIA Results Review and preparation for DR  1 (1).msg.eml</t>
         </is>
       </c>
       <c r="E36" s="64" t="inlineStr">
@@ -15858,17 +15268,17 @@
       </c>
       <c r="F36" s="64" t="inlineStr">
         <is>
-          <t>BCiC screenshot</t>
+          <t>Meeting invite</t>
         </is>
       </c>
       <c r="G36" s="64" t="inlineStr">
         <is>
-          <t>09/10/2026 – Cesar Vidal</t>
+          <t>09/18/2025 – Elizabeth Noda</t>
         </is>
       </c>
       <c r="H36" s="64" t="inlineStr">
         <is>
-          <t>BCiC 'Data Integrity Validation Testing' screen (1–20 of 66 items) showing tester, validation date, manager, approval date, Y/N results and attestation fields.</t>
+          <t>Follow-up IT BIA results / DR preparation meeting (applications list review).</t>
         </is>
       </c>
       <c r="I36" s="64" t="inlineStr">
@@ -15878,7 +15288,7 @@
       </c>
       <c r="J36" s="64" t="inlineStr">
         <is>
-          <t>D, E, F, G, H, K, P</t>
+          <t>M, N</t>
         </is>
       </c>
       <c r="K36" s="64" t="inlineStr"/>
@@ -15887,12 +15297,12 @@
     <row r="37">
       <c r="A37" s="64" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>E07</t>
         </is>
       </c>
       <c r="B37" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg</t>
+          <t>BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg</t>
         </is>
       </c>
       <c r="C37" s="64" t="inlineStr">
@@ -15902,7 +15312,7 @@
       </c>
       <c r="D37" s="64" t="inlineStr">
         <is>
-          <t>IT BIA Results Review and preparation for DR .msg</t>
+          <t>DATA INTERITY FILS FROM 111425.msg</t>
         </is>
       </c>
       <c r="E37" s="64" t="inlineStr">
@@ -15912,27 +15322,27 @@
       </c>
       <c r="F37" s="64" t="inlineStr">
         <is>
-          <t>Meeting invite</t>
+          <t>Email + 13 attachments</t>
         </is>
       </c>
       <c r="G37" s="64" t="inlineStr">
         <is>
-          <t>09/15/2025 – Elizabeth Noda</t>
+          <t>11/15/2025 – Frank Puentes</t>
         </is>
       </c>
       <c r="H37" s="64" t="inlineStr">
         <is>
-          <t>IT DR meeting to review the 2025 BIA results and applications list ahead of the DR exercise.</t>
+          <t>Pre-DR (11/14/2025) source reports: Fedlink, OFAC ACH/FED/SWIFT, Payment Monitor, SWIFT Interface Monitor, outgoing Fedwire/SWIFT. Attachments extracted to E07_Attachments_extracted.</t>
         </is>
       </c>
       <c r="I37" s="64" t="inlineStr">
         <is>
-          <t>1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
+          <t>3301, 1903, 1936, 1937</t>
         </is>
       </c>
       <c r="J37" s="64" t="inlineStr">
         <is>
-          <t>M, N</t>
+          <t>F</t>
         </is>
       </c>
       <c r="K37" s="64" t="inlineStr"/>
@@ -15941,12 +15351,12 @@
     <row r="38">
       <c r="A38" s="64" t="inlineStr">
         <is>
-          <t>E06</t>
+          <t>E08</t>
         </is>
       </c>
       <c r="B38" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml</t>
+          <t>BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg</t>
         </is>
       </c>
       <c r="C38" s="64" t="inlineStr">
@@ -15956,7 +15366,7 @@
       </c>
       <c r="D38" s="64" t="inlineStr">
         <is>
-          <t>IT BIA Results Review and preparation for DR  1 (1).msg.eml</t>
+          <t>FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg</t>
         </is>
       </c>
       <c r="E38" s="64" t="inlineStr">
@@ -15966,27 +15376,27 @@
       </c>
       <c r="F38" s="64" t="inlineStr">
         <is>
-          <t>Meeting invite</t>
+          <t>Email + 13 attachments</t>
         </is>
       </c>
       <c r="G38" s="64" t="inlineStr">
         <is>
-          <t>09/18/2025 – Elizabeth Noda</t>
+          <t>11/15/2025 – Frank Puentes</t>
         </is>
       </c>
       <c r="H38" s="64" t="inlineStr">
         <is>
-          <t>Follow-up IT BIA results / DR preparation meeting (applications list review).</t>
+          <t>DR test-day (11/15/2025) re-run of the same reports for comparison with 11/14/2025 source. Attachments extracted to E08_Attachments_extracted.</t>
         </is>
       </c>
       <c r="I38" s="64" t="inlineStr">
         <is>
-          <t>1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
+          <t>3301, 1903, 1936, 1937</t>
         </is>
       </c>
       <c r="J38" s="64" t="inlineStr">
         <is>
-          <t>M, N</t>
+          <t>F, M</t>
         </is>
       </c>
       <c r="K38" s="64" t="inlineStr"/>
@@ -15995,12 +15405,12 @@
     <row r="39">
       <c r="A39" s="64" t="inlineStr">
         <is>
-          <t>E07</t>
+          <t>E09</t>
         </is>
       </c>
       <c r="B39" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg</t>
+          <t>BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg</t>
         </is>
       </c>
       <c r="C39" s="64" t="inlineStr">
@@ -16010,7 +15420,7 @@
       </c>
       <c r="D39" s="64" t="inlineStr">
         <is>
-          <t>DATA INTERITY FILS FROM 111425.msg</t>
+          <t>RE_ Yearly Backup and restore exercise (Client Back Office)</t>
         </is>
       </c>
       <c r="E39" s="64" t="inlineStr">
@@ -16020,27 +15430,27 @@
       </c>
       <c r="F39" s="64" t="inlineStr">
         <is>
-          <t>Email + 13 attachments</t>
+          <t>Email approval</t>
         </is>
       </c>
       <c r="G39" s="64" t="inlineStr">
         <is>
-          <t>11/15/2025 – Frank Puentes</t>
+          <t>03/03/2026 – 05/05/2026 – Claudia Romero</t>
         </is>
       </c>
       <c r="H39" s="64" t="inlineStr">
         <is>
-          <t>Pre-DR (11/14/2025) source reports: Fedlink, OFAC ACH/FED/SWIFT, Payment Monitor, SWIFT Interface Monitor, outgoing Fedwire/SWIFT. Attachments extracted to E07_Attachments_extracted.</t>
+          <t>Client Back Office test evidence (Mariorly Morales, Ilumel Rodriguez, Rolando Bonilla) and Claudia Romero "Approved." 05/05/2026. Thread maps ACH Express, FedExport, FedImport, Imaging101 to Client Back Office / Claudia Romero.</t>
         </is>
       </c>
       <c r="I39" s="64" t="inlineStr">
         <is>
-          <t>3301, 1903, 1936, 1937</t>
+          <t>1822, 1867, 1868, 3299, 1937</t>
         </is>
       </c>
       <c r="J39" s="64" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E, G, H, J, M, N, O</t>
         </is>
       </c>
       <c r="K39" s="64" t="inlineStr"/>
@@ -16049,12 +15459,12 @@
     <row r="40">
       <c r="A40" s="64" t="inlineStr">
         <is>
-          <t>E08</t>
+          <t>E10</t>
         </is>
       </c>
       <c r="B40" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg</t>
+          <t>BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg</t>
         </is>
       </c>
       <c r="C40" s="64" t="inlineStr">
@@ -16064,7 +15474,7 @@
       </c>
       <c r="D40" s="64" t="inlineStr">
         <is>
-          <t>FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg</t>
+          <t>RE_ Yearly Backup and restore exercise-- re-run (Finance)</t>
         </is>
       </c>
       <c r="E40" s="64" t="inlineStr">
@@ -16074,27 +15484,27 @@
       </c>
       <c r="F40" s="64" t="inlineStr">
         <is>
-          <t>Email + 13 attachments</t>
+          <t>Email approval</t>
         </is>
       </c>
       <c r="G40" s="64" t="inlineStr">
         <is>
-          <t>11/15/2025 – Frank Puentes</t>
+          <t>03/09/2026 – Lina Acuna</t>
         </is>
       </c>
       <c r="H40" s="64" t="inlineStr">
         <is>
-          <t>DR test-day (11/15/2025) re-run of the same reports for comparison with 11/14/2025 source. Attachments extracted to E08_Attachments_extracted.</t>
+          <t>Finance DIV results chart (Jose Acero) and Lina Acuna "Approved" 03/09/2026 (T24 / ReconXpert backup-restore).</t>
         </is>
       </c>
       <c r="I40" s="64" t="inlineStr">
         <is>
-          <t>3301, 1903, 1936, 1937</t>
+          <t>1917, 1937</t>
         </is>
       </c>
       <c r="J40" s="64" t="inlineStr">
         <is>
-          <t>F, M</t>
+          <t>M</t>
         </is>
       </c>
       <c r="K40" s="64" t="inlineStr"/>
@@ -16103,12 +15513,12 @@
     <row r="41">
       <c r="A41" s="64" t="inlineStr">
         <is>
-          <t>E09</t>
+          <t>E13</t>
         </is>
       </c>
       <c r="B41" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg</t>
+          <t>BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg</t>
         </is>
       </c>
       <c r="C41" s="64" t="inlineStr">
@@ -16118,7 +15528,7 @@
       </c>
       <c r="D41" s="64" t="inlineStr">
         <is>
-          <t>RE_ Yearly Backup and restore exercise (Client Back Office)</t>
+          <t>miasx2 T24 environment(s) miaeod miabed01 refreshed correctly.msg</t>
         </is>
       </c>
       <c r="E41" s="64" t="inlineStr">
@@ -16128,27 +15538,27 @@
       </c>
       <c r="F41" s="64" t="inlineStr">
         <is>
-          <t>Email approval</t>
+          <t>System email</t>
         </is>
       </c>
       <c r="G41" s="64" t="inlineStr">
         <is>
-          <t>03/03/2026 – 05/05/2026 – Claudia Romero</t>
+          <t>11/13/2024 – T24 backup user</t>
         </is>
       </c>
       <c r="H41" s="64" t="inlineStr">
         <is>
-          <t>Client Back Office test evidence (Mariorly Morales, Ilumel Rodriguez, Rolando Bonilla) and Claudia Romero "Approved." 05/05/2026. Thread maps ACH Express, FedExport, FedImport, Imaging101 to Client Back Office / Claudia Romero.</t>
+          <t>T24 environment refresh log – prior period (outside review period); supplemental only.</t>
         </is>
       </c>
       <c r="I41" s="64" t="inlineStr">
         <is>
-          <t>1822, 1867, 1868, 3299, 1937</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J41" s="64" t="inlineStr">
         <is>
-          <t>E, G, H, J, M, N, O</t>
+          <t>Supplemental</t>
         </is>
       </c>
       <c r="K41" s="64" t="inlineStr"/>
@@ -16157,12 +15567,12 @@
     <row r="42">
       <c r="A42" s="64" t="inlineStr">
         <is>
-          <t>E10</t>
+          <t>E16b</t>
         </is>
       </c>
       <c r="B42" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg</t>
+          <t>BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
         </is>
       </c>
       <c r="C42" s="64" t="inlineStr">
@@ -16172,7 +15582,7 @@
       </c>
       <c r="D42" s="64" t="inlineStr">
         <is>
-          <t>RE_ Yearly Backup and restore exercise-- re-run (Finance)</t>
+          <t>All Data Integrity Validation Testing-BSI 2025-26.xlsx (attachment of DMA05 email)</t>
         </is>
       </c>
       <c r="E42" s="64" t="inlineStr">
@@ -16182,735 +15592,39 @@
       </c>
       <c r="F42" s="64" t="inlineStr">
         <is>
-          <t>Email approval</t>
+          <t>BCiC export</t>
         </is>
       </c>
       <c r="G42" s="64" t="inlineStr">
         <is>
-          <t>03/09/2026 – Lina Acuna</t>
+          <t>08/2026 – BCiC export sent with attestation request</t>
         </is>
       </c>
       <c r="H42" s="64" t="inlineStr">
         <is>
-          <t>Finance DIV results chart (Jose Acero) and Lina Acuna "Approved" 03/09/2026 (T24 / ReconXpert backup-restore).</t>
+          <t>BCiC DIV export 2025-26 (64 rows; no manager columns) sent to managers with the attestation request and returned by M. T. Del Cerro (DMA05). Row numbers are Excel rows.</t>
         </is>
       </c>
       <c r="I42" s="64" t="inlineStr">
         <is>
-          <t>1917, 1937</t>
+          <t>1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
         </is>
       </c>
       <c r="J42" s="64" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="K42" s="64" t="inlineStr">
-        <is>
-          <t>Same thread as E11</t>
-        </is>
-      </c>
+          <t>B, D, E, F, I, K, P</t>
+        </is>
+      </c>
+      <c r="K42" s="64" t="inlineStr"/>
       <c r="L42" s="82" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="64" t="inlineStr">
         <is>
-          <t>E11</t>
+          <t>E07.01–E07.13</t>
         </is>
       </c>
       <c r="B43" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3_E11_BSI.IT.6.C7.3 Manager Approval.msg</t>
-        </is>
-      </c>
-      <c r="C43" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
-        </is>
-      </c>
-      <c r="D43" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3 Manager Approval.msg</t>
-        </is>
-      </c>
-      <c r="E43" s="64" t="inlineStr">
-        <is>
-          <t>Data Integrity &amp; Email Testing Evidence.zip</t>
-        </is>
-      </c>
-      <c r="F43" s="64" t="inlineStr">
-        <is>
-          <t>Email approval</t>
-        </is>
-      </c>
-      <c r="G43" s="64" t="inlineStr">
-        <is>
-          <t>03/09/2026 – Lina Acuna</t>
-        </is>
-      </c>
-      <c r="H43" s="64" t="inlineStr">
-        <is>
-          <t>Same Finance approval thread as E10 (separate save).</t>
-        </is>
-      </c>
-      <c r="I43" s="64" t="inlineStr">
-        <is>
-          <t>1917, 1937</t>
-        </is>
-      </c>
-      <c r="J43" s="64" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="K43" s="64" t="inlineStr">
-        <is>
-          <t>Same thread as E10</t>
-        </is>
-      </c>
-      <c r="L43" s="82" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="64" t="inlineStr">
-        <is>
-          <t>E12</t>
-        </is>
-      </c>
-      <c r="B44" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3_E12_RE_ Testing enviroment Financial Analysis manager approval.msg</t>
-        </is>
-      </c>
-      <c r="C44" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
-        </is>
-      </c>
-      <c r="D44" s="64" t="inlineStr">
-        <is>
-          <t>RE_ Testing enviroment Financial Analysis manager approval.msg</t>
-        </is>
-      </c>
-      <c r="E44" s="64" t="inlineStr">
-        <is>
-          <t>Data Integrity &amp; Email Testing Evidence.zip</t>
-        </is>
-      </c>
-      <c r="F44" s="64" t="inlineStr">
-        <is>
-          <t>Email approval</t>
-        </is>
-      </c>
-      <c r="G44" s="64" t="inlineStr">
-        <is>
-          <t>12/31/2025 &amp; 01/26/2026 – Sadis Alvarenga</t>
-        </is>
-      </c>
-      <c r="H44" s="64" t="inlineStr">
-        <is>
-          <t>Same message as BLA06 – Sadis Alvarenga "Approved."</t>
-        </is>
-      </c>
-      <c r="I44" s="64" t="inlineStr">
-        <is>
-          <t>1917, 1937</t>
-        </is>
-      </c>
-      <c r="J44" s="64" t="inlineStr">
-        <is>
-          <t>G, H, J, O</t>
-        </is>
-      </c>
-      <c r="K44" s="64" t="inlineStr">
-        <is>
-          <t>Same message as BLA06</t>
-        </is>
-      </c>
-      <c r="L44" s="82" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="64" t="inlineStr">
-        <is>
-          <t>E13</t>
-        </is>
-      </c>
-      <c r="B45" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg</t>
-        </is>
-      </c>
-      <c r="C45" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
-        </is>
-      </c>
-      <c r="D45" s="64" t="inlineStr">
-        <is>
-          <t>miasx2 T24 environment(s) miaeod miabed01 refreshed correctly.msg</t>
-        </is>
-      </c>
-      <c r="E45" s="64" t="inlineStr">
-        <is>
-          <t>Data Integrity &amp; Email Testing Evidence.zip</t>
-        </is>
-      </c>
-      <c r="F45" s="64" t="inlineStr">
-        <is>
-          <t>System email</t>
-        </is>
-      </c>
-      <c r="G45" s="64" t="inlineStr">
-        <is>
-          <t>11/13/2024 – T24 backup user</t>
-        </is>
-      </c>
-      <c r="H45" s="64" t="inlineStr">
-        <is>
-          <t>T24 environment refresh log – prior period (outside review period); supplemental only.</t>
-        </is>
-      </c>
-      <c r="I45" s="64" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J45" s="64" t="inlineStr">
-        <is>
-          <t>Supplemental</t>
-        </is>
-      </c>
-      <c r="K45" s="64" t="inlineStr"/>
-      <c r="L45" s="82" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="64" t="inlineStr">
-        <is>
-          <t>E14</t>
-        </is>
-      </c>
-      <c r="B46" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml</t>
-        </is>
-      </c>
-      <c r="C46" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
-        </is>
-      </c>
-      <c r="D46" s="64" t="inlineStr">
-        <is>
-          <t>RE_ Management Attestation … (1).msg.eml</t>
-        </is>
-      </c>
-      <c r="E46" s="64" t="inlineStr">
-        <is>
-          <t>Data Integrity &amp; Email Testing Evidence.zip</t>
-        </is>
-      </c>
-      <c r="F46" s="64" t="inlineStr">
-        <is>
-          <t>Email attestation</t>
-        </is>
-      </c>
-      <c r="G46" s="64" t="inlineStr">
-        <is>
-          <t>08/17/2026 request / 08/19/2026 reply – David Marquez</t>
-        </is>
-      </c>
-      <c r="H46" s="64" t="inlineStr">
-        <is>
-          <t>Cesar Vidal request to Department Managers (DR exercises 11/15/2025 and 02/21/2026; BCiC export attached) and David Marquez's signed reply.</t>
-        </is>
-      </c>
-      <c r="I46" s="64" t="inlineStr">
-        <is>
-          <t>1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
-        </is>
-      </c>
-      <c r="J46" s="64" t="inlineStr">
-        <is>
-          <t>B, H, J, L, O</t>
-        </is>
-      </c>
-      <c r="K46" s="64" t="inlineStr">
-        <is>
-          <t>Same as DMA02</t>
-        </is>
-      </c>
-      <c r="L46" s="82" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="64" t="inlineStr">
-        <is>
-          <t>E14a</t>
-        </is>
-      </c>
-      <c r="B47" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf</t>
-        </is>
-      </c>
-      <c r="C47" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
-        </is>
-      </c>
-      <c r="D47" s="64" t="inlineStr">
-        <is>
-          <t>attachment of E14</t>
-        </is>
-      </c>
-      <c r="E47" s="64" t="inlineStr">
-        <is>
-          <t>Data Integrity &amp; Email Testing Evidence.zip</t>
-        </is>
-      </c>
-      <c r="F47" s="64" t="inlineStr">
-        <is>
-          <t>Signed attestation</t>
-        </is>
-      </c>
-      <c r="G47" s="64" t="inlineStr">
-        <is>
-          <t>08/19/2026 – David Marquez</t>
-        </is>
-      </c>
-      <c r="H47" s="64" t="inlineStr">
-        <is>
-          <t>Signed attestation – OFAC Manager, BSA/AML-OFAC Compliance. States IT DR team facilitates DIV annually; 63 entries / 13 applications, all Y/Y/Y.</t>
-        </is>
-      </c>
-      <c r="I47" s="64" t="inlineStr">
-        <is>
-          <t>1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
-        </is>
-      </c>
-      <c r="J47" s="64" t="inlineStr">
-        <is>
-          <t>C, H, J, L, M, N, O, P</t>
-        </is>
-      </c>
-      <c r="K47" s="64" t="inlineStr">
-        <is>
-          <t>Identical to DMA02a</t>
-        </is>
-      </c>
-      <c r="L47" s="82" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="64" t="inlineStr">
-        <is>
-          <t>E15</t>
-        </is>
-      </c>
-      <c r="B48" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3_E15_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 1 (1).msg.eml</t>
-        </is>
-      </c>
-      <c r="C48" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
-        </is>
-      </c>
-      <c r="D48" s="64" t="inlineStr">
-        <is>
-          <t>RE_ Management Attestation … 1 (1).msg.eml</t>
-        </is>
-      </c>
-      <c r="E48" s="64" t="inlineStr">
-        <is>
-          <t>Data Integrity &amp; Email Testing Evidence.zip</t>
-        </is>
-      </c>
-      <c r="F48" s="64" t="inlineStr">
-        <is>
-          <t>Email attestation</t>
-        </is>
-      </c>
-      <c r="G48" s="64" t="inlineStr">
-        <is>
-          <t>08/17/2026 – Michelle Oropesa</t>
-        </is>
-      </c>
-      <c r="H48" s="64" t="inlineStr">
-        <is>
-          <t>Michelle Oropesa returns signed attestation.</t>
-        </is>
-      </c>
-      <c r="I48" s="64" t="inlineStr">
-        <is>
-          <t>4052, 1936, 1937</t>
-        </is>
-      </c>
-      <c r="J48" s="64" t="inlineStr">
-        <is>
-          <t>H, J, O</t>
-        </is>
-      </c>
-      <c r="K48" s="64" t="inlineStr">
-        <is>
-          <t>Same as DMA04</t>
-        </is>
-      </c>
-      <c r="L48" s="82" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="64" t="inlineStr">
-        <is>
-          <t>E15a</t>
-        </is>
-      </c>
-      <c r="B49" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3_E15a_Data_Integrity_Attestation_Santander-BCiC.pdf</t>
-        </is>
-      </c>
-      <c r="C49" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
-        </is>
-      </c>
-      <c r="D49" s="64" t="inlineStr">
-        <is>
-          <t>attachment of E15</t>
-        </is>
-      </c>
-      <c r="E49" s="64" t="inlineStr">
-        <is>
-          <t>Data Integrity &amp; Email Testing Evidence.zip</t>
-        </is>
-      </c>
-      <c r="F49" s="64" t="inlineStr">
-        <is>
-          <t>Signed attestation</t>
-        </is>
-      </c>
-      <c r="G49" s="64" t="inlineStr">
-        <is>
-          <t>08/17/2026 – Michelle Oropesa</t>
-        </is>
-      </c>
-      <c r="H49" s="64" t="inlineStr">
-        <is>
-          <t>Signed attestation – Investment Operations.</t>
-        </is>
-      </c>
-      <c r="I49" s="64" t="inlineStr">
-        <is>
-          <t>4052, 1936, 1937</t>
-        </is>
-      </c>
-      <c r="J49" s="64" t="inlineStr">
-        <is>
-          <t>H, J, O</t>
-        </is>
-      </c>
-      <c r="K49" s="64" t="inlineStr">
-        <is>
-          <t>Identical to DMA04a</t>
-        </is>
-      </c>
-      <c r="L49" s="82" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="64" t="inlineStr">
-        <is>
-          <t>E16</t>
-        </is>
-      </c>
-      <c r="B50" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3_E16_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 2 (1).msg.eml</t>
-        </is>
-      </c>
-      <c r="C50" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
-        </is>
-      </c>
-      <c r="D50" s="64" t="inlineStr">
-        <is>
-          <t>RE_ Management Attestation … 2 (1).msg.eml</t>
-        </is>
-      </c>
-      <c r="E50" s="64" t="inlineStr">
-        <is>
-          <t>Data Integrity &amp; Email Testing Evidence.zip</t>
-        </is>
-      </c>
-      <c r="F50" s="64" t="inlineStr">
-        <is>
-          <t>Email attestation</t>
-        </is>
-      </c>
-      <c r="G50" s="64" t="inlineStr">
-        <is>
-          <t>08/19/2026 – Maria Teresa Del Cerro</t>
-        </is>
-      </c>
-      <c r="H50" s="64" t="inlineStr">
-        <is>
-          <t>Signed attestation and BCiC export returned.</t>
-        </is>
-      </c>
-      <c r="I50" s="64" t="inlineStr">
-        <is>
-          <t>3299, 1903, 1937</t>
-        </is>
-      </c>
-      <c r="J50" s="64" t="inlineStr">
-        <is>
-          <t>H, J, O</t>
-        </is>
-      </c>
-      <c r="K50" s="64" t="inlineStr">
-        <is>
-          <t>Same as DMA05</t>
-        </is>
-      </c>
-      <c r="L50" s="82" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="64" t="inlineStr">
-        <is>
-          <t>E16a</t>
-        </is>
-      </c>
-      <c r="B51" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3_E16a_Data_Integrity_Attestation_Santander-BCiC.pdf</t>
-        </is>
-      </c>
-      <c r="C51" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
-        </is>
-      </c>
-      <c r="D51" s="64" t="inlineStr">
-        <is>
-          <t>attachment of E16</t>
-        </is>
-      </c>
-      <c r="E51" s="64" t="inlineStr">
-        <is>
-          <t>Data Integrity &amp; Email Testing Evidence.zip</t>
-        </is>
-      </c>
-      <c r="F51" s="64" t="inlineStr">
-        <is>
-          <t>Signed attestation</t>
-        </is>
-      </c>
-      <c r="G51" s="64" t="inlineStr">
-        <is>
-          <t>08/19/2026 – Maria Teresa Del Cerro Hontanilla</t>
-        </is>
-      </c>
-      <c r="H51" s="64" t="inlineStr">
-        <is>
-          <t>Signed attestation – Operations.</t>
-        </is>
-      </c>
-      <c r="I51" s="64" t="inlineStr">
-        <is>
-          <t>3299, 1903, 1937</t>
-        </is>
-      </c>
-      <c r="J51" s="64" t="inlineStr">
-        <is>
-          <t>H, J, O</t>
-        </is>
-      </c>
-      <c r="K51" s="64" t="inlineStr">
-        <is>
-          <t>Identical to DMA05a</t>
-        </is>
-      </c>
-      <c r="L51" s="82" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="64" t="inlineStr">
-        <is>
-          <t>E16b</t>
-        </is>
-      </c>
-      <c r="B52" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
-        </is>
-      </c>
-      <c r="C52" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
-        </is>
-      </c>
-      <c r="D52" s="64" t="inlineStr">
-        <is>
-          <t>attachment of E16</t>
-        </is>
-      </c>
-      <c r="E52" s="64" t="inlineStr">
-        <is>
-          <t>Data Integrity &amp; Email Testing Evidence.zip</t>
-        </is>
-      </c>
-      <c r="F52" s="64" t="inlineStr">
-        <is>
-          <t>BCiC export</t>
-        </is>
-      </c>
-      <c r="G52" s="64" t="inlineStr">
-        <is>
-          <t>08/2026 – BCiC export sent with attestation request</t>
-        </is>
-      </c>
-      <c r="H52" s="64" t="inlineStr">
-        <is>
-          <t>BCiC DIV export 2025-26 (64 rows; no manager columns) reviewed by managers with the attestation. Row numbers are Excel rows.</t>
-        </is>
-      </c>
-      <c r="I52" s="64" t="inlineStr">
-        <is>
-          <t>1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
-        </is>
-      </c>
-      <c r="J52" s="64" t="inlineStr">
-        <is>
-          <t>B, D, E, F, I, K, P</t>
-        </is>
-      </c>
-      <c r="K52" s="64" t="inlineStr">
-        <is>
-          <t>Identical to DMA05b</t>
-        </is>
-      </c>
-      <c r="L52" s="82" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="64" t="inlineStr">
-        <is>
-          <t>E17</t>
-        </is>
-      </c>
-      <c r="B53" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3_E17_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 3 (1).msg.eml</t>
-        </is>
-      </c>
-      <c r="C53" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
-        </is>
-      </c>
-      <c r="D53" s="64" t="inlineStr">
-        <is>
-          <t>RE_ Management Attestation … 3 (1).msg.eml</t>
-        </is>
-      </c>
-      <c r="E53" s="64" t="inlineStr">
-        <is>
-          <t>Data Integrity &amp; Email Testing Evidence.zip</t>
-        </is>
-      </c>
-      <c r="F53" s="64" t="inlineStr">
-        <is>
-          <t>Email attestation</t>
-        </is>
-      </c>
-      <c r="G53" s="64" t="inlineStr">
-        <is>
-          <t>08/18/2026 – Frank Puentes</t>
-        </is>
-      </c>
-      <c r="H53" s="64" t="inlineStr">
-        <is>
-          <t>Frank Puentes returns signed attestation.</t>
-        </is>
-      </c>
-      <c r="I53" s="64" t="inlineStr">
-        <is>
-          <t>3301, 1903, 1937</t>
-        </is>
-      </c>
-      <c r="J53" s="64" t="inlineStr">
-        <is>
-          <t>H, J, O</t>
-        </is>
-      </c>
-      <c r="K53" s="64" t="inlineStr">
-        <is>
-          <t>Same as DMA03 / MA02</t>
-        </is>
-      </c>
-      <c r="L53" s="82" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="64" t="inlineStr">
-        <is>
-          <t>E17a</t>
-        </is>
-      </c>
-      <c r="B54" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3_E17a_4069_001.pdf</t>
-        </is>
-      </c>
-      <c r="C54" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
-        </is>
-      </c>
-      <c r="D54" s="64" t="inlineStr">
-        <is>
-          <t>attachment of E17</t>
-        </is>
-      </c>
-      <c r="E54" s="64" t="inlineStr">
-        <is>
-          <t>Data Integrity &amp; Email Testing Evidence.zip</t>
-        </is>
-      </c>
-      <c r="F54" s="64" t="inlineStr">
-        <is>
-          <t>Signed attestation (scan)</t>
-        </is>
-      </c>
-      <c r="G54" s="64" t="inlineStr">
-        <is>
-          <t>08/18/2026 – Frank Puentes</t>
-        </is>
-      </c>
-      <c r="H54" s="64" t="inlineStr">
-        <is>
-          <t>Scanned signed attestation – Executive Director, Payments &amp; Cash Management.</t>
-        </is>
-      </c>
-      <c r="I54" s="64" t="inlineStr">
-        <is>
-          <t>3301, 1903, 1937</t>
-        </is>
-      </c>
-      <c r="J54" s="64" t="inlineStr">
-        <is>
-          <t>H, J, O</t>
-        </is>
-      </c>
-      <c r="K54" s="64" t="inlineStr">
-        <is>
-          <t>Identical to DMA03a</t>
-        </is>
-      </c>
-      <c r="L54" s="82" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="64" t="inlineStr">
-        <is>
-          <t>E07.01–E07.13</t>
-        </is>
-      </c>
-      <c r="B55" s="64" t="inlineStr">
         <is>
           <t>E07.01_FEDLINK INCOMING FEDWIRES 111425 0523PM.pdf
 E07.02_FEDLINK OUTGOING FEDWIRES 111425 0523PM.pdf
@@ -16927,60 +15641,60 @@
 E07.13_SWIFT INTERFACE MONITOR 111425 520PM 2ND SAMPLE.pdf</t>
         </is>
       </c>
-      <c r="C55" s="64" t="inlineStr">
+      <c r="C43" s="64" t="inlineStr">
         <is>
           <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\E07_Attachments_extracted</t>
         </is>
       </c>
-      <c r="D55" s="64" t="inlineStr">
+      <c r="D43" s="64" t="inlineStr">
         <is>
           <t>attachments of E07</t>
         </is>
       </c>
-      <c r="E55" s="64" t="inlineStr">
+      <c r="E43" s="64" t="inlineStr">
         <is>
           <t>Data Integrity &amp; Email Testing Evidence.zip</t>
         </is>
       </c>
-      <c r="F55" s="64" t="inlineStr">
+      <c r="F43" s="64" t="inlineStr">
         <is>
           <t>Report attachments (extracted)</t>
         </is>
       </c>
-      <c r="G55" s="64" t="inlineStr">
+      <c r="G43" s="64" t="inlineStr">
         <is>
           <t>11/15/2025 – Frank Puentes</t>
         </is>
       </c>
-      <c r="H55" s="64" t="inlineStr">
+      <c r="H43" s="64" t="inlineStr">
         <is>
           <t>Pre-DR 11/14/2025 source reports extracted from the email for direct review.</t>
         </is>
       </c>
-      <c r="I55" s="64" t="inlineStr">
+      <c r="I43" s="64" t="inlineStr">
         <is>
           <t>3301, 1903, 1936, 1937</t>
         </is>
       </c>
-      <c r="J55" s="64" t="inlineStr">
+      <c r="J43" s="64" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="K55" s="64" t="inlineStr">
+      <c r="K43" s="64" t="inlineStr">
         <is>
           <t>Attachments of E07</t>
         </is>
       </c>
-      <c r="L55" s="82" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="64" t="inlineStr">
+      <c r="L43" s="82" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="64" t="inlineStr">
         <is>
           <t>E08.01–E08.13</t>
         </is>
       </c>
-      <c r="B56" s="64" t="inlineStr">
+      <c r="B44" s="64" t="inlineStr">
         <is>
           <t>E08.01_FEDLINK INCOMING FEDWIRES 111425 -1115 1148AM.pdf
 E08.02_FEDLINK OUTGOINT TRANSFERS 114125 - 111525 1144AM.pdf
@@ -16997,59 +15711,451 @@
 E08.13_SWIFT INTERFACE MONITOR INCOMING MT199 111425 -111525 1152AM.pdf</t>
         </is>
       </c>
+      <c r="C44" s="64" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\E08_Attachments_extracted</t>
+        </is>
+      </c>
+      <c r="D44" s="64" t="inlineStr">
+        <is>
+          <t>attachments of E08</t>
+        </is>
+      </c>
+      <c r="E44" s="64" t="inlineStr">
+        <is>
+          <t>Data Integrity &amp; Email Testing Evidence.zip</t>
+        </is>
+      </c>
+      <c r="F44" s="64" t="inlineStr">
+        <is>
+          <t>Report attachments (extracted)</t>
+        </is>
+      </c>
+      <c r="G44" s="64" t="inlineStr">
+        <is>
+          <t>11/15/2025 – Frank Puentes</t>
+        </is>
+      </c>
+      <c r="H44" s="64" t="inlineStr">
+        <is>
+          <t>DR test-day 11/15/2025 comparison reports extracted from the email for direct review.</t>
+        </is>
+      </c>
+      <c r="I44" s="64" t="inlineStr">
+        <is>
+          <t>3301, 1903, 1936, 1937</t>
+        </is>
+      </c>
+      <c r="J44" s="64" t="inlineStr">
+        <is>
+          <t>F, M</t>
+        </is>
+      </c>
+      <c r="K44" s="64" t="inlineStr">
+        <is>
+          <t>Attachments of E08</t>
+        </is>
+      </c>
+      <c r="L44" s="82" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="82" t="n"/>
+      <c r="B45" s="82" t="n"/>
+      <c r="C45" s="82" t="n"/>
+      <c r="D45" s="82" t="n"/>
+      <c r="E45" s="82" t="n"/>
+      <c r="F45" s="82" t="n"/>
+      <c r="G45" s="82" t="n"/>
+      <c r="H45" s="82" t="n"/>
+      <c r="I45" s="82" t="n"/>
+      <c r="J45" s="82" t="n"/>
+      <c r="K45" s="82" t="n"/>
+      <c r="L45" s="82" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="60" t="inlineStr">
+        <is>
+          <t>Duplicate files removed from the repository (one copy of each retained)</t>
+        </is>
+      </c>
+      <c r="B46" s="82" t="n"/>
+      <c r="C46" s="82" t="n"/>
+      <c r="D46" s="82" t="n"/>
+      <c r="E46" s="82" t="n"/>
+      <c r="F46" s="82" t="n"/>
+      <c r="G46" s="82" t="n"/>
+      <c r="H46" s="82" t="n"/>
+      <c r="I46" s="82" t="n"/>
+      <c r="J46" s="82" t="n"/>
+      <c r="K46" s="82" t="n"/>
+      <c r="L46" s="82" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Removed ref</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Former location</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Retained ref</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Retained file location</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+      <c r="F47" s="82" t="n"/>
+      <c r="G47" s="82" t="n"/>
+      <c r="H47" s="82" t="n"/>
+      <c r="I47" s="82" t="n"/>
+      <c r="J47" s="82" t="n"/>
+      <c r="K47" s="82" t="n"/>
+      <c r="L47" s="82" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="64" t="inlineStr">
+        <is>
+          <t>MA02</t>
+        </is>
+      </c>
+      <c r="B48" s="64" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg</t>
+        </is>
+      </c>
+      <c r="C48" s="64" t="inlineStr">
+        <is>
+          <t>DMA03</t>
+        </is>
+      </c>
+      <c r="D48" s="64" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
+        </is>
+      </c>
+      <c r="E48" s="64" t="inlineStr">
+        <is>
+          <t>same email message (subject, sent 08/18/2026 14:50, attachment 4069_001.pdf)</t>
+        </is>
+      </c>
+      <c r="F48" s="82" t="n"/>
+      <c r="G48" s="82" t="n"/>
+      <c r="H48" s="82" t="n"/>
+      <c r="I48" s="82" t="n"/>
+      <c r="J48" s="82" t="n"/>
+      <c r="K48" s="82" t="n"/>
+      <c r="L48" s="82" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="64" t="inlineStr">
+        <is>
+          <t>DMA05b</t>
+        </is>
+      </c>
+      <c r="B49" s="64" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05b_Operations (Governance &amp; Static Data, Multi-Family Office) - All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
+        </is>
+      </c>
+      <c r="C49" s="64" t="inlineStr">
+        <is>
+          <t>E16b</t>
+        </is>
+      </c>
+      <c r="D49" s="64" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
+        </is>
+      </c>
+      <c r="E49" s="64" t="inlineStr">
+        <is>
+          <t>byte-identical file (MD5 match)</t>
+        </is>
+      </c>
+      <c r="F49" s="82" t="n"/>
+      <c r="G49" s="82" t="n"/>
+      <c r="H49" s="82" t="n"/>
+      <c r="I49" s="82" t="n"/>
+      <c r="J49" s="82" t="n"/>
+      <c r="K49" s="82" t="n"/>
+      <c r="L49" s="82" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="64" t="inlineStr">
+        <is>
+          <t>E11</t>
+        </is>
+      </c>
+      <c r="B50" s="64" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E11_BSI.IT.6.C7.3 Manager Approval.msg</t>
+        </is>
+      </c>
+      <c r="C50" s="64" t="inlineStr">
+        <is>
+          <t>E10</t>
+        </is>
+      </c>
+      <c r="D50" s="64" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg</t>
+        </is>
+      </c>
+      <c r="E50" s="64" t="inlineStr">
+        <is>
+          <t>same email message (sent 03/09/2026 18:43) saved twice</t>
+        </is>
+      </c>
+      <c r="F50" s="82" t="n"/>
+      <c r="G50" s="82" t="n"/>
+      <c r="H50" s="82" t="n"/>
+      <c r="I50" s="82" t="n"/>
+      <c r="J50" s="82" t="n"/>
+      <c r="K50" s="82" t="n"/>
+      <c r="L50" s="82" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="64" t="inlineStr">
+        <is>
+          <t>E12</t>
+        </is>
+      </c>
+      <c r="B51" s="64" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E12_RE_ Testing enviroment Financial Analysis manager approval.msg</t>
+        </is>
+      </c>
+      <c r="C51" s="64" t="inlineStr">
+        <is>
+          <t>BLA06</t>
+        </is>
+      </c>
+      <c r="D51" s="64" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg</t>
+        </is>
+      </c>
+      <c r="E51" s="64" t="inlineStr">
+        <is>
+          <t>same email message (sent 01/26/2026 20:43)</t>
+        </is>
+      </c>
+      <c r="F51" s="82" t="n"/>
+      <c r="G51" s="82" t="n"/>
+      <c r="H51" s="82" t="n"/>
+      <c r="I51" s="82" t="n"/>
+      <c r="J51" s="82" t="n"/>
+      <c r="K51" s="82" t="n"/>
+      <c r="L51" s="82" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="64" t="inlineStr">
+        <is>
+          <t>E14</t>
+        </is>
+      </c>
+      <c r="B52" s="64" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml</t>
+        </is>
+      </c>
+      <c r="C52" s="64" t="inlineStr">
+        <is>
+          <t>DMA02</t>
+        </is>
+      </c>
+      <c r="D52" s="64" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg</t>
+        </is>
+      </c>
+      <c r="E52" s="64" t="inlineStr">
+        <is>
+          <t>same email message saved as .eml</t>
+        </is>
+      </c>
+      <c r="F52" s="82" t="n"/>
+      <c r="G52" s="82" t="n"/>
+      <c r="H52" s="82" t="n"/>
+      <c r="I52" s="82" t="n"/>
+      <c r="J52" s="82" t="n"/>
+      <c r="K52" s="82" t="n"/>
+      <c r="L52" s="82" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="64" t="inlineStr">
+        <is>
+          <t>E14a</t>
+        </is>
+      </c>
+      <c r="B53" s="64" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf</t>
+        </is>
+      </c>
+      <c r="C53" s="64" t="inlineStr">
+        <is>
+          <t>DMA02a</t>
+        </is>
+      </c>
+      <c r="D53" s="64" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf</t>
+        </is>
+      </c>
+      <c r="E53" s="64" t="inlineStr">
+        <is>
+          <t>byte-identical file (MD5 match)</t>
+        </is>
+      </c>
+      <c r="F53" s="82" t="n"/>
+      <c r="G53" s="82" t="n"/>
+      <c r="H53" s="82" t="n"/>
+      <c r="I53" s="82" t="n"/>
+      <c r="J53" s="82" t="n"/>
+      <c r="K53" s="82" t="n"/>
+      <c r="L53" s="82" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="64" t="inlineStr">
+        <is>
+          <t>E15</t>
+        </is>
+      </c>
+      <c r="B54" s="64" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 1 (1).msg.eml</t>
+        </is>
+      </c>
+      <c r="C54" s="64" t="inlineStr">
+        <is>
+          <t>DMA04</t>
+        </is>
+      </c>
+      <c r="D54" s="64" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
+        </is>
+      </c>
+      <c r="E54" s="64" t="inlineStr">
+        <is>
+          <t>same email message saved as .eml</t>
+        </is>
+      </c>
+      <c r="F54" s="82" t="n"/>
+      <c r="G54" s="82" t="n"/>
+      <c r="H54" s="82" t="n"/>
+      <c r="I54" s="82" t="n"/>
+      <c r="J54" s="82" t="n"/>
+      <c r="K54" s="82" t="n"/>
+      <c r="L54" s="82" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="64" t="inlineStr">
+        <is>
+          <t>E15a</t>
+        </is>
+      </c>
+      <c r="B55" s="64" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15a_Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+        </is>
+      </c>
+      <c r="C55" s="64" t="inlineStr">
+        <is>
+          <t>DMA04a</t>
+        </is>
+      </c>
+      <c r="D55" s="64" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+        </is>
+      </c>
+      <c r="E55" s="64" t="inlineStr">
+        <is>
+          <t>byte-identical file (MD5 match)</t>
+        </is>
+      </c>
+      <c r="F55" s="82" t="n"/>
+      <c r="G55" s="82" t="n"/>
+      <c r="H55" s="82" t="n"/>
+      <c r="I55" s="82" t="n"/>
+      <c r="J55" s="82" t="n"/>
+      <c r="K55" s="82" t="n"/>
+      <c r="L55" s="82" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="64" t="inlineStr">
+        <is>
+          <t>E16</t>
+        </is>
+      </c>
+      <c r="B56" s="64" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 2 (1).msg.eml</t>
+        </is>
+      </c>
       <c r="C56" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\E08_Attachments_extracted</t>
+          <t>DMA05</t>
         </is>
       </c>
       <c r="D56" s="64" t="inlineStr">
         <is>
-          <t>attachments of E08</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
         </is>
       </c>
       <c r="E56" s="64" t="inlineStr">
         <is>
-          <t>Data Integrity &amp; Email Testing Evidence.zip</t>
-        </is>
-      </c>
-      <c r="F56" s="64" t="inlineStr">
-        <is>
-          <t>Report attachments (extracted)</t>
-        </is>
-      </c>
-      <c r="G56" s="64" t="inlineStr">
-        <is>
-          <t>11/15/2025 – Frank Puentes</t>
-        </is>
-      </c>
-      <c r="H56" s="64" t="inlineStr">
-        <is>
-          <t>DR test-day 11/15/2025 comparison reports extracted from the email for direct review.</t>
-        </is>
-      </c>
-      <c r="I56" s="64" t="inlineStr">
-        <is>
-          <t>3301, 1903, 1936, 1937</t>
-        </is>
-      </c>
-      <c r="J56" s="64" t="inlineStr">
-        <is>
-          <t>F, M</t>
-        </is>
-      </c>
-      <c r="K56" s="64" t="inlineStr">
-        <is>
-          <t>Attachments of E08</t>
-        </is>
-      </c>
+          <t>same email message saved as .eml</t>
+        </is>
+      </c>
+      <c r="F56" s="82" t="n"/>
+      <c r="G56" s="82" t="n"/>
+      <c r="H56" s="82" t="n"/>
+      <c r="I56" s="82" t="n"/>
+      <c r="J56" s="82" t="n"/>
+      <c r="K56" s="82" t="n"/>
       <c r="L56" s="82" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="82" t="n"/>
-      <c r="B57" s="82" t="n"/>
-      <c r="C57" s="82" t="n"/>
-      <c r="D57" s="82" t="n"/>
-      <c r="E57" s="82" t="n"/>
+      <c r="A57" s="64" t="inlineStr">
+        <is>
+          <t>E16a</t>
+        </is>
+      </c>
+      <c r="B57" s="64" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16a_Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+        </is>
+      </c>
+      <c r="C57" s="64" t="inlineStr">
+        <is>
+          <t>DMA05a</t>
+        </is>
+      </c>
+      <c r="D57" s="64" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+        </is>
+      </c>
+      <c r="E57" s="64" t="inlineStr">
+        <is>
+          <t>byte-identical file (MD5 match)</t>
+        </is>
+      </c>
       <c r="F57" s="82" t="n"/>
       <c r="G57" s="82" t="n"/>
       <c r="H57" s="82" t="n"/>
@@ -17059,11 +16165,31 @@
       <c r="L57" s="82" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="82" t="n"/>
-      <c r="B58" s="82" t="n"/>
-      <c r="C58" s="82" t="n"/>
-      <c r="D58" s="82" t="n"/>
-      <c r="E58" s="82" t="n"/>
+      <c r="A58" s="64" t="inlineStr">
+        <is>
+          <t>E17</t>
+        </is>
+      </c>
+      <c r="B58" s="64" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 3 (1).msg.eml</t>
+        </is>
+      </c>
+      <c r="C58" s="64" t="inlineStr">
+        <is>
+          <t>DMA03</t>
+        </is>
+      </c>
+      <c r="D58" s="64" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
+        </is>
+      </c>
+      <c r="E58" s="64" t="inlineStr">
+        <is>
+          <t>same email message saved as .eml</t>
+        </is>
+      </c>
       <c r="F58" s="82" t="n"/>
       <c r="G58" s="82" t="n"/>
       <c r="H58" s="82" t="n"/>
@@ -17073,11 +16199,31 @@
       <c r="L58" s="82" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="82" t="n"/>
-      <c r="B59" s="82" t="n"/>
-      <c r="C59" s="82" t="n"/>
-      <c r="D59" s="82" t="n"/>
-      <c r="E59" s="82" t="n"/>
+      <c r="A59" s="64" t="inlineStr">
+        <is>
+          <t>E17a</t>
+        </is>
+      </c>
+      <c r="B59" s="64" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17a_4069_001.pdf</t>
+        </is>
+      </c>
+      <c r="C59" s="64" t="inlineStr">
+        <is>
+          <t>DMA03a</t>
+        </is>
+      </c>
+      <c r="D59" s="64" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf</t>
+        </is>
+      </c>
+      <c r="E59" s="64" t="inlineStr">
+        <is>
+          <t>byte-identical file (MD5 match)</t>
+        </is>
+      </c>
       <c r="F59" s="82" t="n"/>
       <c r="G59" s="82" t="n"/>
       <c r="H59" s="82" t="n"/>
@@ -17941,7 +17087,7 @@
       <c r="L120" s="82" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:K56"/>
+  <autoFilter ref="A2:K44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/BSI.IT.6.C7.3-Evidences/BSI.IT.6.C7.3_E00_Workpaper_DR_DIV_INTEGRATED_APPLICATION_Evidence.xlsx
+++ b/BSI.IT.6.C7.3-Evidences/BSI.IT.6.C7.3_E00_Workpaper_DR_DIV_INTEGRATED_APPLICATION_Evidence.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BSI.IT.6.C7.3 Evidence Index" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'BSI.IT.6.C7.3 Evidence Index'!$A$2:$K$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'BSI.IT.6.C7.3 Evidence Index'!$A$2:$K$33</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -2393,7 +2393,7 @@
       <c r="BM4" s="58" t="n"/>
       <c r="BN4" s="58" t="n"/>
     </row>
-    <row r="5" ht="380" customFormat="1" customHeight="1" s="47">
+    <row r="5" ht="332" customFormat="1" customHeight="1" s="47">
       <c r="A5" s="45" t="n">
         <v>1822</v>
       </c>
@@ -2414,7 +2414,7 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 3 – 2025 DR Test Scope = True, Exercise Date 12/11/2025
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 47 – Business Data Validation Date 11/15/2025
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 Background: 'the IT DR team facilitates, on an annual basis, data integrity validation testing'</t>
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §1 Background: 'the IT DR team facilitates, on an annual basis, data integrity validation testing'</t>
         </is>
       </c>
       <c r="D5" s="45" t="inlineStr">
@@ -2464,8 +2464,7 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 47 – 'Department Manager Approval Date' and 'Attestation Date' columns
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-• DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-• DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf</t>
+• DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
         </is>
       </c>
       <c r="I5" s="45" t="inlineStr">
@@ -2481,11 +2480,10 @@
       <c r="J5" s="45" t="inlineStr">
         <is>
           <t>Yes – application-specific business line manager approval evidence obtained for every DIV record:
-Claudia Romero: E09 email "Approved." 05/05/2026 (Client Back Office results); DMA01/DMA01a signed attestation 08/18/2026
+Claudia Romero: E09 email "Approved." 05/05/2026 (Client Back Office results); DMA01 email with attached signed attestation 08/18/2026
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-• DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-• DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf</t>
+• DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
         </is>
       </c>
       <c r="K5" s="46" t="inlineStr">
@@ -2506,8 +2504,7 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 3 – Exercise Date 12/11/2025 / 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 47 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
-• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026; attached signed attestation §1 – DIV facilitated on an annual basis
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – dated 11/15/2025</t>
         </is>
       </c>
@@ -2515,9 +2512,8 @@
         <is>
           <t>PASS – The IT DR team (IT Business Control, Governance &amp; PMO – Elizabeth Noda) facilitated the Data Integrity Validation: application list/BIA review, DIV test scripts issued to the business, evidence collected and results recorded in BCiC. The business-line tester(s) executed the validation during the 11/15/2025 DR exercise.
 Evidence location (BSI.IT.6.C7.3-Evidences):
-• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review 09/15/2025
-• E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – follow-up 09/18/2025
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
+• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review (invite 09/15/2025, re-sent 09/18/2025)
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg – IT DR (Elizabeth Noda) issued test script, collected evidence and requested approval
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 47 – Y/N Format, Headers, Content = Y</t>
@@ -2531,8 +2527,7 @@
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 3 – 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
-• E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – BIA results &amp; applications list review
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §2 – application listed among the 13 in-scope applications that store business data
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg – scope table: application → Client Back Office → Claudia Romero</t>
         </is>
       </c>
@@ -2543,7 +2538,6 @@
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – business line DIV results document – 11/15/2025 – Client Back Office (operator Raimy Ayala)
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
 • DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-• DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 47 – Department Manager / Approval Date / Attestation fields</t>
         </is>
       </c>
@@ -2554,7 +2548,7 @@
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 47
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – row 48
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – BCiC report screen (record on a later page of the 66-item report)
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="Q5" s="49" t="inlineStr">
@@ -2573,16 +2567,13 @@
 BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf
 [03 DIV Manager Attestation Email Approvals]
 DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
 DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 [04 Data Integrity &amp; Email Testing Evidence]
 E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx
 E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg
 E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls
 E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
-E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml
 E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
 E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
         </is>
@@ -2640,7 +2631,7 @@
       <c r="BM5" s="58" t="n"/>
       <c r="BN5" s="58" t="n"/>
     </row>
-    <row r="6" ht="380" customFormat="1" customHeight="1" s="39">
+    <row r="6" ht="332" customFormat="1" customHeight="1" s="39">
       <c r="A6" s="45" t="n">
         <v>1867</v>
       </c>
@@ -2661,7 +2652,7 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 19 – 2025 DR Test Scope = True, Exercise Date 12/11/2025
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 9 – Business Data Validation Date 11/15/2025
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 Background: 'the IT DR team facilitates, on an annual basis, data integrity validation testing'</t>
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §1 Background: 'the IT DR team facilitates, on an annual basis, data integrity validation testing'</t>
         </is>
       </c>
       <c r="D6" s="45" t="inlineStr">
@@ -2715,8 +2706,7 @@
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 9 – 'Department Manager Approval Date' and 'Attestation Date' columns
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – Department Manager Approval Date column
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-• DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-• DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf</t>
+• DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
         </is>
       </c>
       <c r="I6" s="45" t="inlineStr">
@@ -2732,11 +2722,10 @@
       <c r="J6" s="45" t="inlineStr">
         <is>
           <t>Yes – application-specific business line manager approval evidence obtained for every DIV record:
-Claudia Romero: E09 email "Approved." 05/05/2026 (Client Back Office results); DMA01/DMA01a signed attestation 08/18/2026
+Claudia Romero: E09 email "Approved." 05/05/2026 (Client Back Office results); DMA01 email with attached signed attestation 08/18/2026
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-• DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-• DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf</t>
+• DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
         </is>
       </c>
       <c r="K6" s="46" t="inlineStr">
@@ -2757,8 +2746,7 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 19 – Exercise Date 12/11/2025 / 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 9 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
-• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026; attached signed attestation §1 – DIV facilitated on an annual basis
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – dated 11/15/2025</t>
         </is>
       </c>
@@ -2766,9 +2754,8 @@
         <is>
           <t>PASS – The IT DR team (IT Business Control, Governance &amp; PMO – Elizabeth Noda) facilitated the Data Integrity Validation: application list/BIA review, DIV test scripts issued to the business, evidence collected and results recorded in BCiC. The business-line tester(s) executed the validation during the 11/15/2025 DR exercise.
 Evidence location (BSI.IT.6.C7.3-Evidences):
-• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review 09/15/2025
-• E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – follow-up 09/18/2025
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
+• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review (invite 09/15/2025, re-sent 09/18/2025)
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg – IT DR (Elizabeth Noda) issued test script, collected evidence and requested approval
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 9 – Y/N Format, Headers, Content = Y</t>
@@ -2782,8 +2769,7 @@
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 19 – 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
-• E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – BIA results &amp; applications list review
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §2 – application listed among the 13 in-scope applications that store business data
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg – scope table: application → Client Back Office → Claudia Romero</t>
         </is>
       </c>
@@ -2794,7 +2780,6 @@
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – business line DIV results document – 11/15/2025 – Client Back Office (operator Raimy Ayala)
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
 • DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-• DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 9 – Department Manager / Approval Date / Attestation fields</t>
         </is>
       </c>
@@ -2805,7 +2790,7 @@
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 9
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – row 9
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – record(s) visible on screen
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="Q6" s="49" t="inlineStr">
@@ -2824,16 +2809,13 @@
 BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf
 [03 DIV Manager Attestation Email Approvals]
 DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
 DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 [04 Data Integrity &amp; Email Testing Evidence]
 E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx
 E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg
 E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls
 E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
-E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml
 E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
 E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
         </is>
@@ -2891,7 +2873,7 @@
       <c r="BM6" s="58" t="n"/>
       <c r="BN6" s="58" t="n"/>
     </row>
-    <row r="7" ht="380" customFormat="1" customHeight="1" s="39">
+    <row r="7" ht="332" customFormat="1" customHeight="1" s="39">
       <c r="A7" s="45" t="n">
         <v>1868</v>
       </c>
@@ -2912,7 +2894,7 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 20 – 2025 DR Test Scope = True, Exercise Date 12/11/2025
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 10 – Business Data Validation Date 11/15/2025
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 Background: 'the IT DR team facilitates, on an annual basis, data integrity validation testing'</t>
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §1 Background: 'the IT DR team facilitates, on an annual basis, data integrity validation testing'</t>
         </is>
       </c>
       <c r="D7" s="45" t="inlineStr">
@@ -2966,8 +2948,7 @@
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 10 – 'Department Manager Approval Date' and 'Attestation Date' columns
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – Department Manager Approval Date column
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-• DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-• DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf</t>
+• DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
         </is>
       </c>
       <c r="I7" s="45" t="inlineStr">
@@ -2983,11 +2964,10 @@
       <c r="J7" s="45" t="inlineStr">
         <is>
           <t>Yes – application-specific business line manager approval evidence obtained for every DIV record:
-Claudia Romero: E09 email "Approved." 05/05/2026 (Client Back Office results); DMA01/DMA01a signed attestation 08/18/2026
+Claudia Romero: E09 email "Approved." 05/05/2026 (Client Back Office results); DMA01 email with attached signed attestation 08/18/2026
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-• DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-• DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf</t>
+• DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
         </is>
       </c>
       <c r="K7" s="46" t="inlineStr">
@@ -3008,8 +2988,7 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 20 – Exercise Date 12/11/2025 / 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 10 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
-• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026; attached signed attestation §1 – DIV facilitated on an annual basis
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – dated 11/15/2025</t>
         </is>
       </c>
@@ -3017,9 +2996,8 @@
         <is>
           <t>PASS – The IT DR team (IT Business Control, Governance &amp; PMO – Elizabeth Noda) facilitated the Data Integrity Validation: application list/BIA review, DIV test scripts issued to the business, evidence collected and results recorded in BCiC. The business-line tester(s) executed the validation during the 11/15/2025 DR exercise.
 Evidence location (BSI.IT.6.C7.3-Evidences):
-• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review 09/15/2025
-• E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – follow-up 09/18/2025
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
+• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review (invite 09/15/2025, re-sent 09/18/2025)
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg – IT DR (Elizabeth Noda) issued test script, collected evidence and requested approval
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 10 – Y/N Format, Headers, Content = Y</t>
@@ -3033,8 +3011,7 @@
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 20 – 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
-• E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – BIA results &amp; applications list review
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §2 – application listed among the 13 in-scope applications that store business data
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg – scope table: application → Client Back Office → Claudia Romero</t>
         </is>
       </c>
@@ -3045,7 +3022,6 @@
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – business line DIV results document – 11/15/2025 – Client Back Office (operator Raimy Ayala)
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
 • DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-• DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 10 – Department Manager / Approval Date / Attestation fields</t>
         </is>
       </c>
@@ -3056,7 +3032,7 @@
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 10
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – row 10
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – record(s) visible on screen
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="Q7" s="49" t="inlineStr">
@@ -3074,16 +3050,13 @@
 BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf
 [03 DIV Manager Attestation Email Approvals]
 DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
 DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 [04 Data Integrity &amp; Email Testing Evidence]
 E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx
 E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg
 E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls
 E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
-E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml
 E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
 E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
         </is>
@@ -3163,7 +3136,7 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 24 – 2025 DR Test Scope = True, Exercise Date 11/15/2025
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 5, 11, 13, 51, 53, 57 – Business Data Validation Date 11/15/2025
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 Background: 'the IT DR team facilitates, on an annual basis, data integrity validation testing'</t>
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §1 Background: 'the IT DR team facilitates, on an annual basis, data integrity validation testing'</t>
         </is>
       </c>
       <c r="D8" s="45" t="inlineStr">
@@ -3217,12 +3190,10 @@
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 5, 11, 13, 51, 53, 57 – 'Department Manager' column
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – Department Manager column
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
 • DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
 • DMA11 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
-• DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-• DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+• DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
         </is>
       </c>
       <c r="H8" s="45" t="inlineStr">
@@ -3235,13 +3206,10 @@
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 5, 11, 13, 51, 53, 57 – 'Department Manager Approval Date' and 'Attestation Date' columns
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – Department Manager Approval Date column
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
 • DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-• DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
 • DMA11 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
-• DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-• DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+• DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
         </is>
       </c>
       <c r="I8" s="45" t="inlineStr">
@@ -3263,19 +3231,16 @@
       <c r="J8" s="45" t="inlineStr">
         <is>
           <t>Yes – application-specific business line manager approval evidence obtained for every DIV record:
-David Marquez: DMA02 email + DMA02a signed attestation 08/19/2026
-Claudia Romero: E09 email "Approved." 05/05/2026 (Client Back Office results); DMA01/DMA01a signed attestation 08/18/2026
+David Marquez: DMA02 email with attached signed attestation 08/19/2026
+Claudia Romero: E09 email "Approved." 05/05/2026 (Client Back Office results); DMA01 email with attached signed attestation 08/18/2026
 Miguel Orozco: DMA11 email "I approve the integrity validation…" 09/09/2026
-Maria del Cerro Hontanilla: DMA05 email + DMA05a signed attestation 08/19/2026
+Maria del Cerro Hontanilla: DMA05 email with attached signed attestation 08/19/2026
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
 • DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-• DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
 • DMA11 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
-• DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-• DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+• DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
         </is>
       </c>
       <c r="K8" s="46" t="inlineStr">
@@ -3296,8 +3261,7 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 24 – Exercise Date 11/15/2025 / 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 5, 11, 13, 51, 53, 57 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
-• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026; attached signed attestation §1 – DIV facilitated on an annual basis
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – dated 11/15/2025
 • BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf – dated 11/15/2025</t>
         </is>
@@ -3306,9 +3270,8 @@
         <is>
           <t>PASS – The IT DR team (IT Business Control, Governance &amp; PMO – Elizabeth Noda) facilitated the Data Integrity Validation: application list/BIA review, DIV test scripts issued to the business, evidence collected and results recorded in BCiC. The business-line tester(s) executed the validation during the 11/15/2025 DR exercise.
 Evidence location (BSI.IT.6.C7.3-Evidences):
-• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review 09/15/2025
-• E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – follow-up 09/18/2025
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
+• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review (invite 09/15/2025, re-sent 09/18/2025)
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg – IT DR (Elizabeth Noda) issued test script, collected evidence and requested approval
@@ -3323,8 +3286,7 @@
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 24 – 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
-• E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – BIA results &amp; applications list review
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §2 – application listed among the 13 in-scope applications that store business data
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg – scope table: application → Client Back Office → Claudia Romero</t>
         </is>
       </c>
@@ -3335,13 +3297,10 @@
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – business line DIV results document – 11/15/2025 – Client Back Office (operator Raimy Ayala)
 • BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf – business line DIV results document – 11/15/2025 – BSA/AML/OFAC Compliance (operator David Marquez)
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
 • DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-• DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
 • DMA11 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
 • DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-• DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 5, 11, 13, 51, 53, 57 – Department Manager / Approval Date / Attestation fields</t>
         </is>
       </c>
@@ -3352,17 +3311,17 @@
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 5, 11, 13, 51, 53, 57
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – rows 5, 11, 13, 52, 54, 58
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – record(s) visible on screen
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="Q8" s="49" t="inlineStr">
         <is>
           <t>PASS – all five control attributes satisfied (Annual Testing Executed, DIV Performed by IT DR Team, Applications in Scope Identified, Business Line Approval of Results, Results Documented in BCMS).
 Observations (do not change the attribute conclusions – reviewer to confirm):
-1. Timing – Miguel Orozco: 1 record(s), BCiC approval 09/09/2026; Maria del Cerro Hontanilla: 2 record(s), BCiC approval 08/19/2026 – business line approval obtained after the review period end (06/01/2026) through retrospective management attestation (DMA02a §3.6 commits to contemporaneous approval going forward).
+1. Timing – Miguel Orozco: 1 record(s), BCiC approval 09/09/2026; Maria del Cerro Hontanilla: 2 record(s), BCiC approval 08/19/2026 – business line approval obtained after the review period end (06/01/2026) through retrospective management attestation (DMA02 attachment §3.6 commits to contemporaneous approval going forward).
 2. Approval evidence – David Marquez: 1 record(s), BCiC approval 11/15/2025 (in period) confirmed by signed attestation 08/19/2026 – no contemporaneous approval email for the BCiC approval date is in the package; approval is confirmed retrospectively.
 3. Segregation – business tester and approving manager are the same person for: David Marquez, Miguel Orozco.
-4. Results document – BLA02 (BSA/AML/OFAC) DIV Yes/No boxes are blank; mitigated by BLA02 production vs test-day screenshots, BCiC Y/Y/Y (E03) and David Marquez signed attestation (DMA02a).</t>
+4. Results document – BLA02 (BSA/AML/OFAC) DIV Yes/No boxes are blank; mitigated by BLA02 production vs test-day screenshots, BCiC Y/Y/Y (E03) and David Marquez signed attestation (DMA02 attachment).</t>
         </is>
       </c>
       <c r="R8" s="43" t="inlineStr">
@@ -3374,11 +3333,8 @@
 BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf
 [03 DIV Manager Attestation Email Approvals]
 DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
 DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf
 DMA11 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
 [04 Data Integrity &amp; Email Testing Evidence]
 E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx
@@ -3386,7 +3342,6 @@
 E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls
 E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
-E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml
 E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
 E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
         </is>
@@ -3444,7 +3399,7 @@
       <c r="BM8" s="58" t="n"/>
       <c r="BN8" s="58" t="n"/>
     </row>
-    <row r="9" ht="356" customFormat="1" customHeight="1" s="39">
+    <row r="9" ht="296" customFormat="1" customHeight="1" s="39">
       <c r="A9" s="45" t="n">
         <v>4052</v>
       </c>
@@ -3465,7 +3420,7 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 25 – 2025 DR Test Scope = True, Exercise Date 11/15/2025
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 61 – Business Data Validation Date 11/15/2025
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 Background: 'the IT DR team facilitates, on an annual basis, data integrity validation testing'</t>
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §1 Background: 'the IT DR team facilitates, on an annual basis, data integrity validation testing'</t>
         </is>
       </c>
       <c r="D9" s="45" t="inlineStr">
@@ -3504,8 +3459,7 @@
           <t>Michelle Oropesa (Investment Operations) – E03 row 61
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 61 – 'Department Manager' column
-• DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-• DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+• DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
         </is>
       </c>
       <c r="H9" s="45" t="inlineStr">
@@ -3513,8 +3467,7 @@
           <t>Michelle Oropesa: BCiC approval 08/17/2026; approval evidence 08/17/2026
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 61 – 'Department Manager Approval Date' and 'Attestation Date' columns
-• DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-• DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+• DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
         </is>
       </c>
       <c r="I9" s="45" t="inlineStr">
@@ -3530,10 +3483,9 @@
       <c r="J9" s="45" t="inlineStr">
         <is>
           <t>Yes – application-specific business line manager approval evidence obtained for every DIV record:
-Michelle Oropesa: DMA04 email + DMA04a signed attestation 08/17/2026
+Michelle Oropesa: DMA04 email with attached signed attestation 08/17/2026
 Evidence location (BSI.IT.6.C7.3-Evidences):
-• DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-• DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+• DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
         </is>
       </c>
       <c r="K9" s="46" t="inlineStr">
@@ -3554,8 +3506,7 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 25 – Exercise Date 11/15/2025 / 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 61 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
-• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026; attached signed attestation §1 – DIV facilitated on an annual basis
 • BLA04 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx – dated 11/15/2025</t>
         </is>
       </c>
@@ -3563,9 +3514,8 @@
         <is>
           <t>PASS – The IT DR team (IT Business Control, Governance &amp; PMO – Elizabeth Noda) facilitated the Data Integrity Validation: application list/BIA review, DIV test scripts issued to the business, evidence collected and results recorded in BCiC. The business-line tester(s) executed the validation during the 11/15/2025 DR exercise.
 Evidence location (BSI.IT.6.C7.3-Evidences):
-• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review 09/15/2025
-• E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – follow-up 09/18/2025
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
+• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review (invite 09/15/2025, re-sent 09/18/2025)
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
 • BLA04 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx – IT DR test script completed by the business-line tester
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 61 – Y/N Format, Headers, Content = Y</t>
         </is>
@@ -3578,8 +3528,7 @@
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 25 – 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
-• E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – BIA results &amp; applications list review
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data</t>
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §2 – application listed among the 13 in-scope applications that store business data</t>
         </is>
       </c>
       <c r="O9" s="69" t="inlineStr">
@@ -3588,7 +3537,6 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • BLA04 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx – business line DIV results document – 11/15/2025 – Investment Operations (operator Michelle Oropesa)
 • DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-• DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 61 – Department Manager / Approval Date / Attestation fields</t>
         </is>
       </c>
@@ -3599,14 +3547,14 @@
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 61
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – row 62
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – BCiC report screen (record on a later page of the 66-item report)
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="Q9" s="49" t="inlineStr">
         <is>
           <t>PASS – all five control attributes satisfied (Annual Testing Executed, DIV Performed by IT DR Team, Applications in Scope Identified, Business Line Approval of Results, Results Documented in BCMS).
 Observations (do not change the attribute conclusions – reviewer to confirm):
-1. Timing – Michelle Oropesa: 1 record(s), BCiC approval 08/17/2026 – business line approval obtained after the review period end (06/01/2026) through retrospective management attestation (DMA02a §3.6 commits to contemporaneous approval going forward).
+1. Timing – Michelle Oropesa: 1 record(s), BCiC approval 08/17/2026 – business line approval obtained after the review period end (06/01/2026) through retrospective management attestation (DMA02 attachment §3.6 commits to contemporaneous approval going forward).
 2. Segregation – business tester and approving manager are the same person for: Michelle Oropesa.
 3. Scope wording – BLA04 names "Swift Interface Monitor – BSI" / "Swift Interface – BSI" rather than "Interface Monitor"; BCiC full name of 1936 is "Interface Monitor::Swift Interface - BSI" (MA01). DIV record: E03 row 61.</t>
         </is>
@@ -3619,16 +3567,13 @@
 BLA04 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx
 [03 DIV Manager Attestation Email Approvals]
 DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf
 [04 Data Integrity &amp; Email Testing Evidence]
 E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx
 E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg
 E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls
 E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
-E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml
 E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
         </is>
       </c>
@@ -3685,7 +3630,7 @@
       <c r="BM9" s="58" t="n"/>
       <c r="BN9" s="58" t="n"/>
     </row>
-    <row r="10" ht="404" customFormat="1" customHeight="1" s="39">
+    <row r="10" ht="332" customFormat="1" customHeight="1" s="39">
       <c r="A10" s="45" t="n">
         <v>3301</v>
       </c>
@@ -3706,7 +3651,7 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 31 – 2025 DR Test Scope = True, Exercise Date 11/15/2025
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 25, 29 – Business Data Validation Date 11/15/2025
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 Background: 'the IT DR team facilitates, on an annual basis, data integrity validation testing'</t>
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §1 Background: 'the IT DR team facilitates, on an annual basis, data integrity validation testing'</t>
         </is>
       </c>
       <c r="D10" s="45" t="inlineStr">
@@ -3747,8 +3692,7 @@
           <t>Franklin Puentes (Payments &amp; Cash Management) – E03 rows 25, 29
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 25, 29 – 'Department Manager' column
-• DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-• DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf</t>
+• DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
         </is>
       </c>
       <c r="H10" s="45" t="inlineStr">
@@ -3756,8 +3700,7 @@
           <t>Franklin Puentes: BCiC approval 12/18/2025; approval evidence 08/18/2026
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 25, 29 – 'Department Manager Approval Date' and 'Attestation Date' columns
-• DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-• DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf</t>
+• DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
         </is>
       </c>
       <c r="I10" s="45" t="inlineStr">
@@ -3774,10 +3717,9 @@
       <c r="J10" s="45" t="inlineStr">
         <is>
           <t>Yes – application-specific business line manager approval evidence obtained for every DIV record:
-Franklin Puentes: DMA03 email + DMA03a signed attestation 08/18/2026
+Franklin Puentes: DMA03 email with attached signed attestation 08/18/2026
 Evidence location (BSI.IT.6.C7.3-Evidences):
-• DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-• DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf</t>
+• DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
         </is>
       </c>
       <c r="K10" s="46" t="inlineStr">
@@ -3798,8 +3740,7 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 31 – Exercise Date 11/15/2025 / 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 25, 29 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
-• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026; attached signed attestation §1 – DIV facilitated on an annual basis
 • BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – dated 11/15/2025</t>
         </is>
       </c>
@@ -3807,9 +3748,8 @@
         <is>
           <t>PASS – The IT DR team (IT Business Control, Governance &amp; PMO – Elizabeth Noda) facilitated the Data Integrity Validation: application list/BIA review, DIV test scripts issued to the business, evidence collected and results recorded in BCiC. The business-line tester(s) executed the validation during the 11/15/2025 DR exercise.
 Evidence location (BSI.IT.6.C7.3-Evidences):
-• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review 09/15/2025
-• E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – follow-up 09/18/2025
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
+• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review (invite 09/15/2025, re-sent 09/18/2025)
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
 • BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • E08 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg – business-line DIV comparison files sent to IT DR (Elizabeth Noda) on 11/15/2025
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 25, 29 – Y/N Format, Headers, Content = Y</t>
@@ -3823,8 +3763,7 @@
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 31 – 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
-• E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – BIA results &amp; applications list review
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data</t>
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §2 – application listed among the 13 in-scope applications that store business data</t>
         </is>
       </c>
       <c r="O10" s="69" t="inlineStr">
@@ -3833,7 +3772,6 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – business line DIV results document – 11/15/2025 – Payments &amp; Position Management (operators Frank Puentes / Gustavo Bucaro)
 • DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-• DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 25, 29 – Department Manager / Approval Date / Attestation fields</t>
         </is>
       </c>
@@ -3844,7 +3782,7 @@
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 25, 29
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – rows 25, 29
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – BCiC report screen (record on a later page of the 66-item report)
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="Q10" s="49" t="inlineStr">
@@ -3863,16 +3801,13 @@
 BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf
 [03 DIV Manager Attestation Email Approvals]
 DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf
 [04 Data Integrity &amp; Email Testing Evidence]
 E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx
 E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg
 E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls
 E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
-E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml
 E07 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg
 E08 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg
 E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
@@ -3931,7 +3866,7 @@
       <c r="BM10" s="58" t="n"/>
       <c r="BN10" s="58" t="n"/>
     </row>
-    <row r="11" ht="409" customFormat="1" customHeight="1" s="39">
+    <row r="11" ht="380" customFormat="1" customHeight="1" s="39">
       <c r="A11" s="45" t="n">
         <v>1903</v>
       </c>
@@ -3953,7 +3888,7 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 34 – 2025 DR Test Scope = True, Exercise Date 11/15/2025
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 6, 26, 30, 34, 58 – Business Data Validation Date 11/15/2025
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 Background: 'the IT DR team facilitates, on an annual basis, data integrity validation testing'</t>
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §1 Background: 'the IT DR team facilitates, on an annual basis, data integrity validation testing'</t>
         </is>
       </c>
       <c r="D11" s="45" t="inlineStr">
@@ -4004,11 +3939,8 @@
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 6, 26, 30, 34, 58 – 'Department Manager' column
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – Department Manager column
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-• DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf
-• DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-• DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+• DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
         </is>
       </c>
       <c r="H11" s="66" t="inlineStr">
@@ -4020,11 +3952,8 @@
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 6, 26, 30, 34, 58 – 'Department Manager Approval Date' and 'Attestation Date' columns
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – Department Manager Approval Date column
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-• DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf
-• DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-• DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+• DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
         </is>
       </c>
       <c r="I11" s="40" t="inlineStr">
@@ -4045,16 +3974,13 @@
       <c r="J11" s="40" t="inlineStr">
         <is>
           <t>Yes – application-specific business line manager approval evidence obtained for every DIV record:
-David Marquez: DMA02 email + DMA02a signed attestation 08/19/2026
-Franklin Puentes: DMA03 email + DMA03a signed attestation 08/18/2026
-Maria del Cerro Hontanilla: DMA05 email + DMA05a signed attestation 08/19/2026
+David Marquez: DMA02 email with attached signed attestation 08/19/2026
+Franklin Puentes: DMA03 email with attached signed attestation 08/18/2026
+Maria del Cerro Hontanilla: DMA05 email with attached signed attestation 08/19/2026
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-• DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf
-• DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-• DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+• DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
         </is>
       </c>
       <c r="K11" s="41" t="inlineStr">
@@ -4075,8 +4001,7 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 34 – Exercise Date 11/15/2025 / 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 6, 26, 30, 34, 58 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
-• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026; attached signed attestation §1 – DIV facilitated on an annual basis
 • BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf – dated 11/15/2025
 • BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – dated 11/15/2025</t>
         </is>
@@ -4085,9 +4010,8 @@
         <is>
           <t>PASS – The IT DR team (IT Business Control, Governance &amp; PMO – Elizabeth Noda) facilitated the Data Integrity Validation: application list/BIA review, DIV test scripts issued to the business, evidence collected and results recorded in BCiC. The business-line tester(s) executed the validation during the 11/15/2025 DR exercise.
 Evidence location (BSI.IT.6.C7.3-Evidences):
-• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review 09/15/2025
-• E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – follow-up 09/18/2025
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
+• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review (invite 09/15/2025, re-sent 09/18/2025)
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
 • BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • E08 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg – business-line DIV comparison files sent to IT DR (Elizabeth Noda) on 11/15/2025
@@ -4102,8 +4026,7 @@
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 34 – 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
-• E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – BIA results &amp; applications list review
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data</t>
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §2 – application listed among the 13 in-scope applications that store business data</t>
         </is>
       </c>
       <c r="O11" s="69" t="inlineStr">
@@ -4113,11 +4036,8 @@
 • BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf – business line DIV results document – 11/15/2025 – BSA/AML/OFAC Compliance (operator David Marquez)
 • BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – business line DIV results document – 11/15/2025 – Payments &amp; Position Management (operators Frank Puentes / Gustavo Bucaro)
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-• DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf
 • DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-• DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 6, 26, 30, 34, 58 – Department Manager / Approval Date / Attestation fields</t>
         </is>
       </c>
@@ -4128,17 +4048,17 @@
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 6, 26, 30, 34, 58
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – rows 6, 26, 30, 34, 59
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – record(s) visible on screen
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="Q11" s="49" t="inlineStr">
         <is>
           <t>PASS – all five control attributes satisfied (Annual Testing Executed, DIV Performed by IT DR Team, Applications in Scope Identified, Business Line Approval of Results, Results Documented in BCMS).
 Observations (do not change the attribute conclusions – reviewer to confirm):
-1. Timing – Maria del Cerro Hontanilla: 1 record(s), BCiC approval 08/19/2026 – business line approval obtained after the review period end (06/01/2026) through retrospective management attestation (DMA02a §3.6 commits to contemporaneous approval going forward).
+1. Timing – Maria del Cerro Hontanilla: 1 record(s), BCiC approval 08/19/2026 – business line approval obtained after the review period end (06/01/2026) through retrospective management attestation (DMA02 attachment §3.6 commits to contemporaneous approval going forward).
 2. Approval evidence – David Marquez: 1 record(s), BCiC approval 11/15/2025 (in period) confirmed by signed attestation 08/19/2026; Franklin Puentes: 3 record(s), BCiC approval 12/18/2025 (in period) confirmed by signed attestation 08/18/2026 – no contemporaneous approval email for the BCiC approval date is in the package; approval is confirmed retrospectively.
 3. Segregation – business tester and approving manager are the same person for: David Marquez, Franklin Puentes.
-4. Results document – BLA02 (BSA/AML/OFAC) DIV Yes/No boxes are blank; mitigated by BLA02 production vs test-day screenshots, BCiC Y/Y/Y (E03) and David Marquez signed attestation (DMA02a).</t>
+4. Results document – BLA02 (BSA/AML/OFAC) DIV Yes/No boxes are blank; mitigated by BLA02 production vs test-day screenshots, BCiC Y/Y/Y (E03) and David Marquez signed attestation (DMA02 attachment).</t>
         </is>
       </c>
       <c r="R11" s="40" t="inlineStr">
@@ -4150,18 +4070,14 @@
 BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf
 [03 DIV Manager Attestation Email Approvals]
 DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf
 DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf
 [04 Data Integrity &amp; Email Testing Evidence]
 E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx
 E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg
 E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls
 E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
-E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml
 E07 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg
 E08 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg
 E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
@@ -4220,7 +4136,7 @@
       <c r="BM11" s="58" t="n"/>
       <c r="BN11" s="58" t="n"/>
     </row>
-    <row r="12" ht="356" customFormat="1" customHeight="1" s="39">
+    <row r="12" ht="308" customFormat="1" customHeight="1" s="39">
       <c r="A12" s="45" t="n">
         <v>1917</v>
       </c>
@@ -4241,7 +4157,7 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 36 – 2025 DR Test Scope = True, Exercise Date 11/15/2025
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 17 – Business Data Validation Date 11/15/2025
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 Background: 'the IT DR team facilitates, on an annual basis, data integrity validation testing'</t>
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §1 Background: 'the IT DR team facilitates, on an annual basis, data integrity validation testing'</t>
         </is>
       </c>
       <c r="D12" s="45" t="inlineStr">
@@ -4327,8 +4243,7 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 36 – Exercise Date 11/15/2025 / 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 17 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
-• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026; attached signed attestation §1 – DIV facilitated on an annual basis
 • BLA05 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf – dated 11/15/2025</t>
         </is>
       </c>
@@ -4336,9 +4251,8 @@
         <is>
           <t>PASS – The IT DR team (IT Business Control, Governance &amp; PMO – Elizabeth Noda) facilitated the Data Integrity Validation: application list/BIA review, DIV test scripts issued to the business, evidence collected and results recorded in BCiC. The business-line tester(s) executed the validation during the 11/15/2025 DR exercise.
 Evidence location (BSI.IT.6.C7.3-Evidences):
-• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review 09/15/2025
-• E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – follow-up 09/18/2025
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
+• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review (invite 09/15/2025, re-sent 09/18/2025)
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
 • BLA05 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • E10 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg – IT DR (Elizabeth Noda) Finance DIV chart and approval request
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 17 – Y/N Format, Headers, Content = Y</t>
@@ -4352,8 +4266,7 @@
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 36 – 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
-• E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – BIA results &amp; applications list review
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data</t>
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §2 – application listed among the 13 in-scope applications that store business data</t>
         </is>
       </c>
       <c r="O12" s="69" t="inlineStr">
@@ -4372,7 +4285,7 @@
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 17
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – row 17
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – BCiC report screen (record on a later page of the 66-item report)
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="Q12" s="49" t="inlineStr">
@@ -4392,14 +4305,12 @@
 BLA06 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg
 [03 DIV Manager Attestation Email Approvals]
 DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 [04 Data Integrity &amp; Email Testing Evidence]
 E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx
 E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg
 E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls
 E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
-E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml
 E10 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg
 E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
         </is>
@@ -4457,7 +4368,7 @@
       <c r="BM12" s="58" t="n"/>
       <c r="BN12" s="58" t="n"/>
     </row>
-    <row r="13" ht="409" customFormat="1" customHeight="1" s="39">
+    <row r="13" ht="356" customFormat="1" customHeight="1" s="39">
       <c r="A13" s="45" t="n">
         <v>1936</v>
       </c>
@@ -4479,7 +4390,7 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 42 – 2025 DR Test Scope = True, Exercise Date 11/15/2025
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 7, 60 – Business Data Validation Date 11/15/2025
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 Background: 'the IT DR team facilitates, on an annual basis, data integrity validation testing'</t>
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §1 Background: 'the IT DR team facilitates, on an annual basis, data integrity validation testing'</t>
         </is>
       </c>
       <c r="D13" s="45" t="inlineStr">
@@ -4528,9 +4439,7 @@
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 7, 60 – 'Department Manager' column
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – Department Manager column
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
-• DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-• DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+• DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
         </is>
       </c>
       <c r="H13" s="45" t="inlineStr">
@@ -4541,9 +4450,7 @@
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 7, 60 – 'Department Manager Approval Date' and 'Attestation Date' columns
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – Department Manager Approval Date column
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
-• DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-• DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+• DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
         </is>
       </c>
       <c r="I13" s="40" t="inlineStr">
@@ -4561,13 +4468,11 @@
       <c r="J13" s="40" t="inlineStr">
         <is>
           <t>Yes – application-specific business line manager approval evidence obtained for every DIV record:
-David Marquez: DMA02 email + DMA02a signed attestation 08/19/2026
-Michelle Oropesa: DMA04 email + DMA04a signed attestation 08/17/2026
+David Marquez: DMA02 email with attached signed attestation 08/19/2026
+Michelle Oropesa: DMA04 email with attached signed attestation 08/17/2026
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
-• DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-• DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+• DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
         </is>
       </c>
       <c r="K13" s="41" t="inlineStr">
@@ -4588,8 +4493,7 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 42 – Exercise Date 11/15/2025 / 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 7, 60 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
-• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026; attached signed attestation §1 – DIV facilitated on an annual basis
 • BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – dated 11/15/2025
 • BLA04 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx – dated 11/15/2025</t>
         </is>
@@ -4598,9 +4502,8 @@
         <is>
           <t>PASS – The IT DR team (IT Business Control, Governance &amp; PMO – Elizabeth Noda) facilitated the Data Integrity Validation: application list/BIA review, DIV test scripts issued to the business, evidence collected and results recorded in BCiC. The business-line tester(s) executed the validation during the 11/15/2025 DR exercise.
 Evidence location (BSI.IT.6.C7.3-Evidences):
-• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review 09/15/2025
-• E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – follow-up 09/18/2025
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
+• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review (invite 09/15/2025, re-sent 09/18/2025)
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
 • BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • BLA04 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx – IT DR test script completed by the business-line tester
 • E08 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg – business-line DIV comparison files sent to IT DR (Elizabeth Noda) on 11/15/2025
@@ -4615,8 +4518,7 @@
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 42 – 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
-• E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – BIA results &amp; applications list review
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data</t>
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §2 – application listed among the 13 in-scope applications that store business data</t>
         </is>
       </c>
       <c r="O13" s="69" t="inlineStr">
@@ -4626,9 +4528,7 @@
 • BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – business line DIV results document – 11/15/2025 – Payments &amp; Position Management (operators Frank Puentes / Gustavo Bucaro)
 • BLA04 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx – business line DIV results document – 11/15/2025 – Investment Operations (operator Michelle Oropesa)
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-• DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 7, 60 – Department Manager / Approval Date / Attestation fields</t>
         </is>
       </c>
@@ -4639,17 +4539,17 @@
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 7, 60
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – rows 7, 61
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – record(s) visible on screen
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="Q13" s="49" t="inlineStr">
         <is>
           <t>PASS – all five control attributes satisfied (Annual Testing Executed, DIV Performed by IT DR Team, Applications in Scope Identified, Business Line Approval of Results, Results Documented in BCMS).
 Observations (do not change the attribute conclusions – reviewer to confirm):
-1. Timing – Michelle Oropesa: 1 record(s), BCiC approval 08/17/2026 – business line approval obtained after the review period end (06/01/2026) through retrospective management attestation (DMA02a §3.6 commits to contemporaneous approval going forward).
+1. Timing – Michelle Oropesa: 1 record(s), BCiC approval 08/17/2026 – business line approval obtained after the review period end (06/01/2026) through retrospective management attestation (DMA02 attachment §3.6 commits to contemporaneous approval going forward).
 2. Approval evidence – David Marquez: 1 record(s), BCiC approval 11/15/2025 (in period) confirmed by signed attestation 08/19/2026 – no contemporaneous approval email for the BCiC approval date is in the package; approval is confirmed retrospectively.
 3. Segregation – business tester and approving manager are the same person for: David Marquez, Michelle Oropesa.
-4. Results document – BLA02 (BSA/AML/OFAC) DIV Yes/No boxes are blank; mitigated by BLA02 production vs test-day screenshots, BCiC Y/Y/Y (E03) and David Marquez signed attestation (DMA02a).</t>
+4. Results document – BLA02 (BSA/AML/OFAC) DIV Yes/No boxes are blank; mitigated by BLA02 production vs test-day screenshots, BCiC Y/Y/Y (E03) and David Marquez signed attestation (DMA02 attachment).</t>
         </is>
       </c>
       <c r="R13" s="40" t="inlineStr">
@@ -4661,16 +4561,13 @@
 BLA04 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx
 [03 DIV Manager Attestation Email Approvals]
 DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf
 [04 Data Integrity &amp; Email Testing Evidence]
 E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx
 E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg
 E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls
 E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
-E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml
 E07 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg
 E08 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg
 E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
@@ -4754,7 +4651,7 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 43 – 2025 DR Test Scope = True, Exercise Date 11/15/2025
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63 – Business Data Validation Date 11/15/2025
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 Background: 'the IT DR team facilitates, on an annual basis, data integrity validation testing'</t>
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §1 Background: 'the IT DR team facilitates, on an annual basis, data integrity validation testing'</t>
         </is>
       </c>
       <c r="D14" s="43" t="inlineStr">
@@ -4835,26 +4732,19 @@
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63 – 'Department Manager' column
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – Department Manager column
 • DMA06 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg
-• DMA06a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA06a_Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Data_Integrity_Attestation_Santander-BCiC_signed.pdf
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
 • DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
 • DMA11 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
 • BLA06 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg
 • DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-• DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf
 • DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-• DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf
 • DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-• DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf
 • DMA07 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg
-• DMA07a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA07a_Treasury &amp; Capital Planning - Data_Integrity_Attestation_Santander-BCiC.pdf
 • DMA12 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml
 • DMA10 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml
 • DMA08 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg
-• DMA09 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg
-• DMA09a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA09a_General Services (Marketing &amp; General Services) - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+• DMA09 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg</t>
         </is>
       </c>
       <c r="H14" s="81" t="inlineStr">
@@ -4876,27 +4766,19 @@
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63 – 'Department Manager Approval Date' and 'Attestation Date' columns
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – Department Manager Approval Date column
 • DMA06 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg
-• DMA06a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA06a_Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Data_Integrity_Attestation_Santander-BCiC_signed.pdf
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
 • DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-• DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
 • DMA11 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
 • BLA06 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg
 • DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-• DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf
 • DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-• DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf
 • DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-• DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf
 • DMA07 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg
-• DMA07a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA07a_Treasury &amp; Capital Planning - Data_Integrity_Attestation_Santander-BCiC.pdf
 • DMA12 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml
 • DMA10 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml
 • DMA08 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg
-• DMA09 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg
-• DMA09a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA09a_General Services (Marketing &amp; General Services) - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+• DMA09 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg</t>
         </is>
       </c>
       <c r="I14" s="43" t="inlineStr">
@@ -4923,42 +4805,34 @@
       <c r="J14" s="43" t="inlineStr">
         <is>
           <t>Yes – application-specific business line manager approval evidence obtained for every DIV record:
-Ricardo Garcia: DMA06 email + DMA06a e-signed attestation 08/18/2026
-David Marquez: DMA02 email + DMA02a signed attestation 08/19/2026
-Claudia Romero: E09 email "Approved." 05/05/2026 (Client Back Office results); DMA01/DMA01a signed attestation 08/18/2026
+Ricardo Garcia: DMA06 email with attached e-signed attestation 08/18/2026
+David Marquez: DMA02 email with attached signed attestation 08/19/2026
+Claudia Romero: E09 email "Approved." 05/05/2026 (Client Back Office results); DMA01 email with attached signed attestation 08/18/2026
 Miguel Orozco: DMA11 email "I approve the integrity validation…" 09/09/2026
 Sadis Alvarenga Hernandez: BLA06 email "Approved." 12/31/2025 &amp; 01/26/2026 (supplemental: E10 Finance approval, Lina Acuna 03/09/2026)
-Maria del Cerro Hontanilla: DMA05 email + DMA05a signed attestation 08/19/2026
-Michelle Oropesa: DMA04 email + DMA04a signed attestation 08/17/2026
-Franklin Puentes: DMA03 email + DMA03a signed attestation 08/18/2026
-Martha Sullivan: DMA07 email + DMA07a signed attestation 08/18/2026
+Maria del Cerro Hontanilla: DMA05 email with attached signed attestation 08/19/2026
+Michelle Oropesa: DMA04 email with attached signed attestation 08/17/2026
+Franklin Puentes: DMA03 email with attached signed attestation 08/18/2026
+Martha Sullivan: DMA07 email with attached signed attestation 08/18/2026
 Liliana Vizhnay: DMA12 email "I approve." 09/09/2026
 Victoria Fernandez: DMA10 email "Approved" 08/21/2026
 Xavier Caisapanta: DMA08 email "You have my approval" 08/18/2026 (sent by Ivan Caisapanta)
-Clara De Castro: DMA09 email + DMA09a signed attestation 08/18/2026
+Clara De Castro: DMA09 email with attached signed attestation 08/18/2026
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • DMA06 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg
-• DMA06a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA06a_Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Data_Integrity_Attestation_Santander-BCiC_signed.pdf
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
 • DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-• DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
 • DMA11 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
 • BLA06 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg
 • DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-• DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf
 • DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-• DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf
 • DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-• DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf
 • DMA07 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg
-• DMA07a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA07a_Treasury &amp; Capital Planning - Data_Integrity_Attestation_Santander-BCiC.pdf
 • DMA12 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml
 • DMA10 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml
 • DMA08 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg
-• DMA09 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg
-• DMA09a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA09a_General Services (Marketing &amp; General Services) - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+• DMA09 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg</t>
         </is>
       </c>
       <c r="K14" s="44" t="inlineStr">
@@ -4979,8 +4853,7 @@
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 43 – Exercise Date 11/15/2025 / 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
-• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026; attached signed attestation §1 – DIV facilitated on an annual basis
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – dated 11/15/2025
 • BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf – dated 11/15/2025
 • BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – dated 11/15/2025
@@ -4992,9 +4865,8 @@
         <is>
           <t>PASS – The IT DR team (IT Business Control, Governance &amp; PMO – Elizabeth Noda) facilitated the Data Integrity Validation: application list/BIA review, DIV test scripts issued to the business, evidence collected and results recorded in BCiC. The business-line tester(s) executed the validation during the 11/15/2025 DR exercise.
 Evidence location (BSI.IT.6.C7.3-Evidences):
-• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review 09/15/2025
-• E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – follow-up 09/18/2025
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
+• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review (invite 09/15/2025, re-sent 09/18/2025)
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
@@ -5013,8 +4885,7 @@
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 43 – 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
-• E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – BIA results &amp; applications list review
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data</t>
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §2 – application listed among the 13 in-scope applications that store business data</t>
         </is>
       </c>
       <c r="O14" s="69" t="inlineStr">
@@ -5027,27 +4898,19 @@
 • BLA04 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx – business line DIV results document – 11/15/2025 – Investment Operations (operator Michelle Oropesa)
 • BLA05 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf – business line DIV results document – 11/15/2025 – Finance &amp; Accounting Reporting (operator Dunia Gonzalez Collado)
 • DMA06 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg
-• DMA06a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA06a_Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Data_Integrity_Attestation_Santander-BCiC_signed.pdf
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
 • DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-• DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
 • DMA11 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
 • BLA06 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg
 • DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-• DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf
 • DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-• DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf
 • DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-• DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf
 • DMA07 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg
-• DMA07a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA07a_Treasury &amp; Capital Planning - Data_Integrity_Attestation_Santander-BCiC.pdf
 • DMA12 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml
 • DMA10 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml
 • DMA08 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg
 • DMA09 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg
-• DMA09a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA09a_General Services (Marketing &amp; General Services) - Data_Integrity_Attestation_Santander-BCiC.pdf
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63 – Department Manager / Approval Date / Attestation fields</t>
         </is>
       </c>
@@ -5058,18 +4921,18 @@
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 47, 49, 50, 51, 53, 55, 56, 57, 60, 63, 64
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – record(s) visible on screen
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="Q14" s="49" t="inlineStr">
         <is>
           <t>PASS – all five control attributes satisfied (Annual Testing Executed, DIV Performed by IT DR Team, Applications in Scope Identified, Business Line Approval of Results, Results Documented in BCMS).
 Observations (do not change the attribute conclusions – reviewer to confirm):
-1. Timing – Ricardo Garcia: 8 record(s), BCiC approval 08/18/2026; Miguel Orozco: 2 record(s), BCiC approval 09/09/2026; Maria del Cerro Hontanilla: 3 record(s), BCiC approval 08/19/2026; Michelle Oropesa: 3 record(s), BCiC approval 08/17/2026; Martha Sullivan: 6 record(s), BCiC approval 08/18/2026; Liliana Vizhnay: 1 record(s), BCiC approval 09/09/2026; Victoria Fernandez: 1 record(s), BCiC approval 08/21/2026; Xavier Caisapanta: 2 record(s), BCiC approval 08/18/2026; Clara De Castro: 1 record(s), BCiC approval 08/18/2026 – business line approval obtained after the review period end (06/01/2026) through retrospective management attestation (DMA02a §3.6 commits to contemporaneous approval going forward).
+1. Timing – Ricardo Garcia: 8 record(s), BCiC approval 08/18/2026; Miguel Orozco: 2 record(s), BCiC approval 09/09/2026; Maria del Cerro Hontanilla: 3 record(s), BCiC approval 08/19/2026; Michelle Oropesa: 3 record(s), BCiC approval 08/17/2026; Martha Sullivan: 6 record(s), BCiC approval 08/18/2026; Liliana Vizhnay: 1 record(s), BCiC approval 09/09/2026; Victoria Fernandez: 1 record(s), BCiC approval 08/21/2026; Xavier Caisapanta: 2 record(s), BCiC approval 08/18/2026; Clara De Castro: 1 record(s), BCiC approval 08/18/2026 – business line approval obtained after the review period end (06/01/2026) through retrospective management attestation (DMA02 attachment §3.6 commits to contemporaneous approval going forward).
 2. Approval evidence – David Marquez: 1 record(s), BCiC approval 11/15/2025 (in period) confirmed by signed attestation 08/19/2026; Franklin Puentes: 4 record(s), BCiC approval 12/18/2025 (in period) confirmed by signed attestation 08/18/2026 – no contemporaneous approval email for the BCiC approval date is in the package; approval is confirmed retrospectively.
 3. Segregation – business tester and approving manager are the same person for: David Marquez, Miguel Orozco, Sadis Alvarenga Hernandez, Michelle Oropesa, Franklin Puentes, Martha Sullivan, Liliana Vizhnay, Victoria Fernandez.
-4. Results document – BLA02 (BSA/AML/OFAC) DIV Yes/No boxes are blank; mitigated by BLA02 production vs test-day screenshots, BCiC Y/Y/Y (E03) and David Marquez signed attestation (DMA02a).
-5. Data – E03 row 8 (BSA T24) Attestation Date 08/29/2026 vs signed attestation 8/19/2026 (DMA02a); Financial Risk manager recorded as "Xavier Caisapanta" in BCiC while approval email is from Ivan Caisapanta (DMA08); E16b contains one additional Treasury T24 row (row 45, blank department) vs E03.</t>
+4. Results document – BLA02 (BSA/AML/OFAC) DIV Yes/No boxes are blank; mitigated by BLA02 production vs test-day screenshots, BCiC Y/Y/Y (E03) and David Marquez signed attestation (DMA02 attachment).
+5. Data – E03 row 8 (BSA T24) Attestation Date 08/29/2026 vs signed attestation 8/19/2026 (DMA02 attachment); Financial Risk manager recorded as "Xavier Caisapanta" in BCiC while approval email is from Ivan Caisapanta (DMA08); E16b contains one additional Treasury T24 row (row 45, blank department) vs E03.</t>
         </is>
       </c>
       <c r="R14" s="43" t="inlineStr">
@@ -5085,22 +4948,14 @@
 BLA06 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg
 [03 DIV Manager Attestation Email Approvals]
 DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
 DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf
 DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf
 DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf
 DMA06 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg
-DMA06a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA06a_Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Data_Integrity_Attestation_Santander-BCiC_signed.pdf
 DMA07 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg
-DMA07a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA07a_Treasury &amp; Capital Planning - Data_Integrity_Attestation_Santander-BCiC.pdf
 DMA08 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg
 DMA09 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg
-DMA09a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA09a_General Services (Marketing &amp; General Services) - Data_Integrity_Attestation_Santander-BCiC.pdf
 DMA10 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml
 DMA11 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
 DMA12 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml
@@ -5110,7 +4965,6 @@
 E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls
 E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
-E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml
 E07 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg
 E08 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg
 E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
@@ -5988,7 +5842,7 @@
       </c>
       <c r="E39" s="86" t="inlineStr">
         <is>
-          <t>Claudia Romero (Client Back Office Manager VP) returns signed attestation (DMA01a).</t>
+          <t>Claudia Romero (Client Back Office Manager VP) returns the signed Management Attestation – attachment: Data_Integrity_Attestation_Santander-BCiC (002).pdf (signed Claudia Romero).</t>
         </is>
       </c>
       <c r="F39" s="86" t="inlineStr">
@@ -6010,35 +5864,35 @@
       <c r="R39" s="82" t="n"/>
       <c r="S39" s="82" t="n"/>
     </row>
-    <row r="40" ht="42" customHeight="1" s="71">
+    <row r="40" ht="90" customHeight="1" s="71">
       <c r="A40" s="86" t="inlineStr">
         <is>
-          <t>DMA01a</t>
+          <t>DMA02</t>
         </is>
       </c>
       <c r="B40" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg</t>
         </is>
       </c>
       <c r="C40" s="86" t="inlineStr">
         <is>
-          <t>08/18/2026 – Claudia Romero</t>
+          <t>08/19/2026 – David Marquez</t>
         </is>
       </c>
       <c r="D40" s="86" t="inlineStr">
         <is>
-          <t>FedExport - BSI (row 9); FedImport - BSI (row 10); Imaging101 (rows 11, 13); T24 (rows 12, 14, 48); ACH Express (row 47)</t>
+          <t>Imaging101 (row 5); OFAC - BSI (row 6); Swift Interface - BSI (row 7); T24 (row 8)</t>
         </is>
       </c>
       <c r="E40" s="86" t="inlineStr">
         <is>
-          <t>Signed Management Attestation – Client Back Office.</t>
+          <t>Cesar Vidal request to Department Managers (08/17/2026; DR exercises 11/15/2025 and 02/21/2026; BCiC export attached) and David Marquez (OFAC Manager) reply. Attachment: Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – signed OFAC Manager, VP, BSA/AML-OFAC Compliance, 8/19/2026. Attestation §1: IT DR team facilitates DIV annually; §2: 63 entries / 13 applications, all Y/Y/Y; §3.5: retained in BCMS/BCiC; §3.6: contemporaneous approval going forward.</t>
         </is>
       </c>
       <c r="F40" s="86" t="inlineStr">
         <is>
-          <t>Signed attachment extracted from DMA01 – samples 1822, 1867, 1868, 3299, 1937</t>
+          <t>Approval evidence for 4 DIV record(s) – approval evidence dated after 06/01/2026 (BCiC approval 11/15/2025) – samples 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
         </is>
       </c>
       <c r="G40" s="82" t="n"/>
@@ -6058,32 +5912,32 @@
     <row r="41" ht="42" customHeight="1" s="71">
       <c r="A41" s="86" t="inlineStr">
         <is>
-          <t>DMA02</t>
+          <t>DMA03</t>
         </is>
       </c>
       <c r="B41" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
         </is>
       </c>
       <c r="C41" s="86" t="inlineStr">
         <is>
-          <t>08/19/2026 – David Marquez</t>
+          <t>08/18/2026 – Frank Puentes</t>
         </is>
       </c>
       <c r="D41" s="86" t="inlineStr">
         <is>
-          <t>Imaging101 (row 5); OFAC - BSI (row 6); Swift Interface - BSI (row 7); T24 (row 8)</t>
+          <t>T24 (rows 23, 27, 31, 33); MQ Payment Monitor (rows 25, 29); OFAC - BSI (rows 26, 30, 34)</t>
         </is>
       </c>
       <c r="E41" s="86" t="inlineStr">
         <is>
-          <t>Cesar Vidal request to Department Managers (08/17/2026; DR exercises 11/15/2025 and 02/21/2026; BCiC export attached) and David Marquez (OFAC Manager) reply returning the signed attestation.</t>
+          <t>Frank Puentes returns the signed attestation – attachment: 4069_001.pdf (scan, signed Executive Director, Payments &amp; Cash Management, 8/18/2026).</t>
         </is>
       </c>
       <c r="F41" s="86" t="inlineStr">
         <is>
-          <t>Approval evidence for 4 DIV record(s) – approval evidence dated after 06/01/2026 (BCiC approval 11/15/2025) – samples 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
+          <t>Approval evidence for 9 DIV record(s) – approval evidence dated after 06/01/2026 (BCiC approval 12/18/2025) – samples 3301, 1903, 1937</t>
         </is>
       </c>
       <c r="G41" s="82" t="n"/>
@@ -6100,35 +5954,35 @@
       <c r="R41" s="82" t="n"/>
       <c r="S41" s="82" t="n"/>
     </row>
-    <row r="42" ht="54" customHeight="1" s="71">
+    <row r="42" ht="42" customHeight="1" s="71">
       <c r="A42" s="86" t="inlineStr">
         <is>
-          <t>DMA02a</t>
+          <t>DMA04</t>
         </is>
       </c>
       <c r="B42" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
         </is>
       </c>
       <c r="C42" s="86" t="inlineStr">
         <is>
-          <t>08/19/2026 – David Marquez</t>
+          <t>08/17/2026 – Michelle Oropesa</t>
         </is>
       </c>
       <c r="D42" s="86" t="inlineStr">
         <is>
-          <t>Imaging101 (row 5); OFAC - BSI (row 6); Swift Interface - BSI (row 7); T24 (row 8)</t>
+          <t>T24 (rows 19, 20, 21); Swift Interface - BSI (row 60); Interface Monitor (row 61)</t>
         </is>
       </c>
       <c r="E42" s="86" t="inlineStr">
         <is>
-          <t>Signed attestation – OFAC Manager, VP, BSA/AML-OFAC Compliance, dated 8/19/2026. §1 states the IT DR team facilitates DIV annually; §2 lists 63 entries / 13 applications, all Y/Y/Y; §3.5 retention in BCMS/BCiC; §3.6 contemporaneous approval going forward.</t>
+          <t>Michelle Oropesa (Investment Operations Director) returns the signed attestation – attachment: Data_Integrity_Attestation_Santander-BCiC.pdf (signed Investment Operations Director, VP, 8/17/2026).</t>
         </is>
       </c>
       <c r="F42" s="86" t="inlineStr">
         <is>
-          <t>Signed attachment extracted from DMA02 – samples 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
+          <t>Approval evidence for 5 DIV record(s) – approval evidence dated after 06/01/2026 (BCiC approval 08/17/2026) – samples 4052, 1936, 1937</t>
         </is>
       </c>
       <c r="G42" s="82" t="n"/>
@@ -6145,35 +5999,35 @@
       <c r="R42" s="82" t="n"/>
       <c r="S42" s="82" t="n"/>
     </row>
-    <row r="43" ht="42" customHeight="1" s="71">
+    <row r="43" ht="54" customHeight="1" s="71">
       <c r="A43" s="86" t="inlineStr">
         <is>
-          <t>DMA03</t>
+          <t>DMA05</t>
         </is>
       </c>
       <c r="B43" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
         </is>
       </c>
       <c r="C43" s="86" t="inlineStr">
         <is>
-          <t>08/18/2026 – Frank Puentes</t>
+          <t>08/19/2026 – Maria Teresa (Mayte) Del Cerro</t>
         </is>
       </c>
       <c r="D43" s="86" t="inlineStr">
         <is>
-          <t>T24 (rows 23, 27, 31, 33); MQ Payment Monitor (rows 25, 29); OFAC - BSI (rows 26, 30, 34)</t>
+          <t>T24 (rows 18, 54, 59); Imaging101 (rows 53, 57); OFAC - BSI (row 58)</t>
         </is>
       </c>
       <c r="E43" s="86" t="inlineStr">
         <is>
-          <t>Frank Puentes returns signed attestation (DMA03a).</t>
+          <t>Senior Director of Operations returns the signed attestation – attachments: Data_Integrity_Attestation_Santander-BCiC.pdf (signed Maria Teresa Del Cerro Hontanilla, Director of Operations, 08/19/2026) and the BCiC export (same file as E16b).</t>
         </is>
       </c>
       <c r="F43" s="86" t="inlineStr">
         <is>
-          <t>Approval evidence for 9 DIV record(s) – approval evidence dated after 06/01/2026 (BCiC approval 12/18/2025) – samples 3301, 1903, 1937</t>
+          <t>Approval evidence for 6 DIV record(s) – approval evidence dated after 06/01/2026 (BCiC approval 08/19/2026) – samples 3299, 1903, 1937</t>
         </is>
       </c>
       <c r="G43" s="82" t="n"/>
@@ -6190,35 +6044,35 @@
       <c r="R43" s="82" t="n"/>
       <c r="S43" s="82" t="n"/>
     </row>
-    <row r="44" ht="30" customHeight="1" s="71">
+    <row r="44" ht="54" customHeight="1" s="71">
       <c r="A44" s="86" t="inlineStr">
         <is>
-          <t>DMA03a</t>
+          <t>DMA06</t>
         </is>
       </c>
       <c r="B44" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg</t>
         </is>
       </c>
       <c r="C44" s="86" t="inlineStr">
         <is>
-          <t>08/18/2026 – Frank Puentes</t>
+          <t>08/18/2026 – Ricardo Garcia-Marques</t>
         </is>
       </c>
       <c r="D44" s="86" t="inlineStr">
         <is>
-          <t>T24 (rows 23, 27, 31, 33); MQ Payment Monitor (rows 25, 29); OFAC - BSI (rows 26, 30, 34)</t>
+          <t>T24 (rows 3, 35, 36, 37, 38, 39, 40, 63)</t>
         </is>
       </c>
       <c r="E44" s="86" t="inlineStr">
         <is>
-          <t>Scanned signed attestation – Executive Director, Payments &amp; Cash Management.</t>
+          <t>Attestation and approval from Trading &amp; Capital Markets (covers BCiC records approved by Ricardo Garcia) – attachment: Data_Integrity_Attestation_Santander-BCiC_signed.pdf (e-signed MD, Head of Trading &amp; Capital Markets, 08/18/2026 11:45 AM EDT).</t>
         </is>
       </c>
       <c r="F44" s="86" t="inlineStr">
         <is>
-          <t>Signed attachment extracted from DMA03 – samples 3301, 1903, 1937</t>
+          <t>Approval evidence for 8 DIV record(s) – approval evidence dated after 06/01/2026 (BCiC approval 08/18/2026) – samples 1937</t>
         </is>
       </c>
       <c r="G44" s="82" t="n"/>
@@ -6238,32 +6092,32 @@
     <row r="45" ht="42" customHeight="1" s="71">
       <c r="A45" s="86" t="inlineStr">
         <is>
-          <t>DMA04</t>
+          <t>DMA07</t>
         </is>
       </c>
       <c r="B45" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg</t>
         </is>
       </c>
       <c r="C45" s="86" t="inlineStr">
         <is>
-          <t>08/17/2026 – Michelle Oropesa</t>
+          <t>08/18/2026 – Martha Sullivan</t>
         </is>
       </c>
       <c r="D45" s="86" t="inlineStr">
         <is>
-          <t>T24 (rows 19, 20, 21); Swift Interface - BSI (row 60); Interface Monitor (row 61)</t>
+          <t>T24 (rows 41, 42, 43, 44, 45, 46)</t>
         </is>
       </c>
       <c r="E45" s="86" t="inlineStr">
         <is>
-          <t>Michelle Oropesa (Investment Operations Director) returns signed attestation (DMA04a).</t>
+          <t>Martha Sullivan returns the signed attestation – attachment: Data_Integrity_Attestation_Santander-BCiC.pdf (signed Balance Sheet Manager, Treasury).</t>
         </is>
       </c>
       <c r="F45" s="86" t="inlineStr">
         <is>
-          <t>Approval evidence for 5 DIV record(s) – approval evidence dated after 06/01/2026 (BCiC approval 08/17/2026) – samples 4052, 1936, 1937</t>
+          <t>Approval evidence for 6 DIV record(s) – approval evidence dated after 06/01/2026 (BCiC approval 08/18/2026) – samples 1937</t>
         </is>
       </c>
       <c r="G45" s="82" t="n"/>
@@ -6283,32 +6137,32 @@
     <row r="46" ht="42" customHeight="1" s="71">
       <c r="A46" s="86" t="inlineStr">
         <is>
-          <t>DMA04a</t>
+          <t>DMA08</t>
         </is>
       </c>
       <c r="B46" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg</t>
         </is>
       </c>
       <c r="C46" s="86" t="inlineStr">
         <is>
-          <t>08/17/2026 – Michelle Oropesa</t>
+          <t>08/18/2026 – Ivan Caisapanta</t>
         </is>
       </c>
       <c r="D46" s="86" t="inlineStr">
         <is>
-          <t>T24 (rows 19, 20, 21); Swift Interface - BSI (row 60); Interface Monitor (row 61)</t>
+          <t>T24 (rows 55, 56)</t>
         </is>
       </c>
       <c r="E46" s="86" t="inlineStr">
         <is>
-          <t>Signed attestation – Investment Operations Director, VP, dated 8/17/2026.</t>
+          <t>"Hi Elizabeth, You have my approval" – Financial Risk (BCiC Department Manager recorded as Xavier Caisapanta).</t>
         </is>
       </c>
       <c r="F46" s="86" t="inlineStr">
         <is>
-          <t>Signed attachment extracted from DMA04 – samples 4052, 1936, 1937</t>
+          <t>Approval evidence for 2 DIV record(s) – approval evidence dated after 06/01/2026 (BCiC approval 08/18/2026) – samples 1937</t>
         </is>
       </c>
       <c r="G46" s="82" t="n"/>
@@ -6328,32 +6182,32 @@
     <row r="47" ht="42" customHeight="1" s="71">
       <c r="A47" s="86" t="inlineStr">
         <is>
-          <t>DMA05</t>
+          <t>DMA09</t>
         </is>
       </c>
       <c r="B47" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg</t>
         </is>
       </c>
       <c r="C47" s="86" t="inlineStr">
         <is>
-          <t>08/19/2026 – Maria Teresa (Mayte) Del Cerro</t>
+          <t>08/18/2026 – Clara G. De Castro</t>
         </is>
       </c>
       <c r="D47" s="86" t="inlineStr">
         <is>
-          <t>T24 (rows 18, 54, 59); Imaging101 (rows 53, 57); OFAC - BSI (row 58)</t>
+          <t>T24 (row 62)</t>
         </is>
       </c>
       <c r="E47" s="86" t="inlineStr">
         <is>
-          <t>Signed attestation + BCiC export (E16b) returned by Senior Director of Operations.</t>
+          <t>Clara De Castro (Director, General Services &amp; Facilities) returns the signed attestation – attachment: Data_Integrity_Attestation_Santander-BCiC.pdf (signed Clara G. De Castro).</t>
         </is>
       </c>
       <c r="F47" s="86" t="inlineStr">
         <is>
-          <t>Approval evidence for 6 DIV record(s) – approval evidence dated after 06/01/2026 (BCiC approval 08/19/2026) – samples 3299, 1903, 1937</t>
+          <t>Approval evidence for 1 DIV record(s) – approval evidence dated after 06/01/2026 (BCiC approval 08/18/2026) – samples 1937</t>
         </is>
       </c>
       <c r="G47" s="82" t="n"/>
@@ -6373,32 +6227,32 @@
     <row r="48" ht="42" customHeight="1" s="71">
       <c r="A48" s="86" t="inlineStr">
         <is>
-          <t>DMA05a</t>
+          <t>DMA10</t>
         </is>
       </c>
       <c r="B48" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml</t>
         </is>
       </c>
       <c r="C48" s="86" t="inlineStr">
         <is>
-          <t>08/19/2026 – Maria Teresa Del Cerro Hontanilla</t>
+          <t>08/21/2026 – Victoria Fernandez</t>
         </is>
       </c>
       <c r="D48" s="86" t="inlineStr">
         <is>
-          <t>T24 (rows 18, 54, 59); Imaging101 (rows 53, 57); OFAC - BSI (row 58)</t>
+          <t>T24 (row 52)</t>
         </is>
       </c>
       <c r="E48" s="86" t="inlineStr">
         <is>
-          <t>Signed attestation – Director of Operations, dated 08/19/2026.</t>
+          <t>"Approved" – Digital Wealth.</t>
         </is>
       </c>
       <c r="F48" s="86" t="inlineStr">
         <is>
-          <t>Signed attachment extracted from DMA05 – samples 3299, 1903, 1937</t>
+          <t>Approval evidence for 1 DIV record(s) – approval evidence dated after 06/01/2026 (BCiC approval 08/21/2026) – samples 1937</t>
         </is>
       </c>
       <c r="G48" s="82" t="n"/>
@@ -6418,32 +6272,32 @@
     <row r="49" ht="42" customHeight="1" s="71">
       <c r="A49" s="86" t="inlineStr">
         <is>
-          <t>DMA06</t>
+          <t>DMA11</t>
         </is>
       </c>
       <c r="B49" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml</t>
         </is>
       </c>
       <c r="C49" s="86" t="inlineStr">
         <is>
-          <t>08/18/2026 – Ricardo Garcia-Marques</t>
+          <t>09/09/2026 – Miguel Orozco</t>
         </is>
       </c>
       <c r="D49" s="86" t="inlineStr">
         <is>
-          <t>T24 (rows 3, 35, 36, 37, 38, 39, 40, 63)</t>
+          <t>T24 (rows 15, 50); Imaging101 (row 51)</t>
         </is>
       </c>
       <c r="E49" s="86" t="inlineStr">
         <is>
-          <t>Attestation and approval from Trading &amp; Capital Markets (covers BCiC records approved by Ricardo Garcia).</t>
+          <t>"I approve the integrity validation for the testing performed by the Commercial Middle Office."</t>
         </is>
       </c>
       <c r="F49" s="86" t="inlineStr">
         <is>
-          <t>Approval evidence for 8 DIV record(s) – approval evidence dated after 06/01/2026 (BCiC approval 08/18/2026) – samples 1937</t>
+          <t>Approval evidence for 3 DIV record(s) – approval evidence dated after 06/01/2026 (BCiC approval 09/09/2026) – samples 3299, 1937</t>
         </is>
       </c>
       <c r="G49" s="82" t="n"/>
@@ -6463,32 +6317,32 @@
     <row r="50" ht="42" customHeight="1" s="71">
       <c r="A50" s="86" t="inlineStr">
         <is>
-          <t>DMA06a</t>
+          <t>DMA12</t>
         </is>
       </c>
       <c r="B50" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA06a_Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Data_Integrity_Attestation_Santander-BCiC_signed.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml</t>
         </is>
       </c>
       <c r="C50" s="86" t="inlineStr">
         <is>
-          <t>08/18/2026 11:45 AM EDT – Ricardo Garcia Marques</t>
+          <t>09/09/2026 – Liliana Vizhnay</t>
         </is>
       </c>
       <c r="D50" s="86" t="inlineStr">
         <is>
-          <t>T24 (rows 3, 35, 36, 37, 38, 39, 40, 63)</t>
+          <t>T24 (row 49)</t>
         </is>
       </c>
       <c r="E50" s="86" t="inlineStr">
         <is>
-          <t>e-signed attestation – MD, Head of Trading &amp; Capital Markets.</t>
+          <t>"I approve." – Client Servicing Unit.</t>
         </is>
       </c>
       <c r="F50" s="86" t="inlineStr">
         <is>
-          <t>Signed attachment extracted from DMA06 – samples 1937</t>
+          <t>Approval evidence for 1 DIV record(s) – approval evidence dated after 06/01/2026 (BCiC approval 09/09/2026) – samples 1937</t>
         </is>
       </c>
       <c r="G50" s="82" t="n"/>
@@ -6508,32 +6362,32 @@
     <row r="51" ht="42" customHeight="1" s="71">
       <c r="A51" s="86" t="inlineStr">
         <is>
-          <t>DMA07</t>
+          <t>DMA13</t>
         </is>
       </c>
       <c r="B51" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml</t>
         </is>
       </c>
       <c r="C51" s="86" t="inlineStr">
         <is>
-          <t>08/18/2026 – Martha Sullivan</t>
+          <t>09/09/2026 – Elizabeth Noda</t>
         </is>
       </c>
       <c r="D51" s="86" t="inlineStr">
         <is>
-          <t>T24 (rows 41, 42, 43, 44, 45, 46)</t>
+          <t>Cisco Call Manager – not one of the 10 tested applications</t>
         </is>
       </c>
       <c r="E51" s="86" t="inlineStr">
         <is>
-          <t>Martha Sullivan returns signed attestation (DMA07a).</t>
+          <t>"approve" – Cisco Call Manager (IT). Cisco Call Manager is NOT one of the 10 tested applications – retained for completeness only.</t>
         </is>
       </c>
       <c r="F51" s="86" t="inlineStr">
         <is>
-          <t>Approval evidence for 6 DIV record(s) – approval evidence dated after 06/01/2026 (BCiC approval 08/18/2026) – samples 1937</t>
+          <t>Out of scope – retained for completeness – samples —</t>
         </is>
       </c>
       <c r="G51" s="82" t="n"/>
@@ -6550,37 +6404,13 @@
       <c r="R51" s="82" t="n"/>
       <c r="S51" s="82" t="n"/>
     </row>
-    <row r="52" ht="42" customHeight="1" s="71">
-      <c r="A52" s="86" t="inlineStr">
-        <is>
-          <t>DMA07a</t>
-        </is>
-      </c>
-      <c r="B52" s="86" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA07a_Treasury &amp; Capital Planning - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
-        </is>
-      </c>
-      <c r="C52" s="86" t="inlineStr">
-        <is>
-          <t>08/18/2026 – Martha Sullivan</t>
-        </is>
-      </c>
-      <c r="D52" s="86" t="inlineStr">
-        <is>
-          <t>T24 (rows 41, 42, 43, 44, 45, 46)</t>
-        </is>
-      </c>
-      <c r="E52" s="86" t="inlineStr">
-        <is>
-          <t>Signed attestation – Balance Sheet Manager, Treasury.</t>
-        </is>
-      </c>
-      <c r="F52" s="86" t="inlineStr">
-        <is>
-          <t>Signed attachment extracted from DMA07 – samples 1937</t>
-        </is>
-      </c>
+    <row r="52" s="71">
+      <c r="A52" s="82" t="n"/>
+      <c r="B52" s="82" t="n"/>
+      <c r="C52" s="82" t="n"/>
+      <c r="D52" s="82" t="n"/>
+      <c r="E52" s="82" t="n"/>
+      <c r="F52" s="82" t="n"/>
       <c r="G52" s="82" t="n"/>
       <c r="H52" s="82" t="n"/>
       <c r="I52" s="82" t="n"/>
@@ -6595,43 +6425,12 @@
       <c r="R52" s="82" t="n"/>
       <c r="S52" s="82" t="n"/>
     </row>
-    <row r="53" ht="42" customHeight="1" s="71">
-      <c r="A53" s="86" t="inlineStr">
-        <is>
-          <t>DMA08</t>
-        </is>
-      </c>
-      <c r="B53" s="86" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg</t>
-        </is>
-      </c>
-      <c r="C53" s="86" t="inlineStr">
-        <is>
-          <t>08/18/2026 – Ivan Caisapanta</t>
-        </is>
-      </c>
-      <c r="D53" s="86" t="inlineStr">
-        <is>
-          <t>T24 (rows 55, 56)</t>
-        </is>
-      </c>
-      <c r="E53" s="86" t="inlineStr">
-        <is>
-          <t>"Hi Elizabeth, You have my approval" – Financial Risk (BCiC Department Manager recorded as Xavier Caisapanta).</t>
-        </is>
-      </c>
-      <c r="F53" s="86" t="inlineStr">
-        <is>
-          <t>Approval evidence for 2 DIV record(s) – approval evidence dated after 06/01/2026 (BCiC approval 08/18/2026) – samples 1937</t>
-        </is>
-      </c>
-      <c r="G53" s="82" t="n"/>
-      <c r="H53" s="82" t="n"/>
-      <c r="I53" s="82" t="n"/>
-      <c r="J53" s="82" t="n"/>
-      <c r="K53" s="82" t="n"/>
-      <c r="L53" s="82" t="n"/>
+    <row r="53" ht="22" customHeight="1" s="71">
+      <c r="A53" s="73" t="inlineStr">
+        <is>
+          <t>Management Attestation / In-Scope Applications (folder 01) and Data Integrity &amp; Email Testing Evidence (folder 04) – Review</t>
+        </is>
+      </c>
       <c r="M53" s="82" t="n"/>
       <c r="N53" s="82" t="n"/>
       <c r="O53" s="82" t="n"/>
@@ -6640,35 +6439,35 @@
       <c r="R53" s="82" t="n"/>
       <c r="S53" s="82" t="n"/>
     </row>
-    <row r="54" ht="42" customHeight="1" s="71">
-      <c r="A54" s="86" t="inlineStr">
-        <is>
-          <t>DMA09</t>
-        </is>
-      </c>
-      <c r="B54" s="86" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg</t>
-        </is>
-      </c>
-      <c r="C54" s="86" t="inlineStr">
-        <is>
-          <t>08/18/2026 – Clara G. De Castro</t>
-        </is>
-      </c>
-      <c r="D54" s="86" t="inlineStr">
-        <is>
-          <t>T24 (row 62)</t>
-        </is>
-      </c>
-      <c r="E54" s="86" t="inlineStr">
-        <is>
-          <t>Clara De Castro (Director, General Services &amp; Facilities) returns signed attestation (DMA09a).</t>
-        </is>
-      </c>
-      <c r="F54" s="86" t="inlineStr">
-        <is>
-          <t>Approval evidence for 1 DIV record(s) – approval evidence dated after 06/01/2026 (BCiC approval 08/18/2026) – samples 1937</t>
+    <row r="54" ht="30" customHeight="1" s="71">
+      <c r="A54" s="85" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="B54" s="85" t="inlineStr">
+        <is>
+          <t>Evidence file (repository location)</t>
+        </is>
+      </c>
+      <c r="C54" s="85" t="inlineStr">
+        <is>
+          <t>Date / owner</t>
+        </is>
+      </c>
+      <c r="D54" s="85" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E54" s="85" t="inlineStr">
+        <is>
+          <t>Content reviewed</t>
+        </is>
+      </c>
+      <c r="F54" s="85" t="inlineStr">
+        <is>
+          <t>Samples / workpaper columns supported</t>
         </is>
       </c>
       <c r="G54" s="82" t="n"/>
@@ -6685,35 +6484,35 @@
       <c r="R54" s="82" t="n"/>
       <c r="S54" s="82" t="n"/>
     </row>
-    <row r="55" ht="42" customHeight="1" s="71">
+    <row r="55" ht="66" customHeight="1" s="71">
       <c r="A55" s="86" t="inlineStr">
         <is>
-          <t>DMA09a</t>
+          <t>MA01</t>
         </is>
       </c>
       <c r="B55" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA09a_General Services (Marketing &amp; General Services) - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png</t>
         </is>
       </c>
       <c r="C55" s="86" t="inlineStr">
         <is>
-          <t>08/18/2026 – Clara G. De Castro</t>
+          <t>09/23/2026 – Cesar Vidal (BCiC walkthrough)</t>
         </is>
       </c>
       <c r="D55" s="86" t="inlineStr">
         <is>
-          <t>T24 (row 62)</t>
+          <t>BCiC screenshot</t>
         </is>
       </c>
       <c r="E55" s="86" t="inlineStr">
         <is>
-          <t>Signed attestation – General Services.</t>
+          <t>BC in the Cloud 'Applications In Scope for DR Test BSI' view (filter Scope Entity = BSI; 43 items). The 10 tested applications are selected (1822, 1867, 1868, 1903, 1917, 1937, 1936, 3301, 3299, 4052) and each shows 2025 DR Test Scope = True, 2025 Backup/Restore Test Scope = True and 2025 Backup/Restore DIV Scope = True.</t>
         </is>
       </c>
       <c r="F55" s="86" t="inlineStr">
         <is>
-          <t>Signed attachment extracted from DMA09 – samples 1937</t>
+          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: D, K, N</t>
         </is>
       </c>
       <c r="G55" s="82" t="n"/>
@@ -6730,35 +6529,35 @@
       <c r="R55" s="82" t="n"/>
       <c r="S55" s="82" t="n"/>
     </row>
-    <row r="56" ht="42" customHeight="1" s="71">
+    <row r="56" ht="30" customHeight="1" s="71">
       <c r="A56" s="86" t="inlineStr">
         <is>
-          <t>DMA10</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="B56" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
         </is>
       </c>
       <c r="C56" s="86" t="inlineStr">
         <is>
-          <t>08/21/2026 – Victoria Fernandez</t>
+          <t>BCiC – Applications In Scope for DR Test BSI</t>
         </is>
       </c>
       <c r="D56" s="86" t="inlineStr">
         <is>
-          <t>T24 (row 52)</t>
+          <t>BCiC export</t>
         </is>
       </c>
       <c r="E56" s="86" t="inlineStr">
         <is>
-          <t>"Approved" – Digital Wealth.</t>
+          <t>BCiC export of the BSI DR-scope population (43 applications) with Exercise Date and 2025 DR / Backup-Restore / DIV scope flags.</t>
         </is>
       </c>
       <c r="F56" s="86" t="inlineStr">
         <is>
-          <t>Approval evidence for 1 DIV record(s) – approval evidence dated after 06/01/2026 (BCiC approval 08/21/2026) – samples 1937</t>
+          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: B, C, D, K, L, N</t>
         </is>
       </c>
       <c r="G56" s="82" t="n"/>
@@ -6775,35 +6574,35 @@
       <c r="R56" s="82" t="n"/>
       <c r="S56" s="82" t="n"/>
     </row>
-    <row r="57" ht="42" customHeight="1" s="71">
+    <row r="57" ht="30" customHeight="1" s="71">
       <c r="A57" s="86" t="inlineStr">
         <is>
-          <t>DMA11</t>
+          <t>E02</t>
         </is>
       </c>
       <c r="B57" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg</t>
         </is>
       </c>
       <c r="C57" s="86" t="inlineStr">
         <is>
-          <t>09/09/2026 – Miguel Orozco</t>
+          <t>09/10/2026 – Cesar Vidal</t>
         </is>
       </c>
       <c r="D57" s="86" t="inlineStr">
         <is>
-          <t>T24 (rows 15, 50); Imaging101 (row 51)</t>
+          <t>BCiC screenshot</t>
         </is>
       </c>
       <c r="E57" s="86" t="inlineStr">
         <is>
-          <t>"I approve the integrity validation for the testing performed by the Commercial Middle Office."</t>
+          <t>BCiC Applications screen with view 'Applications In Scope for DR Test BSI' selected (1–20 of 43 items).</t>
         </is>
       </c>
       <c r="F57" s="86" t="inlineStr">
         <is>
-          <t>Approval evidence for 3 DIV record(s) – approval evidence dated after 06/01/2026 (BCiC approval 09/09/2026) – samples 3299, 1937</t>
+          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: D, K, N</t>
         </is>
       </c>
       <c r="G57" s="82" t="n"/>
@@ -6823,32 +6622,32 @@
     <row r="58" ht="42" customHeight="1" s="71">
       <c r="A58" s="86" t="inlineStr">
         <is>
-          <t>DMA12</t>
+          <t>E03</t>
         </is>
       </c>
       <c r="B58" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
         </is>
       </c>
       <c r="C58" s="86" t="inlineStr">
         <is>
-          <t>09/09/2026 – Liliana Vizhnay</t>
+          <t>BCiC – Data Integrity Validation Testing (62 records)</t>
         </is>
       </c>
       <c r="D58" s="86" t="inlineStr">
         <is>
-          <t>T24 (row 49)</t>
+          <t>BCiC export</t>
         </is>
       </c>
       <c r="E58" s="86" t="inlineStr">
         <is>
-          <t>"I approve." – Client Servicing Unit.</t>
+          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Y/N Format/Headers/Content, Attestation Date / Provided By. Row numbers quoted are Excel rows.</t>
         </is>
       </c>
       <c r="F58" s="86" t="inlineStr">
         <is>
-          <t>Approval evidence for 1 DIV record(s) – approval evidence dated after 06/01/2026 (BCiC approval 09/09/2026) – samples 1937</t>
+          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: B, C, D, E, F, G, H, I, K, L, M, O, P</t>
         </is>
       </c>
       <c r="G58" s="82" t="n"/>
@@ -6868,32 +6667,32 @@
     <row r="59" ht="42" customHeight="1" s="71">
       <c r="A59" s="86" t="inlineStr">
         <is>
-          <t>DMA13</t>
+          <t>E04</t>
         </is>
       </c>
       <c r="B59" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg</t>
         </is>
       </c>
       <c r="C59" s="86" t="inlineStr">
         <is>
-          <t>09/09/2026 – Elizabeth Noda</t>
+          <t>09/10/2026 – Cesar Vidal</t>
         </is>
       </c>
       <c r="D59" s="86" t="inlineStr">
         <is>
-          <t>Cisco Call Manager – not one of the 10 tested applications</t>
+          <t>BCiC screenshot</t>
         </is>
       </c>
       <c r="E59" s="86" t="inlineStr">
         <is>
-          <t>"approve" – Cisco Call Manager (IT). Cisco Call Manager is NOT one of the 10 tested applications – retained for completeness only.</t>
+          <t>BCiC 'Data Integrity Validation Testing' screen (1–20 of 66 items) showing tester, validation date, manager, approval date, Y/N results and attestation fields.</t>
         </is>
       </c>
       <c r="F59" s="86" t="inlineStr">
         <is>
-          <t>Out of scope – retained for completeness – samples —</t>
+          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: D, E, F, G, H, K, P</t>
         </is>
       </c>
       <c r="G59" s="82" t="n"/>
@@ -6910,13 +6709,37 @@
       <c r="R59" s="82" t="n"/>
       <c r="S59" s="82" t="n"/>
     </row>
-    <row r="60" s="71">
-      <c r="A60" s="82" t="n"/>
-      <c r="B60" s="82" t="n"/>
-      <c r="C60" s="82" t="n"/>
-      <c r="D60" s="82" t="n"/>
-      <c r="E60" s="82" t="n"/>
-      <c r="F60" s="82" t="n"/>
+    <row r="60" ht="42" customHeight="1" s="71">
+      <c r="A60" s="86" t="inlineStr">
+        <is>
+          <t>E05</t>
+        </is>
+      </c>
+      <c r="B60" s="86" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg</t>
+        </is>
+      </c>
+      <c r="C60" s="86" t="inlineStr">
+        <is>
+          <t>09/15/2025 – Elizabeth Noda</t>
+        </is>
+      </c>
+      <c r="D60" s="86" t="inlineStr">
+        <is>
+          <t>Meeting invite</t>
+        </is>
+      </c>
+      <c r="E60" s="86" t="inlineStr">
+        <is>
+          <t>IT DR meeting invite to review the 2025 BIA results and applications list ahead of the DR exercise (same invite re-sent 09/18/2025 – duplicate E06 removed).</t>
+        </is>
+      </c>
+      <c r="F60" s="86" t="inlineStr">
+        <is>
+          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: M, N</t>
+        </is>
+      </c>
       <c r="G60" s="82" t="n"/>
       <c r="H60" s="82" t="n"/>
       <c r="I60" s="82" t="n"/>
@@ -6931,12 +6754,43 @@
       <c r="R60" s="82" t="n"/>
       <c r="S60" s="82" t="n"/>
     </row>
-    <row r="61" ht="22" customHeight="1" s="71">
-      <c r="A61" s="73" t="inlineStr">
-        <is>
-          <t>Management Attestation / In-Scope Applications (folder 01) and Data Integrity &amp; Email Testing Evidence (folder 04) – Review</t>
-        </is>
-      </c>
+    <row r="61" ht="126" customHeight="1" s="71">
+      <c r="A61" s="86" t="inlineStr">
+        <is>
+          <t>E07</t>
+        </is>
+      </c>
+      <c r="B61" s="86" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg</t>
+        </is>
+      </c>
+      <c r="C61" s="86" t="inlineStr">
+        <is>
+          <t>11/15/2025 – Frank Puentes</t>
+        </is>
+      </c>
+      <c r="D61" s="86" t="inlineStr">
+        <is>
+          <t>Email + report attachments</t>
+        </is>
+      </c>
+      <c r="E61" s="86" t="inlineStr">
+        <is>
+          <t>Pre-DR (11/14/2025) source reports: Fedlink, OFAC ACH/FED/SWIFT, Payment Monitor, SWIFT Interface Monitor, outgoing Fedwire/SWIFT. Embedded attachments: FEDLINK INCOMING FEDWIRES 111425 0523PM.pdf; FEDLINK OUTGOING FEDWIRES 111425 0523PM.pdf; OFAC ACH 111425 0512PM.pdf; OFAC FED 111425 0511PM.pdf; OFAC SWIFT 111425 0511PM.pdf; OUTGOING FEDWIRE 111425 506PM.xls; OUTGOING SWIFT 111425 509PM.xls; PAYMENT MONITOR INCOMING FEDWIRE 111425 516PM PG1.pdf; PAYMENT MONITOR INCOMING FEDWIRE 111425 516PM PG2.pdf; PAYMENT MONITOR OUTGOING FEDWIRE 111425 516PM PG1.pdf; PAYMENT MONITOR OUTGOING FEDWIRE 111425 516PM PG2.pdf; SWIFT INTERFACE MONITOR 111425 519PM.pdf; SWIFT INTERFACE MONITOR 111425 520PM 2ND SAMPLE.pdf.</t>
+        </is>
+      </c>
+      <c r="F61" s="86" t="inlineStr">
+        <is>
+          <t>Samples: 3301, 1903, 1936, 1937; columns: F</t>
+        </is>
+      </c>
+      <c r="G61" s="82" t="n"/>
+      <c r="H61" s="82" t="n"/>
+      <c r="I61" s="82" t="n"/>
+      <c r="J61" s="82" t="n"/>
+      <c r="K61" s="82" t="n"/>
+      <c r="L61" s="82" t="n"/>
       <c r="M61" s="82" t="n"/>
       <c r="N61" s="82" t="n"/>
       <c r="O61" s="82" t="n"/>
@@ -6945,35 +6799,35 @@
       <c r="R61" s="82" t="n"/>
       <c r="S61" s="82" t="n"/>
     </row>
-    <row r="62" ht="30" customHeight="1" s="71">
-      <c r="A62" s="85" t="inlineStr">
-        <is>
-          <t>Ref</t>
-        </is>
-      </c>
-      <c r="B62" s="85" t="inlineStr">
-        <is>
-          <t>Evidence file (repository location)</t>
-        </is>
-      </c>
-      <c r="C62" s="85" t="inlineStr">
-        <is>
-          <t>Date / owner</t>
-        </is>
-      </c>
-      <c r="D62" s="85" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="E62" s="85" t="inlineStr">
-        <is>
-          <t>Content reviewed</t>
-        </is>
-      </c>
-      <c r="F62" s="85" t="inlineStr">
-        <is>
-          <t>Samples / workpaper columns supported</t>
+    <row r="62" ht="126" customHeight="1" s="71">
+      <c r="A62" s="86" t="inlineStr">
+        <is>
+          <t>E08</t>
+        </is>
+      </c>
+      <c r="B62" s="86" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg</t>
+        </is>
+      </c>
+      <c r="C62" s="86" t="inlineStr">
+        <is>
+          <t>11/15/2025 – Frank Puentes</t>
+        </is>
+      </c>
+      <c r="D62" s="86" t="inlineStr">
+        <is>
+          <t>Email + report attachments</t>
+        </is>
+      </c>
+      <c r="E62" s="86" t="inlineStr">
+        <is>
+          <t>DR test-day (11/15/2025) re-run of the same reports for comparison with 11/14/2025 source. Embedded attachments: FEDLINK INCOMING FEDWIRES 111425 -1115 1148AM.pdf; FEDLINK OUTGOINT TRANSFERS 114125 - 111525 1144AM.pdf; OFAC ACH 111425 - 11152025 1126AM.pdf; OFAC FED 111425 - 111525 1126AM.pdf; OFAC SWIFT 111425 - 111525 1128AM.pdf; OUTGOING FEDWIRE 111525 1025AM.xls; OUTGOING SWIFT 111525 1026AM.xls; PAYMENT MONITOR 111424 - 111525 PG 11156AM.pdf; PAYMENT MONITOR 111425 - 111525 PG 2 1158AM.pdf; PAYMENT MONITOR OUTGOING 111425 - 111525 PG 1 1156AM.pdf; PAYMENT MONITOR OUTGOING 111425 - 111525 PG 2 1156AM.pdf; SWIFT INTERFACE MONITOR INCOMING MT103 111425 - 111525 1152AM.pdf; SWIFT INTERFACE MONITOR INCOMING MT199 111425 -111525 1152AM.pdf.</t>
+        </is>
+      </c>
+      <c r="F62" s="86" t="inlineStr">
+        <is>
+          <t>Samples: 3301, 1903, 1936, 1937; columns: F, M</t>
         </is>
       </c>
       <c r="G62" s="82" t="n"/>
@@ -6990,35 +6844,35 @@
       <c r="R62" s="82" t="n"/>
       <c r="S62" s="82" t="n"/>
     </row>
-    <row r="63" ht="66" customHeight="1" s="71">
+    <row r="63" ht="54" customHeight="1" s="71">
       <c r="A63" s="86" t="inlineStr">
         <is>
-          <t>MA01</t>
+          <t>E09</t>
         </is>
       </c>
       <c r="B63" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg</t>
         </is>
       </c>
       <c r="C63" s="86" t="inlineStr">
         <is>
-          <t>09/23/2026 – Cesar Vidal (BCiC walkthrough)</t>
+          <t>03/03/2026 – 05/05/2026 – Claudia Romero</t>
         </is>
       </c>
       <c r="D63" s="86" t="inlineStr">
         <is>
-          <t>BCiC screenshot</t>
+          <t>Email approval</t>
         </is>
       </c>
       <c r="E63" s="86" t="inlineStr">
         <is>
-          <t>BC in the Cloud 'Applications In Scope for DR Test BSI' view (filter Scope Entity = BSI; 43 items). The 10 tested applications are selected (1822, 1867, 1868, 1903, 1917, 1937, 1936, 3301, 3299, 4052) and each shows 2025 DR Test Scope = True, 2025 Backup/Restore Test Scope = True and 2025 Backup/Restore DIV Scope = True.</t>
+          <t>Client Back Office test evidence (Mariorly Morales, Ilumel Rodriguez, Rolando Bonilla) and Claudia Romero "Approved." 05/05/2026. Thread maps ACH Express, FedExport, FedImport, Imaging101 to Client Back Office / Claudia Romero.</t>
         </is>
       </c>
       <c r="F63" s="86" t="inlineStr">
         <is>
-          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: D, K, N</t>
+          <t>Samples: 1822, 1867, 1868, 3299, 1937; columns: E, G, H, J, M, N, O</t>
         </is>
       </c>
       <c r="G63" s="82" t="n"/>
@@ -7035,35 +6889,35 @@
       <c r="R63" s="82" t="n"/>
       <c r="S63" s="82" t="n"/>
     </row>
-    <row r="64" ht="30" customHeight="1" s="71">
+    <row r="64" ht="42" customHeight="1" s="71">
       <c r="A64" s="86" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>E10</t>
         </is>
       </c>
       <c r="B64" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg</t>
         </is>
       </c>
       <c r="C64" s="86" t="inlineStr">
         <is>
-          <t>BCiC – Applications In Scope for DR Test BSI</t>
+          <t>03/09/2026 – Lina Acuna</t>
         </is>
       </c>
       <c r="D64" s="86" t="inlineStr">
         <is>
-          <t>BCiC export</t>
+          <t>Email approval</t>
         </is>
       </c>
       <c r="E64" s="86" t="inlineStr">
         <is>
-          <t>BCiC export of the BSI DR-scope population (43 applications) with Exercise Date and 2025 DR / Backup-Restore / DIV scope flags.</t>
+          <t>Finance DIV results chart (Jose Acero) and Lina Acuna "Approved" 03/09/2026 (T24 / ReconXpert backup-restore).</t>
         </is>
       </c>
       <c r="F64" s="86" t="inlineStr">
         <is>
-          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: B, C, D, K, L, N</t>
+          <t>Samples: 1917, 1937; columns: M</t>
         </is>
       </c>
       <c r="G64" s="82" t="n"/>
@@ -7080,35 +6934,35 @@
       <c r="R64" s="82" t="n"/>
       <c r="S64" s="82" t="n"/>
     </row>
-    <row r="65" ht="30" customHeight="1" s="71">
+    <row r="65" ht="42" customHeight="1" s="71">
       <c r="A65" s="86" t="inlineStr">
         <is>
-          <t>E02</t>
+          <t>E13</t>
         </is>
       </c>
       <c r="B65" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg</t>
         </is>
       </c>
       <c r="C65" s="86" t="inlineStr">
         <is>
-          <t>09/10/2026 – Cesar Vidal</t>
+          <t>11/13/2024 – T24 backup user</t>
         </is>
       </c>
       <c r="D65" s="86" t="inlineStr">
         <is>
-          <t>BCiC screenshot</t>
+          <t>System email</t>
         </is>
       </c>
       <c r="E65" s="86" t="inlineStr">
         <is>
-          <t>BCiC Applications screen with view 'Applications In Scope for DR Test BSI' selected (1–20 of 43 items).</t>
+          <t>T24 environment refresh log – prior period (outside review period); supplemental only.</t>
         </is>
       </c>
       <c r="F65" s="86" t="inlineStr">
         <is>
-          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: D, K, N</t>
+          <t>Samples: —; columns: — (supplemental)</t>
         </is>
       </c>
       <c r="G65" s="82" t="n"/>
@@ -7128,17 +6982,17 @@
     <row r="66" ht="42" customHeight="1" s="71">
       <c r="A66" s="86" t="inlineStr">
         <is>
-          <t>E03</t>
+          <t>E16b</t>
         </is>
       </c>
       <c r="B66" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
         </is>
       </c>
       <c r="C66" s="86" t="inlineStr">
         <is>
-          <t>BCiC – Data Integrity Validation Testing (62 records)</t>
+          <t>08/2026 – BCiC export sent with attestation request</t>
         </is>
       </c>
       <c r="D66" s="86" t="inlineStr">
@@ -7148,12 +7002,12 @@
       </c>
       <c r="E66" s="86" t="inlineStr">
         <is>
-          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Y/N Format/Headers/Content, Attestation Date / Provided By. Row numbers quoted are Excel rows.</t>
+          <t>BCiC DIV export 2025-26 (64 rows; no manager columns) sent to managers with the attestation request and returned by M. T. Del Cerro (DMA05). Row numbers are Excel rows.</t>
         </is>
       </c>
       <c r="F66" s="86" t="inlineStr">
         <is>
-          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: B, C, D, E, F, G, H, I, K, L, M, O, P</t>
+          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: B, D, E, F, I, K, P</t>
         </is>
       </c>
       <c r="G66" s="82" t="n"/>
@@ -7170,37 +7024,13 @@
       <c r="R66" s="82" t="n"/>
       <c r="S66" s="82" t="n"/>
     </row>
-    <row r="67" ht="42" customHeight="1" s="71">
-      <c r="A67" s="86" t="inlineStr">
-        <is>
-          <t>E04</t>
-        </is>
-      </c>
-      <c r="B67" s="86" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg</t>
-        </is>
-      </c>
-      <c r="C67" s="86" t="inlineStr">
-        <is>
-          <t>09/10/2026 – Cesar Vidal</t>
-        </is>
-      </c>
-      <c r="D67" s="86" t="inlineStr">
-        <is>
-          <t>BCiC screenshot</t>
-        </is>
-      </c>
-      <c r="E67" s="86" t="inlineStr">
-        <is>
-          <t>BCiC 'Data Integrity Validation Testing' screen (1–20 of 66 items) showing tester, validation date, manager, approval date, Y/N results and attestation fields.</t>
-        </is>
-      </c>
-      <c r="F67" s="86" t="inlineStr">
-        <is>
-          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: D, E, F, G, H, K, P</t>
-        </is>
-      </c>
+    <row r="67" s="71">
+      <c r="A67" s="82" t="n"/>
+      <c r="B67" s="82" t="n"/>
+      <c r="C67" s="82" t="n"/>
+      <c r="D67" s="82" t="n"/>
+      <c r="E67" s="82" t="n"/>
+      <c r="F67" s="82" t="n"/>
       <c r="G67" s="82" t="n"/>
       <c r="H67" s="82" t="n"/>
       <c r="I67" s="82" t="n"/>
@@ -7215,43 +7045,12 @@
       <c r="R67" s="82" t="n"/>
       <c r="S67" s="82" t="n"/>
     </row>
-    <row r="68" ht="30" customHeight="1" s="71">
-      <c r="A68" s="86" t="inlineStr">
-        <is>
-          <t>E05</t>
-        </is>
-      </c>
-      <c r="B68" s="86" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg</t>
-        </is>
-      </c>
-      <c r="C68" s="86" t="inlineStr">
-        <is>
-          <t>09/15/2025 – Elizabeth Noda</t>
-        </is>
-      </c>
-      <c r="D68" s="86" t="inlineStr">
-        <is>
-          <t>Meeting invite</t>
-        </is>
-      </c>
-      <c r="E68" s="86" t="inlineStr">
-        <is>
-          <t>IT DR meeting to review the 2025 BIA results and applications list ahead of the DR exercise.</t>
-        </is>
-      </c>
-      <c r="F68" s="86" t="inlineStr">
-        <is>
-          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: M, N</t>
-        </is>
-      </c>
-      <c r="G68" s="82" t="n"/>
-      <c r="H68" s="82" t="n"/>
-      <c r="I68" s="82" t="n"/>
-      <c r="J68" s="82" t="n"/>
-      <c r="K68" s="82" t="n"/>
-      <c r="L68" s="82" t="n"/>
+    <row r="68" ht="22" customHeight="1" s="71">
+      <c r="A68" s="73" t="inlineStr">
+        <is>
+          <t>Observations for reviewer consideration (do not change the PASS conclusions unless the reviewer determines otherwise)</t>
+        </is>
+      </c>
       <c r="M68" s="82" t="n"/>
       <c r="N68" s="82" t="n"/>
       <c r="O68" s="82" t="n"/>
@@ -7261,36 +7060,32 @@
       <c r="S68" s="82" t="n"/>
     </row>
     <row r="69" ht="30" customHeight="1" s="71">
-      <c r="A69" s="86" t="inlineStr">
-        <is>
-          <t>E06</t>
-        </is>
-      </c>
-      <c r="B69" s="86" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml</t>
-        </is>
-      </c>
-      <c r="C69" s="86" t="inlineStr">
-        <is>
-          <t>09/18/2025 – Elizabeth Noda</t>
-        </is>
-      </c>
-      <c r="D69" s="86" t="inlineStr">
-        <is>
-          <t>Meeting invite</t>
-        </is>
-      </c>
-      <c r="E69" s="86" t="inlineStr">
-        <is>
-          <t>Follow-up IT BIA results / DR preparation meeting (applications list review).</t>
-        </is>
-      </c>
-      <c r="F69" s="86" t="inlineStr">
-        <is>
-          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: M, N</t>
-        </is>
-      </c>
+      <c r="A69" s="85" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B69" s="85" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="C69" s="85" t="inlineStr">
+        <is>
+          <t>Samples affected</t>
+        </is>
+      </c>
+      <c r="D69" s="85" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="E69" s="85" t="inlineStr">
+        <is>
+          <t>Impact / reviewer consideration</t>
+        </is>
+      </c>
+      <c r="F69" s="85" t="inlineStr"/>
       <c r="G69" s="82" t="n"/>
       <c r="H69" s="82" t="n"/>
       <c r="I69" s="82" t="n"/>
@@ -7305,37 +7100,31 @@
       <c r="R69" s="82" t="n"/>
       <c r="S69" s="82" t="n"/>
     </row>
-    <row r="70" ht="42" customHeight="1" s="71">
-      <c r="A70" s="86" t="inlineStr">
-        <is>
-          <t>E07</t>
-        </is>
-      </c>
-      <c r="B70" s="86" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg</t>
-        </is>
-      </c>
-      <c r="C70" s="86" t="inlineStr">
-        <is>
-          <t>11/15/2025 – Frank Puentes</t>
-        </is>
-      </c>
-      <c r="D70" s="86" t="inlineStr">
-        <is>
-          <t>Email + 13 attachments</t>
-        </is>
-      </c>
-      <c r="E70" s="86" t="inlineStr">
-        <is>
-          <t>Pre-DR (11/14/2025) source reports: Fedlink, OFAC ACH/FED/SWIFT, Payment Monitor, SWIFT Interface Monitor, outgoing Fedwire/SWIFT. Attachments extracted to E07_Attachments_extracted.</t>
-        </is>
-      </c>
-      <c r="F70" s="86" t="inlineStr">
-        <is>
-          <t>Samples: 3301, 1903, 1936, 1937; columns: F</t>
-        </is>
-      </c>
+    <row r="70" ht="90" customHeight="1" s="71">
+      <c r="A70" s="87" t="n">
+        <v>1</v>
+      </c>
+      <c r="B70" s="87" t="inlineStr">
+        <is>
+          <t>Business line approvals for 33 of 56 in-scope DIV records were obtained through retrospective management attestations dated 08/17/2026 – 09/09/2026, i.e. after the review period end (06/01/2026) and ~9-10 months after the 11/15/2025 DIV testing. A further 13 records (BSA/AML/OFAC and Payments) carry in-period BCiC approval dates (11/15/2025, 12/18/2025) supported only by 08/2026 signed attestations. 10 records have in-period approval emails (E09, BLA06).</t>
+        </is>
+      </c>
+      <c r="C70" s="87" t="inlineStr">
+        <is>
+          <t>3299, 4052, 3301, 1903, 1936, 1937</t>
+        </is>
+      </c>
+      <c r="D70" s="87" t="inlineStr">
+        <is>
+          <t>Folder 03 (DMA01–DMA12); E03 approval dates</t>
+        </is>
+      </c>
+      <c r="E70" s="87" t="inlineStr">
+        <is>
+          <t>Approval is evidenced for 100% of records; timing is an observation. The attestation (DMA02 attachment §3.6) commits to contemporaneous approval going forward. Reviewer to conclude whether retrospective approval satisfies the control for the period.</t>
+        </is>
+      </c>
+      <c r="F70" s="87" t="inlineStr"/>
       <c r="G70" s="82" t="n"/>
       <c r="H70" s="82" t="n"/>
       <c r="I70" s="82" t="n"/>
@@ -7350,37 +7139,31 @@
       <c r="R70" s="82" t="n"/>
       <c r="S70" s="82" t="n"/>
     </row>
-    <row r="71" ht="30" customHeight="1" s="71">
-      <c r="A71" s="86" t="inlineStr">
-        <is>
-          <t>E08</t>
-        </is>
-      </c>
-      <c r="B71" s="86" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg</t>
-        </is>
-      </c>
-      <c r="C71" s="86" t="inlineStr">
-        <is>
-          <t>11/15/2025 – Frank Puentes</t>
-        </is>
-      </c>
-      <c r="D71" s="86" t="inlineStr">
-        <is>
-          <t>Email + 13 attachments</t>
-        </is>
-      </c>
-      <c r="E71" s="86" t="inlineStr">
-        <is>
-          <t>DR test-day (11/15/2025) re-run of the same reports for comparison with 11/14/2025 source. Attachments extracted to E08_Attachments_extracted.</t>
-        </is>
-      </c>
-      <c r="F71" s="86" t="inlineStr">
-        <is>
-          <t>Samples: 3301, 1903, 1936, 1937; columns: F, M</t>
-        </is>
-      </c>
+    <row r="71" ht="78" customHeight="1" s="71">
+      <c r="A71" s="87" t="n">
+        <v>2</v>
+      </c>
+      <c r="B71" s="87" t="inlineStr">
+        <is>
+          <t>Self-approval: the business tester and the approving Department Manager are the same person for BSA/AML/OFAC (David Marquez), Payments (Franklin Puentes), Investment Operations (Michelle Oropesa), Treasury (Martha Sullivan), Digital Wealth (Victoria Fernandez), Client Servicing Unit (Liliana Vizhnay), Commercial Middle Office (Miguel Orozco – Imaging101 / T24 row 15, 51) and Financial Analysis (Sadis Alvarenga).</t>
+        </is>
+      </c>
+      <c r="C71" s="87" t="inlineStr">
+        <is>
+          <t>3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
+        </is>
+      </c>
+      <c r="D71" s="87" t="inlineStr">
+        <is>
+          <t>E03 tester vs manager columns</t>
+        </is>
+      </c>
+      <c r="E71" s="87" t="inlineStr">
+        <is>
+          <t>Segregation-of-duties observation; the approvers are the business line heads for those areas.</t>
+        </is>
+      </c>
+      <c r="F71" s="87" t="inlineStr"/>
       <c r="G71" s="82" t="n"/>
       <c r="H71" s="82" t="n"/>
       <c r="I71" s="82" t="n"/>
@@ -7395,37 +7178,31 @@
       <c r="R71" s="82" t="n"/>
       <c r="S71" s="82" t="n"/>
     </row>
-    <row r="72" ht="54" customHeight="1" s="71">
-      <c r="A72" s="86" t="inlineStr">
-        <is>
-          <t>E09</t>
-        </is>
-      </c>
-      <c r="B72" s="86" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg</t>
-        </is>
-      </c>
-      <c r="C72" s="86" t="inlineStr">
-        <is>
-          <t>03/03/2026 – 05/05/2026 – Claudia Romero</t>
-        </is>
-      </c>
-      <c r="D72" s="86" t="inlineStr">
-        <is>
-          <t>Email approval</t>
-        </is>
-      </c>
-      <c r="E72" s="86" t="inlineStr">
-        <is>
-          <t>Client Back Office test evidence (Mariorly Morales, Ilumel Rodriguez, Rolando Bonilla) and Claudia Romero "Approved." 05/05/2026. Thread maps ACH Express, FedExport, FedImport, Imaging101 to Client Back Office / Claudia Romero.</t>
-        </is>
-      </c>
-      <c r="F72" s="86" t="inlineStr">
-        <is>
-          <t>Samples: 1822, 1867, 1868, 3299, 1937; columns: E, G, H, J, M, N, O</t>
-        </is>
-      </c>
+    <row r="72" ht="30" customHeight="1" s="71">
+      <c r="A72" s="87" t="n">
+        <v>3</v>
+      </c>
+      <c r="B72" s="87" t="inlineStr">
+        <is>
+          <t>FedExport – BCiC Department Manager Approval Date 06/05/2026 (E03 row 9, E04) vs Claudia Romero "Approved." 05/05/2026 (E09).</t>
+        </is>
+      </c>
+      <c r="C72" s="87" t="inlineStr">
+        <is>
+          <t>1867</t>
+        </is>
+      </c>
+      <c r="D72" s="87" t="inlineStr">
+        <is>
+          <t>E03, E04, E09</t>
+        </is>
+      </c>
+      <c r="E72" s="87" t="inlineStr">
+        <is>
+          <t>Likely BCiC data-entry error; recommend management correct the BCiC record.</t>
+        </is>
+      </c>
+      <c r="F72" s="87" t="inlineStr"/>
       <c r="G72" s="82" t="n"/>
       <c r="H72" s="82" t="n"/>
       <c r="I72" s="82" t="n"/>
@@ -7440,37 +7217,31 @@
       <c r="R72" s="82" t="n"/>
       <c r="S72" s="82" t="n"/>
     </row>
-    <row r="73" ht="42" customHeight="1" s="71">
-      <c r="A73" s="86" t="inlineStr">
-        <is>
-          <t>E10</t>
-        </is>
-      </c>
-      <c r="B73" s="86" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg</t>
-        </is>
-      </c>
-      <c r="C73" s="86" t="inlineStr">
-        <is>
-          <t>03/09/2026 – Lina Acuna</t>
-        </is>
-      </c>
-      <c r="D73" s="86" t="inlineStr">
-        <is>
-          <t>Email approval</t>
-        </is>
-      </c>
-      <c r="E73" s="86" t="inlineStr">
-        <is>
-          <t>Finance DIV results chart (Jose Acero) and Lina Acuna "Approved" 03/09/2026 (T24 / ReconXpert backup-restore).</t>
-        </is>
-      </c>
-      <c r="F73" s="86" t="inlineStr">
-        <is>
-          <t>Samples: 1917, 1937; columns: M</t>
-        </is>
-      </c>
+    <row r="73" ht="30" customHeight="1" s="71">
+      <c r="A73" s="87" t="n">
+        <v>4</v>
+      </c>
+      <c r="B73" s="87" t="inlineStr">
+        <is>
+          <t>BLA02 (BSA/AML/OFAC) test script – DIV Yes/No answer boxes are blank.</t>
+        </is>
+      </c>
+      <c r="C73" s="87" t="inlineStr">
+        <is>
+          <t>3299, 1903, 1936, 1937</t>
+        </is>
+      </c>
+      <c r="D73" s="87" t="inlineStr">
+        <is>
+          <t>BLA02 p.1</t>
+        </is>
+      </c>
+      <c r="E73" s="87" t="inlineStr">
+        <is>
+          <t>Mitigated by production vs test-day screenshots in BLA02, BCiC Y/Y/Y (E03) and signed attestation (DMA02 attachment).</t>
+        </is>
+      </c>
+      <c r="F73" s="87" t="inlineStr"/>
       <c r="G73" s="82" t="n"/>
       <c r="H73" s="82" t="n"/>
       <c r="I73" s="82" t="n"/>
@@ -7485,37 +7256,31 @@
       <c r="R73" s="82" t="n"/>
       <c r="S73" s="82" t="n"/>
     </row>
-    <row r="74" ht="42" customHeight="1" s="71">
-      <c r="A74" s="86" t="inlineStr">
-        <is>
-          <t>E13</t>
-        </is>
-      </c>
-      <c r="B74" s="86" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg</t>
-        </is>
-      </c>
-      <c r="C74" s="86" t="inlineStr">
-        <is>
-          <t>11/13/2024 – T24 backup user</t>
-        </is>
-      </c>
-      <c r="D74" s="86" t="inlineStr">
-        <is>
-          <t>System email</t>
-        </is>
-      </c>
-      <c r="E74" s="86" t="inlineStr">
-        <is>
-          <t>T24 environment refresh log – prior period (outside review period); supplemental only.</t>
-        </is>
-      </c>
-      <c r="F74" s="86" t="inlineStr">
-        <is>
-          <t>Samples: —; columns: — (supplemental)</t>
-        </is>
-      </c>
+    <row r="74" ht="54" customHeight="1" s="71">
+      <c r="A74" s="87" t="n">
+        <v>5</v>
+      </c>
+      <c r="B74" s="87" t="inlineStr">
+        <is>
+          <t>BSA T24 record (E03 row 8) Attestation Date 08/29/2026 vs signed attestation 8/19/2026 (DMA02 attachment); Financial Risk manager recorded as "Xavier Caisapanta" in BCiC while the approval email is from Ivan Caisapanta (DMA08).</t>
+        </is>
+      </c>
+      <c r="C74" s="87" t="inlineStr">
+        <is>
+          <t>1937</t>
+        </is>
+      </c>
+      <c r="D74" s="87" t="inlineStr">
+        <is>
+          <t>E03, DMA02, DMA08</t>
+        </is>
+      </c>
+      <c r="E74" s="87" t="inlineStr">
+        <is>
+          <t>BCiC data-entry / naming consistency; confirm identity of Financial Risk approver.</t>
+        </is>
+      </c>
+      <c r="F74" s="87" t="inlineStr"/>
       <c r="G74" s="82" t="n"/>
       <c r="H74" s="82" t="n"/>
       <c r="I74" s="82" t="n"/>
@@ -7531,36 +7296,30 @@
       <c r="S74" s="82" t="n"/>
     </row>
     <row r="75" ht="42" customHeight="1" s="71">
-      <c r="A75" s="86" t="inlineStr">
-        <is>
-          <t>E16b</t>
-        </is>
-      </c>
-      <c r="B75" s="86" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
-        </is>
-      </c>
-      <c r="C75" s="86" t="inlineStr">
-        <is>
-          <t>08/2026 – BCiC export sent with attestation request</t>
-        </is>
-      </c>
-      <c r="D75" s="86" t="inlineStr">
-        <is>
-          <t>BCiC export</t>
-        </is>
-      </c>
-      <c r="E75" s="86" t="inlineStr">
-        <is>
-          <t>BCiC DIV export 2025-26 (64 rows; no manager columns) sent to managers with the attestation request and returned by M. T. Del Cerro (DMA05). Row numbers are Excel rows.</t>
-        </is>
-      </c>
-      <c r="F75" s="86" t="inlineStr">
-        <is>
-          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: B, D, E, F, I, K, P</t>
-        </is>
-      </c>
+      <c r="A75" s="87" t="n">
+        <v>6</v>
+      </c>
+      <c r="B75" s="87" t="inlineStr">
+        <is>
+          <t>ACH Express and Interface Monitor are not named verbatim in the DIV "Application In-scope" lines of BLA01 / BLA04; BLA01 operator (Raimy Ayala) differs from BCiC tester (Andreina De Stefano).</t>
+        </is>
+      </c>
+      <c r="C75" s="87" t="inlineStr">
+        <is>
+          <t>1822, 4052, 1867, 1868</t>
+        </is>
+      </c>
+      <c r="D75" s="87" t="inlineStr">
+        <is>
+          <t>BLA01, BLA04, E03, MA01</t>
+        </is>
+      </c>
+      <c r="E75" s="87" t="inlineStr">
+        <is>
+          <t>Application-level DIV records exist in BCiC (E03 rows 47 and 61) with Y/Y/Y results and manager approval.</t>
+        </is>
+      </c>
+      <c r="F75" s="87" t="inlineStr"/>
       <c r="G75" s="82" t="n"/>
       <c r="H75" s="82" t="n"/>
       <c r="I75" s="82" t="n"/>
@@ -7575,13 +7334,31 @@
       <c r="R75" s="82" t="n"/>
       <c r="S75" s="82" t="n"/>
     </row>
-    <row r="76" s="71">
-      <c r="A76" s="82" t="n"/>
-      <c r="B76" s="82" t="n"/>
-      <c r="C76" s="82" t="n"/>
-      <c r="D76" s="82" t="n"/>
-      <c r="E76" s="82" t="n"/>
-      <c r="F76" s="82" t="n"/>
+    <row r="76" ht="54" customHeight="1" s="71">
+      <c r="A76" s="87" t="n">
+        <v>7</v>
+      </c>
+      <c r="B76" s="87" t="inlineStr">
+        <is>
+          <t>Count reconciliation – E03 contains 62 DIV records (56 for the 10 tested applications); E16b contains 64 rows (one additional Treasury T24 row with blank department, row 45); the attestation states 63 entries / 13 applications.</t>
+        </is>
+      </c>
+      <c r="C76" s="87" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D76" s="87" t="inlineStr">
+        <is>
+          <t>E03, E16b, DMA02</t>
+        </is>
+      </c>
+      <c r="E76" s="87" t="inlineStr">
+        <is>
+          <t>Testing performed on E03 (the export containing the manager approval fields).</t>
+        </is>
+      </c>
+      <c r="F76" s="87" t="inlineStr"/>
       <c r="G76" s="82" t="n"/>
       <c r="H76" s="82" t="n"/>
       <c r="I76" s="82" t="n"/>
@@ -7596,12 +7373,37 @@
       <c r="R76" s="82" t="n"/>
       <c r="S76" s="82" t="n"/>
     </row>
-    <row r="77" ht="22" customHeight="1" s="71">
-      <c r="A77" s="73" t="inlineStr">
-        <is>
-          <t>Observations for reviewer consideration (do not change the PASS conclusions unless the reviewer determines otherwise)</t>
-        </is>
-      </c>
+    <row r="77" ht="30" customHeight="1" s="71">
+      <c r="A77" s="87" t="n">
+        <v>8</v>
+      </c>
+      <c r="B77" s="87" t="inlineStr">
+        <is>
+          <t>Annual interval – prior DR exercise 10/19/2024 to 11/15/2025 = 392 days; one exercise per annual DR cycle (2024, 2025) and within the review period.</t>
+        </is>
+      </c>
+      <c r="C77" s="87" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D77" s="87" t="inlineStr">
+        <is>
+          <t>Tab 'DR 2024 Testing Results'; E01; E03</t>
+        </is>
+      </c>
+      <c r="E77" s="87" t="inlineStr">
+        <is>
+          <t>Annual requirement assessed per DR cycle.</t>
+        </is>
+      </c>
+      <c r="F77" s="87" t="inlineStr"/>
+      <c r="G77" s="82" t="n"/>
+      <c r="H77" s="82" t="n"/>
+      <c r="I77" s="82" t="n"/>
+      <c r="J77" s="82" t="n"/>
+      <c r="K77" s="82" t="n"/>
+      <c r="L77" s="82" t="n"/>
       <c r="M77" s="82" t="n"/>
       <c r="N77" s="82" t="n"/>
       <c r="O77" s="82" t="n"/>
@@ -7610,33 +7412,31 @@
       <c r="R77" s="82" t="n"/>
       <c r="S77" s="82" t="n"/>
     </row>
-    <row r="78" ht="30" customHeight="1" s="71">
-      <c r="A78" s="85" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B78" s="85" t="inlineStr">
-        <is>
-          <t>Observation</t>
-        </is>
-      </c>
-      <c r="C78" s="85" t="inlineStr">
-        <is>
-          <t>Samples affected</t>
-        </is>
-      </c>
-      <c r="D78" s="85" t="inlineStr">
-        <is>
-          <t>Evidence</t>
-        </is>
-      </c>
-      <c r="E78" s="85" t="inlineStr">
-        <is>
-          <t>Impact / reviewer consideration</t>
-        </is>
-      </c>
-      <c r="F78" s="85" t="inlineStr"/>
+    <row r="78" ht="102" customHeight="1" s="71">
+      <c r="A78" s="87" t="n">
+        <v>9</v>
+      </c>
+      <c r="B78" s="87" t="inlineStr">
+        <is>
+          <t>Redundant files removed: 13 duplicate evidence files (byte-identical copies or the same email saved twice: E11, E12, E14, E14a, E15, E15a, E16, E16a, E17, E17a, MA02, DMA05b, E06) and the extracted attachment copies (8 signed attestation PDFs, 26 E07/E08 report files) and E06 (same meeting invite as E05, re-sent) were removed; each item is retained once – signed attestations and report files are cited through the email that contains them (see Evidence Index – files removed). E13 (11/13/2024) is prior period – supplemental only. DMA13 (Cisco Call Manager) is out of scope.</t>
+        </is>
+      </c>
+      <c r="C78" s="87" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D78" s="87" t="inlineStr">
+        <is>
+          <t>Evidence Index tab</t>
+        </is>
+      </c>
+      <c r="E78" s="87" t="inlineStr">
+        <is>
+          <t>No impact – retained copy carries identical content.</t>
+        </is>
+      </c>
+      <c r="F78" s="87" t="inlineStr"/>
       <c r="G78" s="82" t="n"/>
       <c r="H78" s="82" t="n"/>
       <c r="I78" s="82" t="n"/>
@@ -7651,31 +7451,13 @@
       <c r="R78" s="82" t="n"/>
       <c r="S78" s="82" t="n"/>
     </row>
-    <row r="79" ht="90" customHeight="1" s="71">
-      <c r="A79" s="87" t="n">
-        <v>1</v>
-      </c>
-      <c r="B79" s="87" t="inlineStr">
-        <is>
-          <t>Business line approvals for 33 of 56 in-scope DIV records were obtained through retrospective management attestations dated 08/17/2026 – 09/09/2026, i.e. after the review period end (06/01/2026) and ~9-10 months after the 11/15/2025 DIV testing. A further 13 records (BSA/AML/OFAC and Payments) carry in-period BCiC approval dates (11/15/2025, 12/18/2025) supported only by 08/2026 signed attestations. 10 records have in-period approval emails (E09, BLA06).</t>
-        </is>
-      </c>
-      <c r="C79" s="87" t="inlineStr">
-        <is>
-          <t>3299, 4052, 3301, 1903, 1936, 1937</t>
-        </is>
-      </c>
-      <c r="D79" s="87" t="inlineStr">
-        <is>
-          <t>Folder 03 (DMA01–DMA12); E03 approval dates</t>
-        </is>
-      </c>
-      <c r="E79" s="87" t="inlineStr">
-        <is>
-          <t>Approval is evidenced for 100% of records; timing is an observation. The attestation (DMA02a §3.6) commits to contemporaneous approval going forward. Reviewer to conclude whether retrospective approval satisfies the control for the period.</t>
-        </is>
-      </c>
-      <c r="F79" s="87" t="inlineStr"/>
+    <row r="79" s="71">
+      <c r="A79" s="82" t="n"/>
+      <c r="B79" s="82" t="n"/>
+      <c r="C79" s="82" t="n"/>
+      <c r="D79" s="82" t="n"/>
+      <c r="E79" s="82" t="n"/>
+      <c r="F79" s="82" t="n"/>
       <c r="G79" s="82" t="n"/>
       <c r="H79" s="82" t="n"/>
       <c r="I79" s="82" t="n"/>
@@ -7690,37 +7472,12 @@
       <c r="R79" s="82" t="n"/>
       <c r="S79" s="82" t="n"/>
     </row>
-    <row r="80" ht="78" customHeight="1" s="71">
-      <c r="A80" s="87" t="n">
-        <v>2</v>
-      </c>
-      <c r="B80" s="87" t="inlineStr">
-        <is>
-          <t>Self-approval: the business tester and the approving Department Manager are the same person for BSA/AML/OFAC (David Marquez), Payments (Franklin Puentes), Investment Operations (Michelle Oropesa), Treasury (Martha Sullivan), Digital Wealth (Victoria Fernandez), Client Servicing Unit (Liliana Vizhnay), Commercial Middle Office (Miguel Orozco – Imaging101 / T24 row 15, 51) and Financial Analysis (Sadis Alvarenga).</t>
-        </is>
-      </c>
-      <c r="C80" s="87" t="inlineStr">
-        <is>
-          <t>3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
-        </is>
-      </c>
-      <c r="D80" s="87" t="inlineStr">
-        <is>
-          <t>E03 tester vs manager columns</t>
-        </is>
-      </c>
-      <c r="E80" s="87" t="inlineStr">
-        <is>
-          <t>Segregation-of-duties observation; the approvers are the business line heads for those areas.</t>
-        </is>
-      </c>
-      <c r="F80" s="87" t="inlineStr"/>
-      <c r="G80" s="82" t="n"/>
-      <c r="H80" s="82" t="n"/>
-      <c r="I80" s="82" t="n"/>
-      <c r="J80" s="82" t="n"/>
-      <c r="K80" s="82" t="n"/>
-      <c r="L80" s="82" t="n"/>
+    <row r="80" ht="22" customHeight="1" s="71">
+      <c r="A80" s="73" t="inlineStr">
+        <is>
+          <t>Reviewer Note</t>
+        </is>
+      </c>
       <c r="M80" s="82" t="n"/>
       <c r="N80" s="82" t="n"/>
       <c r="O80" s="82" t="n"/>
@@ -7729,37 +7486,12 @@
       <c r="R80" s="82" t="n"/>
       <c r="S80" s="82" t="n"/>
     </row>
-    <row r="81" ht="30" customHeight="1" s="71">
-      <c r="A81" s="87" t="n">
-        <v>3</v>
-      </c>
-      <c r="B81" s="87" t="inlineStr">
-        <is>
-          <t>FedExport – BCiC Department Manager Approval Date 06/05/2026 (E03 row 9, E04) vs Claudia Romero "Approved." 05/05/2026 (E09).</t>
-        </is>
-      </c>
-      <c r="C81" s="87" t="inlineStr">
-        <is>
-          <t>1867</t>
-        </is>
-      </c>
-      <c r="D81" s="87" t="inlineStr">
-        <is>
-          <t>E03, E04, E09</t>
-        </is>
-      </c>
-      <c r="E81" s="87" t="inlineStr">
-        <is>
-          <t>Likely BCiC data-entry error; recommend management correct the BCiC record.</t>
-        </is>
-      </c>
-      <c r="F81" s="87" t="inlineStr"/>
-      <c r="G81" s="82" t="n"/>
-      <c r="H81" s="82" t="n"/>
-      <c r="I81" s="82" t="n"/>
-      <c r="J81" s="82" t="n"/>
-      <c r="K81" s="82" t="n"/>
-      <c r="L81" s="82" t="n"/>
+    <row r="81" ht="75" customHeight="1" s="71">
+      <c r="A81" s="88" t="inlineStr">
+        <is>
+          <t>All requested attributes (IT DR exercise name, annual execution, application, tester, business data validation, manager name/approval dates, DIV procedures, approval emails, BCiC evidence, Annual Testing Executed, DIV Performed by IT DR Team, Applications in Scope Identified, Business Line Approval of Results, Results Documented in BCMS, overall assessment, supporting evidence and sample result) are completed for the 10 in-scope applications (56 DIV records) and every conclusion is linked to its evidence file and folder location in BSI.IT.6.C7.3-Evidences. Applications in Scope Identified is based on MA01 (BSI In-Scope Applications-2026). Business Line Approval of Results is based on the Business Line Approval Results – Email folder (BLA01–BLA06) together with the application-specific approval emails / signed attestations (folder 03, E09).</t>
+        </is>
+      </c>
       <c r="M81" s="82" t="n"/>
       <c r="N81" s="82" t="n"/>
       <c r="O81" s="82" t="n"/>
@@ -7768,31 +7500,13 @@
       <c r="R81" s="82" t="n"/>
       <c r="S81" s="82" t="n"/>
     </row>
-    <row r="82" ht="30" customHeight="1" s="71">
-      <c r="A82" s="87" t="n">
-        <v>4</v>
-      </c>
-      <c r="B82" s="87" t="inlineStr">
-        <is>
-          <t>BLA02 (BSA/AML/OFAC) test script – DIV Yes/No answer boxes are blank.</t>
-        </is>
-      </c>
-      <c r="C82" s="87" t="inlineStr">
-        <is>
-          <t>3299, 1903, 1936, 1937</t>
-        </is>
-      </c>
-      <c r="D82" s="87" t="inlineStr">
-        <is>
-          <t>BLA02 p.1</t>
-        </is>
-      </c>
-      <c r="E82" s="87" t="inlineStr">
-        <is>
-          <t>Mitigated by production vs test-day screenshots in BLA02, BCiC Y/Y/Y (E03) and signed attestation (DMA02a).</t>
-        </is>
-      </c>
-      <c r="F82" s="87" t="inlineStr"/>
+    <row r="82" s="71">
+      <c r="A82" s="82" t="n"/>
+      <c r="B82" s="82" t="n"/>
+      <c r="C82" s="82" t="n"/>
+      <c r="D82" s="82" t="n"/>
+      <c r="E82" s="82" t="n"/>
+      <c r="F82" s="82" t="n"/>
       <c r="G82" s="82" t="n"/>
       <c r="H82" s="82" t="n"/>
       <c r="I82" s="82" t="n"/>
@@ -7807,31 +7521,13 @@
       <c r="R82" s="82" t="n"/>
       <c r="S82" s="82" t="n"/>
     </row>
-    <row r="83" ht="42" customHeight="1" s="71">
-      <c r="A83" s="87" t="n">
-        <v>5</v>
-      </c>
-      <c r="B83" s="87" t="inlineStr">
-        <is>
-          <t>BSA T24 record (E03 row 8) Attestation Date 08/29/2026 vs signed attestation 8/19/2026 (DMA02a); Financial Risk manager recorded as "Xavier Caisapanta" in BCiC while the approval email is from Ivan Caisapanta (DMA08).</t>
-        </is>
-      </c>
-      <c r="C83" s="87" t="inlineStr">
-        <is>
-          <t>1937</t>
-        </is>
-      </c>
-      <c r="D83" s="87" t="inlineStr">
-        <is>
-          <t>E03, DMA02a, DMA08</t>
-        </is>
-      </c>
-      <c r="E83" s="87" t="inlineStr">
-        <is>
-          <t>BCiC data-entry / naming consistency; confirm identity of Financial Risk approver.</t>
-        </is>
-      </c>
-      <c r="F83" s="87" t="inlineStr"/>
+    <row r="83" s="71">
+      <c r="A83" s="82" t="n"/>
+      <c r="B83" s="82" t="n"/>
+      <c r="C83" s="82" t="n"/>
+      <c r="D83" s="82" t="n"/>
+      <c r="E83" s="82" t="n"/>
+      <c r="F83" s="82" t="n"/>
       <c r="G83" s="82" t="n"/>
       <c r="H83" s="82" t="n"/>
       <c r="I83" s="82" t="n"/>
@@ -7846,31 +7542,13 @@
       <c r="R83" s="82" t="n"/>
       <c r="S83" s="82" t="n"/>
     </row>
-    <row r="84" ht="42" customHeight="1" s="71">
-      <c r="A84" s="87" t="n">
-        <v>6</v>
-      </c>
-      <c r="B84" s="87" t="inlineStr">
-        <is>
-          <t>ACH Express and Interface Monitor are not named verbatim in the DIV "Application In-scope" lines of BLA01 / BLA04; BLA01 operator (Raimy Ayala) differs from BCiC tester (Andreina De Stefano).</t>
-        </is>
-      </c>
-      <c r="C84" s="87" t="inlineStr">
-        <is>
-          <t>1822, 4052, 1867, 1868</t>
-        </is>
-      </c>
-      <c r="D84" s="87" t="inlineStr">
-        <is>
-          <t>BLA01, BLA04, E03, MA01</t>
-        </is>
-      </c>
-      <c r="E84" s="87" t="inlineStr">
-        <is>
-          <t>Application-level DIV records exist in BCiC (E03 rows 47 and 61) with Y/Y/Y results and manager approval.</t>
-        </is>
-      </c>
-      <c r="F84" s="87" t="inlineStr"/>
+    <row r="84" s="71">
+      <c r="A84" s="82" t="n"/>
+      <c r="B84" s="82" t="n"/>
+      <c r="C84" s="82" t="n"/>
+      <c r="D84" s="82" t="n"/>
+      <c r="E84" s="82" t="n"/>
+      <c r="F84" s="82" t="n"/>
       <c r="G84" s="82" t="n"/>
       <c r="H84" s="82" t="n"/>
       <c r="I84" s="82" t="n"/>
@@ -7885,31 +7563,13 @@
       <c r="R84" s="82" t="n"/>
       <c r="S84" s="82" t="n"/>
     </row>
-    <row r="85" ht="54" customHeight="1" s="71">
-      <c r="A85" s="87" t="n">
-        <v>7</v>
-      </c>
-      <c r="B85" s="87" t="inlineStr">
-        <is>
-          <t>Count reconciliation – E03 contains 62 DIV records (56 for the 10 tested applications); E16b contains 64 rows (one additional Treasury T24 row with blank department, row 45); the attestation states 63 entries / 13 applications.</t>
-        </is>
-      </c>
-      <c r="C85" s="87" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D85" s="87" t="inlineStr">
-        <is>
-          <t>E03, E16b, DMA02a</t>
-        </is>
-      </c>
-      <c r="E85" s="87" t="inlineStr">
-        <is>
-          <t>Testing performed on E03 (the export containing the manager approval fields).</t>
-        </is>
-      </c>
-      <c r="F85" s="87" t="inlineStr"/>
+    <row r="85" s="71">
+      <c r="A85" s="82" t="n"/>
+      <c r="B85" s="82" t="n"/>
+      <c r="C85" s="82" t="n"/>
+      <c r="D85" s="82" t="n"/>
+      <c r="E85" s="82" t="n"/>
+      <c r="F85" s="82" t="n"/>
       <c r="G85" s="82" t="n"/>
       <c r="H85" s="82" t="n"/>
       <c r="I85" s="82" t="n"/>
@@ -7924,31 +7584,13 @@
       <c r="R85" s="82" t="n"/>
       <c r="S85" s="82" t="n"/>
     </row>
-    <row r="86" ht="30" customHeight="1" s="71">
-      <c r="A86" s="87" t="n">
-        <v>8</v>
-      </c>
-      <c r="B86" s="87" t="inlineStr">
-        <is>
-          <t>Annual interval – prior DR exercise 10/19/2024 to 11/15/2025 = 392 days; one exercise per annual DR cycle (2024, 2025) and within the review period.</t>
-        </is>
-      </c>
-      <c r="C86" s="87" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D86" s="87" t="inlineStr">
-        <is>
-          <t>Tab 'DR 2024 Testing Results'; E01; E03</t>
-        </is>
-      </c>
-      <c r="E86" s="87" t="inlineStr">
-        <is>
-          <t>Annual requirement assessed per DR cycle.</t>
-        </is>
-      </c>
-      <c r="F86" s="87" t="inlineStr"/>
+    <row r="86" s="71">
+      <c r="A86" s="82" t="n"/>
+      <c r="B86" s="82" t="n"/>
+      <c r="C86" s="82" t="n"/>
+      <c r="D86" s="82" t="n"/>
+      <c r="E86" s="82" t="n"/>
+      <c r="F86" s="82" t="n"/>
       <c r="G86" s="82" t="n"/>
       <c r="H86" s="82" t="n"/>
       <c r="I86" s="82" t="n"/>
@@ -7963,31 +7605,13 @@
       <c r="R86" s="82" t="n"/>
       <c r="S86" s="82" t="n"/>
     </row>
-    <row r="87" ht="66" customHeight="1" s="71">
-      <c r="A87" s="87" t="n">
-        <v>9</v>
-      </c>
-      <c r="B87" s="87" t="inlineStr">
-        <is>
-          <t>Duplicate evidence removed: 12 files that were byte-identical copies or the same email message saved twice (E11, E12, E14, E14a, E15, E15a, E16, E16a, E17, E17a, MA02, DMA05b) were removed; one copy of each is retained (see Evidence Index – Duplicate files removed). E13 (11/13/2024) is prior period – supplemental only. DMA13 (Cisco Call Manager) is out of scope.</t>
-        </is>
-      </c>
-      <c r="C87" s="87" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D87" s="87" t="inlineStr">
-        <is>
-          <t>Evidence Index tab</t>
-        </is>
-      </c>
-      <c r="E87" s="87" t="inlineStr">
-        <is>
-          <t>No impact – retained copy carries identical content.</t>
-        </is>
-      </c>
-      <c r="F87" s="87" t="inlineStr"/>
+    <row r="87" s="71">
+      <c r="A87" s="82" t="n"/>
+      <c r="B87" s="82" t="n"/>
+      <c r="C87" s="82" t="n"/>
+      <c r="D87" s="82" t="n"/>
+      <c r="E87" s="82" t="n"/>
+      <c r="F87" s="82" t="n"/>
       <c r="G87" s="82" t="n"/>
       <c r="H87" s="82" t="n"/>
       <c r="I87" s="82" t="n"/>
@@ -8023,12 +7647,19 @@
       <c r="R88" s="82" t="n"/>
       <c r="S88" s="82" t="n"/>
     </row>
-    <row r="89" ht="22" customHeight="1" s="71">
-      <c r="A89" s="73" t="inlineStr">
-        <is>
-          <t>Reviewer Note</t>
-        </is>
-      </c>
+    <row r="89" s="71">
+      <c r="A89" s="82" t="n"/>
+      <c r="B89" s="82" t="n"/>
+      <c r="C89" s="82" t="n"/>
+      <c r="D89" s="82" t="n"/>
+      <c r="E89" s="82" t="n"/>
+      <c r="F89" s="82" t="n"/>
+      <c r="G89" s="82" t="n"/>
+      <c r="H89" s="82" t="n"/>
+      <c r="I89" s="82" t="n"/>
+      <c r="J89" s="82" t="n"/>
+      <c r="K89" s="82" t="n"/>
+      <c r="L89" s="82" t="n"/>
       <c r="M89" s="82" t="n"/>
       <c r="N89" s="82" t="n"/>
       <c r="O89" s="82" t="n"/>
@@ -8037,12 +7668,19 @@
       <c r="R89" s="82" t="n"/>
       <c r="S89" s="82" t="n"/>
     </row>
-    <row r="90" ht="75" customHeight="1" s="71">
-      <c r="A90" s="88" t="inlineStr">
-        <is>
-          <t>All requested attributes (IT DR exercise name, annual execution, application, tester, business data validation, manager name/approval dates, DIV procedures, approval emails, BCiC evidence, Annual Testing Executed, DIV Performed by IT DR Team, Applications in Scope Identified, Business Line Approval of Results, Results Documented in BCMS, overall assessment, supporting evidence and sample result) are completed for the 10 in-scope applications (56 DIV records) and every conclusion is linked to its evidence file and folder location in BSI.IT.6.C7.3-Evidences. Applications in Scope Identified is based on MA01 (BSI In-Scope Applications-2026). Business Line Approval of Results is based on the Business Line Approval Results – Email folder (BLA01–BLA06) together with the application-specific approval emails / signed attestations (folder 03, E09).</t>
-        </is>
-      </c>
+    <row r="90" s="71">
+      <c r="A90" s="82" t="n"/>
+      <c r="B90" s="82" t="n"/>
+      <c r="C90" s="82" t="n"/>
+      <c r="D90" s="82" t="n"/>
+      <c r="E90" s="82" t="n"/>
+      <c r="F90" s="82" t="n"/>
+      <c r="G90" s="82" t="n"/>
+      <c r="H90" s="82" t="n"/>
+      <c r="I90" s="82" t="n"/>
+      <c r="J90" s="82" t="n"/>
+      <c r="K90" s="82" t="n"/>
+      <c r="L90" s="82" t="n"/>
       <c r="M90" s="82" t="n"/>
       <c r="N90" s="82" t="n"/>
       <c r="O90" s="82" t="n"/>
@@ -9103,14 +8741,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A81:L81"/>
     <mergeCell ref="A15:L15"/>
-    <mergeCell ref="A90:L90"/>
+    <mergeCell ref="A68:L68"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A28:L28"/>
     <mergeCell ref="A37:L37"/>
-    <mergeCell ref="A89:L89"/>
-    <mergeCell ref="A61:L61"/>
-    <mergeCell ref="A77:L77"/>
+    <mergeCell ref="A80:L80"/>
+    <mergeCell ref="A53:L53"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -9306,8 +8944,7 @@
         <is>
           <t>• E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 47 – 'Department Manager Approval Date' and 'Attestation Date' columns
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-• DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-• DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf</t>
+• DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
         </is>
       </c>
       <c r="H5" s="62" t="inlineStr">
@@ -9320,8 +8957,7 @@
       <c r="I5" s="62" t="inlineStr">
         <is>
           <t>• E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-• DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-• DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf</t>
+• DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
         </is>
       </c>
       <c r="J5" s="62" t="inlineStr">
@@ -9338,16 +8974,14 @@
         <is>
           <t>• E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 3 – Exercise Date 12/11/2025 / 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 47 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
-• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026; attached signed attestation §1 – DIV facilitated on an annual basis
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – dated 11/15/2025</t>
         </is>
       </c>
       <c r="L5" s="62" t="inlineStr">
         <is>
-          <t>• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review 09/15/2025
-• E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – follow-up 09/18/2025
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
+          <t>• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review (invite 09/15/2025, re-sent 09/18/2025)
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg – IT DR (Elizabeth Noda) issued test script, collected evidence and requested approval
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 47 – Y/N Format, Headers, Content = Y</t>
@@ -9359,8 +8993,7 @@
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 3 – 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
-• E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – BIA results &amp; applications list review
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §2 – application listed among the 13 in-scope applications that store business data
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg – scope table: application → Client Back Office → Claudia Romero</t>
         </is>
       </c>
@@ -9369,7 +9002,6 @@
           <t>• BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – business line DIV results document – 11/15/2025 – Client Back Office (operator Raimy Ayala)
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
 • DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-• DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 47 – Department Manager / Approval Date / Attestation fields</t>
         </is>
       </c>
@@ -9378,7 +9010,7 @@
           <t>• E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 47
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – row 48
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – BCiC report screen (record on a later page of the 66-item report)
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="P5" s="62" t="inlineStr">
@@ -9389,23 +9021,20 @@
 BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf
 [03 DIV Manager Attestation Email Approvals]
 DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
 DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 [04 Data Integrity &amp; Email Testing Evidence]
 E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx
 E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg
 E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls
 E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
-E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml
 E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
 E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
         </is>
       </c>
       <c r="Q5" s="62" t="inlineStr">
         <is>
-          <t>PASS – with observations – MA01, BLA01, DMA01, DMA01a, DMA02, DMA02a, E01, E02, E03, E04, E05, E06, E09, E16b</t>
+          <t>PASS – with observations – MA01, BLA01, DMA01, DMA02, E01, E02, E03, E04, E05, E09, E16b</t>
         </is>
       </c>
     </row>
@@ -9462,8 +9091,7 @@
           <t>• E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 9 – 'Department Manager Approval Date' and 'Attestation Date' columns
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – Department Manager Approval Date column
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-• DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-• DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf</t>
+• DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
         </is>
       </c>
       <c r="H6" s="62" t="inlineStr">
@@ -9476,8 +9104,7 @@
       <c r="I6" s="62" t="inlineStr">
         <is>
           <t>• E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-• DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-• DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf</t>
+• DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
         </is>
       </c>
       <c r="J6" s="62" t="inlineStr">
@@ -9494,16 +9121,14 @@
         <is>
           <t>• E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 19 – Exercise Date 12/11/2025 / 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 9 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
-• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026; attached signed attestation §1 – DIV facilitated on an annual basis
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – dated 11/15/2025</t>
         </is>
       </c>
       <c r="L6" s="62" t="inlineStr">
         <is>
-          <t>• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review 09/15/2025
-• E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – follow-up 09/18/2025
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
+          <t>• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review (invite 09/15/2025, re-sent 09/18/2025)
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg – IT DR (Elizabeth Noda) issued test script, collected evidence and requested approval
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 9 – Y/N Format, Headers, Content = Y</t>
@@ -9515,8 +9140,7 @@
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 19 – 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
-• E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – BIA results &amp; applications list review
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §2 – application listed among the 13 in-scope applications that store business data
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg – scope table: application → Client Back Office → Claudia Romero</t>
         </is>
       </c>
@@ -9525,7 +9149,6 @@
           <t>• BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – business line DIV results document – 11/15/2025 – Client Back Office (operator Raimy Ayala)
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
 • DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-• DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 9 – Department Manager / Approval Date / Attestation fields</t>
         </is>
       </c>
@@ -9534,7 +9157,7 @@
           <t>• E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 9
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – row 9
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – record(s) visible on screen
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="P6" s="62" t="inlineStr">
@@ -9545,23 +9168,20 @@
 BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf
 [03 DIV Manager Attestation Email Approvals]
 DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
 DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 [04 Data Integrity &amp; Email Testing Evidence]
 E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx
 E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg
 E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls
 E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
-E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml
 E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
 E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
         </is>
       </c>
       <c r="Q6" s="62" t="inlineStr">
         <is>
-          <t>PASS – with observations – MA01, BLA01, DMA01, DMA01a, DMA02, DMA02a, E01, E02, E03, E04, E05, E06, E09, E16b</t>
+          <t>PASS – with observations – MA01, BLA01, DMA01, DMA02, E01, E02, E03, E04, E05, E09, E16b</t>
         </is>
       </c>
     </row>
@@ -9618,8 +9238,7 @@
           <t>• E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 10 – 'Department Manager Approval Date' and 'Attestation Date' columns
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – Department Manager Approval Date column
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-• DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-• DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf</t>
+• DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
         </is>
       </c>
       <c r="H7" s="62" t="inlineStr">
@@ -9632,8 +9251,7 @@
       <c r="I7" s="62" t="inlineStr">
         <is>
           <t>• E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-• DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-• DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf</t>
+• DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
         </is>
       </c>
       <c r="J7" s="62" t="inlineStr">
@@ -9650,16 +9268,14 @@
         <is>
           <t>• E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 20 – Exercise Date 12/11/2025 / 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 10 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
-• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026; attached signed attestation §1 – DIV facilitated on an annual basis
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – dated 11/15/2025</t>
         </is>
       </c>
       <c r="L7" s="62" t="inlineStr">
         <is>
-          <t>• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review 09/15/2025
-• E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – follow-up 09/18/2025
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
+          <t>• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review (invite 09/15/2025, re-sent 09/18/2025)
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg – IT DR (Elizabeth Noda) issued test script, collected evidence and requested approval
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 10 – Y/N Format, Headers, Content = Y</t>
@@ -9671,8 +9287,7 @@
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 20 – 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
-• E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – BIA results &amp; applications list review
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §2 – application listed among the 13 in-scope applications that store business data
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg – scope table: application → Client Back Office → Claudia Romero</t>
         </is>
       </c>
@@ -9681,7 +9296,6 @@
           <t>• BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – business line DIV results document – 11/15/2025 – Client Back Office (operator Raimy Ayala)
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
 • DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-• DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 10 – Department Manager / Approval Date / Attestation fields</t>
         </is>
       </c>
@@ -9690,7 +9304,7 @@
           <t>• E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 10
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – row 10
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – record(s) visible on screen
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="P7" s="62" t="inlineStr">
@@ -9701,23 +9315,20 @@
 BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf
 [03 DIV Manager Attestation Email Approvals]
 DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
 DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 [04 Data Integrity &amp; Email Testing Evidence]
 E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx
 E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg
 E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls
 E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
-E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml
 E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
 E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
         </is>
       </c>
       <c r="Q7" s="62" t="inlineStr">
         <is>
-          <t>PASS – with observations – MA01, BLA01, DMA01, DMA01a, DMA02, DMA02a, E01, E02, E03, E04, E05, E06, E09, E16b</t>
+          <t>PASS – with observations – MA01, BLA01, DMA01, DMA02, E01, E02, E03, E04, E05, E09, E16b</t>
         </is>
       </c>
     </row>
@@ -9769,12 +9380,10 @@
           <t>• E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 5, 11, 13, 51, 53, 57 – 'Department Manager' column
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – Department Manager column
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
 • DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
 • DMA11 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
-• DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-• DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+• DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
         </is>
       </c>
       <c r="G8" s="62" t="inlineStr">
@@ -9782,13 +9391,10 @@
           <t>• E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 5, 11, 13, 51, 53, 57 – 'Department Manager Approval Date' and 'Attestation Date' columns
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – Department Manager Approval Date column
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
 • DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-• DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
 • DMA11 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
-• DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-• DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+• DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
         </is>
       </c>
       <c r="H8" s="62" t="inlineStr">
@@ -9802,13 +9408,10 @@
       <c r="I8" s="62" t="inlineStr">
         <is>
           <t>• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
 • DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-• DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
 • DMA11 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
-• DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-• DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+• DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
         </is>
       </c>
       <c r="J8" s="62" t="inlineStr">
@@ -9825,17 +9428,15 @@
         <is>
           <t>• E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 24 – Exercise Date 11/15/2025 / 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 5, 11, 13, 51, 53, 57 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
-• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026; attached signed attestation §1 – DIV facilitated on an annual basis
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – dated 11/15/2025
 • BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf – dated 11/15/2025</t>
         </is>
       </c>
       <c r="L8" s="62" t="inlineStr">
         <is>
-          <t>• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review 09/15/2025
-• E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – follow-up 09/18/2025
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
+          <t>• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review (invite 09/15/2025, re-sent 09/18/2025)
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg – IT DR (Elizabeth Noda) issued test script, collected evidence and requested approval
@@ -9848,8 +9449,7 @@
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 24 – 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
-• E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – BIA results &amp; applications list review
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §2 – application listed among the 13 in-scope applications that store business data
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg – scope table: application → Client Back Office → Claudia Romero</t>
         </is>
       </c>
@@ -9858,13 +9458,10 @@
           <t>• BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – business line DIV results document – 11/15/2025 – Client Back Office (operator Raimy Ayala)
 • BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf – business line DIV results document – 11/15/2025 – BSA/AML/OFAC Compliance (operator David Marquez)
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
 • DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-• DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
 • DMA11 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
 • DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-• DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 5, 11, 13, 51, 53, 57 – Department Manager / Approval Date / Attestation fields</t>
         </is>
       </c>
@@ -9873,7 +9470,7 @@
           <t>• E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 5, 11, 13, 51, 53, 57
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – rows 5, 11, 13, 52, 54, 58
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – record(s) visible on screen
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="P8" s="62" t="inlineStr">
@@ -9885,11 +9482,8 @@
 BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf
 [03 DIV Manager Attestation Email Approvals]
 DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
 DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf
 DMA11 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
 [04 Data Integrity &amp; Email Testing Evidence]
 E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx
@@ -9897,14 +9491,13 @@
 E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls
 E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
-E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml
 E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
 E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
         </is>
       </c>
       <c r="Q8" s="62" t="inlineStr">
         <is>
-          <t>PASS – with observations – MA01, BLA01, BLA02, DMA01, DMA01a, DMA02, DMA02a, DMA05, DMA05a, DMA11, E01, E02, E03, E04, E05, E06, E09, E16b</t>
+          <t>PASS – with observations – MA01, BLA01, BLA02, DMA01, DMA02, DMA05, DMA11, E01, E02, E03, E04, E05, E09, E16b</t>
         </is>
       </c>
     </row>
@@ -9948,15 +9541,13 @@
       <c r="F9" s="62" t="inlineStr">
         <is>
           <t>• E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 61 – 'Department Manager' column
-• DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-• DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+• DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
         </is>
       </c>
       <c r="G9" s="62" t="inlineStr">
         <is>
           <t>• E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 61 – 'Department Manager Approval Date' and 'Attestation Date' columns
-• DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-• DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+• DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
         </is>
       </c>
       <c r="H9" s="62" t="inlineStr">
@@ -9968,8 +9559,7 @@
       </c>
       <c r="I9" s="62" t="inlineStr">
         <is>
-          <t>• DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-• DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+          <t>• DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
         </is>
       </c>
       <c r="J9" s="62" t="inlineStr">
@@ -9986,16 +9576,14 @@
         <is>
           <t>• E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 25 – Exercise Date 11/15/2025 / 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 61 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
-• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026; attached signed attestation §1 – DIV facilitated on an annual basis
 • BLA04 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx – dated 11/15/2025</t>
         </is>
       </c>
       <c r="L9" s="62" t="inlineStr">
         <is>
-          <t>• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review 09/15/2025
-• E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – follow-up 09/18/2025
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
+          <t>• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review (invite 09/15/2025, re-sent 09/18/2025)
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
 • BLA04 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx – IT DR test script completed by the business-line tester
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 61 – Y/N Format, Headers, Content = Y</t>
         </is>
@@ -10006,15 +9594,13 @@
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 25 – 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
-• E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – BIA results &amp; applications list review
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data</t>
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §2 – application listed among the 13 in-scope applications that store business data</t>
         </is>
       </c>
       <c r="N9" s="62" t="inlineStr">
         <is>
           <t>• BLA04 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx – business line DIV results document – 11/15/2025 – Investment Operations (operator Michelle Oropesa)
 • DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-• DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 61 – Department Manager / Approval Date / Attestation fields</t>
         </is>
       </c>
@@ -10023,7 +9609,7 @@
           <t>• E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 61
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – row 62
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – BCiC report screen (record on a later page of the 66-item report)
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="P9" s="62" t="inlineStr">
@@ -10034,22 +9620,19 @@
 BLA04 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx
 [03 DIV Manager Attestation Email Approvals]
 DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf
 [04 Data Integrity &amp; Email Testing Evidence]
 E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx
 E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg
 E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls
 E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
-E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml
 E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
         </is>
       </c>
       <c r="Q9" s="62" t="inlineStr">
         <is>
-          <t>PASS – with observations – MA01, BLA04, DMA02, DMA02a, DMA04, DMA04a, E01, E02, E03, E04, E05, E06, E16b</t>
+          <t>PASS – with observations – MA01, BLA04, DMA02, DMA04, E01, E02, E03, E04, E05, E16b</t>
         </is>
       </c>
     </row>
@@ -10095,15 +9678,13 @@
       <c r="F10" s="62" t="inlineStr">
         <is>
           <t>• E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 25, 29 – 'Department Manager' column
-• DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-• DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf</t>
+• DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
         </is>
       </c>
       <c r="G10" s="62" t="inlineStr">
         <is>
           <t>• E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 25, 29 – 'Department Manager Approval Date' and 'Attestation Date' columns
-• DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-• DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf</t>
+• DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
         </is>
       </c>
       <c r="H10" s="62" t="inlineStr">
@@ -10115,8 +9696,7 @@
       </c>
       <c r="I10" s="62" t="inlineStr">
         <is>
-          <t>• DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-• DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf</t>
+          <t>• DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
         </is>
       </c>
       <c r="J10" s="62" t="inlineStr">
@@ -10133,16 +9713,14 @@
         <is>
           <t>• E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 31 – Exercise Date 11/15/2025 / 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 25, 29 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
-• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026; attached signed attestation §1 – DIV facilitated on an annual basis
 • BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – dated 11/15/2025</t>
         </is>
       </c>
       <c r="L10" s="62" t="inlineStr">
         <is>
-          <t>• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review 09/15/2025
-• E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – follow-up 09/18/2025
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
+          <t>• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review (invite 09/15/2025, re-sent 09/18/2025)
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
 • BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • E08 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg – business-line DIV comparison files sent to IT DR (Elizabeth Noda) on 11/15/2025
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 25, 29 – Y/N Format, Headers, Content = Y</t>
@@ -10154,15 +9732,13 @@
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 31 – 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
-• E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – BIA results &amp; applications list review
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data</t>
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §2 – application listed among the 13 in-scope applications that store business data</t>
         </is>
       </c>
       <c r="N10" s="62" t="inlineStr">
         <is>
           <t>• BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – business line DIV results document – 11/15/2025 – Payments &amp; Position Management (operators Frank Puentes / Gustavo Bucaro)
 • DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-• DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 25, 29 – Department Manager / Approval Date / Attestation fields</t>
         </is>
       </c>
@@ -10171,7 +9747,7 @@
           <t>• E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 25, 29
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – rows 25, 29
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – BCiC report screen (record on a later page of the 66-item report)
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="P10" s="62" t="inlineStr">
@@ -10182,16 +9758,13 @@
 BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf
 [03 DIV Manager Attestation Email Approvals]
 DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf
 [04 Data Integrity &amp; Email Testing Evidence]
 E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx
 E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg
 E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls
 E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
-E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml
 E07 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg
 E08 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg
 E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
@@ -10199,7 +9772,7 @@
       </c>
       <c r="Q10" s="62" t="inlineStr">
         <is>
-          <t>PASS – with observations – MA01, BLA03, DMA02, DMA02a, DMA03, DMA03a, E01, E02, E03, E04, E05, E06, E07, E08, E16b</t>
+          <t>PASS – with observations – MA01, BLA03, DMA02, DMA03, E01, E02, E03, E04, E05, E07, E08, E16b</t>
         </is>
       </c>
     </row>
@@ -10252,11 +9825,8 @@
           <t>• E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 6, 26, 30, 34, 58 – 'Department Manager' column
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – Department Manager column
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-• DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf
-• DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-• DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+• DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
         </is>
       </c>
       <c r="G11" s="62" t="inlineStr">
@@ -10264,11 +9834,8 @@
           <t>• E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 6, 26, 30, 34, 58 – 'Department Manager Approval Date' and 'Attestation Date' columns
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – Department Manager Approval Date column
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-• DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf
-• DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-• DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+• DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
         </is>
       </c>
       <c r="H11" s="62" t="inlineStr">
@@ -10282,11 +9849,8 @@
       <c r="I11" s="62" t="inlineStr">
         <is>
           <t>• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-• DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf
-• DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-• DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+• DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
         </is>
       </c>
       <c r="J11" s="62" t="inlineStr">
@@ -10303,17 +9867,15 @@
         <is>
           <t>• E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 34 – Exercise Date 11/15/2025 / 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 6, 26, 30, 34, 58 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
-• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026; attached signed attestation §1 – DIV facilitated on an annual basis
 • BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf – dated 11/15/2025
 • BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – dated 11/15/2025</t>
         </is>
       </c>
       <c r="L11" s="62" t="inlineStr">
         <is>
-          <t>• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review 09/15/2025
-• E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – follow-up 09/18/2025
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
+          <t>• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review (invite 09/15/2025, re-sent 09/18/2025)
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
 • BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • E08 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg – business-line DIV comparison files sent to IT DR (Elizabeth Noda) on 11/15/2025
@@ -10326,8 +9888,7 @@
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 34 – 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
-• E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – BIA results &amp; applications list review
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data</t>
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §2 – application listed among the 13 in-scope applications that store business data</t>
         </is>
       </c>
       <c r="N11" s="62" t="inlineStr">
@@ -10335,11 +9896,8 @@
           <t>• BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf – business line DIV results document – 11/15/2025 – BSA/AML/OFAC Compliance (operator David Marquez)
 • BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – business line DIV results document – 11/15/2025 – Payments &amp; Position Management (operators Frank Puentes / Gustavo Bucaro)
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-• DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf
 • DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-• DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 6, 26, 30, 34, 58 – Department Manager / Approval Date / Attestation fields</t>
         </is>
       </c>
@@ -10348,7 +9906,7 @@
           <t>• E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 6, 26, 30, 34, 58
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – rows 6, 26, 30, 34, 59
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – record(s) visible on screen
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="P11" s="62" t="inlineStr">
@@ -10360,18 +9918,14 @@
 BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf
 [03 DIV Manager Attestation Email Approvals]
 DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf
 DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf
 [04 Data Integrity &amp; Email Testing Evidence]
 E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx
 E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg
 E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls
 E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
-E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml
 E07 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg
 E08 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg
 E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
@@ -10379,7 +9933,7 @@
       </c>
       <c r="Q11" s="62" t="inlineStr">
         <is>
-          <t>PASS – with observations – MA01, BLA02, BLA03, DMA02, DMA02a, DMA03, DMA03a, DMA05, DMA05a, E01, E02, E03, E04, E05, E06, E07, E08, E16b</t>
+          <t>PASS – with observations – MA01, BLA02, BLA03, DMA02, DMA03, DMA05, E01, E02, E03, E04, E05, E07, E08, E16b</t>
         </is>
       </c>
     </row>
@@ -10458,16 +10012,14 @@
         <is>
           <t>• E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 36 – Exercise Date 11/15/2025 / 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 17 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
-• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026; attached signed attestation §1 – DIV facilitated on an annual basis
 • BLA05 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf – dated 11/15/2025</t>
         </is>
       </c>
       <c r="L12" s="62" t="inlineStr">
         <is>
-          <t>• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review 09/15/2025
-• E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – follow-up 09/18/2025
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
+          <t>• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review (invite 09/15/2025, re-sent 09/18/2025)
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
 • BLA05 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • E10 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg – IT DR (Elizabeth Noda) Finance DIV chart and approval request
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 17 – Y/N Format, Headers, Content = Y</t>
@@ -10479,8 +10031,7 @@
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 36 – 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
-• E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – BIA results &amp; applications list review
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data</t>
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §2 – application listed among the 13 in-scope applications that store business data</t>
         </is>
       </c>
       <c r="N12" s="62" t="inlineStr">
@@ -10495,7 +10046,7 @@
           <t>• E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – row 17
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – row 17
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – BCiC report screen (record on a later page of the 66-item report)
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="P12" s="62" t="inlineStr">
@@ -10507,21 +10058,19 @@
 BLA06 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg
 [03 DIV Manager Attestation Email Approvals]
 DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 [04 Data Integrity &amp; Email Testing Evidence]
 E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx
 E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg
 E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls
 E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
-E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml
 E10 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg
 E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
         </is>
       </c>
       <c r="Q12" s="62" t="inlineStr">
         <is>
-          <t>PASS – with observations – MA01, BLA05, BLA06, DMA02, DMA02a, E01, E02, E03, E04, E05, E06, E10, E16b</t>
+          <t>PASS – with observations – MA01, BLA05, BLA06, DMA02, E01, E02, E03, E04, E05, E10, E16b</t>
         </is>
       </c>
     </row>
@@ -10574,9 +10123,7 @@
           <t>• E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 7, 60 – 'Department Manager' column
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – Department Manager column
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
-• DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-• DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+• DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
         </is>
       </c>
       <c r="G13" s="62" t="inlineStr">
@@ -10584,9 +10131,7 @@
           <t>• E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 7, 60 – 'Department Manager Approval Date' and 'Attestation Date' columns
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – Department Manager Approval Date column
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
-• DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-• DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+• DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
         </is>
       </c>
       <c r="H13" s="62" t="inlineStr">
@@ -10600,9 +10145,7 @@
       <c r="I13" s="62" t="inlineStr">
         <is>
           <t>• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
-• DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-• DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+• DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
         </is>
       </c>
       <c r="J13" s="62" t="inlineStr">
@@ -10619,17 +10162,15 @@
         <is>
           <t>• E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 42 – Exercise Date 11/15/2025 / 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 7, 60 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
-• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026; attached signed attestation §1 – DIV facilitated on an annual basis
 • BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – dated 11/15/2025
 • BLA04 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx – dated 11/15/2025</t>
         </is>
       </c>
       <c r="L13" s="62" t="inlineStr">
         <is>
-          <t>• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review 09/15/2025
-• E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – follow-up 09/18/2025
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
+          <t>• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review (invite 09/15/2025, re-sent 09/18/2025)
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
 • BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • BLA04 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx – IT DR test script completed by the business-line tester
 • E08 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg – business-line DIV comparison files sent to IT DR (Elizabeth Noda) on 11/15/2025
@@ -10642,8 +10183,7 @@
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 42 – 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
-• E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – BIA results &amp; applications list review
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data</t>
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §2 – application listed among the 13 in-scope applications that store business data</t>
         </is>
       </c>
       <c r="N13" s="62" t="inlineStr">
@@ -10651,9 +10191,7 @@
           <t>• BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – business line DIV results document – 11/15/2025 – Payments &amp; Position Management (operators Frank Puentes / Gustavo Bucaro)
 • BLA04 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx – business line DIV results document – 11/15/2025 – Investment Operations (operator Michelle Oropesa)
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-• DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 7, 60 – Department Manager / Approval Date / Attestation fields</t>
         </is>
       </c>
@@ -10662,7 +10200,7 @@
           <t>• E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 7, 60
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – rows 7, 61
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – record(s) visible on screen
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="P13" s="62" t="inlineStr">
@@ -10674,16 +10212,13 @@
 BLA04 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx
 [03 DIV Manager Attestation Email Approvals]
 DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf
 [04 Data Integrity &amp; Email Testing Evidence]
 E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx
 E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg
 E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls
 E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
-E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml
 E07 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg
 E08 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg
 E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
@@ -10691,7 +10226,7 @@
       </c>
       <c r="Q13" s="62" t="inlineStr">
         <is>
-          <t>PASS – with observations – MA01, BLA03, BLA04, DMA02, DMA02a, DMA04, DMA04a, E01, E02, E03, E04, E05, E06, E07, E08, E16b</t>
+          <t>PASS – with observations – MA01, BLA03, BLA04, DMA02, DMA04, E01, E02, E03, E04, E05, E07, E08, E16b</t>
         </is>
       </c>
     </row>
@@ -10753,26 +10288,19 @@
           <t>• E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63 – 'Department Manager' column
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – Department Manager column
 • DMA06 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg
-• DMA06a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA06a_Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Data_Integrity_Attestation_Santander-BCiC_signed.pdf
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
 • DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
 • DMA11 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
 • BLA06 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg
 • DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-• DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf
 • DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-• DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf
 • DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-• DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf
 • DMA07 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg
-• DMA07a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA07a_Treasury &amp; Capital Planning - Data_Integrity_Attestation_Santander-BCiC.pdf
 • DMA12 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml
 • DMA10 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml
 • DMA08 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg
-• DMA09 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg
-• DMA09a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA09a_General Services (Marketing &amp; General Services) - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+• DMA09 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg</t>
         </is>
       </c>
       <c r="G14" s="62" t="inlineStr">
@@ -10780,27 +10308,19 @@
           <t>• E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63 – 'Department Manager Approval Date' and 'Attestation Date' columns
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – Department Manager Approval Date column
 • DMA06 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg
-• DMA06a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA06a_Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Data_Integrity_Attestation_Santander-BCiC_signed.pdf
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
 • DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-• DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
 • DMA11 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
 • BLA06 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg
 • DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-• DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf
 • DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-• DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf
 • DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-• DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf
 • DMA07 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg
-• DMA07a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA07a_Treasury &amp; Capital Planning - Data_Integrity_Attestation_Santander-BCiC.pdf
 • DMA12 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml
 • DMA10 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml
 • DMA08 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg
-• DMA09 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg
-• DMA09a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA09a_General Services (Marketing &amp; General Services) - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+• DMA09 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg</t>
         </is>
       </c>
       <c r="H14" s="62" t="inlineStr">
@@ -10817,27 +10337,19 @@
       <c r="I14" s="62" t="inlineStr">
         <is>
           <t>• DMA06 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg
-• DMA06a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA06a_Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Data_Integrity_Attestation_Santander-BCiC_signed.pdf
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
 • DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-• DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
 • DMA11 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
 • BLA06 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg
 • DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-• DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf
 • DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-• DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf
 • DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-• DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf
 • DMA07 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg
-• DMA07a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA07a_Treasury &amp; Capital Planning - Data_Integrity_Attestation_Santander-BCiC.pdf
 • DMA12 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml
 • DMA10 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml
 • DMA08 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg
-• DMA09 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg
-• DMA09a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA09a_General Services (Marketing &amp; General Services) - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+• DMA09 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg</t>
         </is>
       </c>
       <c r="J14" s="62" t="inlineStr">
@@ -10854,8 +10366,7 @@
         <is>
           <t>• E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 43 – Exercise Date 11/15/2025 / 2025 DR Test Scope = True
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63 – Business Data Validation Date 11/15/2025 / Last App DR Test Date
-• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1 – DIV facilitated on an annual basis
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – quoted request: DR exercises 11/15/2025 and 02/21/2026; attached signed attestation §1 – DIV facilitated on an annual basis
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – dated 11/15/2025
 • BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf – dated 11/15/2025
 • BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – dated 11/15/2025
@@ -10865,9 +10376,8 @@
       </c>
       <c r="L14" s="62" t="inlineStr">
         <is>
-          <t>• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review 09/15/2025
-• E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – follow-up 09/18/2025
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
+          <t>• E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – IT DR: 2025 BIA results &amp; applications list review (invite 09/15/2025, re-sent 09/18/2025)
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §1-2 – IT DR team facilitates DIV performed by business line testers during actual DR testing
 • BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
 • BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf – IT DR test script completed by the business-line tester
@@ -10884,8 +10394,7 @@
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 43 – 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
-• E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml – BIA results &amp; applications list review
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §2 – application listed among the 13 in-scope applications that store business data</t>
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §2 – application listed among the 13 in-scope applications that store business data</t>
         </is>
       </c>
       <c r="N14" s="62" t="inlineStr">
@@ -10896,27 +10405,19 @@
 • BLA04 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx – business line DIV results document – 11/15/2025 – Investment Operations (operator Michelle Oropesa)
 • BLA05 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf – business line DIV results document – 11/15/2025 – Finance &amp; Accounting Reporting (operator Dunia Gonzalez Collado)
 • DMA06 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg
-• DMA06a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA06a_Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Data_Integrity_Attestation_Santander-BCiC_signed.pdf
 • DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 • E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
 • DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-• DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
 • DMA11 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
 • BLA06 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg
 • DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-• DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf
 • DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-• DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf
 • DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-• DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf
 • DMA07 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg
-• DMA07a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA07a_Treasury &amp; Capital Planning - Data_Integrity_Attestation_Santander-BCiC.pdf
 • DMA12 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml
 • DMA10 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml
 • DMA08 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg
 • DMA09 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg
-• DMA09a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA09a_General Services (Marketing &amp; General Services) - Data_Integrity_Attestation_Santander-BCiC.pdf
 • E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63 – Department Manager / Approval Date / Attestation fields</t>
         </is>
       </c>
@@ -10925,7 +10426,7 @@
           <t>• E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls – rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 48, 49, 50, 52, 54, 55, 56, 59, 62, 63
 • E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx – rows 3, 8, 12, 14, 15, 16, 18, 19, 20, 21, 23, 27, 31, 33, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 47, 49, 50, 51, 53, 55, 56, 57, 60, 63, 64
 • E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg – record(s) visible on screen
-• DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
+• DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg – attached signed attestation §3.5 – attestation and DIV record retained in BCMS/BCiC; Attestation Date / Provided By fields updated</t>
         </is>
       </c>
       <c r="P14" s="62" t="inlineStr">
@@ -10941,22 +10442,14 @@
 BLA06 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg
 [03 DIV Manager Attestation Email Approvals]
 DMA01 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg
-DMA01a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf
 DMA02 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg
-DMA02a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf
 DMA03 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg
-DMA03a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf
 DMA04 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg
-DMA04a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf
 DMA05 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg
-DMA05a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf
 DMA06 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg
-DMA06a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA06a_Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Data_Integrity_Attestation_Santander-BCiC_signed.pdf
 DMA07 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg
-DMA07a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA07a_Treasury &amp; Capital Planning - Data_Integrity_Attestation_Santander-BCiC.pdf
 DMA08 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg
 DMA09 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg
-DMA09a – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA09a_General Services (Marketing &amp; General Services) - Data_Integrity_Attestation_Santander-BCiC.pdf
 DMA10 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml
 DMA11 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml
 DMA12 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml
@@ -10966,7 +10459,6 @@
 E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls
 E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
-E06 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml
 E07 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg
 E08 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg
 E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
@@ -10976,7 +10468,7 @@
       </c>
       <c r="Q14" s="62" t="inlineStr">
         <is>
-          <t>PASS – with observations – MA01, BLA01, BLA02, BLA03, BLA04, BLA05, BLA06, DMA01, DMA01a, DMA02, DMA02a, DMA03, DMA03a, DMA04, DMA04a, DMA05, DMA05a, DMA06, DMA06a, DMA07, DMA07a, DMA08, DMA09, DMA09a, DMA10, DMA11, DMA12, E01, E02, E03, E04, E05, E06, E07, E08, E09, E10, E16b</t>
+          <t>PASS – with observations – MA01, BLA01, BLA02, BLA03, BLA04, BLA05, BLA06, DMA01, DMA02, DMA03, DMA04, DMA05, DMA06, DMA07, DMA08, DMA09, DMA10, DMA11, DMA12, E01, E02, E03, E04, E05, E07, E08, E09, E10, E16b</t>
         </is>
       </c>
     </row>
@@ -11033,7 +10525,7 @@
       </c>
       <c r="B21" s="81" t="inlineStr">
         <is>
-          <t>BSA T24 record (E03 row 8) Attestation Date 08/29/2026 vs signed attestation 8/19/2026 (DMA02a); Financial Risk manager recorded as "Xavier Caisapanta" in BCiC while the approval email is from Ivan Caisapanta (DMA08).</t>
+          <t>BSA T24 record (E03 row 8) Attestation Date 08/29/2026 vs signed attestation 8/19/2026 (DMA02 attachment); Financial Risk manager recorded as "Xavier Caisapanta" in BCiC while the approval email is from Ivan Caisapanta (DMA08).</t>
         </is>
       </c>
     </row>
@@ -13874,7 +13366,7 @@
       </c>
       <c r="H10" s="64" t="inlineStr">
         <is>
-          <t>Claudia Romero (Client Back Office Manager VP) returns signed attestation (DMA01a).</t>
+          <t>Claudia Romero (Client Back Office Manager VP) returns the signed Management Attestation – attachment: Data_Integrity_Attestation_Santander-BCiC (002).pdf (signed Claudia Romero).</t>
         </is>
       </c>
       <c r="I10" s="64" t="inlineStr">
@@ -13893,22 +13385,22 @@
     <row r="11" ht="23" customHeight="1" s="71">
       <c r="A11" s="64" t="inlineStr">
         <is>
-          <t>DMA01a</t>
+          <t>DMA02</t>
         </is>
       </c>
       <c r="B11" s="64" t="inlineStr">
         <is>
-          <t>DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf</t>
+          <t>DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg</t>
         </is>
       </c>
       <c r="C11" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
         </is>
       </c>
       <c r="D11" s="64" t="inlineStr">
         <is>
-          <t>Data_Integrity_Attestation_Santander-BCiC (002).pdf (attachment of DMA01)</t>
+          <t>RE_ Management Attestation – OFAC.msg</t>
         </is>
       </c>
       <c r="E11" s="64" t="inlineStr">
@@ -13918,27 +13410,27 @@
       </c>
       <c r="F11" s="64" t="inlineStr">
         <is>
-          <t>Signed attestation</t>
+          <t>Email attestation</t>
         </is>
       </c>
       <c r="G11" s="64" t="inlineStr">
         <is>
-          <t>08/18/2026 – Claudia Romero</t>
+          <t>08/19/2026 – David Marquez</t>
         </is>
       </c>
       <c r="H11" s="64" t="inlineStr">
         <is>
-          <t>Signed Management Attestation – Client Back Office.</t>
+          <t>Cesar Vidal request to Department Managers (08/17/2026; DR exercises 11/15/2025 and 02/21/2026; BCiC export attached) and David Marquez (OFAC Manager) reply. Attachment: Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – signed OFAC Manager, VP, BSA/AML-OFAC Compliance, 8/19/2026. Attestation §1: IT DR team facilitates DIV annually; §2: 63 entries / 13 applications, all Y/Y/Y; §3.5: retained in BCMS/BCiC; §3.6: contemporaneous approval going forward.</t>
         </is>
       </c>
       <c r="I11" s="64" t="inlineStr">
         <is>
-          <t>1822, 1867, 1868, 3299, 1937</t>
+          <t>1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
         </is>
       </c>
       <c r="J11" s="64" t="inlineStr">
         <is>
-          <t>H, J, O</t>
+          <t>B, C, G, H, J, L, M, N, O, P</t>
         </is>
       </c>
       <c r="K11" s="64" t="inlineStr"/>
@@ -13947,12 +13439,12 @@
     <row r="12" ht="34.5" customHeight="1" s="71">
       <c r="A12" s="64" t="inlineStr">
         <is>
-          <t>DMA02</t>
+          <t>DMA03</t>
         </is>
       </c>
       <c r="B12" s="64" t="inlineStr">
         <is>
-          <t>DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg</t>
+          <t>DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
         </is>
       </c>
       <c r="C12" s="64" t="inlineStr">
@@ -13962,7 +13454,7 @@
       </c>
       <c r="D12" s="64" t="inlineStr">
         <is>
-          <t>RE_ Management Attestation – OFAC.msg</t>
+          <t>Management Attestation – DIV Payment &amp; Cash Management.msg</t>
         </is>
       </c>
       <c r="E12" s="64" t="inlineStr">
@@ -13977,22 +13469,22 @@
       </c>
       <c r="G12" s="64" t="inlineStr">
         <is>
-          <t>08/19/2026 – David Marquez</t>
+          <t>08/18/2026 – Frank Puentes</t>
         </is>
       </c>
       <c r="H12" s="64" t="inlineStr">
         <is>
-          <t>Cesar Vidal request to Department Managers (08/17/2026; DR exercises 11/15/2025 and 02/21/2026; BCiC export attached) and David Marquez (OFAC Manager) reply returning the signed attestation.</t>
+          <t>Frank Puentes returns the signed attestation – attachment: 4069_001.pdf (scan, signed Executive Director, Payments &amp; Cash Management, 8/18/2026).</t>
         </is>
       </c>
       <c r="I12" s="64" t="inlineStr">
         <is>
-          <t>1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
+          <t>3301, 1903, 1937</t>
         </is>
       </c>
       <c r="J12" s="64" t="inlineStr">
         <is>
-          <t>B, G, H, J, L, O</t>
+          <t>G, H, J, O</t>
         </is>
       </c>
       <c r="K12" s="64" t="inlineStr"/>
@@ -14001,22 +13493,22 @@
     <row r="13" ht="34.5" customHeight="1" s="71">
       <c r="A13" s="64" t="inlineStr">
         <is>
-          <t>DMA02a</t>
+          <t>DMA04</t>
         </is>
       </c>
       <c r="B13" s="64" t="inlineStr">
         <is>
-          <t>DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf</t>
+          <t>DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
         </is>
       </c>
       <c r="C13" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
         </is>
       </c>
       <c r="D13" s="64" t="inlineStr">
         <is>
-          <t>Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf (attachment of DMA02)</t>
+          <t>RE_ Management Attestation – DIV Investment Operations.msg</t>
         </is>
       </c>
       <c r="E13" s="64" t="inlineStr">
@@ -14026,27 +13518,27 @@
       </c>
       <c r="F13" s="64" t="inlineStr">
         <is>
-          <t>Signed attestation</t>
+          <t>Email attestation</t>
         </is>
       </c>
       <c r="G13" s="64" t="inlineStr">
         <is>
-          <t>08/19/2026 – David Marquez</t>
+          <t>08/17/2026 – Michelle Oropesa</t>
         </is>
       </c>
       <c r="H13" s="64" t="inlineStr">
         <is>
-          <t>Signed attestation – OFAC Manager, VP, BSA/AML-OFAC Compliance, dated 8/19/2026. §1 states the IT DR team facilitates DIV annually; §2 lists 63 entries / 13 applications, all Y/Y/Y; §3.5 retention in BCMS/BCiC; §3.6 contemporaneous approval going forward.</t>
+          <t>Michelle Oropesa (Investment Operations Director) returns the signed attestation – attachment: Data_Integrity_Attestation_Santander-BCiC.pdf (signed Investment Operations Director, VP, 8/17/2026).</t>
         </is>
       </c>
       <c r="I13" s="64" t="inlineStr">
         <is>
-          <t>1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
+          <t>4052, 1936, 1937</t>
         </is>
       </c>
       <c r="J13" s="64" t="inlineStr">
         <is>
-          <t>C, G, H, J, L, M, N, O, P</t>
+          <t>G, H, J, O</t>
         </is>
       </c>
       <c r="K13" s="64" t="inlineStr"/>
@@ -14055,12 +13547,12 @@
     <row r="14" ht="34.5" customHeight="1" s="71">
       <c r="A14" s="64" t="inlineStr">
         <is>
-          <t>DMA03</t>
+          <t>DMA05</t>
         </is>
       </c>
       <c r="B14" s="64" t="inlineStr">
         <is>
-          <t>DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
+          <t>DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
         </is>
       </c>
       <c r="C14" s="64" t="inlineStr">
@@ -14070,7 +13562,7 @@
       </c>
       <c r="D14" s="64" t="inlineStr">
         <is>
-          <t>Management Attestation – DIV Payment &amp; Cash Management.msg</t>
+          <t>RE_ Management Attestation – DIV Operations.msg</t>
         </is>
       </c>
       <c r="E14" s="64" t="inlineStr">
@@ -14085,17 +13577,17 @@
       </c>
       <c r="G14" s="64" t="inlineStr">
         <is>
-          <t>08/18/2026 – Frank Puentes</t>
+          <t>08/19/2026 – Maria Teresa (Mayte) Del Cerro</t>
         </is>
       </c>
       <c r="H14" s="64" t="inlineStr">
         <is>
-          <t>Frank Puentes returns signed attestation (DMA03a).</t>
+          <t>Senior Director of Operations returns the signed attestation – attachments: Data_Integrity_Attestation_Santander-BCiC.pdf (signed Maria Teresa Del Cerro Hontanilla, Director of Operations, 08/19/2026) and the BCiC export (same file as E16b).</t>
         </is>
       </c>
       <c r="I14" s="64" t="inlineStr">
         <is>
-          <t>3301, 1903, 1937</t>
+          <t>3299, 1903, 1937</t>
         </is>
       </c>
       <c r="J14" s="64" t="inlineStr">
@@ -14109,22 +13601,22 @@
     <row r="15" ht="34.5" customHeight="1" s="71">
       <c r="A15" s="64" t="inlineStr">
         <is>
-          <t>DMA03a</t>
+          <t>DMA06</t>
         </is>
       </c>
       <c r="B15" s="64" t="inlineStr">
         <is>
-          <t>DMA03a_Payments &amp; Cash Management - 4069_001.pdf</t>
+          <t>DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg</t>
         </is>
       </c>
       <c r="C15" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
         </is>
       </c>
       <c r="D15" s="64" t="inlineStr">
         <is>
-          <t>4069_001.pdf (attachment of DMA03)</t>
+          <t>RE_ Management Attestation – DIV Trading and Capital Markets.msg</t>
         </is>
       </c>
       <c r="E15" s="64" t="inlineStr">
@@ -14134,22 +13626,22 @@
       </c>
       <c r="F15" s="64" t="inlineStr">
         <is>
-          <t>Signed attestation (scan)</t>
+          <t>Email attestation</t>
         </is>
       </c>
       <c r="G15" s="64" t="inlineStr">
         <is>
-          <t>08/18/2026 – Frank Puentes</t>
+          <t>08/18/2026 – Ricardo Garcia-Marques</t>
         </is>
       </c>
       <c r="H15" s="64" t="inlineStr">
         <is>
-          <t>Scanned signed attestation – Executive Director, Payments &amp; Cash Management.</t>
+          <t>Attestation and approval from Trading &amp; Capital Markets (covers BCiC records approved by Ricardo Garcia) – attachment: Data_Integrity_Attestation_Santander-BCiC_signed.pdf (e-signed MD, Head of Trading &amp; Capital Markets, 08/18/2026 11:45 AM EDT).</t>
         </is>
       </c>
       <c r="I15" s="64" t="inlineStr">
         <is>
-          <t>3301, 1903, 1937</t>
+          <t>1937</t>
         </is>
       </c>
       <c r="J15" s="64" t="inlineStr">
@@ -14163,12 +13655,12 @@
     <row r="16" ht="23" customHeight="1" s="71">
       <c r="A16" s="64" t="inlineStr">
         <is>
-          <t>DMA04</t>
+          <t>DMA07</t>
         </is>
       </c>
       <c r="B16" s="64" t="inlineStr">
         <is>
-          <t>DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
+          <t>DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg</t>
         </is>
       </c>
       <c r="C16" s="64" t="inlineStr">
@@ -14178,7 +13670,7 @@
       </c>
       <c r="D16" s="64" t="inlineStr">
         <is>
-          <t>RE_ Management Attestation – DIV Investment Operations.msg</t>
+          <t>RE_ Management Attestation – DIV Treasury and Capital Planning.msg</t>
         </is>
       </c>
       <c r="E16" s="64" t="inlineStr">
@@ -14193,17 +13685,17 @@
       </c>
       <c r="G16" s="64" t="inlineStr">
         <is>
-          <t>08/17/2026 – Michelle Oropesa</t>
+          <t>08/18/2026 – Martha Sullivan</t>
         </is>
       </c>
       <c r="H16" s="64" t="inlineStr">
         <is>
-          <t>Michelle Oropesa (Investment Operations Director) returns signed attestation (DMA04a).</t>
+          <t>Martha Sullivan returns the signed attestation – attachment: Data_Integrity_Attestation_Santander-BCiC.pdf (signed Balance Sheet Manager, Treasury).</t>
         </is>
       </c>
       <c r="I16" s="64" t="inlineStr">
         <is>
-          <t>4052, 1936, 1937</t>
+          <t>1937</t>
         </is>
       </c>
       <c r="J16" s="64" t="inlineStr">
@@ -14217,22 +13709,22 @@
     <row r="17" ht="23" customHeight="1" s="71">
       <c r="A17" s="64" t="inlineStr">
         <is>
-          <t>DMA04a</t>
+          <t>DMA08</t>
         </is>
       </c>
       <c r="B17" s="64" t="inlineStr">
         <is>
-          <t>DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+          <t>DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg</t>
         </is>
       </c>
       <c r="C17" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
         </is>
       </c>
       <c r="D17" s="64" t="inlineStr">
         <is>
-          <t>Data_Integrity_Attestation_Santander-BCiC.pdf (attachment of DMA04)</t>
+          <t>RE_ Management Attestation – DIV Solvency and Market Risk.msg</t>
         </is>
       </c>
       <c r="E17" s="64" t="inlineStr">
@@ -14242,22 +13734,22 @@
       </c>
       <c r="F17" s="64" t="inlineStr">
         <is>
-          <t>Signed attestation</t>
+          <t>Email approval</t>
         </is>
       </c>
       <c r="G17" s="64" t="inlineStr">
         <is>
-          <t>08/17/2026 – Michelle Oropesa</t>
+          <t>08/18/2026 – Ivan Caisapanta</t>
         </is>
       </c>
       <c r="H17" s="64" t="inlineStr">
         <is>
-          <t>Signed attestation – Investment Operations Director, VP, dated 8/17/2026.</t>
+          <t>"Hi Elizabeth, You have my approval" – Financial Risk (BCiC Department Manager recorded as Xavier Caisapanta).</t>
         </is>
       </c>
       <c r="I17" s="64" t="inlineStr">
         <is>
-          <t>4052, 1936, 1937</t>
+          <t>1937</t>
         </is>
       </c>
       <c r="J17" s="64" t="inlineStr">
@@ -14271,12 +13763,12 @@
     <row r="18" ht="23" customHeight="1" s="71">
       <c r="A18" s="64" t="inlineStr">
         <is>
-          <t>DMA05</t>
+          <t>DMA09</t>
         </is>
       </c>
       <c r="B18" s="64" t="inlineStr">
         <is>
-          <t>DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
+          <t>DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg</t>
         </is>
       </c>
       <c r="C18" s="64" t="inlineStr">
@@ -14286,7 +13778,7 @@
       </c>
       <c r="D18" s="64" t="inlineStr">
         <is>
-          <t>RE_ Management Attestation – DIV Operations.msg</t>
+          <t>RE_ Management Attestation – DIV General Services.msg</t>
         </is>
       </c>
       <c r="E18" s="64" t="inlineStr">
@@ -14301,17 +13793,17 @@
       </c>
       <c r="G18" s="64" t="inlineStr">
         <is>
-          <t>08/19/2026 – Maria Teresa (Mayte) Del Cerro</t>
+          <t>08/18/2026 – Clara G. De Castro</t>
         </is>
       </c>
       <c r="H18" s="64" t="inlineStr">
         <is>
-          <t>Signed attestation + BCiC export (E16b) returned by Senior Director of Operations.</t>
+          <t>Clara De Castro (Director, General Services &amp; Facilities) returns the signed attestation – attachment: Data_Integrity_Attestation_Santander-BCiC.pdf (signed Clara G. De Castro).</t>
         </is>
       </c>
       <c r="I18" s="64" t="inlineStr">
         <is>
-          <t>3299, 1903, 1937</t>
+          <t>1937</t>
         </is>
       </c>
       <c r="J18" s="64" t="inlineStr">
@@ -14325,22 +13817,22 @@
     <row r="19" ht="23" customHeight="1" s="71">
       <c r="A19" s="64" t="inlineStr">
         <is>
-          <t>DMA05a</t>
+          <t>DMA10</t>
         </is>
       </c>
       <c r="B19" s="64" t="inlineStr">
         <is>
-          <t>DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+          <t>DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml</t>
         </is>
       </c>
       <c r="C19" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
         </is>
       </c>
       <c r="D19" s="64" t="inlineStr">
         <is>
-          <t>Data_Integrity_Attestation_Santander-BCiC.pdf (attachment of DMA05)</t>
+          <t>RE Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises).eml</t>
         </is>
       </c>
       <c r="E19" s="64" t="inlineStr">
@@ -14350,22 +13842,22 @@
       </c>
       <c r="F19" s="64" t="inlineStr">
         <is>
-          <t>Signed attestation</t>
+          <t>Email approval</t>
         </is>
       </c>
       <c r="G19" s="64" t="inlineStr">
         <is>
-          <t>08/19/2026 – Maria Teresa Del Cerro Hontanilla</t>
+          <t>08/21/2026 – Victoria Fernandez</t>
         </is>
       </c>
       <c r="H19" s="64" t="inlineStr">
         <is>
-          <t>Signed attestation – Director of Operations, dated 08/19/2026.</t>
+          <t>"Approved" – Digital Wealth.</t>
         </is>
       </c>
       <c r="I19" s="64" t="inlineStr">
         <is>
-          <t>3299, 1903, 1937</t>
+          <t>1937</t>
         </is>
       </c>
       <c r="J19" s="64" t="inlineStr">
@@ -14379,12 +13871,12 @@
     <row r="20" ht="23" customHeight="1" s="71">
       <c r="A20" s="64" t="inlineStr">
         <is>
-          <t>DMA06</t>
+          <t>DMA11</t>
         </is>
       </c>
       <c r="B20" s="64" t="inlineStr">
         <is>
-          <t>DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg</t>
+          <t>DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml</t>
         </is>
       </c>
       <c r="C20" s="64" t="inlineStr">
@@ -14394,7 +13886,7 @@
       </c>
       <c r="D20" s="64" t="inlineStr">
         <is>
-          <t>RE_ Management Attestation – DIV Trading and Capital Markets.msg</t>
+          <t>RE Management Attestation – DIV Commercial Middle Office.eml</t>
         </is>
       </c>
       <c r="E20" s="64" t="inlineStr">
@@ -14404,22 +13896,22 @@
       </c>
       <c r="F20" s="64" t="inlineStr">
         <is>
-          <t>Email attestation</t>
+          <t>Email approval</t>
         </is>
       </c>
       <c r="G20" s="64" t="inlineStr">
         <is>
-          <t>08/18/2026 – Ricardo Garcia-Marques</t>
+          <t>09/09/2026 – Miguel Orozco</t>
         </is>
       </c>
       <c r="H20" s="64" t="inlineStr">
         <is>
-          <t>Attestation and approval from Trading &amp; Capital Markets (covers BCiC records approved by Ricardo Garcia).</t>
+          <t>"I approve the integrity validation for the testing performed by the Commercial Middle Office."</t>
         </is>
       </c>
       <c r="I20" s="64" t="inlineStr">
         <is>
-          <t>1937</t>
+          <t>3299, 1937</t>
         </is>
       </c>
       <c r="J20" s="64" t="inlineStr">
@@ -14433,22 +13925,22 @@
     <row r="21" ht="23" customHeight="1" s="71">
       <c r="A21" s="64" t="inlineStr">
         <is>
-          <t>DMA06a</t>
+          <t>DMA12</t>
         </is>
       </c>
       <c r="B21" s="64" t="inlineStr">
         <is>
-          <t>DMA06a_Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Data_Integrity_Attestation_Santander-BCiC_signed.pdf</t>
+          <t>DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml</t>
         </is>
       </c>
       <c r="C21" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
         </is>
       </c>
       <c r="D21" s="64" t="inlineStr">
         <is>
-          <t>Data_Integrity_Attestation_Santander-BCiC_signed.pdf (attachment of DMA06)</t>
+          <t>RE Management Attestation – DIV Client Servicing Unit.eml</t>
         </is>
       </c>
       <c r="E21" s="64" t="inlineStr">
@@ -14458,17 +13950,17 @@
       </c>
       <c r="F21" s="64" t="inlineStr">
         <is>
-          <t>Signed attestation (e-signature)</t>
+          <t>Email approval</t>
         </is>
       </c>
       <c r="G21" s="64" t="inlineStr">
         <is>
-          <t>08/18/2026 11:45 AM EDT – Ricardo Garcia Marques</t>
+          <t>09/09/2026 – Liliana Vizhnay</t>
         </is>
       </c>
       <c r="H21" s="64" t="inlineStr">
         <is>
-          <t>e-signed attestation – MD, Head of Trading &amp; Capital Markets.</t>
+          <t>"I approve." – Client Servicing Unit.</t>
         </is>
       </c>
       <c r="I21" s="64" t="inlineStr">
@@ -14487,12 +13979,12 @@
     <row r="22" ht="23" customHeight="1" s="71">
       <c r="A22" s="64" t="inlineStr">
         <is>
-          <t>DMA07</t>
+          <t>DMA13</t>
         </is>
       </c>
       <c r="B22" s="64" t="inlineStr">
         <is>
-          <t>DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg</t>
+          <t>DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml</t>
         </is>
       </c>
       <c r="C22" s="64" t="inlineStr">
@@ -14502,7 +13994,7 @@
       </c>
       <c r="D22" s="64" t="inlineStr">
         <is>
-          <t>RE_ Management Attestation – DIV Treasury and Capital Planning.msg</t>
+          <t>RE Management Attestation – DIV Unified Communication - Cisco Call Manager.eml</t>
         </is>
       </c>
       <c r="E22" s="64" t="inlineStr">
@@ -14512,27 +14004,27 @@
       </c>
       <c r="F22" s="64" t="inlineStr">
         <is>
-          <t>Email attestation</t>
+          <t>Email approval</t>
         </is>
       </c>
       <c r="G22" s="64" t="inlineStr">
         <is>
-          <t>08/18/2026 – Martha Sullivan</t>
+          <t>09/09/2026 – Elizabeth Noda</t>
         </is>
       </c>
       <c r="H22" s="64" t="inlineStr">
         <is>
-          <t>Martha Sullivan returns signed attestation (DMA07a).</t>
+          <t>"approve" – Cisco Call Manager (IT). Cisco Call Manager is NOT one of the 10 tested applications – retained for completeness only.</t>
         </is>
       </c>
       <c r="I22" s="64" t="inlineStr">
         <is>
-          <t>1937</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J22" s="64" t="inlineStr">
         <is>
-          <t>G, H, J, O</t>
+          <t>Supplemental</t>
         </is>
       </c>
       <c r="K22" s="64" t="inlineStr"/>
@@ -14541,52 +14033,52 @@
     <row r="23" ht="23" customHeight="1" s="71">
       <c r="A23" s="64" t="inlineStr">
         <is>
-          <t>DMA07a</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="B23" s="64" t="inlineStr">
         <is>
-          <t>DMA07a_Treasury &amp; Capital Planning - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+          <t>BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
         </is>
       </c>
       <c r="C23" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
         </is>
       </c>
       <c r="D23" s="64" t="inlineStr">
         <is>
-          <t>attachment of DMA07</t>
+          <t>Applications In Scope for DR Test BSI (13).xlsx</t>
         </is>
       </c>
       <c r="E23" s="64" t="inlineStr">
         <is>
-          <t>DIV Manager Attestation Email_Approvals.zip</t>
+          <t>Data Integrity &amp; Email Testing Evidence.zip</t>
         </is>
       </c>
       <c r="F23" s="64" t="inlineStr">
         <is>
-          <t>Signed attestation</t>
+          <t>BCiC export</t>
         </is>
       </c>
       <c r="G23" s="64" t="inlineStr">
         <is>
-          <t>08/18/2026 – Martha Sullivan</t>
+          <t>BCiC – Applications In Scope for DR Test BSI</t>
         </is>
       </c>
       <c r="H23" s="64" t="inlineStr">
         <is>
-          <t>Signed attestation – Balance Sheet Manager, Treasury.</t>
+          <t>BCiC export of the BSI DR-scope population (43 applications) with Exercise Date and 2025 DR / Backup-Restore / DIV scope flags.</t>
         </is>
       </c>
       <c r="I23" s="64" t="inlineStr">
         <is>
-          <t>1937</t>
+          <t>1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
         </is>
       </c>
       <c r="J23" s="64" t="inlineStr">
         <is>
-          <t>G, H, J, O</t>
+          <t>B, C, D, K, L, N</t>
         </is>
       </c>
       <c r="K23" s="64" t="inlineStr"/>
@@ -14595,52 +14087,52 @@
     <row r="24" ht="23" customHeight="1" s="71">
       <c r="A24" s="64" t="inlineStr">
         <is>
-          <t>DMA08</t>
+          <t>E02</t>
         </is>
       </c>
       <c r="B24" s="64" t="inlineStr">
         <is>
-          <t>DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg</t>
         </is>
       </c>
       <c r="C24" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
         </is>
       </c>
       <c r="D24" s="64" t="inlineStr">
         <is>
-          <t>RE_ Management Attestation – DIV Solvency and Market Risk.msg</t>
+          <t>screenshot BCiC apps in scope for DR Testing.jpg</t>
         </is>
       </c>
       <c r="E24" s="64" t="inlineStr">
         <is>
-          <t>DIV Manager Attestation Email_Approvals.zip</t>
+          <t>Data Integrity &amp; Email Testing Evidence.zip</t>
         </is>
       </c>
       <c r="F24" s="64" t="inlineStr">
         <is>
-          <t>Email approval</t>
+          <t>BCiC screenshot</t>
         </is>
       </c>
       <c r="G24" s="64" t="inlineStr">
         <is>
-          <t>08/18/2026 – Ivan Caisapanta</t>
+          <t>09/10/2026 – Cesar Vidal</t>
         </is>
       </c>
       <c r="H24" s="64" t="inlineStr">
         <is>
-          <t>"Hi Elizabeth, You have my approval" – Financial Risk (BCiC Department Manager recorded as Xavier Caisapanta).</t>
+          <t>BCiC Applications screen with view 'Applications In Scope for DR Test BSI' selected (1–20 of 43 items).</t>
         </is>
       </c>
       <c r="I24" s="64" t="inlineStr">
         <is>
-          <t>1937</t>
+          <t>1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
         </is>
       </c>
       <c r="J24" s="64" t="inlineStr">
         <is>
-          <t>G, H, J, O</t>
+          <t>D, K, N</t>
         </is>
       </c>
       <c r="K24" s="64" t="inlineStr"/>
@@ -14649,52 +14141,52 @@
     <row r="25" ht="23" customHeight="1" s="71">
       <c r="A25" s="64" t="inlineStr">
         <is>
-          <t>DMA09</t>
+          <t>E03</t>
         </is>
       </c>
       <c r="B25" s="64" t="inlineStr">
         <is>
-          <t>DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
         </is>
       </c>
       <c r="C25" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
         </is>
       </c>
       <c r="D25" s="64" t="inlineStr">
         <is>
-          <t>RE_ Management Attestation – DIV General Services.msg</t>
+          <t>All Data Integrity Validation Testing_FV.xls</t>
         </is>
       </c>
       <c r="E25" s="64" t="inlineStr">
         <is>
-          <t>DIV Manager Attestation Email_Approvals.zip</t>
+          <t>Data Integrity &amp; Email Testing Evidence.zip</t>
         </is>
       </c>
       <c r="F25" s="64" t="inlineStr">
         <is>
-          <t>Email attestation</t>
+          <t>BCiC export</t>
         </is>
       </c>
       <c r="G25" s="64" t="inlineStr">
         <is>
-          <t>08/18/2026 – Clara G. De Castro</t>
+          <t>BCiC – Data Integrity Validation Testing (62 records)</t>
         </is>
       </c>
       <c r="H25" s="64" t="inlineStr">
         <is>
-          <t>Clara De Castro (Director, General Services &amp; Facilities) returns signed attestation (DMA09a).</t>
+          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Y/N Format/Headers/Content, Attestation Date / Provided By. Row numbers quoted are Excel rows.</t>
         </is>
       </c>
       <c r="I25" s="64" t="inlineStr">
         <is>
-          <t>1937</t>
+          <t>1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
         </is>
       </c>
       <c r="J25" s="64" t="inlineStr">
         <is>
-          <t>G, H, J, O</t>
+          <t>B, C, D, E, F, G, H, I, K, L, M, O, P</t>
         </is>
       </c>
       <c r="K25" s="64" t="inlineStr"/>
@@ -14703,52 +14195,52 @@
     <row r="26">
       <c r="A26" s="64" t="inlineStr">
         <is>
-          <t>DMA09a</t>
+          <t>E04</t>
         </is>
       </c>
       <c r="B26" s="64" t="inlineStr">
         <is>
-          <t>DMA09a_General Services (Marketing &amp; General Services) - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+          <t>BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg</t>
         </is>
       </c>
       <c r="C26" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
         </is>
       </c>
       <c r="D26" s="64" t="inlineStr">
         <is>
-          <t>attachment of DMA09</t>
+          <t>BCiC_Screenshot for Data Integrity Validation report.jpg</t>
         </is>
       </c>
       <c r="E26" s="64" t="inlineStr">
         <is>
-          <t>DIV Manager Attestation Email_Approvals.zip</t>
+          <t>Data Integrity &amp; Email Testing Evidence.zip</t>
         </is>
       </c>
       <c r="F26" s="64" t="inlineStr">
         <is>
-          <t>Signed attestation</t>
+          <t>BCiC screenshot</t>
         </is>
       </c>
       <c r="G26" s="64" t="inlineStr">
         <is>
-          <t>08/18/2026 – Clara G. De Castro</t>
+          <t>09/10/2026 – Cesar Vidal</t>
         </is>
       </c>
       <c r="H26" s="64" t="inlineStr">
         <is>
-          <t>Signed attestation – General Services.</t>
+          <t>BCiC 'Data Integrity Validation Testing' screen (1–20 of 66 items) showing tester, validation date, manager, approval date, Y/N results and attestation fields.</t>
         </is>
       </c>
       <c r="I26" s="64" t="inlineStr">
         <is>
-          <t>1937</t>
+          <t>1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
         </is>
       </c>
       <c r="J26" s="64" t="inlineStr">
         <is>
-          <t>G, H, J, O</t>
+          <t>D, E, F, G, H, K, P</t>
         </is>
       </c>
       <c r="K26" s="64" t="inlineStr"/>
@@ -14757,52 +14249,52 @@
     <row r="27">
       <c r="A27" s="64" t="inlineStr">
         <is>
-          <t>DMA10</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="B27" s="64" t="inlineStr">
         <is>
-          <t>DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml</t>
+          <t>BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg</t>
         </is>
       </c>
       <c r="C27" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
         </is>
       </c>
       <c r="D27" s="64" t="inlineStr">
         <is>
-          <t>RE Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises).eml</t>
+          <t>IT BIA Results Review and preparation for DR .msg</t>
         </is>
       </c>
       <c r="E27" s="64" t="inlineStr">
         <is>
-          <t>DIV Manager Attestation Email_Approvals.zip</t>
+          <t>Data Integrity &amp; Email Testing Evidence.zip</t>
         </is>
       </c>
       <c r="F27" s="64" t="inlineStr">
         <is>
-          <t>Email approval</t>
+          <t>Meeting invite</t>
         </is>
       </c>
       <c r="G27" s="64" t="inlineStr">
         <is>
-          <t>08/21/2026 – Victoria Fernandez</t>
+          <t>09/15/2025 – Elizabeth Noda</t>
         </is>
       </c>
       <c r="H27" s="64" t="inlineStr">
         <is>
-          <t>"Approved" – Digital Wealth.</t>
+          <t>IT DR meeting invite to review the 2025 BIA results and applications list ahead of the DR exercise (same invite re-sent 09/18/2025 – duplicate E06 removed).</t>
         </is>
       </c>
       <c r="I27" s="64" t="inlineStr">
         <is>
-          <t>1937</t>
+          <t>1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
         </is>
       </c>
       <c r="J27" s="64" t="inlineStr">
         <is>
-          <t>G, H, J, O</t>
+          <t>M, N</t>
         </is>
       </c>
       <c r="K27" s="64" t="inlineStr"/>
@@ -14811,52 +14303,52 @@
     <row r="28">
       <c r="A28" s="64" t="inlineStr">
         <is>
-          <t>DMA11</t>
+          <t>E07</t>
         </is>
       </c>
       <c r="B28" s="64" t="inlineStr">
         <is>
-          <t>DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml</t>
+          <t>BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg</t>
         </is>
       </c>
       <c r="C28" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
         </is>
       </c>
       <c r="D28" s="64" t="inlineStr">
         <is>
-          <t>RE Management Attestation – DIV Commercial Middle Office.eml</t>
+          <t>DATA INTERITY FILS FROM 111425.msg</t>
         </is>
       </c>
       <c r="E28" s="64" t="inlineStr">
         <is>
-          <t>DIV Manager Attestation Email_Approvals.zip</t>
+          <t>Data Integrity &amp; Email Testing Evidence.zip</t>
         </is>
       </c>
       <c r="F28" s="64" t="inlineStr">
         <is>
-          <t>Email approval</t>
+          <t>Email + report attachments</t>
         </is>
       </c>
       <c r="G28" s="64" t="inlineStr">
         <is>
-          <t>09/09/2026 – Miguel Orozco</t>
+          <t>11/15/2025 – Frank Puentes</t>
         </is>
       </c>
       <c r="H28" s="64" t="inlineStr">
         <is>
-          <t>"I approve the integrity validation for the testing performed by the Commercial Middle Office."</t>
+          <t>Pre-DR (11/14/2025) source reports: Fedlink, OFAC ACH/FED/SWIFT, Payment Monitor, SWIFT Interface Monitor, outgoing Fedwire/SWIFT. Embedded attachments: FEDLINK INCOMING FEDWIRES 111425 0523PM.pdf; FEDLINK OUTGOING FEDWIRES 111425 0523PM.pdf; OFAC ACH 111425 0512PM.pdf; OFAC FED 111425 0511PM.pdf; OFAC SWIFT 111425 0511PM.pdf; OUTGOING FEDWIRE 111425 506PM.xls; OUTGOING SWIFT 111425 509PM.xls; PAYMENT MONITOR INCOMING FEDWIRE 111425 516PM PG1.pdf; PAYMENT MONITOR INCOMING FEDWIRE 111425 516PM PG2.pdf; PAYMENT MONITOR OUTGOING FEDWIRE 111425 516PM PG1.pdf; PAYMENT MONITOR OUTGOING FEDWIRE 111425 516PM PG2.pdf; SWIFT INTERFACE MONITOR 111425 519PM.pdf; SWIFT INTERFACE MONITOR 111425 520PM 2ND SAMPLE.pdf.</t>
         </is>
       </c>
       <c r="I28" s="64" t="inlineStr">
         <is>
-          <t>3299, 1937</t>
+          <t>3301, 1903, 1936, 1937</t>
         </is>
       </c>
       <c r="J28" s="64" t="inlineStr">
         <is>
-          <t>G, H, J, O</t>
+          <t>F</t>
         </is>
       </c>
       <c r="K28" s="64" t="inlineStr"/>
@@ -14865,52 +14357,52 @@
     <row r="29">
       <c r="A29" s="64" t="inlineStr">
         <is>
-          <t>DMA12</t>
+          <t>E08</t>
         </is>
       </c>
       <c r="B29" s="64" t="inlineStr">
         <is>
-          <t>DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml</t>
+          <t>BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg</t>
         </is>
       </c>
       <c r="C29" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
         </is>
       </c>
       <c r="D29" s="64" t="inlineStr">
         <is>
-          <t>RE Management Attestation – DIV Client Servicing Unit.eml</t>
+          <t>FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg</t>
         </is>
       </c>
       <c r="E29" s="64" t="inlineStr">
         <is>
-          <t>DIV Manager Attestation Email_Approvals.zip</t>
+          <t>Data Integrity &amp; Email Testing Evidence.zip</t>
         </is>
       </c>
       <c r="F29" s="64" t="inlineStr">
         <is>
-          <t>Email approval</t>
+          <t>Email + report attachments</t>
         </is>
       </c>
       <c r="G29" s="64" t="inlineStr">
         <is>
-          <t>09/09/2026 – Liliana Vizhnay</t>
+          <t>11/15/2025 – Frank Puentes</t>
         </is>
       </c>
       <c r="H29" s="64" t="inlineStr">
         <is>
-          <t>"I approve." – Client Servicing Unit.</t>
+          <t>DR test-day (11/15/2025) re-run of the same reports for comparison with 11/14/2025 source. Embedded attachments: FEDLINK INCOMING FEDWIRES 111425 -1115 1148AM.pdf; FEDLINK OUTGOINT TRANSFERS 114125 - 111525 1144AM.pdf; OFAC ACH 111425 - 11152025 1126AM.pdf; OFAC FED 111425 - 111525 1126AM.pdf; OFAC SWIFT 111425 - 111525 1128AM.pdf; OUTGOING FEDWIRE 111525 1025AM.xls; OUTGOING SWIFT 111525 1026AM.xls; PAYMENT MONITOR 111424 - 111525 PG 11156AM.pdf; PAYMENT MONITOR 111425 - 111525 PG 2 1158AM.pdf; PAYMENT MONITOR OUTGOING 111425 - 111525 PG 1 1156AM.pdf; PAYMENT MONITOR OUTGOING 111425 - 111525 PG 2 1156AM.pdf; SWIFT INTERFACE MONITOR INCOMING MT103 111425 - 111525 1152AM.pdf; SWIFT INTERFACE MONITOR INCOMING MT199 111425 -111525 1152AM.pdf.</t>
         </is>
       </c>
       <c r="I29" s="64" t="inlineStr">
         <is>
-          <t>1937</t>
+          <t>3301, 1903, 1936, 1937</t>
         </is>
       </c>
       <c r="J29" s="64" t="inlineStr">
         <is>
-          <t>G, H, J, O</t>
+          <t>F, M</t>
         </is>
       </c>
       <c r="K29" s="64" t="inlineStr"/>
@@ -14919,27 +14411,27 @@
     <row r="30">
       <c r="A30" s="64" t="inlineStr">
         <is>
-          <t>DMA13</t>
+          <t>E09</t>
         </is>
       </c>
       <c r="B30" s="64" t="inlineStr">
         <is>
-          <t>DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml</t>
+          <t>BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg</t>
         </is>
       </c>
       <c r="C30" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
         </is>
       </c>
       <c r="D30" s="64" t="inlineStr">
         <is>
-          <t>RE Management Attestation – DIV Unified Communication - Cisco Call Manager.eml</t>
+          <t>RE_ Yearly Backup and restore exercise (Client Back Office)</t>
         </is>
       </c>
       <c r="E30" s="64" t="inlineStr">
         <is>
-          <t>DIV Manager Attestation Email_Approvals.zip</t>
+          <t>Data Integrity &amp; Email Testing Evidence.zip</t>
         </is>
       </c>
       <c r="F30" s="64" t="inlineStr">
@@ -14949,22 +14441,22 @@
       </c>
       <c r="G30" s="64" t="inlineStr">
         <is>
-          <t>09/09/2026 – Elizabeth Noda</t>
+          <t>03/03/2026 – 05/05/2026 – Claudia Romero</t>
         </is>
       </c>
       <c r="H30" s="64" t="inlineStr">
         <is>
-          <t>"approve" – Cisco Call Manager (IT). Cisco Call Manager is NOT one of the 10 tested applications – retained for completeness only.</t>
+          <t>Client Back Office test evidence (Mariorly Morales, Ilumel Rodriguez, Rolando Bonilla) and Claudia Romero "Approved." 05/05/2026. Thread maps ACH Express, FedExport, FedImport, Imaging101 to Client Back Office / Claudia Romero.</t>
         </is>
       </c>
       <c r="I30" s="64" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1822, 1867, 1868, 3299, 1937</t>
         </is>
       </c>
       <c r="J30" s="64" t="inlineStr">
         <is>
-          <t>Supplemental</t>
+          <t>E, G, H, J, M, N, O</t>
         </is>
       </c>
       <c r="K30" s="64" t="inlineStr"/>
@@ -14973,12 +14465,12 @@
     <row r="31">
       <c r="A31" s="64" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>E10</t>
         </is>
       </c>
       <c r="B31" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
+          <t>BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg</t>
         </is>
       </c>
       <c r="C31" s="64" t="inlineStr">
@@ -14988,7 +14480,7 @@
       </c>
       <c r="D31" s="64" t="inlineStr">
         <is>
-          <t>Applications In Scope for DR Test BSI (13).xlsx</t>
+          <t>RE_ Yearly Backup and restore exercise-- re-run (Finance)</t>
         </is>
       </c>
       <c r="E31" s="64" t="inlineStr">
@@ -14998,27 +14490,27 @@
       </c>
       <c r="F31" s="64" t="inlineStr">
         <is>
-          <t>BCiC export</t>
+          <t>Email approval</t>
         </is>
       </c>
       <c r="G31" s="64" t="inlineStr">
         <is>
-          <t>BCiC – Applications In Scope for DR Test BSI</t>
+          <t>03/09/2026 – Lina Acuna</t>
         </is>
       </c>
       <c r="H31" s="64" t="inlineStr">
         <is>
-          <t>BCiC export of the BSI DR-scope population (43 applications) with Exercise Date and 2025 DR / Backup-Restore / DIV scope flags.</t>
+          <t>Finance DIV results chart (Jose Acero) and Lina Acuna "Approved" 03/09/2026 (T24 / ReconXpert backup-restore).</t>
         </is>
       </c>
       <c r="I31" s="64" t="inlineStr">
         <is>
-          <t>1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
+          <t>1917, 1937</t>
         </is>
       </c>
       <c r="J31" s="64" t="inlineStr">
         <is>
-          <t>B, C, D, K, L, N</t>
+          <t>M</t>
         </is>
       </c>
       <c r="K31" s="64" t="inlineStr"/>
@@ -15027,12 +14519,12 @@
     <row r="32">
       <c r="A32" s="64" t="inlineStr">
         <is>
-          <t>E02</t>
+          <t>E13</t>
         </is>
       </c>
       <c r="B32" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg</t>
+          <t>BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg</t>
         </is>
       </c>
       <c r="C32" s="64" t="inlineStr">
@@ -15042,7 +14534,7 @@
       </c>
       <c r="D32" s="64" t="inlineStr">
         <is>
-          <t>screenshot BCiC apps in scope for DR Testing.jpg</t>
+          <t>miasx2 T24 environment(s) miaeod miabed01 refreshed correctly.msg</t>
         </is>
       </c>
       <c r="E32" s="64" t="inlineStr">
@@ -15052,27 +14544,27 @@
       </c>
       <c r="F32" s="64" t="inlineStr">
         <is>
-          <t>BCiC screenshot</t>
+          <t>System email</t>
         </is>
       </c>
       <c r="G32" s="64" t="inlineStr">
         <is>
-          <t>09/10/2026 – Cesar Vidal</t>
+          <t>11/13/2024 – T24 backup user</t>
         </is>
       </c>
       <c r="H32" s="64" t="inlineStr">
         <is>
-          <t>BCiC Applications screen with view 'Applications In Scope for DR Test BSI' selected (1–20 of 43 items).</t>
+          <t>T24 environment refresh log – prior period (outside review period); supplemental only.</t>
         </is>
       </c>
       <c r="I32" s="64" t="inlineStr">
         <is>
-          <t>1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J32" s="64" t="inlineStr">
         <is>
-          <t>D, K, N</t>
+          <t>Supplemental</t>
         </is>
       </c>
       <c r="K32" s="64" t="inlineStr"/>
@@ -15081,12 +14573,12 @@
     <row r="33">
       <c r="A33" s="64" t="inlineStr">
         <is>
-          <t>E03</t>
+          <t>E16b</t>
         </is>
       </c>
       <c r="B33" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+          <t>BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
         </is>
       </c>
       <c r="C33" s="64" t="inlineStr">
@@ -15096,7 +14588,7 @@
       </c>
       <c r="D33" s="64" t="inlineStr">
         <is>
-          <t>All Data Integrity Validation Testing_FV.xls</t>
+          <t>All Data Integrity Validation Testing-BSI 2025-26.xlsx (attachment of DMA05 email)</t>
         </is>
       </c>
       <c r="E33" s="64" t="inlineStr">
@@ -15111,12 +14603,12 @@
       </c>
       <c r="G33" s="64" t="inlineStr">
         <is>
-          <t>BCiC – Data Integrity Validation Testing (62 records)</t>
+          <t>08/2026 – BCiC export sent with attestation request</t>
         </is>
       </c>
       <c r="H33" s="64" t="inlineStr">
         <is>
-          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Y/N Format/Headers/Content, Attestation Date / Provided By. Row numbers quoted are Excel rows.</t>
+          <t>BCiC DIV export 2025-26 (64 rows; no manager columns) sent to managers with the attestation request and returned by M. T. Del Cerro (DMA05). Row numbers are Excel rows.</t>
         </is>
       </c>
       <c r="I33" s="64" t="inlineStr">
@@ -15126,644 +14618,376 @@
       </c>
       <c r="J33" s="64" t="inlineStr">
         <is>
-          <t>B, C, D, E, F, G, H, I, K, L, M, O, P</t>
+          <t>B, D, E, F, I, K, P</t>
         </is>
       </c>
       <c r="K33" s="64" t="inlineStr"/>
       <c r="L33" s="82" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="64" t="inlineStr">
-        <is>
-          <t>E04</t>
-        </is>
-      </c>
-      <c r="B34" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg</t>
-        </is>
-      </c>
-      <c r="C34" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
-        </is>
-      </c>
-      <c r="D34" s="64" t="inlineStr">
-        <is>
-          <t>BCiC_Screenshot for Data Integrity Validation report.jpg</t>
-        </is>
-      </c>
-      <c r="E34" s="64" t="inlineStr">
-        <is>
-          <t>Data Integrity &amp; Email Testing Evidence.zip</t>
-        </is>
-      </c>
-      <c r="F34" s="64" t="inlineStr">
-        <is>
-          <t>BCiC screenshot</t>
-        </is>
-      </c>
-      <c r="G34" s="64" t="inlineStr">
-        <is>
-          <t>09/10/2026 – Cesar Vidal</t>
-        </is>
-      </c>
-      <c r="H34" s="64" t="inlineStr">
-        <is>
-          <t>BCiC 'Data Integrity Validation Testing' screen (1–20 of 66 items) showing tester, validation date, manager, approval date, Y/N results and attestation fields.</t>
-        </is>
-      </c>
-      <c r="I34" s="64" t="inlineStr">
-        <is>
-          <t>1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
-        </is>
-      </c>
-      <c r="J34" s="64" t="inlineStr">
-        <is>
-          <t>D, E, F, G, H, K, P</t>
-        </is>
-      </c>
-      <c r="K34" s="64" t="inlineStr"/>
+      <c r="A34" s="82" t="n"/>
+      <c r="B34" s="82" t="n"/>
+      <c r="C34" s="82" t="n"/>
+      <c r="D34" s="82" t="n"/>
+      <c r="E34" s="82" t="n"/>
+      <c r="F34" s="82" t="n"/>
+      <c r="G34" s="82" t="n"/>
+      <c r="H34" s="82" t="n"/>
+      <c r="I34" s="82" t="n"/>
+      <c r="J34" s="82" t="n"/>
+      <c r="K34" s="82" t="n"/>
       <c r="L34" s="82" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="64" t="inlineStr">
-        <is>
-          <t>E05</t>
-        </is>
-      </c>
-      <c r="B35" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg</t>
-        </is>
-      </c>
-      <c r="C35" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
-        </is>
-      </c>
-      <c r="D35" s="64" t="inlineStr">
-        <is>
-          <t>IT BIA Results Review and preparation for DR .msg</t>
-        </is>
-      </c>
-      <c r="E35" s="64" t="inlineStr">
-        <is>
-          <t>Data Integrity &amp; Email Testing Evidence.zip</t>
-        </is>
-      </c>
-      <c r="F35" s="64" t="inlineStr">
-        <is>
-          <t>Meeting invite</t>
-        </is>
-      </c>
-      <c r="G35" s="64" t="inlineStr">
-        <is>
-          <t>09/15/2025 – Elizabeth Noda</t>
-        </is>
-      </c>
-      <c r="H35" s="64" t="inlineStr">
-        <is>
-          <t>IT DR meeting to review the 2025 BIA results and applications list ahead of the DR exercise.</t>
-        </is>
-      </c>
-      <c r="I35" s="64" t="inlineStr">
-        <is>
-          <t>1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
-        </is>
-      </c>
-      <c r="J35" s="64" t="inlineStr">
-        <is>
-          <t>M, N</t>
-        </is>
-      </c>
-      <c r="K35" s="64" t="inlineStr"/>
+      <c r="A35" s="60" t="inlineStr">
+        <is>
+          <t>Redundant files removed from the repository (one copy of each item retained)</t>
+        </is>
+      </c>
+      <c r="B35" s="82" t="n"/>
+      <c r="C35" s="82" t="n"/>
+      <c r="D35" s="82" t="n"/>
+      <c r="E35" s="82" t="n"/>
+      <c r="F35" s="82" t="n"/>
+      <c r="G35" s="82" t="n"/>
+      <c r="H35" s="82" t="n"/>
+      <c r="I35" s="82" t="n"/>
+      <c r="J35" s="82" t="n"/>
+      <c r="K35" s="82" t="n"/>
       <c r="L35" s="82" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="64" t="inlineStr">
-        <is>
-          <t>E06</t>
-        </is>
-      </c>
-      <c r="B36" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml</t>
-        </is>
-      </c>
-      <c r="C36" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
-        </is>
-      </c>
-      <c r="D36" s="64" t="inlineStr">
-        <is>
-          <t>IT BIA Results Review and preparation for DR  1 (1).msg.eml</t>
-        </is>
-      </c>
-      <c r="E36" s="64" t="inlineStr">
-        <is>
-          <t>Data Integrity &amp; Email Testing Evidence.zip</t>
-        </is>
-      </c>
-      <c r="F36" s="64" t="inlineStr">
-        <is>
-          <t>Meeting invite</t>
-        </is>
-      </c>
-      <c r="G36" s="64" t="inlineStr">
-        <is>
-          <t>09/18/2025 – Elizabeth Noda</t>
-        </is>
-      </c>
-      <c r="H36" s="64" t="inlineStr">
-        <is>
-          <t>Follow-up IT BIA results / DR preparation meeting (applications list review).</t>
-        </is>
-      </c>
-      <c r="I36" s="64" t="inlineStr">
-        <is>
-          <t>1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
-        </is>
-      </c>
-      <c r="J36" s="64" t="inlineStr">
-        <is>
-          <t>M, N</t>
-        </is>
-      </c>
-      <c r="K36" s="64" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Removed item</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Former location</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Retained ref</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Retained file location</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+      <c r="F36" s="82" t="n"/>
+      <c r="G36" s="82" t="n"/>
+      <c r="H36" s="82" t="n"/>
+      <c r="I36" s="82" t="n"/>
+      <c r="J36" s="82" t="n"/>
+      <c r="K36" s="82" t="n"/>
       <c r="L36" s="82" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="64" t="inlineStr">
         <is>
-          <t>E07</t>
+          <t>MA02</t>
         </is>
       </c>
       <c r="B37" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg</t>
         </is>
       </c>
       <c r="C37" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
+          <t>DMA03</t>
         </is>
       </c>
       <c r="D37" s="64" t="inlineStr">
         <is>
-          <t>DATA INTERITY FILS FROM 111425.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
         </is>
       </c>
       <c r="E37" s="64" t="inlineStr">
         <is>
-          <t>Data Integrity &amp; Email Testing Evidence.zip</t>
-        </is>
-      </c>
-      <c r="F37" s="64" t="inlineStr">
-        <is>
-          <t>Email + 13 attachments</t>
-        </is>
-      </c>
-      <c r="G37" s="64" t="inlineStr">
-        <is>
-          <t>11/15/2025 – Frank Puentes</t>
-        </is>
-      </c>
-      <c r="H37" s="64" t="inlineStr">
-        <is>
-          <t>Pre-DR (11/14/2025) source reports: Fedlink, OFAC ACH/FED/SWIFT, Payment Monitor, SWIFT Interface Monitor, outgoing Fedwire/SWIFT. Attachments extracted to E07_Attachments_extracted.</t>
-        </is>
-      </c>
-      <c r="I37" s="64" t="inlineStr">
-        <is>
-          <t>3301, 1903, 1936, 1937</t>
-        </is>
-      </c>
-      <c r="J37" s="64" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="K37" s="64" t="inlineStr"/>
+          <t>same email message (subject, sent 08/18/2026 14:50, attachment 4069_001.pdf)</t>
+        </is>
+      </c>
+      <c r="F37" s="82" t="n"/>
+      <c r="G37" s="82" t="n"/>
+      <c r="H37" s="82" t="n"/>
+      <c r="I37" s="82" t="n"/>
+      <c r="J37" s="82" t="n"/>
+      <c r="K37" s="82" t="n"/>
       <c r="L37" s="82" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="64" t="inlineStr">
         <is>
-          <t>E08</t>
+          <t>DMA05b</t>
         </is>
       </c>
       <c r="B38" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05b_Operations (Governance &amp; Static Data, Multi-Family Office) - All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
         </is>
       </c>
       <c r="C38" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
+          <t>E16b</t>
         </is>
       </c>
       <c r="D38" s="64" t="inlineStr">
         <is>
-          <t>FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
         </is>
       </c>
       <c r="E38" s="64" t="inlineStr">
         <is>
-          <t>Data Integrity &amp; Email Testing Evidence.zip</t>
-        </is>
-      </c>
-      <c r="F38" s="64" t="inlineStr">
-        <is>
-          <t>Email + 13 attachments</t>
-        </is>
-      </c>
-      <c r="G38" s="64" t="inlineStr">
-        <is>
-          <t>11/15/2025 – Frank Puentes</t>
-        </is>
-      </c>
-      <c r="H38" s="64" t="inlineStr">
-        <is>
-          <t>DR test-day (11/15/2025) re-run of the same reports for comparison with 11/14/2025 source. Attachments extracted to E08_Attachments_extracted.</t>
-        </is>
-      </c>
-      <c r="I38" s="64" t="inlineStr">
-        <is>
-          <t>3301, 1903, 1936, 1937</t>
-        </is>
-      </c>
-      <c r="J38" s="64" t="inlineStr">
-        <is>
-          <t>F, M</t>
-        </is>
-      </c>
-      <c r="K38" s="64" t="inlineStr"/>
+          <t>byte-identical file (MD5 match)</t>
+        </is>
+      </c>
+      <c r="F38" s="82" t="n"/>
+      <c r="G38" s="82" t="n"/>
+      <c r="H38" s="82" t="n"/>
+      <c r="I38" s="82" t="n"/>
+      <c r="J38" s="82" t="n"/>
+      <c r="K38" s="82" t="n"/>
       <c r="L38" s="82" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="64" t="inlineStr">
         <is>
-          <t>E09</t>
+          <t>E11</t>
         </is>
       </c>
       <c r="B39" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E11_BSI.IT.6.C7.3 Manager Approval.msg</t>
         </is>
       </c>
       <c r="C39" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
+          <t>E10</t>
         </is>
       </c>
       <c r="D39" s="64" t="inlineStr">
         <is>
-          <t>RE_ Yearly Backup and restore exercise (Client Back Office)</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg</t>
         </is>
       </c>
       <c r="E39" s="64" t="inlineStr">
         <is>
-          <t>Data Integrity &amp; Email Testing Evidence.zip</t>
-        </is>
-      </c>
-      <c r="F39" s="64" t="inlineStr">
-        <is>
-          <t>Email approval</t>
-        </is>
-      </c>
-      <c r="G39" s="64" t="inlineStr">
-        <is>
-          <t>03/03/2026 – 05/05/2026 – Claudia Romero</t>
-        </is>
-      </c>
-      <c r="H39" s="64" t="inlineStr">
-        <is>
-          <t>Client Back Office test evidence (Mariorly Morales, Ilumel Rodriguez, Rolando Bonilla) and Claudia Romero "Approved." 05/05/2026. Thread maps ACH Express, FedExport, FedImport, Imaging101 to Client Back Office / Claudia Romero.</t>
-        </is>
-      </c>
-      <c r="I39" s="64" t="inlineStr">
-        <is>
-          <t>1822, 1867, 1868, 3299, 1937</t>
-        </is>
-      </c>
-      <c r="J39" s="64" t="inlineStr">
-        <is>
-          <t>E, G, H, J, M, N, O</t>
-        </is>
-      </c>
-      <c r="K39" s="64" t="inlineStr"/>
+          <t>same email message (sent 03/09/2026 18:43) saved twice</t>
+        </is>
+      </c>
+      <c r="F39" s="82" t="n"/>
+      <c r="G39" s="82" t="n"/>
+      <c r="H39" s="82" t="n"/>
+      <c r="I39" s="82" t="n"/>
+      <c r="J39" s="82" t="n"/>
+      <c r="K39" s="82" t="n"/>
       <c r="L39" s="82" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="64" t="inlineStr">
         <is>
-          <t>E10</t>
+          <t>E12</t>
         </is>
       </c>
       <c r="B40" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E12_RE_ Testing enviroment Financial Analysis manager approval.msg</t>
         </is>
       </c>
       <c r="C40" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
+          <t>BLA06</t>
         </is>
       </c>
       <c r="D40" s="64" t="inlineStr">
         <is>
-          <t>RE_ Yearly Backup and restore exercise-- re-run (Finance)</t>
+          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg</t>
         </is>
       </c>
       <c r="E40" s="64" t="inlineStr">
         <is>
-          <t>Data Integrity &amp; Email Testing Evidence.zip</t>
-        </is>
-      </c>
-      <c r="F40" s="64" t="inlineStr">
-        <is>
-          <t>Email approval</t>
-        </is>
-      </c>
-      <c r="G40" s="64" t="inlineStr">
-        <is>
-          <t>03/09/2026 – Lina Acuna</t>
-        </is>
-      </c>
-      <c r="H40" s="64" t="inlineStr">
-        <is>
-          <t>Finance DIV results chart (Jose Acero) and Lina Acuna "Approved" 03/09/2026 (T24 / ReconXpert backup-restore).</t>
-        </is>
-      </c>
-      <c r="I40" s="64" t="inlineStr">
-        <is>
-          <t>1917, 1937</t>
-        </is>
-      </c>
-      <c r="J40" s="64" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="K40" s="64" t="inlineStr"/>
+          <t>same email message (sent 01/26/2026 20:43)</t>
+        </is>
+      </c>
+      <c r="F40" s="82" t="n"/>
+      <c r="G40" s="82" t="n"/>
+      <c r="H40" s="82" t="n"/>
+      <c r="I40" s="82" t="n"/>
+      <c r="J40" s="82" t="n"/>
+      <c r="K40" s="82" t="n"/>
       <c r="L40" s="82" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="64" t="inlineStr">
         <is>
-          <t>E13</t>
+          <t>E14</t>
         </is>
       </c>
       <c r="B41" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml</t>
         </is>
       </c>
       <c r="C41" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
+          <t>DMA02</t>
         </is>
       </c>
       <c r="D41" s="64" t="inlineStr">
         <is>
-          <t>miasx2 T24 environment(s) miaeod miabed01 refreshed correctly.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg</t>
         </is>
       </c>
       <c r="E41" s="64" t="inlineStr">
         <is>
-          <t>Data Integrity &amp; Email Testing Evidence.zip</t>
-        </is>
-      </c>
-      <c r="F41" s="64" t="inlineStr">
-        <is>
-          <t>System email</t>
-        </is>
-      </c>
-      <c r="G41" s="64" t="inlineStr">
-        <is>
-          <t>11/13/2024 – T24 backup user</t>
-        </is>
-      </c>
-      <c r="H41" s="64" t="inlineStr">
-        <is>
-          <t>T24 environment refresh log – prior period (outside review period); supplemental only.</t>
-        </is>
-      </c>
-      <c r="I41" s="64" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J41" s="64" t="inlineStr">
-        <is>
-          <t>Supplemental</t>
-        </is>
-      </c>
-      <c r="K41" s="64" t="inlineStr"/>
+          <t>same email message saved as .eml</t>
+        </is>
+      </c>
+      <c r="F41" s="82" t="n"/>
+      <c r="G41" s="82" t="n"/>
+      <c r="H41" s="82" t="n"/>
+      <c r="I41" s="82" t="n"/>
+      <c r="J41" s="82" t="n"/>
+      <c r="K41" s="82" t="n"/>
       <c r="L41" s="82" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="64" t="inlineStr">
         <is>
-          <t>E16b</t>
+          <t>E14a</t>
         </is>
       </c>
       <c r="B42" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf</t>
         </is>
       </c>
       <c r="C42" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
+          <t>DMA02</t>
         </is>
       </c>
       <c r="D42" s="64" t="inlineStr">
         <is>
-          <t>All Data Integrity Validation Testing-BSI 2025-26.xlsx (attachment of DMA05 email)</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg</t>
         </is>
       </c>
       <c r="E42" s="64" t="inlineStr">
         <is>
-          <t>Data Integrity &amp; Email Testing Evidence.zip</t>
-        </is>
-      </c>
-      <c r="F42" s="64" t="inlineStr">
-        <is>
-          <t>BCiC export</t>
-        </is>
-      </c>
-      <c r="G42" s="64" t="inlineStr">
-        <is>
-          <t>08/2026 – BCiC export sent with attestation request</t>
-        </is>
-      </c>
-      <c r="H42" s="64" t="inlineStr">
-        <is>
-          <t>BCiC DIV export 2025-26 (64 rows; no manager columns) sent to managers with the attestation request and returned by M. T. Del Cerro (DMA05). Row numbers are Excel rows.</t>
-        </is>
-      </c>
-      <c r="I42" s="64" t="inlineStr">
-        <is>
-          <t>1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
-        </is>
-      </c>
-      <c r="J42" s="64" t="inlineStr">
-        <is>
-          <t>B, D, E, F, I, K, P</t>
-        </is>
-      </c>
-      <c r="K42" s="64" t="inlineStr"/>
+          <t>byte-identical file (MD5 match) – retained inside DMA02 (attachment)</t>
+        </is>
+      </c>
+      <c r="F42" s="82" t="n"/>
+      <c r="G42" s="82" t="n"/>
+      <c r="H42" s="82" t="n"/>
+      <c r="I42" s="82" t="n"/>
+      <c r="J42" s="82" t="n"/>
+      <c r="K42" s="82" t="n"/>
       <c r="L42" s="82" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="64" t="inlineStr">
         <is>
-          <t>E07.01–E07.13</t>
+          <t>E15</t>
         </is>
       </c>
       <c r="B43" s="64" t="inlineStr">
         <is>
-          <t>E07.01_FEDLINK INCOMING FEDWIRES 111425 0523PM.pdf
-E07.02_FEDLINK OUTGOING FEDWIRES 111425 0523PM.pdf
-E07.03_OFAC ACH 111425 0512PM.pdf
-E07.04_OFAC FED 111425 0511PM.pdf
-E07.05_OFAC SWIFT 111425 0511PM.pdf
-E07.06_OUTGOING FEDWIRE 111425 506PM.xls
-E07.07_OUTGOING SWIFT 111425 509PM.xls
-E07.08_PAYMENT MONITOR INCOMING FEDWIRE 111425 516PM PG1.pdf
-E07.09_PAYMENT MONITOR INCOMING FEDWIRE 111425 516PM PG2.pdf
-E07.10_PAYMENT MONITOR OUTGOING FEDWIRE 111425 516PM PG1.pdf
-E07.11_PAYMENT MONITOR OUTGOING FEDWIRE 111425 516PM PG2.pdf
-E07.12_SWIFT INTERFACE MONITOR 111425 519PM.pdf
-E07.13_SWIFT INTERFACE MONITOR 111425 520PM 2ND SAMPLE.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 1 (1).msg.eml</t>
         </is>
       </c>
       <c r="C43" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\E07_Attachments_extracted</t>
+          <t>DMA04</t>
         </is>
       </c>
       <c r="D43" s="64" t="inlineStr">
         <is>
-          <t>attachments of E07</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
         </is>
       </c>
       <c r="E43" s="64" t="inlineStr">
         <is>
-          <t>Data Integrity &amp; Email Testing Evidence.zip</t>
-        </is>
-      </c>
-      <c r="F43" s="64" t="inlineStr">
-        <is>
-          <t>Report attachments (extracted)</t>
-        </is>
-      </c>
-      <c r="G43" s="64" t="inlineStr">
-        <is>
-          <t>11/15/2025 – Frank Puentes</t>
-        </is>
-      </c>
-      <c r="H43" s="64" t="inlineStr">
-        <is>
-          <t>Pre-DR 11/14/2025 source reports extracted from the email for direct review.</t>
-        </is>
-      </c>
-      <c r="I43" s="64" t="inlineStr">
-        <is>
-          <t>3301, 1903, 1936, 1937</t>
-        </is>
-      </c>
-      <c r="J43" s="64" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="K43" s="64" t="inlineStr">
-        <is>
-          <t>Attachments of E07</t>
-        </is>
-      </c>
+          <t>same email message saved as .eml</t>
+        </is>
+      </c>
+      <c r="F43" s="82" t="n"/>
+      <c r="G43" s="82" t="n"/>
+      <c r="H43" s="82" t="n"/>
+      <c r="I43" s="82" t="n"/>
+      <c r="J43" s="82" t="n"/>
+      <c r="K43" s="82" t="n"/>
       <c r="L43" s="82" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="64" t="inlineStr">
         <is>
-          <t>E08.01–E08.13</t>
+          <t>E15a</t>
         </is>
       </c>
       <c r="B44" s="64" t="inlineStr">
         <is>
-          <t>E08.01_FEDLINK INCOMING FEDWIRES 111425 -1115 1148AM.pdf
-E08.02_FEDLINK OUTGOINT TRANSFERS 114125 - 111525 1144AM.pdf
-E08.03_OFAC ACH 111425 - 11152025 1126AM.pdf
-E08.04_OFAC FED 111425 - 111525 1126AM.pdf
-E08.05_OFAC SWIFT 111425 - 111525 1128AM.pdf
-E08.06_OUTGOING FEDWIRE 111525 1025AM.xls
-E08.07_OUTGOING SWIFT 111525 1026AM.xls
-E08.08_PAYMENT MONITOR 111424 - 111525 PG 11156AM.pdf
-E08.09_PAYMENT MONITOR 111425 - 111525 PG 2 1158AM.pdf
-E08.10_PAYMENT MONITOR OUTGOING 111425 - 111525 PG 1 1156AM.pdf
-E08.11_PAYMENT MONITOR OUTGOING 111425 - 111525 PG 2 1156AM.pdf
-E08.12_SWIFT INTERFACE MONITOR INCOMING MT103 111425 - 111525 1152AM.pdf
-E08.13_SWIFT INTERFACE MONITOR INCOMING MT199 111425 -111525 1152AM.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15a_Data_Integrity_Attestation_Santander-BCiC.pdf</t>
         </is>
       </c>
       <c r="C44" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\E08_Attachments_extracted</t>
+          <t>DMA04</t>
         </is>
       </c>
       <c r="D44" s="64" t="inlineStr">
         <is>
-          <t>attachments of E08</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
         </is>
       </c>
       <c r="E44" s="64" t="inlineStr">
         <is>
-          <t>Data Integrity &amp; Email Testing Evidence.zip</t>
-        </is>
-      </c>
-      <c r="F44" s="64" t="inlineStr">
-        <is>
-          <t>Report attachments (extracted)</t>
-        </is>
-      </c>
-      <c r="G44" s="64" t="inlineStr">
-        <is>
-          <t>11/15/2025 – Frank Puentes</t>
-        </is>
-      </c>
-      <c r="H44" s="64" t="inlineStr">
-        <is>
-          <t>DR test-day 11/15/2025 comparison reports extracted from the email for direct review.</t>
-        </is>
-      </c>
-      <c r="I44" s="64" t="inlineStr">
-        <is>
-          <t>3301, 1903, 1936, 1937</t>
-        </is>
-      </c>
-      <c r="J44" s="64" t="inlineStr">
-        <is>
-          <t>F, M</t>
-        </is>
-      </c>
-      <c r="K44" s="64" t="inlineStr">
-        <is>
-          <t>Attachments of E08</t>
-        </is>
-      </c>
+          <t>byte-identical file (MD5 match) – retained inside DMA04 (attachment)</t>
+        </is>
+      </c>
+      <c r="F44" s="82" t="n"/>
+      <c r="G44" s="82" t="n"/>
+      <c r="H44" s="82" t="n"/>
+      <c r="I44" s="82" t="n"/>
+      <c r="J44" s="82" t="n"/>
+      <c r="K44" s="82" t="n"/>
       <c r="L44" s="82" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="82" t="n"/>
-      <c r="B45" s="82" t="n"/>
-      <c r="C45" s="82" t="n"/>
-      <c r="D45" s="82" t="n"/>
-      <c r="E45" s="82" t="n"/>
+      <c r="A45" s="64" t="inlineStr">
+        <is>
+          <t>E16</t>
+        </is>
+      </c>
+      <c r="B45" s="64" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 2 (1).msg.eml</t>
+        </is>
+      </c>
+      <c r="C45" s="64" t="inlineStr">
+        <is>
+          <t>DMA05</t>
+        </is>
+      </c>
+      <c r="D45" s="64" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
+        </is>
+      </c>
+      <c r="E45" s="64" t="inlineStr">
+        <is>
+          <t>same email message saved as .eml</t>
+        </is>
+      </c>
       <c r="F45" s="82" t="n"/>
       <c r="G45" s="82" t="n"/>
       <c r="H45" s="82" t="n"/>
@@ -15773,15 +14997,31 @@
       <c r="L45" s="82" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="60" t="inlineStr">
-        <is>
-          <t>Duplicate files removed from the repository (one copy of each retained)</t>
-        </is>
-      </c>
-      <c r="B46" s="82" t="n"/>
-      <c r="C46" s="82" t="n"/>
-      <c r="D46" s="82" t="n"/>
-      <c r="E46" s="82" t="n"/>
+      <c r="A46" s="64" t="inlineStr">
+        <is>
+          <t>E16a</t>
+        </is>
+      </c>
+      <c r="B46" s="64" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16a_Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+        </is>
+      </c>
+      <c r="C46" s="64" t="inlineStr">
+        <is>
+          <t>DMA05</t>
+        </is>
+      </c>
+      <c r="D46" s="64" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
+        </is>
+      </c>
+      <c r="E46" s="64" t="inlineStr">
+        <is>
+          <t>byte-identical file (MD5 match) – retained inside DMA05 (attachment)</t>
+        </is>
+      </c>
       <c r="F46" s="82" t="n"/>
       <c r="G46" s="82" t="n"/>
       <c r="H46" s="82" t="n"/>
@@ -15791,29 +15031,29 @@
       <c r="L46" s="82" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Removed ref</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Former location</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Retained ref</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Retained file location</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Reason</t>
+      <c r="A47" s="64" t="inlineStr">
+        <is>
+          <t>E17</t>
+        </is>
+      </c>
+      <c r="B47" s="64" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 3 (1).msg.eml</t>
+        </is>
+      </c>
+      <c r="C47" s="64" t="inlineStr">
+        <is>
+          <t>DMA03</t>
+        </is>
+      </c>
+      <c r="D47" s="64" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
+        </is>
+      </c>
+      <c r="E47" s="64" t="inlineStr">
+        <is>
+          <t>same email message saved as .eml</t>
         </is>
       </c>
       <c r="F47" s="82" t="n"/>
@@ -15827,12 +15067,12 @@
     <row r="48">
       <c r="A48" s="64" t="inlineStr">
         <is>
-          <t>MA02</t>
+          <t>E17a</t>
         </is>
       </c>
       <c r="B48" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17a_4069_001.pdf</t>
         </is>
       </c>
       <c r="C48" s="64" t="inlineStr">
@@ -15847,7 +15087,7 @@
       </c>
       <c r="E48" s="64" t="inlineStr">
         <is>
-          <t>same email message (subject, sent 08/18/2026 14:50, attachment 4069_001.pdf)</t>
+          <t>byte-identical file (MD5 match) – retained inside DMA03 (attachment)</t>
         </is>
       </c>
       <c r="F48" s="82" t="n"/>
@@ -15861,27 +15101,27 @@
     <row r="49">
       <c r="A49" s="64" t="inlineStr">
         <is>
-          <t>DMA05b</t>
+          <t>DMA01a</t>
         </is>
       </c>
       <c r="B49" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05b_Operations (Governance &amp; Static Data, Multi-Family Office) - All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA01a_Client Back Office - Data_Integrity_Attestation_Santander-BCiC (002).pdf</t>
         </is>
       </c>
       <c r="C49" s="64" t="inlineStr">
         <is>
-          <t>E16b</t>
+          <t>DMA01</t>
         </is>
       </c>
       <c r="D49" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
         </is>
       </c>
       <c r="E49" s="64" t="inlineStr">
         <is>
-          <t>byte-identical file (MD5 match)</t>
+          <t>extracted copy of the signed attestation embedded in DMA01 – cited as DMA01 (attachment)</t>
         </is>
       </c>
       <c r="F49" s="82" t="n"/>
@@ -15895,27 +15135,27 @@
     <row r="50">
       <c r="A50" s="64" t="inlineStr">
         <is>
-          <t>E11</t>
+          <t>DMA02a</t>
         </is>
       </c>
       <c r="B50" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E11_BSI.IT.6.C7.3 Manager Approval.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf</t>
         </is>
       </c>
       <c r="C50" s="64" t="inlineStr">
         <is>
-          <t>E10</t>
+          <t>DMA02</t>
         </is>
       </c>
       <c r="D50" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg</t>
         </is>
       </c>
       <c r="E50" s="64" t="inlineStr">
         <is>
-          <t>same email message (sent 03/09/2026 18:43) saved twice</t>
+          <t>extracted copy of the signed attestation embedded in DMA02 – cited as DMA02 (attachment)</t>
         </is>
       </c>
       <c r="F50" s="82" t="n"/>
@@ -15929,27 +15169,27 @@
     <row r="51">
       <c r="A51" s="64" t="inlineStr">
         <is>
-          <t>E12</t>
+          <t>DMA03a</t>
         </is>
       </c>
       <c r="B51" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E12_RE_ Testing enviroment Financial Analysis manager approval.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf</t>
         </is>
       </c>
       <c r="C51" s="64" t="inlineStr">
         <is>
-          <t>BLA06</t>
+          <t>DMA03</t>
         </is>
       </c>
       <c r="D51" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
         </is>
       </c>
       <c r="E51" s="64" t="inlineStr">
         <is>
-          <t>same email message (sent 01/26/2026 20:43)</t>
+          <t>extracted copy of the signed attestation embedded in DMA03 – cited as DMA03 (attachment)</t>
         </is>
       </c>
       <c r="F51" s="82" t="n"/>
@@ -15963,27 +15203,27 @@
     <row r="52">
       <c r="A52" s="64" t="inlineStr">
         <is>
-          <t>E14</t>
+          <t>DMA04a</t>
         </is>
       </c>
       <c r="B52" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) (1).msg.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
         </is>
       </c>
       <c r="C52" s="64" t="inlineStr">
         <is>
-          <t>DMA02</t>
+          <t>DMA04</t>
         </is>
       </c>
       <c r="D52" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
         </is>
       </c>
       <c r="E52" s="64" t="inlineStr">
         <is>
-          <t>same email message saved as .eml</t>
+          <t>extracted copy of the signed attestation embedded in DMA04 – cited as DMA04 (attachment)</t>
         </is>
       </c>
       <c r="F52" s="82" t="n"/>
@@ -15997,27 +15237,27 @@
     <row r="53">
       <c r="A53" s="64" t="inlineStr">
         <is>
-          <t>E14a</t>
+          <t>DMA05a</t>
         </is>
       </c>
       <c r="B53" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E14a_Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
         </is>
       </c>
       <c r="C53" s="64" t="inlineStr">
         <is>
-          <t>DMA02a</t>
+          <t>DMA05</t>
         </is>
       </c>
       <c r="D53" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA02a_BSA-AML-OFAC Compliance - Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
         </is>
       </c>
       <c r="E53" s="64" t="inlineStr">
         <is>
-          <t>byte-identical file (MD5 match)</t>
+          <t>extracted copy of the signed attestation embedded in DMA05 – cited as DMA05 (attachment)</t>
         </is>
       </c>
       <c r="F53" s="82" t="n"/>
@@ -16031,27 +15271,27 @@
     <row r="54">
       <c r="A54" s="64" t="inlineStr">
         <is>
-          <t>E15</t>
+          <t>DMA06a</t>
         </is>
       </c>
       <c r="B54" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 1 (1).msg.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA06a_Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Data_Integrity_Attestation_Santander-BCiC_signed.pdf</t>
         </is>
       </c>
       <c r="C54" s="64" t="inlineStr">
         <is>
-          <t>DMA04</t>
+          <t>DMA06</t>
         </is>
       </c>
       <c r="D54" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg</t>
         </is>
       </c>
       <c r="E54" s="64" t="inlineStr">
         <is>
-          <t>same email message saved as .eml</t>
+          <t>extracted copy of the signed attestation embedded in DMA06 – cited as DMA06 (attachment)</t>
         </is>
       </c>
       <c r="F54" s="82" t="n"/>
@@ -16065,27 +15305,27 @@
     <row r="55">
       <c r="A55" s="64" t="inlineStr">
         <is>
-          <t>E15a</t>
+          <t>DMA07a</t>
         </is>
       </c>
       <c r="B55" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E15a_Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA07a_Treasury &amp; Capital Planning - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
         </is>
       </c>
       <c r="C55" s="64" t="inlineStr">
         <is>
-          <t>DMA04a</t>
+          <t>DMA07</t>
         </is>
       </c>
       <c r="D55" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA04a_Investment Operations - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg</t>
         </is>
       </c>
       <c r="E55" s="64" t="inlineStr">
         <is>
-          <t>byte-identical file (MD5 match)</t>
+          <t>extracted copy of the signed attestation embedded in DMA07 – cited as DMA07 (attachment)</t>
         </is>
       </c>
       <c r="F55" s="82" t="n"/>
@@ -16099,27 +15339,27 @@
     <row r="56">
       <c r="A56" s="64" t="inlineStr">
         <is>
-          <t>E16</t>
+          <t>DMA09a</t>
         </is>
       </c>
       <c r="B56" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 2 (1).msg.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA09a_General Services (Marketing &amp; General Services) - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
         </is>
       </c>
       <c r="C56" s="64" t="inlineStr">
         <is>
-          <t>DMA05</t>
+          <t>DMA09</t>
         </is>
       </c>
       <c r="D56" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg</t>
         </is>
       </c>
       <c r="E56" s="64" t="inlineStr">
         <is>
-          <t>same email message saved as .eml</t>
+          <t>extracted copy of the signed attestation embedded in DMA09 – cited as DMA09 (attachment)</t>
         </is>
       </c>
       <c r="F56" s="82" t="n"/>
@@ -16133,27 +15373,27 @@
     <row r="57">
       <c r="A57" s="64" t="inlineStr">
         <is>
-          <t>E16a</t>
+          <t>E07.01–E07.13</t>
         </is>
       </c>
       <c r="B57" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16a_Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\E07_Attachments_extracted (13 files)</t>
         </is>
       </c>
       <c r="C57" s="64" t="inlineStr">
         <is>
-          <t>DMA05a</t>
+          <t>E07</t>
         </is>
       </c>
       <c r="D57" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA05a_Operations (Governance &amp; Static Data, Multi-Family Office) - Data_Integrity_Attestation_Santander-BCiC.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg</t>
         </is>
       </c>
       <c r="E57" s="64" t="inlineStr">
         <is>
-          <t>byte-identical file (MD5 match)</t>
+          <t>extracted copies of the report attachments embedded in E07 – cited as E07 (attachments)</t>
         </is>
       </c>
       <c r="F57" s="82" t="n"/>
@@ -16167,27 +15407,27 @@
     <row r="58">
       <c r="A58" s="64" t="inlineStr">
         <is>
-          <t>E17</t>
+          <t>E08.01–E08.13</t>
         </is>
       </c>
       <c r="B58" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17_RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 3 (1).msg.eml</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\E08_Attachments_extracted (13 files)</t>
         </is>
       </c>
       <c r="C58" s="64" t="inlineStr">
         <is>
-          <t>DMA03</t>
+          <t>E08</t>
         </is>
       </c>
       <c r="D58" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg</t>
         </is>
       </c>
       <c r="E58" s="64" t="inlineStr">
         <is>
-          <t>same email message saved as .eml</t>
+          <t>extracted copies of the report attachments embedded in E08 – cited as E08 (attachments)</t>
         </is>
       </c>
       <c r="F58" s="82" t="n"/>
@@ -16201,27 +15441,27 @@
     <row r="59">
       <c r="A59" s="64" t="inlineStr">
         <is>
-          <t>E17a</t>
+          <t>E06</t>
         </is>
       </c>
       <c r="B59" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E17a_4069_001.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E06_IT BIA Results Review and preparation for DR  1 (1).msg.eml</t>
         </is>
       </c>
       <c r="C59" s="64" t="inlineStr">
         <is>
-          <t>DMA03a</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="D59" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\Signed_Attestations_extracted\DMA03a_Payments &amp; Cash Management - 4069_001.pdf</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg</t>
         </is>
       </c>
       <c r="E59" s="64" t="inlineStr">
         <is>
-          <t>byte-identical file (MD5 match)</t>
+          <t>same meeting invite (same Teams meeting ID, attendees and body) re-sent 09/18/2025</t>
         </is>
       </c>
       <c r="F59" s="82" t="n"/>
@@ -17087,7 +16327,7 @@
       <c r="L120" s="82" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:K44"/>
+  <autoFilter ref="A2:K33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/BSI.IT.6.C7.3-Evidences/BSI.IT.6.C7.3_E00_Workpaper_DR_DIV_INTEGRATED_APPLICATION_Evidence.xlsx
+++ b/BSI.IT.6.C7.3-Evidences/BSI.IT.6.C7.3_E00_Workpaper_DR_DIV_INTEGRATED_APPLICATION_Evidence.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BSI.IT.6.C7.3 Evidence Index" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'BSI.IT.6.C7.3 Evidence Index'!$A$2:$K$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'BSI.IT.6.C7.3 Evidence Index'!$A$2:$K$34</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -1422,7 +1422,9 @@
       </c>
       <c r="B9" s="51" t="inlineStr">
         <is>
-          <t>MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png; E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
+          <t>MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
+MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg
+E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
         </is>
       </c>
       <c r="C9" s="51" t="n"/>
@@ -1440,7 +1442,8 @@
       </c>
       <c r="B10" s="51" t="inlineStr">
         <is>
-          <t>E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls; E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
+          <t>E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls
+E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
         </is>
       </c>
       <c r="C10" s="51" t="n"/>
@@ -1535,7 +1538,10 @@
       </c>
       <c r="F14" s="51" t="inlineStr">
         <is>
-          <t>MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png; E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx; E02</t>
+          <t>MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
+MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg
+E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx
+E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg</t>
         </is>
       </c>
       <c r="G14" s="53" t="inlineStr">
@@ -1575,7 +1581,9 @@
       </c>
       <c r="F15" s="51" t="inlineStr">
         <is>
-          <t>E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls; E16b; BLA01–BLA05 (BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email)</t>
+          <t>E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls
+E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx
+BLA01–BLA05 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email</t>
         </is>
       </c>
       <c r="G15" s="53" t="inlineStr">
@@ -1615,7 +1623,10 @@
       </c>
       <c r="F16" s="51" t="inlineStr">
         <is>
-          <t>BLA01–BLA06 (BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email); DMA01–DMA12 (BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals); E09; E03 approval fields</t>
+          <t>BLA01–BLA06 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email
+DMA01–DMA12 – BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals
+E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
+E03 – approval fields</t>
         </is>
       </c>
       <c r="G16" s="53" t="inlineStr">
@@ -1655,7 +1666,10 @@
       </c>
       <c r="F17" s="51" t="inlineStr">
         <is>
-          <t>E04, E02, MA01 (BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence / 01_Management_Attestation_In-Scope_Applications); E03 / E16b source data</t>
+          <t>E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
+E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg
+MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
+E03 / E16b – source data</t>
         </is>
       </c>
       <c r="G17" s="55" t="inlineStr">
@@ -2209,24 +2223,24 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="10" customWidth="1" style="71" min="1" max="1"/>
-    <col width="60" customWidth="1" style="71" min="2" max="2"/>
-    <col width="55" customWidth="1" style="71" min="3" max="3"/>
-    <col width="60" customWidth="1" style="71" min="4" max="4"/>
-    <col width="60" customWidth="1" style="71" min="5" max="5"/>
-    <col width="62" customWidth="1" style="71" min="6" max="7"/>
-    <col width="55" customWidth="1" style="71" min="7" max="7"/>
-    <col width="58" customWidth="1" style="71" min="8" max="8"/>
-    <col width="62" customWidth="1" style="71" min="9" max="9"/>
-    <col width="62" customWidth="1" style="71" min="10" max="10"/>
-    <col width="60" customWidth="1" style="71" min="11" max="11"/>
-    <col width="60" customWidth="1" style="71" min="12" max="12"/>
-    <col width="66" customWidth="1" style="71" min="13" max="13"/>
-    <col width="66" customWidth="1" style="71" min="14" max="14"/>
-    <col width="66" customWidth="1" style="71" min="15" max="15"/>
-    <col hidden="1" width="58" customWidth="1" style="71" min="16" max="16"/>
-    <col width="70" customWidth="1" style="71" min="17" max="17"/>
-    <col width="95" customWidth="1" style="71" min="18" max="18"/>
-    <col width="48" customWidth="1" style="57" min="19" max="19"/>
+    <col width="90" customWidth="1" style="71" min="2" max="2"/>
+    <col width="90" customWidth="1" style="71" min="3" max="3"/>
+    <col width="90" customWidth="1" style="71" min="4" max="4"/>
+    <col width="90" customWidth="1" style="71" min="5" max="5"/>
+    <col width="90" customWidth="1" style="71" min="6" max="7"/>
+    <col width="90" customWidth="1" style="71" min="7" max="7"/>
+    <col width="90" customWidth="1" style="71" min="8" max="8"/>
+    <col width="90" customWidth="1" style="71" min="9" max="9"/>
+    <col width="90" customWidth="1" style="71" min="10" max="10"/>
+    <col width="90" customWidth="1" style="71" min="11" max="11"/>
+    <col width="90" customWidth="1" style="71" min="12" max="12"/>
+    <col width="90" customWidth="1" style="71" min="13" max="13"/>
+    <col width="90" customWidth="1" style="71" min="14" max="14"/>
+    <col width="90" customWidth="1" style="71" min="15" max="15"/>
+    <col hidden="1" width="90" customWidth="1" style="71" min="16" max="16"/>
+    <col width="90" customWidth="1" style="71" min="17" max="17"/>
+    <col width="160" customWidth="1" style="71" min="18" max="18"/>
+    <col width="50" customWidth="1" style="57" min="19" max="19"/>
     <col width="8.6640625" customWidth="1" style="57" min="20" max="65"/>
   </cols>
   <sheetData>
@@ -2393,7 +2407,7 @@
       <c r="BM4" s="58" t="n"/>
       <c r="BN4" s="58" t="n"/>
     </row>
-    <row r="5" ht="332" customFormat="1" customHeight="1" s="47">
+    <row r="5" ht="404" customFormat="1" customHeight="1" s="47">
       <c r="A5" s="45" t="n">
         <v>1822</v>
       </c>
@@ -2521,9 +2535,10 @@
       </c>
       <c r="N5" s="69" t="inlineStr">
         <is>
-          <t>PASS – ACH Express is identified as in scope. The BCiC in-scope applications view (BSI In-Scope Applications-2026) shows App ID 1822 selected among the 10 applications flagged 2025 Backup/Restore DIV Scope = True; corroborated by the BCiC DR-scope export, the IT BIA/applications review and the management attestation.
+          <t>PASS – ACH Express is identified as in scope. The BCiC in-scope applications view BSI In-Scope Applications-2026 (MA01, Management_Attestation folder) shows App ID 1822 selected among the 10 applications flagged 2025 Backup/Restore DIV Scope = True, and the signed Management Attestation (MA02, §2) lists it among the 13 in-scope applications that store business data; corroborated by the BCiC DR-scope export (E01, E02), the IT BIA/applications review (E05) and the signed attestations (MA02, DMA02).
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png – BSI In-Scope Applications-2026 – App ID 1822 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
+• MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg – Management Attestation email 08/18/2026 – attached signed attestation (4069_001.pdf) §2 lists the 13 in-scope applications that store business data, including this application
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 3 – 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
@@ -2561,8 +2576,9 @@
       </c>
       <c r="R5" s="68" t="inlineStr">
         <is>
-          <t>[01 Management Attestation / In-Scope Applications]
+          <t xml:space="preserve">[01 Management Attestation / In-Scope Applications]
 MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
+MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg
 [02 Business Line Approval Results – Email]
 BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf
 [03 DIV Manager Attestation Email Approvals]
@@ -2575,7 +2591,8 @@
 E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
 E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
+E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx
+</t>
         </is>
       </c>
       <c r="S5" s="42" t="inlineStr">
@@ -2631,7 +2648,7 @@
       <c r="BM5" s="58" t="n"/>
       <c r="BN5" s="58" t="n"/>
     </row>
-    <row r="6" ht="332" customFormat="1" customHeight="1" s="39">
+    <row r="6" ht="404" customFormat="1" customHeight="1" s="39">
       <c r="A6" s="45" t="n">
         <v>1867</v>
       </c>
@@ -2763,9 +2780,10 @@
       </c>
       <c r="N6" s="69" t="inlineStr">
         <is>
-          <t>PASS – FedExport - BSI is identified as in scope. The BCiC in-scope applications view (BSI In-Scope Applications-2026) shows App ID 1867 selected among the 10 applications flagged 2025 Backup/Restore DIV Scope = True; corroborated by the BCiC DR-scope export, the IT BIA/applications review and the management attestation.
+          <t>PASS – FedExport - BSI is identified as in scope. The BCiC in-scope applications view BSI In-Scope Applications-2026 (MA01, Management_Attestation folder) shows App ID 1867 selected among the 10 applications flagged 2025 Backup/Restore DIV Scope = True, and the signed Management Attestation (MA02, §2) lists it among the 13 in-scope applications that store business data; corroborated by the BCiC DR-scope export (E01, E02), the IT BIA/applications review (E05) and the signed attestations (MA02, DMA02).
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png – BSI In-Scope Applications-2026 – App ID 1867 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
+• MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg – Management Attestation email 08/18/2026 – attached signed attestation (4069_001.pdf) §2 lists the 13 in-scope applications that store business data, including this application
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 19 – 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
@@ -2803,8 +2821,9 @@
       </c>
       <c r="R6" s="43" t="inlineStr">
         <is>
-          <t>[01 Management Attestation / In-Scope Applications]
+          <t xml:space="preserve">[01 Management Attestation / In-Scope Applications]
 MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
+MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg
 [02 Business Line Approval Results – Email]
 BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf
 [03 DIV Manager Attestation Email Approvals]
@@ -2817,7 +2836,8 @@
 E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
 E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
+E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx
+</t>
         </is>
       </c>
       <c r="S6" s="42" t="inlineStr">
@@ -2873,7 +2893,7 @@
       <c r="BM6" s="58" t="n"/>
       <c r="BN6" s="58" t="n"/>
     </row>
-    <row r="7" ht="332" customFormat="1" customHeight="1" s="39">
+    <row r="7" ht="404" customFormat="1" customHeight="1" s="39">
       <c r="A7" s="45" t="n">
         <v>1868</v>
       </c>
@@ -3005,9 +3025,10 @@
       </c>
       <c r="N7" s="69" t="inlineStr">
         <is>
-          <t>PASS – FedImport - BSI is identified as in scope. The BCiC in-scope applications view (BSI In-Scope Applications-2026) shows App ID 1868 selected among the 10 applications flagged 2025 Backup/Restore DIV Scope = True; corroborated by the BCiC DR-scope export, the IT BIA/applications review and the management attestation.
+          <t>PASS – FedImport - BSI is identified as in scope. The BCiC in-scope applications view BSI In-Scope Applications-2026 (MA01, Management_Attestation folder) shows App ID 1868 selected among the 10 applications flagged 2025 Backup/Restore DIV Scope = True, and the signed Management Attestation (MA02, §2) lists it among the 13 in-scope applications that store business data; corroborated by the BCiC DR-scope export (E01, E02), the IT BIA/applications review (E05) and the signed attestations (MA02, DMA02).
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png – BSI In-Scope Applications-2026 – App ID 1868 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
+• MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg – Management Attestation email 08/18/2026 – attached signed attestation (4069_001.pdf) §2 lists the 13 in-scope applications that store business data, including this application
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 20 – 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
@@ -3044,8 +3065,9 @@
       </c>
       <c r="R7" s="40" t="inlineStr">
         <is>
-          <t>[01 Management Attestation / In-Scope Applications]
+          <t xml:space="preserve">[01 Management Attestation / In-Scope Applications]
 MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
+MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg
 [02 Business Line Approval Results – Email]
 BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf
 [03 DIV Manager Attestation Email Approvals]
@@ -3058,7 +3080,8 @@
 E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
 E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
+E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx
+</t>
         </is>
       </c>
       <c r="S7" s="42" t="inlineStr">
@@ -3280,9 +3303,10 @@
       </c>
       <c r="N8" s="69" t="inlineStr">
         <is>
-          <t>PASS – Imaging101 is identified as in scope. The BCiC in-scope applications view (BSI In-Scope Applications-2026) shows App ID 3299 selected among the 10 applications flagged 2025 Backup/Restore DIV Scope = True; corroborated by the BCiC DR-scope export, the IT BIA/applications review and the management attestation.
+          <t>PASS – Imaging101 is identified as in scope. The BCiC in-scope applications view BSI In-Scope Applications-2026 (MA01, Management_Attestation folder) shows App ID 3299 selected among the 10 applications flagged 2025 Backup/Restore DIV Scope = True, and the signed Management Attestation (MA02, §2) lists it among the 13 in-scope applications that store business data; corroborated by the BCiC DR-scope export (E01, E02), the IT BIA/applications review (E05) and the signed attestations (MA02, DMA02).
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png – BSI In-Scope Applications-2026 – App ID 3299 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
+• MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg – Management Attestation email 08/18/2026 – attached signed attestation (4069_001.pdf) §2 lists the 13 in-scope applications that store business data, including this application
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 24 – 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
@@ -3326,8 +3350,9 @@
       </c>
       <c r="R8" s="43" t="inlineStr">
         <is>
-          <t>[01 Management Attestation / In-Scope Applications]
+          <t xml:space="preserve">[01 Management Attestation / In-Scope Applications]
 MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
+MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg
 [02 Business Line Approval Results – Email]
 BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf
 BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf
@@ -3343,7 +3368,8 @@
 E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
 E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
+E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx
+</t>
         </is>
       </c>
       <c r="S8" s="42" t="inlineStr">
@@ -3399,7 +3425,7 @@
       <c r="BM8" s="58" t="n"/>
       <c r="BN8" s="58" t="n"/>
     </row>
-    <row r="9" ht="296" customFormat="1" customHeight="1" s="39">
+    <row r="9" ht="356" customFormat="1" customHeight="1" s="39">
       <c r="A9" s="45" t="n">
         <v>4052</v>
       </c>
@@ -3522,9 +3548,10 @@
       </c>
       <c r="N9" s="69" t="inlineStr">
         <is>
-          <t>PASS – Interface Monitor is identified as in scope. The BCiC in-scope applications view (BSI In-Scope Applications-2026) shows App ID 4052 selected among the 10 applications flagged 2025 Backup/Restore DIV Scope = True; corroborated by the BCiC DR-scope export, the IT BIA/applications review and the management attestation.
+          <t>PASS – Interface Monitor is identified as in scope. The BCiC in-scope applications view BSI In-Scope Applications-2026 (MA01, Management_Attestation folder) shows App ID 4052 selected among the 10 applications flagged 2025 Backup/Restore DIV Scope = True, and the signed Management Attestation (MA02, §2) lists it among the 13 in-scope applications that store business data; corroborated by the BCiC DR-scope export (E01, E02), the IT BIA/applications review (E05) and the signed attestations (MA02, DMA02).
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png – BSI In-Scope Applications-2026 – App ID 4052 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
+• MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg – Management Attestation email 08/18/2026 – attached signed attestation (4069_001.pdf) §2 lists the 13 in-scope applications that store business data, including this application
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 25 – 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
@@ -3561,8 +3588,9 @@
       </c>
       <c r="R9" s="40" t="inlineStr">
         <is>
-          <t>[01 Management Attestation / In-Scope Applications]
+          <t xml:space="preserve">[01 Management Attestation / In-Scope Applications]
 MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
+MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg
 [02 Business Line Approval Results – Email]
 BLA04 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx
 [03 DIV Manager Attestation Email Approvals]
@@ -3574,7 +3602,8 @@
 E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls
 E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
-E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
+E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx
+</t>
         </is>
       </c>
       <c r="S9" s="42" t="inlineStr">
@@ -3630,7 +3659,7 @@
       <c r="BM9" s="58" t="n"/>
       <c r="BN9" s="58" t="n"/>
     </row>
-    <row r="10" ht="332" customFormat="1" customHeight="1" s="39">
+    <row r="10" ht="380" customFormat="1" customHeight="1" s="39">
       <c r="A10" s="45" t="n">
         <v>3301</v>
       </c>
@@ -3757,9 +3786,10 @@
       </c>
       <c r="N10" s="69" t="inlineStr">
         <is>
-          <t>PASS – MQ Payment Monitor is identified as in scope. The BCiC in-scope applications view (BSI In-Scope Applications-2026) shows App ID 3301 selected among the 10 applications flagged 2025 Backup/Restore DIV Scope = True; corroborated by the BCiC DR-scope export, the IT BIA/applications review and the management attestation.
+          <t>PASS – MQ Payment Monitor is identified as in scope. The BCiC in-scope applications view BSI In-Scope Applications-2026 (MA01, Management_Attestation folder) shows App ID 3301 selected among the 10 applications flagged 2025 Backup/Restore DIV Scope = True, and the signed Management Attestation (MA02, §2) lists it among the 13 in-scope applications that store business data; corroborated by the BCiC DR-scope export (E01, E02), the IT BIA/applications review (E05) and the signed attestations (MA02, DMA02).
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png – BSI In-Scope Applications-2026 – App ID 3301 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
+• MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg – Management Attestation email 08/18/2026 – attached signed attestation (4069_001.pdf) §2 lists the 13 in-scope applications that store business data, including this application
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 31 – 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
@@ -3795,8 +3825,9 @@
       </c>
       <c r="R10" s="43" t="inlineStr">
         <is>
-          <t>[01 Management Attestation / In-Scope Applications]
+          <t xml:space="preserve">[01 Management Attestation / In-Scope Applications]
 MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
+MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg
 [02 Business Line Approval Results – Email]
 BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf
 [03 DIV Manager Attestation Email Approvals]
@@ -3810,7 +3841,8 @@
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
 E07 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg
 E08 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg
-E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
+E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx
+</t>
         </is>
       </c>
       <c r="S10" s="42" t="inlineStr">
@@ -3866,7 +3898,7 @@
       <c r="BM10" s="58" t="n"/>
       <c r="BN10" s="58" t="n"/>
     </row>
-    <row r="11" ht="380" customFormat="1" customHeight="1" s="39">
+    <row r="11" ht="409" customFormat="1" customHeight="1" s="39">
       <c r="A11" s="45" t="n">
         <v>1903</v>
       </c>
@@ -4020,9 +4052,10 @@
       </c>
       <c r="N11" s="69" t="inlineStr">
         <is>
-          <t>PASS – OFAC - BSI is identified as in scope. The BCiC in-scope applications view (BSI In-Scope Applications-2026) shows App ID 1903 selected among the 10 applications flagged 2025 Backup/Restore DIV Scope = True; corroborated by the BCiC DR-scope export, the IT BIA/applications review and the management attestation.
+          <t>PASS – OFAC - BSI is identified as in scope. The BCiC in-scope applications view BSI In-Scope Applications-2026 (MA01, Management_Attestation folder) shows App ID 1903 selected among the 10 applications flagged 2025 Backup/Restore DIV Scope = True, and the signed Management Attestation (MA02, §2) lists it among the 13 in-scope applications that store business data; corroborated by the BCiC DR-scope export (E01, E02), the IT BIA/applications review (E05) and the signed attestations (MA02, DMA02).
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png – BSI In-Scope Applications-2026 – App ID 1903 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
+• MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg – Management Attestation email 08/18/2026 – attached signed attestation (4069_001.pdf) §2 lists the 13 in-scope applications that store business data, including this application
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 34 – 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
@@ -4063,8 +4096,9 @@
       </c>
       <c r="R11" s="40" t="inlineStr">
         <is>
-          <t>[01 Management Attestation / In-Scope Applications]
+          <t xml:space="preserve">[01 Management Attestation / In-Scope Applications]
 MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
+MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg
 [02 Business Line Approval Results – Email]
 BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf
 BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf
@@ -4080,7 +4114,8 @@
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
 E07 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg
 E08 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg
-E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
+E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx
+</t>
         </is>
       </c>
       <c r="S11" s="42" t="inlineStr">
@@ -4136,7 +4171,7 @@
       <c r="BM11" s="58" t="n"/>
       <c r="BN11" s="58" t="n"/>
     </row>
-    <row r="12" ht="308" customFormat="1" customHeight="1" s="39">
+    <row r="12" ht="356" customFormat="1" customHeight="1" s="39">
       <c r="A12" s="45" t="n">
         <v>1917</v>
       </c>
@@ -4260,9 +4295,10 @@
       </c>
       <c r="N12" s="69" t="inlineStr">
         <is>
-          <t>PASS – ReconXpert is identified as in scope. The BCiC in-scope applications view (BSI In-Scope Applications-2026) shows App ID 1917 selected among the 10 applications flagged 2025 Backup/Restore DIV Scope = True; corroborated by the BCiC DR-scope export, the IT BIA/applications review and the management attestation.
+          <t>PASS – ReconXpert is identified as in scope. The BCiC in-scope applications view BSI In-Scope Applications-2026 (MA01, Management_Attestation folder) shows App ID 1917 selected among the 10 applications flagged 2025 Backup/Restore DIV Scope = True, and the signed Management Attestation (MA02, §2) lists it among the 13 in-scope applications that store business data; corroborated by the BCiC DR-scope export (E01, E02), the IT BIA/applications review (E05) and the signed attestations (MA02, DMA02).
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png – BSI In-Scope Applications-2026 – App ID 1917 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
+• MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg – Management Attestation email 08/18/2026 – attached signed attestation (4069_001.pdf) §2 lists the 13 in-scope applications that store business data, including this application
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 36 – 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
@@ -4298,8 +4334,9 @@
       </c>
       <c r="R12" s="43" t="inlineStr">
         <is>
-          <t>[01 Management Attestation / In-Scope Applications]
+          <t xml:space="preserve">[01 Management Attestation / In-Scope Applications]
 MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
+MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg
 [02 Business Line Approval Results – Email]
 BLA05 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf
 BLA06 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg
@@ -4312,7 +4349,8 @@
 E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
 E10 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg
-E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
+E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx
+</t>
         </is>
       </c>
       <c r="S12" s="42" t="inlineStr">
@@ -4368,7 +4406,7 @@
       <c r="BM12" s="58" t="n"/>
       <c r="BN12" s="58" t="n"/>
     </row>
-    <row r="13" ht="356" customFormat="1" customHeight="1" s="39">
+    <row r="13" ht="404" customFormat="1" customHeight="1" s="39">
       <c r="A13" s="45" t="n">
         <v>1936</v>
       </c>
@@ -4512,9 +4550,10 @@
       </c>
       <c r="N13" s="69" t="inlineStr">
         <is>
-          <t>PASS – Swift Interface - BSI is identified as in scope. The BCiC in-scope applications view (BSI In-Scope Applications-2026) shows App ID 1936 selected among the 10 applications flagged 2025 Backup/Restore DIV Scope = True; corroborated by the BCiC DR-scope export, the IT BIA/applications review and the management attestation.
+          <t>PASS – Swift Interface - BSI is identified as in scope. The BCiC in-scope applications view BSI In-Scope Applications-2026 (MA01, Management_Attestation folder) shows App ID 1936 selected among the 10 applications flagged 2025 Backup/Restore DIV Scope = True, and the signed Management Attestation (MA02, §2) lists it among the 13 in-scope applications that store business data; corroborated by the BCiC DR-scope export (E01, E02), the IT BIA/applications review (E05) and the signed attestations (MA02, DMA02).
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png – BSI In-Scope Applications-2026 – App ID 1936 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
+• MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg – Management Attestation email 08/18/2026 – attached signed attestation (4069_001.pdf) §2 lists the 13 in-scope applications that store business data, including this application
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 42 – 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
@@ -4554,8 +4593,9 @@
       </c>
       <c r="R13" s="40" t="inlineStr">
         <is>
-          <t>[01 Management Attestation / In-Scope Applications]
+          <t xml:space="preserve">[01 Management Attestation / In-Scope Applications]
 MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
+MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg
 [02 Business Line Approval Results – Email]
 BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf
 BLA04 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx
@@ -4570,7 +4610,8 @@
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
 E07 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg
 E08 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg
-E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
+E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx
+</t>
         </is>
       </c>
       <c r="S13" s="42" t="inlineStr">
@@ -4879,9 +4920,10 @@
       </c>
       <c r="N14" s="69" t="inlineStr">
         <is>
-          <t>PASS – T24 is identified as in scope. The BCiC in-scope applications view (BSI In-Scope Applications-2026) shows App ID 1937 selected among the 10 applications flagged 2025 Backup/Restore DIV Scope = True; corroborated by the BCiC DR-scope export, the IT BIA/applications review and the management attestation.
+          <t>PASS – T24 is identified as in scope. The BCiC in-scope applications view BSI In-Scope Applications-2026 (MA01, Management_Attestation folder) shows App ID 1937 selected among the 10 applications flagged 2025 Backup/Restore DIV Scope = True, and the signed Management Attestation (MA02, §2) lists it among the 13 in-scope applications that store business data; corroborated by the BCiC DR-scope export (E01, E02), the IT BIA/applications review (E05) and the signed attestations (MA02, DMA02).
 Evidence location (BSI.IT.6.C7.3-Evidences):
 • MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png – BSI In-Scope Applications-2026 – App ID 1937 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
+• MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg – Management Attestation email 08/18/2026 – attached signed attestation (4069_001.pdf) §2 lists the 13 in-scope applications that store business data, including this application
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 43 – 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
@@ -4937,8 +4979,9 @@
       </c>
       <c r="R14" s="43" t="inlineStr">
         <is>
-          <t>[01 Management Attestation / In-Scope Applications]
+          <t xml:space="preserve">[01 Management Attestation / In-Scope Applications]
 MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
+MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg
 [02 Business Line Approval Results – Email]
 BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf
 BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf
@@ -4969,7 +5012,8 @@
 E08 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg
 E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
 E10 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg
-E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
+E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx
+</t>
         </is>
       </c>
       <c r="S14" s="42" t="inlineStr">
@@ -5469,7 +5513,7 @@
       <c r="R29" s="82" t="n"/>
       <c r="S29" s="82" t="n"/>
     </row>
-    <row r="30" ht="54" customHeight="1" s="71">
+    <row r="30" ht="42" customHeight="1" s="71">
       <c r="A30" s="86" t="inlineStr">
         <is>
           <t>BLA01</t>
@@ -5514,7 +5558,7 @@
       <c r="R30" s="82" t="n"/>
       <c r="S30" s="82" t="n"/>
     </row>
-    <row r="31" ht="54" customHeight="1" s="71">
+    <row r="31" ht="42" customHeight="1" s="71">
       <c r="A31" s="86" t="inlineStr">
         <is>
           <t>BLA02</t>
@@ -5559,7 +5603,7 @@
       <c r="R31" s="82" t="n"/>
       <c r="S31" s="82" t="n"/>
     </row>
-    <row r="32" ht="54" customHeight="1" s="71">
+    <row r="32" ht="42" customHeight="1" s="71">
       <c r="A32" s="86" t="inlineStr">
         <is>
           <t>BLA03</t>
@@ -5604,7 +5648,7 @@
       <c r="R32" s="82" t="n"/>
       <c r="S32" s="82" t="n"/>
     </row>
-    <row r="33" ht="54" customHeight="1" s="71">
+    <row r="33" ht="42" customHeight="1" s="71">
       <c r="A33" s="86" t="inlineStr">
         <is>
           <t>BLA04</t>
@@ -5649,7 +5693,7 @@
       <c r="R33" s="82" t="n"/>
       <c r="S33" s="82" t="n"/>
     </row>
-    <row r="34" ht="42" customHeight="1" s="71">
+    <row r="34" ht="30" customHeight="1" s="71">
       <c r="A34" s="86" t="inlineStr">
         <is>
           <t>BLA05</t>
@@ -5694,7 +5738,7 @@
       <c r="R34" s="82" t="n"/>
       <c r="S34" s="82" t="n"/>
     </row>
-    <row r="35" ht="42" customHeight="1" s="71">
+    <row r="35" ht="30" customHeight="1" s="71">
       <c r="A35" s="86" t="inlineStr">
         <is>
           <t>BLA06</t>
@@ -5819,7 +5863,7 @@
       <c r="R38" s="82" t="n"/>
       <c r="S38" s="82" t="n"/>
     </row>
-    <row r="39" ht="42" customHeight="1" s="71">
+    <row r="39" ht="30" customHeight="1" s="71">
       <c r="A39" s="86" t="inlineStr">
         <is>
           <t>DMA01</t>
@@ -5864,7 +5908,7 @@
       <c r="R39" s="82" t="n"/>
       <c r="S39" s="82" t="n"/>
     </row>
-    <row r="40" ht="90" customHeight="1" s="71">
+    <row r="40" ht="66" customHeight="1" s="71">
       <c r="A40" s="86" t="inlineStr">
         <is>
           <t>DMA02</t>
@@ -5909,7 +5953,7 @@
       <c r="R40" s="82" t="n"/>
       <c r="S40" s="82" t="n"/>
     </row>
-    <row r="41" ht="42" customHeight="1" s="71">
+    <row r="41" ht="30" customHeight="1" s="71">
       <c r="A41" s="86" t="inlineStr">
         <is>
           <t>DMA03</t>
@@ -5954,7 +5998,7 @@
       <c r="R41" s="82" t="n"/>
       <c r="S41" s="82" t="n"/>
     </row>
-    <row r="42" ht="42" customHeight="1" s="71">
+    <row r="42" ht="30" customHeight="1" s="71">
       <c r="A42" s="86" t="inlineStr">
         <is>
           <t>DMA04</t>
@@ -5999,7 +6043,7 @@
       <c r="R42" s="82" t="n"/>
       <c r="S42" s="82" t="n"/>
     </row>
-    <row r="43" ht="54" customHeight="1" s="71">
+    <row r="43" ht="42" customHeight="1" s="71">
       <c r="A43" s="86" t="inlineStr">
         <is>
           <t>DMA05</t>
@@ -6044,7 +6088,7 @@
       <c r="R43" s="82" t="n"/>
       <c r="S43" s="82" t="n"/>
     </row>
-    <row r="44" ht="54" customHeight="1" s="71">
+    <row r="44" ht="42" customHeight="1" s="71">
       <c r="A44" s="86" t="inlineStr">
         <is>
           <t>DMA06</t>
@@ -6089,7 +6133,7 @@
       <c r="R44" s="82" t="n"/>
       <c r="S44" s="82" t="n"/>
     </row>
-    <row r="45" ht="42" customHeight="1" s="71">
+    <row r="45" ht="30" customHeight="1" s="71">
       <c r="A45" s="86" t="inlineStr">
         <is>
           <t>DMA07</t>
@@ -6134,7 +6178,7 @@
       <c r="R45" s="82" t="n"/>
       <c r="S45" s="82" t="n"/>
     </row>
-    <row r="46" ht="42" customHeight="1" s="71">
+    <row r="46" ht="30" customHeight="1" s="71">
       <c r="A46" s="86" t="inlineStr">
         <is>
           <t>DMA08</t>
@@ -6179,7 +6223,7 @@
       <c r="R46" s="82" t="n"/>
       <c r="S46" s="82" t="n"/>
     </row>
-    <row r="47" ht="42" customHeight="1" s="71">
+    <row r="47" ht="30" customHeight="1" s="71">
       <c r="A47" s="86" t="inlineStr">
         <is>
           <t>DMA09</t>
@@ -6224,7 +6268,7 @@
       <c r="R47" s="82" t="n"/>
       <c r="S47" s="82" t="n"/>
     </row>
-    <row r="48" ht="42" customHeight="1" s="71">
+    <row r="48" ht="30" customHeight="1" s="71">
       <c r="A48" s="86" t="inlineStr">
         <is>
           <t>DMA10</t>
@@ -6269,7 +6313,7 @@
       <c r="R48" s="82" t="n"/>
       <c r="S48" s="82" t="n"/>
     </row>
-    <row r="49" ht="42" customHeight="1" s="71">
+    <row r="49" ht="30" customHeight="1" s="71">
       <c r="A49" s="86" t="inlineStr">
         <is>
           <t>DMA11</t>
@@ -6314,7 +6358,7 @@
       <c r="R49" s="82" t="n"/>
       <c r="S49" s="82" t="n"/>
     </row>
-    <row r="50" ht="42" customHeight="1" s="71">
+    <row r="50" ht="30" customHeight="1" s="71">
       <c r="A50" s="86" t="inlineStr">
         <is>
           <t>DMA12</t>
@@ -6359,7 +6403,7 @@
       <c r="R50" s="82" t="n"/>
       <c r="S50" s="82" t="n"/>
     </row>
-    <row r="51" ht="42" customHeight="1" s="71">
+    <row r="51" ht="30" customHeight="1" s="71">
       <c r="A51" s="86" t="inlineStr">
         <is>
           <t>DMA13</t>
@@ -6484,7 +6528,7 @@
       <c r="R54" s="82" t="n"/>
       <c r="S54" s="82" t="n"/>
     </row>
-    <row r="55" ht="66" customHeight="1" s="71">
+    <row r="55" ht="42" customHeight="1" s="71">
       <c r="A55" s="86" t="inlineStr">
         <is>
           <t>MA01</t>
@@ -6529,35 +6573,35 @@
       <c r="R55" s="82" t="n"/>
       <c r="S55" s="82" t="n"/>
     </row>
-    <row r="56" ht="30" customHeight="1" s="71">
+    <row r="56" ht="78" customHeight="1" s="71">
       <c r="A56" s="86" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>MA02</t>
         </is>
       </c>
       <c r="B56" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
+          <t>BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg</t>
         </is>
       </c>
       <c r="C56" s="86" t="inlineStr">
         <is>
-          <t>BCiC – Applications In Scope for DR Test BSI</t>
+          <t>08/18/2026 – Frank Puentes</t>
         </is>
       </c>
       <c r="D56" s="86" t="inlineStr">
         <is>
-          <t>BCiC export</t>
+          <t>Email + signed management attestation</t>
         </is>
       </c>
       <c r="E56" s="86" t="inlineStr">
         <is>
-          <t>BCiC export of the BSI DR-scope population (43 applications) with Exercise Date and 2025 DR / Backup-Restore / DIV scope flags.</t>
+          <t>Management Attestation email: Frank Puentes (Executive Director, Payments &amp; Cash Management) returns the signed attestation (attachment 4069_001.pdf) to Cesar Vidal. The quoted Cesar Vidal request (08/17/2026) confirms the DR exercises of 11/15/2025 and 02/21/2026 and attaches the BCiC DIV export; the signed attestation §2 lists the 13 in-scope BSI applications that store business data, including all 10 tested applications. Filed in the Management_Attestation folder as received; the same message is also filed as DMA03 for the business line approval attribute.</t>
         </is>
       </c>
       <c r="F56" s="86" t="inlineStr">
         <is>
-          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: B, C, D, K, L, N</t>
+          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: N</t>
         </is>
       </c>
       <c r="G56" s="82" t="n"/>
@@ -6577,32 +6621,32 @@
     <row r="57" ht="30" customHeight="1" s="71">
       <c r="A57" s="86" t="inlineStr">
         <is>
-          <t>E02</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="B57" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
         </is>
       </c>
       <c r="C57" s="86" t="inlineStr">
         <is>
-          <t>09/10/2026 – Cesar Vidal</t>
+          <t>BCiC – Applications In Scope for DR Test BSI</t>
         </is>
       </c>
       <c r="D57" s="86" t="inlineStr">
         <is>
-          <t>BCiC screenshot</t>
+          <t>BCiC export</t>
         </is>
       </c>
       <c r="E57" s="86" t="inlineStr">
         <is>
-          <t>BCiC Applications screen with view 'Applications In Scope for DR Test BSI' selected (1–20 of 43 items).</t>
+          <t>BCiC export of the BSI DR-scope population (43 applications) with Exercise Date and 2025 DR / Backup-Restore / DIV scope flags.</t>
         </is>
       </c>
       <c r="F57" s="86" t="inlineStr">
         <is>
-          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: D, K, N</t>
+          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: B, C, D, K, L, N</t>
         </is>
       </c>
       <c r="G57" s="82" t="n"/>
@@ -6619,35 +6663,35 @@
       <c r="R57" s="82" t="n"/>
       <c r="S57" s="82" t="n"/>
     </row>
-    <row r="58" ht="42" customHeight="1" s="71">
+    <row r="58" ht="30" customHeight="1" s="71">
       <c r="A58" s="86" t="inlineStr">
         <is>
-          <t>E03</t>
+          <t>E02</t>
         </is>
       </c>
       <c r="B58" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg</t>
         </is>
       </c>
       <c r="C58" s="86" t="inlineStr">
         <is>
-          <t>BCiC – Data Integrity Validation Testing (62 records)</t>
+          <t>09/10/2026 – Cesar Vidal</t>
         </is>
       </c>
       <c r="D58" s="86" t="inlineStr">
         <is>
-          <t>BCiC export</t>
+          <t>BCiC screenshot</t>
         </is>
       </c>
       <c r="E58" s="86" t="inlineStr">
         <is>
-          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Y/N Format/Headers/Content, Attestation Date / Provided By. Row numbers quoted are Excel rows.</t>
+          <t>BCiC Applications screen with view 'Applications In Scope for DR Test BSI' selected (1–20 of 43 items).</t>
         </is>
       </c>
       <c r="F58" s="86" t="inlineStr">
         <is>
-          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: B, C, D, E, F, G, H, I, K, L, M, O, P</t>
+          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: D, K, N</t>
         </is>
       </c>
       <c r="G58" s="82" t="n"/>
@@ -6664,35 +6708,35 @@
       <c r="R58" s="82" t="n"/>
       <c r="S58" s="82" t="n"/>
     </row>
-    <row r="59" ht="42" customHeight="1" s="71">
+    <row r="59" ht="30" customHeight="1" s="71">
       <c r="A59" s="86" t="inlineStr">
         <is>
-          <t>E04</t>
+          <t>E03</t>
         </is>
       </c>
       <c r="B59" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
         </is>
       </c>
       <c r="C59" s="86" t="inlineStr">
         <is>
-          <t>09/10/2026 – Cesar Vidal</t>
+          <t>BCiC – Data Integrity Validation Testing (62 records)</t>
         </is>
       </c>
       <c r="D59" s="86" t="inlineStr">
         <is>
-          <t>BCiC screenshot</t>
+          <t>BCiC export</t>
         </is>
       </c>
       <c r="E59" s="86" t="inlineStr">
         <is>
-          <t>BCiC 'Data Integrity Validation Testing' screen (1–20 of 66 items) showing tester, validation date, manager, approval date, Y/N results and attestation fields.</t>
+          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Y/N Format/Headers/Content, Attestation Date / Provided By. Row numbers quoted are Excel rows.</t>
         </is>
       </c>
       <c r="F59" s="86" t="inlineStr">
         <is>
-          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: D, E, F, G, H, K, P</t>
+          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: B, C, D, E, F, G, H, I, K, L, M, O, P</t>
         </is>
       </c>
       <c r="G59" s="82" t="n"/>
@@ -6709,35 +6753,35 @@
       <c r="R59" s="82" t="n"/>
       <c r="S59" s="82" t="n"/>
     </row>
-    <row r="60" ht="42" customHeight="1" s="71">
+    <row r="60" ht="30" customHeight="1" s="71">
       <c r="A60" s="86" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>E04</t>
         </is>
       </c>
       <c r="B60" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg</t>
         </is>
       </c>
       <c r="C60" s="86" t="inlineStr">
         <is>
-          <t>09/15/2025 – Elizabeth Noda</t>
+          <t>09/10/2026 – Cesar Vidal</t>
         </is>
       </c>
       <c r="D60" s="86" t="inlineStr">
         <is>
-          <t>Meeting invite</t>
+          <t>BCiC screenshot</t>
         </is>
       </c>
       <c r="E60" s="86" t="inlineStr">
         <is>
-          <t>IT DR meeting invite to review the 2025 BIA results and applications list ahead of the DR exercise (same invite re-sent 09/18/2025 – duplicate E06 removed).</t>
+          <t>BCiC 'Data Integrity Validation Testing' screen (1–20 of 66 items) showing tester, validation date, manager, approval date, Y/N results and attestation fields.</t>
         </is>
       </c>
       <c r="F60" s="86" t="inlineStr">
         <is>
-          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: M, N</t>
+          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: D, E, F, G, H, K, P</t>
         </is>
       </c>
       <c r="G60" s="82" t="n"/>
@@ -6754,35 +6798,35 @@
       <c r="R60" s="82" t="n"/>
       <c r="S60" s="82" t="n"/>
     </row>
-    <row r="61" ht="126" customHeight="1" s="71">
+    <row r="61" ht="30" customHeight="1" s="71">
       <c r="A61" s="86" t="inlineStr">
         <is>
-          <t>E07</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="B61" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg</t>
         </is>
       </c>
       <c r="C61" s="86" t="inlineStr">
         <is>
-          <t>11/15/2025 – Frank Puentes</t>
+          <t>09/15/2025 – Elizabeth Noda</t>
         </is>
       </c>
       <c r="D61" s="86" t="inlineStr">
         <is>
-          <t>Email + report attachments</t>
+          <t>Meeting invite</t>
         </is>
       </c>
       <c r="E61" s="86" t="inlineStr">
         <is>
-          <t>Pre-DR (11/14/2025) source reports: Fedlink, OFAC ACH/FED/SWIFT, Payment Monitor, SWIFT Interface Monitor, outgoing Fedwire/SWIFT. Embedded attachments: FEDLINK INCOMING FEDWIRES 111425 0523PM.pdf; FEDLINK OUTGOING FEDWIRES 111425 0523PM.pdf; OFAC ACH 111425 0512PM.pdf; OFAC FED 111425 0511PM.pdf; OFAC SWIFT 111425 0511PM.pdf; OUTGOING FEDWIRE 111425 506PM.xls; OUTGOING SWIFT 111425 509PM.xls; PAYMENT MONITOR INCOMING FEDWIRE 111425 516PM PG1.pdf; PAYMENT MONITOR INCOMING FEDWIRE 111425 516PM PG2.pdf; PAYMENT MONITOR OUTGOING FEDWIRE 111425 516PM PG1.pdf; PAYMENT MONITOR OUTGOING FEDWIRE 111425 516PM PG2.pdf; SWIFT INTERFACE MONITOR 111425 519PM.pdf; SWIFT INTERFACE MONITOR 111425 520PM 2ND SAMPLE.pdf.</t>
+          <t>IT DR meeting invite to review the 2025 BIA results and applications list ahead of the DR exercise (same invite re-sent 09/18/2025 – duplicate E06 removed).</t>
         </is>
       </c>
       <c r="F61" s="86" t="inlineStr">
         <is>
-          <t>Samples: 3301, 1903, 1936, 1937; columns: F</t>
+          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: M, N</t>
         </is>
       </c>
       <c r="G61" s="82" t="n"/>
@@ -6799,15 +6843,15 @@
       <c r="R61" s="82" t="n"/>
       <c r="S61" s="82" t="n"/>
     </row>
-    <row r="62" ht="126" customHeight="1" s="71">
+    <row r="62" ht="90" customHeight="1" s="71">
       <c r="A62" s="86" t="inlineStr">
         <is>
-          <t>E08</t>
+          <t>E07</t>
         </is>
       </c>
       <c r="B62" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg</t>
         </is>
       </c>
       <c r="C62" s="86" t="inlineStr">
@@ -6822,12 +6866,12 @@
       </c>
       <c r="E62" s="86" t="inlineStr">
         <is>
-          <t>DR test-day (11/15/2025) re-run of the same reports for comparison with 11/14/2025 source. Embedded attachments: FEDLINK INCOMING FEDWIRES 111425 -1115 1148AM.pdf; FEDLINK OUTGOINT TRANSFERS 114125 - 111525 1144AM.pdf; OFAC ACH 111425 - 11152025 1126AM.pdf; OFAC FED 111425 - 111525 1126AM.pdf; OFAC SWIFT 111425 - 111525 1128AM.pdf; OUTGOING FEDWIRE 111525 1025AM.xls; OUTGOING SWIFT 111525 1026AM.xls; PAYMENT MONITOR 111424 - 111525 PG 11156AM.pdf; PAYMENT MONITOR 111425 - 111525 PG 2 1158AM.pdf; PAYMENT MONITOR OUTGOING 111425 - 111525 PG 1 1156AM.pdf; PAYMENT MONITOR OUTGOING 111425 - 111525 PG 2 1156AM.pdf; SWIFT INTERFACE MONITOR INCOMING MT103 111425 - 111525 1152AM.pdf; SWIFT INTERFACE MONITOR INCOMING MT199 111425 -111525 1152AM.pdf.</t>
+          <t>Pre-DR (11/14/2025) source reports: Fedlink, OFAC ACH/FED/SWIFT, Payment Monitor, SWIFT Interface Monitor, outgoing Fedwire/SWIFT. Embedded attachments: FEDLINK INCOMING FEDWIRES 111425 0523PM.pdf; FEDLINK OUTGOING FEDWIRES 111425 0523PM.pdf; OFAC ACH 111425 0512PM.pdf; OFAC FED 111425 0511PM.pdf; OFAC SWIFT 111425 0511PM.pdf; OUTGOING FEDWIRE 111425 506PM.xls; OUTGOING SWIFT 111425 509PM.xls; PAYMENT MONITOR INCOMING FEDWIRE 111425 516PM PG1.pdf; PAYMENT MONITOR INCOMING FEDWIRE 111425 516PM PG2.pdf; PAYMENT MONITOR OUTGOING FEDWIRE 111425 516PM PG1.pdf; PAYMENT MONITOR OUTGOING FEDWIRE 111425 516PM PG2.pdf; SWIFT INTERFACE MONITOR 111425 519PM.pdf; SWIFT INTERFACE MONITOR 111425 520PM 2ND SAMPLE.pdf.</t>
         </is>
       </c>
       <c r="F62" s="86" t="inlineStr">
         <is>
-          <t>Samples: 3301, 1903, 1936, 1937; columns: F, M</t>
+          <t>Samples: 3301, 1903, 1936, 1937; columns: F</t>
         </is>
       </c>
       <c r="G62" s="82" t="n"/>
@@ -6844,35 +6888,35 @@
       <c r="R62" s="82" t="n"/>
       <c r="S62" s="82" t="n"/>
     </row>
-    <row r="63" ht="54" customHeight="1" s="71">
+    <row r="63" ht="90" customHeight="1" s="71">
       <c r="A63" s="86" t="inlineStr">
         <is>
-          <t>E09</t>
+          <t>E08</t>
         </is>
       </c>
       <c r="B63" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg</t>
         </is>
       </c>
       <c r="C63" s="86" t="inlineStr">
         <is>
-          <t>03/03/2026 – 05/05/2026 – Claudia Romero</t>
+          <t>11/15/2025 – Frank Puentes</t>
         </is>
       </c>
       <c r="D63" s="86" t="inlineStr">
         <is>
-          <t>Email approval</t>
+          <t>Email + report attachments</t>
         </is>
       </c>
       <c r="E63" s="86" t="inlineStr">
         <is>
-          <t>Client Back Office test evidence (Mariorly Morales, Ilumel Rodriguez, Rolando Bonilla) and Claudia Romero "Approved." 05/05/2026. Thread maps ACH Express, FedExport, FedImport, Imaging101 to Client Back Office / Claudia Romero.</t>
+          <t>DR test-day (11/15/2025) re-run of the same reports for comparison with 11/14/2025 source. Embedded attachments: FEDLINK INCOMING FEDWIRES 111425 -1115 1148AM.pdf; FEDLINK OUTGOINT TRANSFERS 114125 - 111525 1144AM.pdf; OFAC ACH 111425 - 11152025 1126AM.pdf; OFAC FED 111425 - 111525 1126AM.pdf; OFAC SWIFT 111425 - 111525 1128AM.pdf; OUTGOING FEDWIRE 111525 1025AM.xls; OUTGOING SWIFT 111525 1026AM.xls; PAYMENT MONITOR 111424 - 111525 PG 11156AM.pdf; PAYMENT MONITOR 111425 - 111525 PG 2 1158AM.pdf; PAYMENT MONITOR OUTGOING 111425 - 111525 PG 1 1156AM.pdf; PAYMENT MONITOR OUTGOING 111425 - 111525 PG 2 1156AM.pdf; SWIFT INTERFACE MONITOR INCOMING MT103 111425 - 111525 1152AM.pdf; SWIFT INTERFACE MONITOR INCOMING MT199 111425 -111525 1152AM.pdf.</t>
         </is>
       </c>
       <c r="F63" s="86" t="inlineStr">
         <is>
-          <t>Samples: 1822, 1867, 1868, 3299, 1937; columns: E, G, H, J, M, N, O</t>
+          <t>Samples: 3301, 1903, 1936, 1937; columns: F, M</t>
         </is>
       </c>
       <c r="G63" s="82" t="n"/>
@@ -6892,17 +6936,17 @@
     <row r="64" ht="42" customHeight="1" s="71">
       <c r="A64" s="86" t="inlineStr">
         <is>
-          <t>E10</t>
+          <t>E09</t>
         </is>
       </c>
       <c r="B64" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg</t>
         </is>
       </c>
       <c r="C64" s="86" t="inlineStr">
         <is>
-          <t>03/09/2026 – Lina Acuna</t>
+          <t>03/03/2026 – 05/05/2026 – Claudia Romero</t>
         </is>
       </c>
       <c r="D64" s="86" t="inlineStr">
@@ -6912,12 +6956,12 @@
       </c>
       <c r="E64" s="86" t="inlineStr">
         <is>
-          <t>Finance DIV results chart (Jose Acero) and Lina Acuna "Approved" 03/09/2026 (T24 / ReconXpert backup-restore).</t>
+          <t>Client Back Office test evidence (Mariorly Morales, Ilumel Rodriguez, Rolando Bonilla) and Claudia Romero "Approved." 05/05/2026. Thread maps ACH Express, FedExport, FedImport, Imaging101 to Client Back Office / Claudia Romero.</t>
         </is>
       </c>
       <c r="F64" s="86" t="inlineStr">
         <is>
-          <t>Samples: 1917, 1937; columns: M</t>
+          <t>Samples: 1822, 1867, 1868, 3299, 1937; columns: E, G, H, J, M, N, O</t>
         </is>
       </c>
       <c r="G64" s="82" t="n"/>
@@ -6934,35 +6978,35 @@
       <c r="R64" s="82" t="n"/>
       <c r="S64" s="82" t="n"/>
     </row>
-    <row r="65" ht="42" customHeight="1" s="71">
+    <row r="65" ht="30" customHeight="1" s="71">
       <c r="A65" s="86" t="inlineStr">
         <is>
-          <t>E13</t>
+          <t>E10</t>
         </is>
       </c>
       <c r="B65" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg</t>
         </is>
       </c>
       <c r="C65" s="86" t="inlineStr">
         <is>
-          <t>11/13/2024 – T24 backup user</t>
+          <t>03/09/2026 – Lina Acuna</t>
         </is>
       </c>
       <c r="D65" s="86" t="inlineStr">
         <is>
-          <t>System email</t>
+          <t>Email approval</t>
         </is>
       </c>
       <c r="E65" s="86" t="inlineStr">
         <is>
-          <t>T24 environment refresh log – prior period (outside review period); supplemental only.</t>
+          <t>Finance DIV results chart (Jose Acero) and Lina Acuna "Approved" 03/09/2026 (T24 / ReconXpert backup-restore).</t>
         </is>
       </c>
       <c r="F65" s="86" t="inlineStr">
         <is>
-          <t>Samples: —; columns: — (supplemental)</t>
+          <t>Samples: 1917, 1937; columns: M</t>
         </is>
       </c>
       <c r="G65" s="82" t="n"/>
@@ -6979,35 +7023,35 @@
       <c r="R65" s="82" t="n"/>
       <c r="S65" s="82" t="n"/>
     </row>
-    <row r="66" ht="42" customHeight="1" s="71">
+    <row r="66" ht="30" customHeight="1" s="71">
       <c r="A66" s="86" t="inlineStr">
         <is>
-          <t>E16b</t>
+          <t>E13</t>
         </is>
       </c>
       <c r="B66" s="86" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg</t>
         </is>
       </c>
       <c r="C66" s="86" t="inlineStr">
         <is>
-          <t>08/2026 – BCiC export sent with attestation request</t>
+          <t>11/13/2024 – T24 backup user</t>
         </is>
       </c>
       <c r="D66" s="86" t="inlineStr">
         <is>
-          <t>BCiC export</t>
+          <t>System email</t>
         </is>
       </c>
       <c r="E66" s="86" t="inlineStr">
         <is>
-          <t>BCiC DIV export 2025-26 (64 rows; no manager columns) sent to managers with the attestation request and returned by M. T. Del Cerro (DMA05). Row numbers are Excel rows.</t>
+          <t>T24 environment refresh log – prior period (outside review period); supplemental only.</t>
         </is>
       </c>
       <c r="F66" s="86" t="inlineStr">
         <is>
-          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: B, D, E, F, I, K, P</t>
+          <t>Samples: —; columns: — (supplemental)</t>
         </is>
       </c>
       <c r="G66" s="82" t="n"/>
@@ -7024,13 +7068,37 @@
       <c r="R66" s="82" t="n"/>
       <c r="S66" s="82" t="n"/>
     </row>
-    <row r="67" s="71">
-      <c r="A67" s="82" t="n"/>
-      <c r="B67" s="82" t="n"/>
-      <c r="C67" s="82" t="n"/>
-      <c r="D67" s="82" t="n"/>
-      <c r="E67" s="82" t="n"/>
-      <c r="F67" s="82" t="n"/>
+    <row r="67" ht="30" customHeight="1" s="71">
+      <c r="A67" s="86" t="inlineStr">
+        <is>
+          <t>E16b</t>
+        </is>
+      </c>
+      <c r="B67" s="86" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
+        </is>
+      </c>
+      <c r="C67" s="86" t="inlineStr">
+        <is>
+          <t>08/2026 – BCiC export sent with attestation request</t>
+        </is>
+      </c>
+      <c r="D67" s="86" t="inlineStr">
+        <is>
+          <t>BCiC export</t>
+        </is>
+      </c>
+      <c r="E67" s="86" t="inlineStr">
+        <is>
+          <t>BCiC DIV export 2025-26 (64 rows; no manager columns) sent to managers with the attestation request and returned by M. T. Del Cerro (DMA05). Row numbers are Excel rows.</t>
+        </is>
+      </c>
+      <c r="F67" s="86" t="inlineStr">
+        <is>
+          <t>Samples: 1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937; columns: B, D, E, F, I, K, P</t>
+        </is>
+      </c>
       <c r="G67" s="82" t="n"/>
       <c r="H67" s="82" t="n"/>
       <c r="I67" s="82" t="n"/>
@@ -7045,12 +7113,19 @@
       <c r="R67" s="82" t="n"/>
       <c r="S67" s="82" t="n"/>
     </row>
-    <row r="68" ht="22" customHeight="1" s="71">
-      <c r="A68" s="73" t="inlineStr">
-        <is>
-          <t>Observations for reviewer consideration (do not change the PASS conclusions unless the reviewer determines otherwise)</t>
-        </is>
-      </c>
+    <row r="68" s="71">
+      <c r="A68" s="82" t="n"/>
+      <c r="B68" s="82" t="n"/>
+      <c r="C68" s="82" t="n"/>
+      <c r="D68" s="82" t="n"/>
+      <c r="E68" s="82" t="n"/>
+      <c r="F68" s="82" t="n"/>
+      <c r="G68" s="82" t="n"/>
+      <c r="H68" s="82" t="n"/>
+      <c r="I68" s="82" t="n"/>
+      <c r="J68" s="82" t="n"/>
+      <c r="K68" s="82" t="n"/>
+      <c r="L68" s="82" t="n"/>
       <c r="M68" s="82" t="n"/>
       <c r="N68" s="82" t="n"/>
       <c r="O68" s="82" t="n"/>
@@ -7059,39 +7134,12 @@
       <c r="R68" s="82" t="n"/>
       <c r="S68" s="82" t="n"/>
     </row>
-    <row r="69" ht="30" customHeight="1" s="71">
-      <c r="A69" s="85" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B69" s="85" t="inlineStr">
-        <is>
-          <t>Observation</t>
-        </is>
-      </c>
-      <c r="C69" s="85" t="inlineStr">
-        <is>
-          <t>Samples affected</t>
-        </is>
-      </c>
-      <c r="D69" s="85" t="inlineStr">
-        <is>
-          <t>Evidence</t>
-        </is>
-      </c>
-      <c r="E69" s="85" t="inlineStr">
-        <is>
-          <t>Impact / reviewer consideration</t>
-        </is>
-      </c>
-      <c r="F69" s="85" t="inlineStr"/>
-      <c r="G69" s="82" t="n"/>
-      <c r="H69" s="82" t="n"/>
-      <c r="I69" s="82" t="n"/>
-      <c r="J69" s="82" t="n"/>
-      <c r="K69" s="82" t="n"/>
-      <c r="L69" s="82" t="n"/>
+    <row r="69" ht="22" customHeight="1" s="71">
+      <c r="A69" s="73" t="inlineStr">
+        <is>
+          <t>Observations for reviewer consideration (do not change the PASS conclusions unless the reviewer determines otherwise)</t>
+        </is>
+      </c>
       <c r="M69" s="82" t="n"/>
       <c r="N69" s="82" t="n"/>
       <c r="O69" s="82" t="n"/>
@@ -7100,31 +7148,33 @@
       <c r="R69" s="82" t="n"/>
       <c r="S69" s="82" t="n"/>
     </row>
-    <row r="70" ht="90" customHeight="1" s="71">
-      <c r="A70" s="87" t="n">
-        <v>1</v>
-      </c>
-      <c r="B70" s="87" t="inlineStr">
-        <is>
-          <t>Business line approvals for 33 of 56 in-scope DIV records were obtained through retrospective management attestations dated 08/17/2026 – 09/09/2026, i.e. after the review period end (06/01/2026) and ~9-10 months after the 11/15/2025 DIV testing. A further 13 records (BSA/AML/OFAC and Payments) carry in-period BCiC approval dates (11/15/2025, 12/18/2025) supported only by 08/2026 signed attestations. 10 records have in-period approval emails (E09, BLA06).</t>
-        </is>
-      </c>
-      <c r="C70" s="87" t="inlineStr">
-        <is>
-          <t>3299, 4052, 3301, 1903, 1936, 1937</t>
-        </is>
-      </c>
-      <c r="D70" s="87" t="inlineStr">
-        <is>
-          <t>Folder 03 (DMA01–DMA12); E03 approval dates</t>
-        </is>
-      </c>
-      <c r="E70" s="87" t="inlineStr">
-        <is>
-          <t>Approval is evidenced for 100% of records; timing is an observation. The attestation (DMA02 attachment §3.6) commits to contemporaneous approval going forward. Reviewer to conclude whether retrospective approval satisfies the control for the period.</t>
-        </is>
-      </c>
-      <c r="F70" s="87" t="inlineStr"/>
+    <row r="70" ht="30" customHeight="1" s="71">
+      <c r="A70" s="85" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B70" s="85" t="inlineStr">
+        <is>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="C70" s="85" t="inlineStr">
+        <is>
+          <t>Samples affected</t>
+        </is>
+      </c>
+      <c r="D70" s="85" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="E70" s="85" t="inlineStr">
+        <is>
+          <t>Impact / reviewer consideration</t>
+        </is>
+      </c>
+      <c r="F70" s="85" t="inlineStr"/>
       <c r="G70" s="82" t="n"/>
       <c r="H70" s="82" t="n"/>
       <c r="I70" s="82" t="n"/>
@@ -7139,28 +7189,28 @@
       <c r="R70" s="82" t="n"/>
       <c r="S70" s="82" t="n"/>
     </row>
-    <row r="71" ht="78" customHeight="1" s="71">
+    <row r="71" ht="66" customHeight="1" s="71">
       <c r="A71" s="87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B71" s="87" t="inlineStr">
         <is>
-          <t>Self-approval: the business tester and the approving Department Manager are the same person for BSA/AML/OFAC (David Marquez), Payments (Franklin Puentes), Investment Operations (Michelle Oropesa), Treasury (Martha Sullivan), Digital Wealth (Victoria Fernandez), Client Servicing Unit (Liliana Vizhnay), Commercial Middle Office (Miguel Orozco – Imaging101 / T24 row 15, 51) and Financial Analysis (Sadis Alvarenga).</t>
+          <t>Business line approvals for 33 of 56 in-scope DIV records were obtained through retrospective management attestations dated 08/17/2026 – 09/09/2026, i.e. after the review period end (06/01/2026) and ~9-10 months after the 11/15/2025 DIV testing. A further 13 records (BSA/AML/OFAC and Payments) carry in-period BCiC approval dates (11/15/2025, 12/18/2025) supported only by 08/2026 signed attestations. 10 records have in-period approval emails (E09, BLA06).</t>
         </is>
       </c>
       <c r="C71" s="87" t="inlineStr">
         <is>
-          <t>3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
+          <t>3299, 4052, 3301, 1903, 1936, 1937</t>
         </is>
       </c>
       <c r="D71" s="87" t="inlineStr">
         <is>
-          <t>E03 tester vs manager columns</t>
+          <t>Folder 03 (DMA01–DMA12); E03 approval dates</t>
         </is>
       </c>
       <c r="E71" s="87" t="inlineStr">
         <is>
-          <t>Segregation-of-duties observation; the approvers are the business line heads for those areas.</t>
+          <t>Approval is evidenced for 100% of records; timing is an observation. The attestation (DMA02 attachment §3.6) commits to contemporaneous approval going forward. Reviewer to conclude whether retrospective approval satisfies the control for the period.</t>
         </is>
       </c>
       <c r="F71" s="87" t="inlineStr"/>
@@ -7178,28 +7228,28 @@
       <c r="R71" s="82" t="n"/>
       <c r="S71" s="82" t="n"/>
     </row>
-    <row r="72" ht="30" customHeight="1" s="71">
+    <row r="72" ht="54" customHeight="1" s="71">
       <c r="A72" s="87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B72" s="87" t="inlineStr">
         <is>
-          <t>FedExport – BCiC Department Manager Approval Date 06/05/2026 (E03 row 9, E04) vs Claudia Romero "Approved." 05/05/2026 (E09).</t>
+          <t>Self-approval: the business tester and the approving Department Manager are the same person for BSA/AML/OFAC (David Marquez), Payments (Franklin Puentes), Investment Operations (Michelle Oropesa), Treasury (Martha Sullivan), Digital Wealth (Victoria Fernandez), Client Servicing Unit (Liliana Vizhnay), Commercial Middle Office (Miguel Orozco – Imaging101 / T24 row 15, 51) and Financial Analysis (Sadis Alvarenga).</t>
         </is>
       </c>
       <c r="C72" s="87" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
         </is>
       </c>
       <c r="D72" s="87" t="inlineStr">
         <is>
-          <t>E03, E04, E09</t>
+          <t>E03 tester vs manager columns</t>
         </is>
       </c>
       <c r="E72" s="87" t="inlineStr">
         <is>
-          <t>Likely BCiC data-entry error; recommend management correct the BCiC record.</t>
+          <t>Segregation-of-duties observation; the approvers are the business line heads for those areas.</t>
         </is>
       </c>
       <c r="F72" s="87" t="inlineStr"/>
@@ -7219,26 +7269,26 @@
     </row>
     <row r="73" ht="30" customHeight="1" s="71">
       <c r="A73" s="87" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B73" s="87" t="inlineStr">
         <is>
-          <t>BLA02 (BSA/AML/OFAC) test script – DIV Yes/No answer boxes are blank.</t>
+          <t>FedExport – BCiC Department Manager Approval Date 06/05/2026 (E03 row 9, E04) vs Claudia Romero "Approved." 05/05/2026 (E09).</t>
         </is>
       </c>
       <c r="C73" s="87" t="inlineStr">
         <is>
-          <t>3299, 1903, 1936, 1937</t>
+          <t>1867</t>
         </is>
       </c>
       <c r="D73" s="87" t="inlineStr">
         <is>
-          <t>BLA02 p.1</t>
+          <t>E03, E04, E09</t>
         </is>
       </c>
       <c r="E73" s="87" t="inlineStr">
         <is>
-          <t>Mitigated by production vs test-day screenshots in BLA02, BCiC Y/Y/Y (E03) and signed attestation (DMA02 attachment).</t>
+          <t>Likely BCiC data-entry error; recommend management correct the BCiC record.</t>
         </is>
       </c>
       <c r="F73" s="87" t="inlineStr"/>
@@ -7256,28 +7306,28 @@
       <c r="R73" s="82" t="n"/>
       <c r="S73" s="82" t="n"/>
     </row>
-    <row r="74" ht="54" customHeight="1" s="71">
+    <row r="74" ht="30" customHeight="1" s="71">
       <c r="A74" s="87" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B74" s="87" t="inlineStr">
         <is>
-          <t>BSA T24 record (E03 row 8) Attestation Date 08/29/2026 vs signed attestation 8/19/2026 (DMA02 attachment); Financial Risk manager recorded as "Xavier Caisapanta" in BCiC while the approval email is from Ivan Caisapanta (DMA08).</t>
+          <t>BLA02 (BSA/AML/OFAC) test script – DIV Yes/No answer boxes are blank.</t>
         </is>
       </c>
       <c r="C74" s="87" t="inlineStr">
         <is>
-          <t>1937</t>
+          <t>3299, 1903, 1936, 1937</t>
         </is>
       </c>
       <c r="D74" s="87" t="inlineStr">
         <is>
-          <t>E03, DMA02, DMA08</t>
+          <t>BLA02 p.1</t>
         </is>
       </c>
       <c r="E74" s="87" t="inlineStr">
         <is>
-          <t>BCiC data-entry / naming consistency; confirm identity of Financial Risk approver.</t>
+          <t>Mitigated by production vs test-day screenshots in BLA02, BCiC Y/Y/Y (E03) and signed attestation (DMA02 attachment).</t>
         </is>
       </c>
       <c r="F74" s="87" t="inlineStr"/>
@@ -7297,26 +7347,26 @@
     </row>
     <row r="75" ht="42" customHeight="1" s="71">
       <c r="A75" s="87" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B75" s="87" t="inlineStr">
         <is>
-          <t>ACH Express and Interface Monitor are not named verbatim in the DIV "Application In-scope" lines of BLA01 / BLA04; BLA01 operator (Raimy Ayala) differs from BCiC tester (Andreina De Stefano).</t>
+          <t>BSA T24 record (E03 row 8) Attestation Date 08/29/2026 vs signed attestation 8/19/2026 (DMA02 attachment); Financial Risk manager recorded as "Xavier Caisapanta" in BCiC while the approval email is from Ivan Caisapanta (DMA08).</t>
         </is>
       </c>
       <c r="C75" s="87" t="inlineStr">
         <is>
-          <t>1822, 4052, 1867, 1868</t>
+          <t>1937</t>
         </is>
       </c>
       <c r="D75" s="87" t="inlineStr">
         <is>
-          <t>BLA01, BLA04, E03, MA01</t>
+          <t>E03, DMA02, DMA08</t>
         </is>
       </c>
       <c r="E75" s="87" t="inlineStr">
         <is>
-          <t>Application-level DIV records exist in BCiC (E03 rows 47 and 61) with Y/Y/Y results and manager approval.</t>
+          <t>BCiC data-entry / naming consistency; confirm identity of Financial Risk approver.</t>
         </is>
       </c>
       <c r="F75" s="87" t="inlineStr"/>
@@ -7334,28 +7384,28 @@
       <c r="R75" s="82" t="n"/>
       <c r="S75" s="82" t="n"/>
     </row>
-    <row r="76" ht="54" customHeight="1" s="71">
+    <row r="76" ht="30" customHeight="1" s="71">
       <c r="A76" s="87" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B76" s="87" t="inlineStr">
         <is>
-          <t>Count reconciliation – E03 contains 62 DIV records (56 for the 10 tested applications); E16b contains 64 rows (one additional Treasury T24 row with blank department, row 45); the attestation states 63 entries / 13 applications.</t>
+          <t>ACH Express and Interface Monitor are not named verbatim in the DIV "Application In-scope" lines of BLA01 / BLA04; BLA01 operator (Raimy Ayala) differs from BCiC tester (Andreina De Stefano).</t>
         </is>
       </c>
       <c r="C76" s="87" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>1822, 4052, 1867, 1868</t>
         </is>
       </c>
       <c r="D76" s="87" t="inlineStr">
         <is>
-          <t>E03, E16b, DMA02</t>
+          <t>BLA01, BLA04, E03, MA01</t>
         </is>
       </c>
       <c r="E76" s="87" t="inlineStr">
         <is>
-          <t>Testing performed on E03 (the export containing the manager approval fields).</t>
+          <t>Application-level DIV records exist in BCiC (E03 rows 47 and 61) with Y/Y/Y results and manager approval.</t>
         </is>
       </c>
       <c r="F76" s="87" t="inlineStr"/>
@@ -7373,13 +7423,13 @@
       <c r="R76" s="82" t="n"/>
       <c r="S76" s="82" t="n"/>
     </row>
-    <row r="77" ht="30" customHeight="1" s="71">
+    <row r="77" ht="42" customHeight="1" s="71">
       <c r="A77" s="87" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B77" s="87" t="inlineStr">
         <is>
-          <t>Annual interval – prior DR exercise 10/19/2024 to 11/15/2025 = 392 days; one exercise per annual DR cycle (2024, 2025) and within the review period.</t>
+          <t>Count reconciliation – E03 contains 62 DIV records (56 for the 10 tested applications); E16b contains 64 rows (one additional Treasury T24 row with blank department, row 45); the attestation states 63 entries / 13 applications.</t>
         </is>
       </c>
       <c r="C77" s="87" t="inlineStr">
@@ -7389,12 +7439,12 @@
       </c>
       <c r="D77" s="87" t="inlineStr">
         <is>
-          <t>Tab 'DR 2024 Testing Results'; E01; E03</t>
+          <t>E03, E16b, DMA02</t>
         </is>
       </c>
       <c r="E77" s="87" t="inlineStr">
         <is>
-          <t>Annual requirement assessed per DR cycle.</t>
+          <t>Testing performed on E03 (the export containing the manager approval fields).</t>
         </is>
       </c>
       <c r="F77" s="87" t="inlineStr"/>
@@ -7412,28 +7462,28 @@
       <c r="R77" s="82" t="n"/>
       <c r="S77" s="82" t="n"/>
     </row>
-    <row r="78" ht="102" customHeight="1" s="71">
+    <row r="78" ht="30" customHeight="1" s="71">
       <c r="A78" s="87" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B78" s="87" t="inlineStr">
         <is>
-          <t>Redundant files removed: 13 duplicate evidence files (byte-identical copies or the same email saved twice: E11, E12, E14, E14a, E15, E15a, E16, E16a, E17, E17a, MA02, DMA05b, E06) and the extracted attachment copies (8 signed attestation PDFs, 26 E07/E08 report files) and E06 (same meeting invite as E05, re-sent) were removed; each item is retained once – signed attestations and report files are cited through the email that contains them (see Evidence Index – files removed). E13 (11/13/2024) is prior period – supplemental only. DMA13 (Cisco Call Manager) is out of scope.</t>
+          <t>Annual interval – prior DR exercise 10/19/2024 to 11/15/2025 = 392 days; one exercise per annual DR cycle (2024, 2025) and within the review period.</t>
         </is>
       </c>
       <c r="C78" s="87" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>All</t>
         </is>
       </c>
       <c r="D78" s="87" t="inlineStr">
         <is>
-          <t>Evidence Index tab</t>
+          <t>Tab 'DR 2024 Testing Results'; E01; E03</t>
         </is>
       </c>
       <c r="E78" s="87" t="inlineStr">
         <is>
-          <t>No impact – retained copy carries identical content.</t>
+          <t>Annual requirement assessed per DR cycle.</t>
         </is>
       </c>
       <c r="F78" s="87" t="inlineStr"/>
@@ -7451,13 +7501,31 @@
       <c r="R78" s="82" t="n"/>
       <c r="S78" s="82" t="n"/>
     </row>
-    <row r="79" s="71">
-      <c r="A79" s="82" t="n"/>
-      <c r="B79" s="82" t="n"/>
-      <c r="C79" s="82" t="n"/>
-      <c r="D79" s="82" t="n"/>
-      <c r="E79" s="82" t="n"/>
-      <c r="F79" s="82" t="n"/>
+    <row r="79" ht="78" customHeight="1" s="71">
+      <c r="A79" s="87" t="n">
+        <v>9</v>
+      </c>
+      <c r="B79" s="87" t="inlineStr">
+        <is>
+          <t>Redundant files removed: 12 duplicate evidence files (byte-identical copies or the same email saved twice: E11, E12, E14, E14a, E15, E15a, E16, E16a, E17, E17a, DMA05b, E06) and the extracted attachment copies (8 signed attestation PDFs, 26 E07/E08 report files) and E06 (same meeting invite as E05, re-sent) were removed; each item is retained once – signed attestations and report files are cited through the email that contains them (see Evidence Index – files removed). E13 (11/13/2024) is prior period – supplemental only. DMA13 (Cisco Call Manager) is out of scope.</t>
+        </is>
+      </c>
+      <c r="C79" s="87" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D79" s="87" t="inlineStr">
+        <is>
+          <t>Evidence Index tab</t>
+        </is>
+      </c>
+      <c r="E79" s="87" t="inlineStr">
+        <is>
+          <t>No impact – retained copy carries identical content.</t>
+        </is>
+      </c>
+      <c r="F79" s="87" t="inlineStr"/>
       <c r="G79" s="82" t="n"/>
       <c r="H79" s="82" t="n"/>
       <c r="I79" s="82" t="n"/>
@@ -7472,12 +7540,19 @@
       <c r="R79" s="82" t="n"/>
       <c r="S79" s="82" t="n"/>
     </row>
-    <row r="80" ht="22" customHeight="1" s="71">
-      <c r="A80" s="73" t="inlineStr">
-        <is>
-          <t>Reviewer Note</t>
-        </is>
-      </c>
+    <row r="80" s="71">
+      <c r="A80" s="82" t="n"/>
+      <c r="B80" s="82" t="n"/>
+      <c r="C80" s="82" t="n"/>
+      <c r="D80" s="82" t="n"/>
+      <c r="E80" s="82" t="n"/>
+      <c r="F80" s="82" t="n"/>
+      <c r="G80" s="82" t="n"/>
+      <c r="H80" s="82" t="n"/>
+      <c r="I80" s="82" t="n"/>
+      <c r="J80" s="82" t="n"/>
+      <c r="K80" s="82" t="n"/>
+      <c r="L80" s="82" t="n"/>
       <c r="M80" s="82" t="n"/>
       <c r="N80" s="82" t="n"/>
       <c r="O80" s="82" t="n"/>
@@ -7486,10 +7561,10 @@
       <c r="R80" s="82" t="n"/>
       <c r="S80" s="82" t="n"/>
     </row>
-    <row r="81" ht="75" customHeight="1" s="71">
-      <c r="A81" s="88" t="inlineStr">
-        <is>
-          <t>All requested attributes (IT DR exercise name, annual execution, application, tester, business data validation, manager name/approval dates, DIV procedures, approval emails, BCiC evidence, Annual Testing Executed, DIV Performed by IT DR Team, Applications in Scope Identified, Business Line Approval of Results, Results Documented in BCMS, overall assessment, supporting evidence and sample result) are completed for the 10 in-scope applications (56 DIV records) and every conclusion is linked to its evidence file and folder location in BSI.IT.6.C7.3-Evidences. Applications in Scope Identified is based on MA01 (BSI In-Scope Applications-2026). Business Line Approval of Results is based on the Business Line Approval Results – Email folder (BLA01–BLA06) together with the application-specific approval emails / signed attestations (folder 03, E09).</t>
+    <row r="81" ht="22" customHeight="1" s="71">
+      <c r="A81" s="73" t="inlineStr">
+        <is>
+          <t>Reviewer Note</t>
         </is>
       </c>
       <c r="M81" s="82" t="n"/>
@@ -7500,19 +7575,12 @@
       <c r="R81" s="82" t="n"/>
       <c r="S81" s="82" t="n"/>
     </row>
-    <row r="82" s="71">
-      <c r="A82" s="82" t="n"/>
-      <c r="B82" s="82" t="n"/>
-      <c r="C82" s="82" t="n"/>
-      <c r="D82" s="82" t="n"/>
-      <c r="E82" s="82" t="n"/>
-      <c r="F82" s="82" t="n"/>
-      <c r="G82" s="82" t="n"/>
-      <c r="H82" s="82" t="n"/>
-      <c r="I82" s="82" t="n"/>
-      <c r="J82" s="82" t="n"/>
-      <c r="K82" s="82" t="n"/>
-      <c r="L82" s="82" t="n"/>
+    <row r="82" ht="75" customHeight="1" s="71">
+      <c r="A82" s="88" t="inlineStr">
+        <is>
+          <t>All requested attributes (IT DR exercise name, annual execution, application, tester, business data validation, manager name/approval dates, DIV procedures, approval emails, BCiC evidence, Annual Testing Executed, DIV Performed by IT DR Team, Applications in Scope Identified, Business Line Approval of Results, Results Documented in BCMS, overall assessment, supporting evidence and sample result) are completed for the 10 in-scope applications (56 DIV records) and every conclusion is linked to its evidence file and folder location in BSI.IT.6.C7.3-Evidences. Applications in Scope Identified is based on MA01 (BSI In-Scope Applications-2026). Business Line Approval of Results is based on the Business Line Approval Results – Email folder (BLA01–BLA06) together with the application-specific approval emails / signed attestations (folder 03, E09).</t>
+        </is>
+      </c>
       <c r="M82" s="82" t="n"/>
       <c r="N82" s="82" t="n"/>
       <c r="O82" s="82" t="n"/>
@@ -8743,12 +8811,12 @@
   <mergeCells count="8">
     <mergeCell ref="A81:L81"/>
     <mergeCell ref="A15:L15"/>
-    <mergeCell ref="A68:L68"/>
+    <mergeCell ref="A82:L82"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A28:L28"/>
     <mergeCell ref="A37:L37"/>
-    <mergeCell ref="A80:L80"/>
     <mergeCell ref="A53:L53"/>
+    <mergeCell ref="A69:L69"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -8990,6 +9058,7 @@
       <c r="M5" s="62" t="inlineStr">
         <is>
           <t>• MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png – BSI In-Scope Applications-2026 – App ID 1822 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
+• MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg – Management Attestation email 08/18/2026 – attached signed attestation (4069_001.pdf) §2 lists the 13 in-scope applications that store business data, including this application
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 3 – 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
@@ -9015,8 +9084,9 @@
       </c>
       <c r="P5" s="62" t="inlineStr">
         <is>
-          <t>[01 Management Attestation / In-Scope Applications]
+          <t xml:space="preserve">[01 Management Attestation / In-Scope Applications]
 MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
+MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg
 [02 Business Line Approval Results – Email]
 BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf
 [03 DIV Manager Attestation Email Approvals]
@@ -9029,12 +9099,13 @@
 E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
 E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
+E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx
+</t>
         </is>
       </c>
       <c r="Q5" s="62" t="inlineStr">
         <is>
-          <t>PASS – with observations – MA01, BLA01, DMA01, DMA02, E01, E02, E03, E04, E05, E09, E16b</t>
+          <t>PASS – with observations – MA01, MA02, BLA01, DMA01, DMA02, E01, E02, E03, E04, E05, E09, E16b</t>
         </is>
       </c>
     </row>
@@ -9137,6 +9208,7 @@
       <c r="M6" s="62" t="inlineStr">
         <is>
           <t>• MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png – BSI In-Scope Applications-2026 – App ID 1867 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
+• MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg – Management Attestation email 08/18/2026 – attached signed attestation (4069_001.pdf) §2 lists the 13 in-scope applications that store business data, including this application
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 19 – 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
@@ -9162,8 +9234,9 @@
       </c>
       <c r="P6" s="62" t="inlineStr">
         <is>
-          <t>[01 Management Attestation / In-Scope Applications]
+          <t xml:space="preserve">[01 Management Attestation / In-Scope Applications]
 MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
+MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg
 [02 Business Line Approval Results – Email]
 BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf
 [03 DIV Manager Attestation Email Approvals]
@@ -9176,12 +9249,13 @@
 E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
 E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
+E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx
+</t>
         </is>
       </c>
       <c r="Q6" s="62" t="inlineStr">
         <is>
-          <t>PASS – with observations – MA01, BLA01, DMA01, DMA02, E01, E02, E03, E04, E05, E09, E16b</t>
+          <t>PASS – with observations – MA01, MA02, BLA01, DMA01, DMA02, E01, E02, E03, E04, E05, E09, E16b</t>
         </is>
       </c>
     </row>
@@ -9284,6 +9358,7 @@
       <c r="M7" s="62" t="inlineStr">
         <is>
           <t>• MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png – BSI In-Scope Applications-2026 – App ID 1868 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
+• MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg – Management Attestation email 08/18/2026 – attached signed attestation (4069_001.pdf) §2 lists the 13 in-scope applications that store business data, including this application
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 20 – 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
@@ -9309,8 +9384,9 @@
       </c>
       <c r="P7" s="62" t="inlineStr">
         <is>
-          <t>[01 Management Attestation / In-Scope Applications]
+          <t xml:space="preserve">[01 Management Attestation / In-Scope Applications]
 MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
+MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg
 [02 Business Line Approval Results – Email]
 BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf
 [03 DIV Manager Attestation Email Approvals]
@@ -9323,12 +9399,13 @@
 E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
 E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
+E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx
+</t>
         </is>
       </c>
       <c r="Q7" s="62" t="inlineStr">
         <is>
-          <t>PASS – with observations – MA01, BLA01, DMA01, DMA02, E01, E02, E03, E04, E05, E09, E16b</t>
+          <t>PASS – with observations – MA01, MA02, BLA01, DMA01, DMA02, E01, E02, E03, E04, E05, E09, E16b</t>
         </is>
       </c>
     </row>
@@ -9446,6 +9523,7 @@
       <c r="M8" s="62" t="inlineStr">
         <is>
           <t>• MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png – BSI In-Scope Applications-2026 – App ID 3299 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
+• MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg – Management Attestation email 08/18/2026 – attached signed attestation (4069_001.pdf) §2 lists the 13 in-scope applications that store business data, including this application
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 24 – 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
@@ -9475,8 +9553,9 @@
       </c>
       <c r="P8" s="62" t="inlineStr">
         <is>
-          <t>[01 Management Attestation / In-Scope Applications]
+          <t xml:space="preserve">[01 Management Attestation / In-Scope Applications]
 MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
+MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg
 [02 Business Line Approval Results – Email]
 BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf
 BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf
@@ -9492,12 +9571,13 @@
 E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
 E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
-E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
+E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx
+</t>
         </is>
       </c>
       <c r="Q8" s="62" t="inlineStr">
         <is>
-          <t>PASS – with observations – MA01, BLA01, BLA02, DMA01, DMA02, DMA05, DMA11, E01, E02, E03, E04, E05, E09, E16b</t>
+          <t>PASS – with observations – MA01, MA02, BLA01, BLA02, DMA01, DMA02, DMA05, DMA11, E01, E02, E03, E04, E05, E09, E16b</t>
         </is>
       </c>
     </row>
@@ -9591,6 +9671,7 @@
       <c r="M9" s="62" t="inlineStr">
         <is>
           <t>• MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png – BSI In-Scope Applications-2026 – App ID 4052 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
+• MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg – Management Attestation email 08/18/2026 – attached signed attestation (4069_001.pdf) §2 lists the 13 in-scope applications that store business data, including this application
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 25 – 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
@@ -9614,8 +9695,9 @@
       </c>
       <c r="P9" s="62" t="inlineStr">
         <is>
-          <t>[01 Management Attestation / In-Scope Applications]
+          <t xml:space="preserve">[01 Management Attestation / In-Scope Applications]
 MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
+MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg
 [02 Business Line Approval Results – Email]
 BLA04 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx
 [03 DIV Manager Attestation Email Approvals]
@@ -9627,12 +9709,13 @@
 E03 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls
 E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
-E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
+E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx
+</t>
         </is>
       </c>
       <c r="Q9" s="62" t="inlineStr">
         <is>
-          <t>PASS – with observations – MA01, BLA04, DMA02, DMA04, E01, E02, E03, E04, E05, E16b</t>
+          <t>PASS – with observations – MA01, MA02, BLA04, DMA02, DMA04, E01, E02, E03, E04, E05, E16b</t>
         </is>
       </c>
     </row>
@@ -9729,6 +9812,7 @@
       <c r="M10" s="62" t="inlineStr">
         <is>
           <t>• MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png – BSI In-Scope Applications-2026 – App ID 3301 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
+• MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg – Management Attestation email 08/18/2026 – attached signed attestation (4069_001.pdf) §2 lists the 13 in-scope applications that store business data, including this application
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 31 – 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
@@ -9752,8 +9836,9 @@
       </c>
       <c r="P10" s="62" t="inlineStr">
         <is>
-          <t>[01 Management Attestation / In-Scope Applications]
+          <t xml:space="preserve">[01 Management Attestation / In-Scope Applications]
 MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
+MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg
 [02 Business Line Approval Results – Email]
 BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf
 [03 DIV Manager Attestation Email Approvals]
@@ -9767,12 +9852,13 @@
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
 E07 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg
 E08 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg
-E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
+E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx
+</t>
         </is>
       </c>
       <c r="Q10" s="62" t="inlineStr">
         <is>
-          <t>PASS – with observations – MA01, BLA03, DMA02, DMA03, E01, E02, E03, E04, E05, E07, E08, E16b</t>
+          <t>PASS – with observations – MA01, MA02, BLA03, DMA02, DMA03, E01, E02, E03, E04, E05, E07, E08, E16b</t>
         </is>
       </c>
     </row>
@@ -9885,6 +9971,7 @@
       <c r="M11" s="62" t="inlineStr">
         <is>
           <t>• MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png – BSI In-Scope Applications-2026 – App ID 1903 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
+• MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg – Management Attestation email 08/18/2026 – attached signed attestation (4069_001.pdf) §2 lists the 13 in-scope applications that store business data, including this application
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 34 – 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
@@ -9911,8 +9998,9 @@
       </c>
       <c r="P11" s="62" t="inlineStr">
         <is>
-          <t>[01 Management Attestation / In-Scope Applications]
+          <t xml:space="preserve">[01 Management Attestation / In-Scope Applications]
 MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
+MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg
 [02 Business Line Approval Results – Email]
 BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf
 BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf
@@ -9928,12 +10016,13 @@
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
 E07 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg
 E08 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg
-E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
+E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx
+</t>
         </is>
       </c>
       <c r="Q11" s="62" t="inlineStr">
         <is>
-          <t>PASS – with observations – MA01, BLA02, BLA03, DMA02, DMA03, DMA05, E01, E02, E03, E04, E05, E07, E08, E16b</t>
+          <t>PASS – with observations – MA01, MA02, BLA02, BLA03, DMA02, DMA03, DMA05, E01, E02, E03, E04, E05, E07, E08, E16b</t>
         </is>
       </c>
     </row>
@@ -10028,6 +10117,7 @@
       <c r="M12" s="62" t="inlineStr">
         <is>
           <t>• MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png – BSI In-Scope Applications-2026 – App ID 1917 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
+• MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg – Management Attestation email 08/18/2026 – attached signed attestation (4069_001.pdf) §2 lists the 13 in-scope applications that store business data, including this application
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 36 – 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
@@ -10051,8 +10141,9 @@
       </c>
       <c r="P12" s="62" t="inlineStr">
         <is>
-          <t>[01 Management Attestation / In-Scope Applications]
+          <t xml:space="preserve">[01 Management Attestation / In-Scope Applications]
 MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
+MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg
 [02 Business Line Approval Results – Email]
 BLA05 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf
 BLA06 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg
@@ -10065,12 +10156,13 @@
 E04 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
 E10 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg
-E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
+E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx
+</t>
         </is>
       </c>
       <c r="Q12" s="62" t="inlineStr">
         <is>
-          <t>PASS – with observations – MA01, BLA05, BLA06, DMA02, E01, E02, E03, E04, E05, E10, E16b</t>
+          <t>PASS – with observations – MA01, MA02, BLA05, BLA06, DMA02, E01, E02, E03, E04, E05, E10, E16b</t>
         </is>
       </c>
     </row>
@@ -10180,6 +10272,7 @@
       <c r="M13" s="62" t="inlineStr">
         <is>
           <t>• MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png – BSI In-Scope Applications-2026 – App ID 1936 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
+• MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg – Management Attestation email 08/18/2026 – attached signed attestation (4069_001.pdf) §2 lists the 13 in-scope applications that store business data, including this application
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 42 – 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
@@ -10205,8 +10298,9 @@
       </c>
       <c r="P13" s="62" t="inlineStr">
         <is>
-          <t>[01 Management Attestation / In-Scope Applications]
+          <t xml:space="preserve">[01 Management Attestation / In-Scope Applications]
 MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
+MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg
 [02 Business Line Approval Results – Email]
 BLA03 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf
 BLA04 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx
@@ -10221,12 +10315,13 @@
 E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg
 E07 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg
 E08 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg
-E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
+E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx
+</t>
         </is>
       </c>
       <c r="Q13" s="62" t="inlineStr">
         <is>
-          <t>PASS – with observations – MA01, BLA03, BLA04, DMA02, DMA04, E01, E02, E03, E04, E05, E07, E08, E16b</t>
+          <t>PASS – with observations – MA01, MA02, BLA03, BLA04, DMA02, DMA04, E01, E02, E03, E04, E05, E07, E08, E16b</t>
         </is>
       </c>
     </row>
@@ -10391,6 +10486,7 @@
       <c r="M14" s="62" t="inlineStr">
         <is>
           <t>• MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png – BSI In-Scope Applications-2026 – App ID 1937 selected; 2025 DR Test Scope, 2025 Backup/Restore Test Scope and 2025 Backup/Restore DIV Scope = True
+• MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg – Management Attestation email 08/18/2026 – attached signed attestation (4069_001.pdf) §2 lists the 13 in-scope applications that store business data, including this application
 • E01 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx – row 43 – 2025 DR Test Scope = True; 2025 Backup/Restore DIV Scope = True
 • E02 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg – view 'Applications In Scope for DR Test BSI'
 • E05 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg – BIA results &amp; applications list review
@@ -10431,8 +10527,9 @@
       </c>
       <c r="P14" s="62" t="inlineStr">
         <is>
-          <t>[01 Management Attestation / In-Scope Applications]
+          <t xml:space="preserve">[01 Management Attestation / In-Scope Applications]
 MA01 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA01_BSI In-Scope Applications-2026.png
+MA02 – BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg
 [02 Business Line Approval Results – Email]
 BLA01 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf
 BLA02 – BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email\BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf
@@ -10463,12 +10560,13 @@
 E08 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg
 E09 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg
 E10 – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg
-E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
+E16b – BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence\BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx
+</t>
         </is>
       </c>
       <c r="Q14" s="62" t="inlineStr">
         <is>
-          <t>PASS – with observations – MA01, BLA01, BLA02, BLA03, BLA04, BLA05, BLA06, DMA01, DMA02, DMA03, DMA04, DMA05, DMA06, DMA07, DMA08, DMA09, DMA10, DMA11, DMA12, E01, E02, E03, E04, E05, E07, E08, E09, E10, E16b</t>
+          <t>PASS – with observations – MA01, MA02, BLA01, BLA02, BLA03, BLA04, BLA05, BLA06, DMA01, DMA02, DMA03, DMA04, DMA05, DMA06, DMA07, DMA08, DMA09, DMA10, DMA11, DMA12, E01, E02, E03, E04, E05, E07, E08, E09, E10, E16b</t>
         </is>
       </c>
     </row>
@@ -13007,52 +13105,52 @@
     <row r="4" ht="34.5" customHeight="1" s="71">
       <c r="A4" s="64" t="inlineStr">
         <is>
-          <t>BLA01</t>
+          <t>MA02</t>
         </is>
       </c>
       <c r="B4" s="64" t="inlineStr">
         <is>
-          <t>BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf</t>
+          <t>MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg</t>
         </is>
       </c>
       <c r="C4" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email</t>
+          <t>BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications</t>
         </is>
       </c>
       <c r="D4" s="64" t="inlineStr">
         <is>
-          <t>Client Back Office - FED inclearing ACH  Cash letter (1).pdf</t>
+          <t>RE_ Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises) 3 (2).msg</t>
         </is>
       </c>
       <c r="E4" s="64" t="inlineStr">
         <is>
-          <t>Business Line Approval Results - Email.zip</t>
+          <t>Management_Attestation.zip</t>
         </is>
       </c>
       <c r="F4" s="64" t="inlineStr">
         <is>
-          <t>DR test script / DIV test results</t>
+          <t>Email + signed management attestation</t>
         </is>
       </c>
       <c r="G4" s="64" t="inlineStr">
         <is>
-          <t>11/15/2025 – Client Back Office (operator Raimy Ayala)</t>
+          <t>08/18/2026 – Frank Puentes</t>
         </is>
       </c>
       <c r="H4" s="64" t="inlineStr">
         <is>
-          <t>DR test script with Data Integrity Validation section. Application in-scope: FedImport, FedExport, Imaging101, T24. Format / Headers / Content = Y – "No data discrepancy found". Steps include ACH Express import and Imaging101 validation screenshots (14 pages).</t>
+          <t>Management Attestation email: Frank Puentes (Executive Director, Payments &amp; Cash Management) returns the signed attestation (attachment 4069_001.pdf) to Cesar Vidal. The quoted Cesar Vidal request (08/17/2026) confirms the DR exercises of 11/15/2025 and 02/21/2026 and attaches the BCiC DIV export; the signed attestation §2 lists the 13 in-scope BSI applications that store business data, including all 10 tested applications. Filed in the Management_Attestation folder as received; the same message is also filed as DMA03 for the business line approval attribute.</t>
         </is>
       </c>
       <c r="I4" s="64" t="inlineStr">
         <is>
-          <t>1822, 1867, 1868, 3299, 1937</t>
+          <t>1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
         </is>
       </c>
       <c r="J4" s="64" t="inlineStr">
         <is>
-          <t>B, E, F, I, L, M, O</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K4" s="64" t="inlineStr"/>
@@ -13061,12 +13159,12 @@
     <row r="5" ht="34.5" customHeight="1" s="71">
       <c r="A5" s="64" t="inlineStr">
         <is>
-          <t>BLA02</t>
+          <t>BLA01</t>
         </is>
       </c>
       <c r="B5" s="64" t="inlineStr">
         <is>
-          <t>BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf</t>
+          <t>BLA01_Client Back Office - FED Inclearing ACH &amp; Cash Letter - DIV Test Results 11-15-2025.pdf</t>
         </is>
       </c>
       <c r="C5" s="64" t="inlineStr">
@@ -13076,7 +13174,7 @@
       </c>
       <c r="D5" s="64" t="inlineStr">
         <is>
-          <t>BSA_AML_OFAC Compliance - DM 11.15.2025 (002) (1).pdf</t>
+          <t>Client Back Office - FED inclearing ACH  Cash letter (1).pdf</t>
         </is>
       </c>
       <c r="E5" s="64" t="inlineStr">
@@ -13091,17 +13189,17 @@
       </c>
       <c r="G5" s="64" t="inlineStr">
         <is>
-          <t>11/15/2025 – BSA/AML/OFAC Compliance (operator David Marquez)</t>
+          <t>11/15/2025 – Client Back Office (operator Raimy Ayala)</t>
         </is>
       </c>
       <c r="H5" s="64" t="inlineStr">
         <is>
-          <t>OFAC Verifier test script. Application in-scope: T24, Imaging101, OFAC. DIV procedure instructions listed; production-day (11/14/2025) vs test-day (11/15/2025) screenshots for T24, Imaging101/ModeloIC and OFAC Report 64. NOTE: DIV Yes/No answer boxes on p.1 are blank.</t>
+          <t>DR test script with Data Integrity Validation section. Application in-scope: FedImport, FedExport, Imaging101, T24. Format / Headers / Content = Y – "No data discrepancy found". Steps include ACH Express import and Imaging101 validation screenshots (14 pages).</t>
         </is>
       </c>
       <c r="I5" s="64" t="inlineStr">
         <is>
-          <t>3299, 1903, 1937</t>
+          <t>1822, 1867, 1868, 3299, 1937</t>
         </is>
       </c>
       <c r="J5" s="64" t="inlineStr">
@@ -13115,12 +13213,12 @@
     <row r="6" ht="69" customHeight="1" s="71">
       <c r="A6" s="64" t="inlineStr">
         <is>
-          <t>BLA03</t>
+          <t>BLA02</t>
         </is>
       </c>
       <c r="B6" s="64" t="inlineStr">
         <is>
-          <t>BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf</t>
+          <t>BLA02_BSA_AML_OFAC Compliance - OFAC Verifier - DIV Test Results 11-15-2025.pdf</t>
         </is>
       </c>
       <c r="C6" s="64" t="inlineStr">
@@ -13130,7 +13228,7 @@
       </c>
       <c r="D6" s="64" t="inlineStr">
         <is>
-          <t>PAYMENTS SCRIPT NOV 2025.pdf</t>
+          <t>BSA_AML_OFAC Compliance - DM 11.15.2025 (002) (1).pdf</t>
         </is>
       </c>
       <c r="E6" s="64" t="inlineStr">
@@ -13145,17 +13243,17 @@
       </c>
       <c r="G6" s="64" t="inlineStr">
         <is>
-          <t>11/15/2025 – Payments &amp; Position Management (operators Frank Puentes / Gustavo Bucaro)</t>
+          <t>11/15/2025 – BSA/AML/OFAC Compliance (operator David Marquez)</t>
         </is>
       </c>
       <c r="H6" s="64" t="inlineStr">
         <is>
-          <t>Wire Transfer / Cash Mgt / Financial Messaging script. DIV application in-scope: T24, MQ Payment Monitor, OFAC – BSI, Fedlink – BSI, Swift Interface – BSI. Format / Headers / Content = yes; data from 11/14/2025 Fed &amp; SWIFT reconciled.</t>
+          <t>OFAC Verifier test script. Application in-scope: T24, Imaging101, OFAC. DIV procedure instructions listed; production-day (11/14/2025) vs test-day (11/15/2025) screenshots for T24, Imaging101/ModeloIC and OFAC Report 64. NOTE: DIV Yes/No answer boxes on p.1 are blank.</t>
         </is>
       </c>
       <c r="I6" s="64" t="inlineStr">
         <is>
-          <t>3301, 1903, 1936, 1937</t>
+          <t>3299, 1903, 1937</t>
         </is>
       </c>
       <c r="J6" s="64" t="inlineStr">
@@ -13169,12 +13267,12 @@
     <row r="7" ht="46" customHeight="1" s="71">
       <c r="A7" s="64" t="inlineStr">
         <is>
-          <t>BLA04</t>
+          <t>BLA03</t>
         </is>
       </c>
       <c r="B7" s="64" t="inlineStr">
         <is>
-          <t>BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx</t>
+          <t>BLA03_Payments &amp; Cash Management - Payments Script - DIV Test Results 11-15-2025.pdf</t>
         </is>
       </c>
       <c r="C7" s="64" t="inlineStr">
@@ -13184,7 +13282,7 @@
       </c>
       <c r="D7" s="64" t="inlineStr">
         <is>
-          <t>Investment Operations- Treasury Hub &amp; Derivatives Operations (1).docx</t>
+          <t>PAYMENTS SCRIPT NOV 2025.pdf</t>
         </is>
       </c>
       <c r="E7" s="64" t="inlineStr">
@@ -13199,17 +13297,17 @@
       </c>
       <c r="G7" s="64" t="inlineStr">
         <is>
-          <t>11/15/2025 – Investment Operations (operator Michelle Oropesa)</t>
+          <t>11/15/2025 – Payments &amp; Position Management (operators Frank Puentes / Gustavo Bucaro)</t>
         </is>
       </c>
       <c r="H7" s="64" t="inlineStr">
         <is>
-          <t>Treasury Hub &amp; Derivatives Operations script. Systems accessed: Swift Interface Monitor – BSI, T24, MS Office, DTCC. DIV application in-scope: T24 &amp; Swift Interface – BSI. Incoming MT300 and FX S reports matched 11/14 vs 11/15; Format / Headers / Content = Yes.</t>
+          <t>Wire Transfer / Cash Mgt / Financial Messaging script. DIV application in-scope: T24, MQ Payment Monitor, OFAC – BSI, Fedlink – BSI, Swift Interface – BSI. Format / Headers / Content = yes; data from 11/14/2025 Fed &amp; SWIFT reconciled.</t>
         </is>
       </c>
       <c r="I7" s="64" t="inlineStr">
         <is>
-          <t>4052, 1936, 1937</t>
+          <t>3301, 1903, 1936, 1937</t>
         </is>
       </c>
       <c r="J7" s="64" t="inlineStr">
@@ -13223,12 +13321,12 @@
     <row r="8" ht="23" customHeight="1" s="71">
       <c r="A8" s="64" t="inlineStr">
         <is>
-          <t>BLA05</t>
+          <t>BLA04</t>
         </is>
       </c>
       <c r="B8" s="64" t="inlineStr">
         <is>
-          <t>BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf</t>
+          <t>BLA04_Investment Operations - Treasury Hub &amp; Derivatives Operations - DIV Test Results 11-15-2025.docx</t>
         </is>
       </c>
       <c r="C8" s="64" t="inlineStr">
@@ -13238,7 +13336,7 @@
       </c>
       <c r="D8" s="64" t="inlineStr">
         <is>
-          <t>Financial Analysis and Control-GL (1).pdf</t>
+          <t>Investment Operations- Treasury Hub &amp; Derivatives Operations (1).docx</t>
         </is>
       </c>
       <c r="E8" s="64" t="inlineStr">
@@ -13253,17 +13351,17 @@
       </c>
       <c r="G8" s="64" t="inlineStr">
         <is>
-          <t>11/15/2025 – Finance &amp; Accounting Reporting (operator Dunia Gonzalez Collado)</t>
+          <t>11/15/2025 – Investment Operations (operator Michelle Oropesa)</t>
         </is>
       </c>
       <c r="H8" s="64" t="inlineStr">
         <is>
-          <t>General ledger review script. DIV application in-scope: T24 &amp; ReconXpert. Reconciliations passed; Format / Headers / Content = Yes, "No discrepancies found on the report".</t>
+          <t>Treasury Hub &amp; Derivatives Operations script. Systems accessed: Swift Interface Monitor – BSI, T24, MS Office, DTCC. DIV application in-scope: T24 &amp; Swift Interface – BSI. Incoming MT300 and FX S reports matched 11/14 vs 11/15; Format / Headers / Content = Yes.</t>
         </is>
       </c>
       <c r="I8" s="64" t="inlineStr">
         <is>
-          <t>1917, 1937</t>
+          <t>4052, 1936, 1937</t>
         </is>
       </c>
       <c r="J8" s="64" t="inlineStr">
@@ -13277,12 +13375,12 @@
     <row r="9" ht="23" customHeight="1" s="71">
       <c r="A9" s="64" t="inlineStr">
         <is>
-          <t>BLA06</t>
+          <t>BLA05</t>
         </is>
       </c>
       <c r="B9" s="64" t="inlineStr">
         <is>
-          <t>BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg</t>
+          <t>BLA05_Financial Analysis and Control - GL ReconXpert - DIV Test Results 11-15-2025.pdf</t>
         </is>
       </c>
       <c r="C9" s="64" t="inlineStr">
@@ -13292,7 +13390,7 @@
       </c>
       <c r="D9" s="64" t="inlineStr">
         <is>
-          <t>RE_ Testing enviroment.msg</t>
+          <t>Financial Analysis and Control-GL (1).pdf</t>
         </is>
       </c>
       <c r="E9" s="64" t="inlineStr">
@@ -13302,17 +13400,17 @@
       </c>
       <c r="F9" s="64" t="inlineStr">
         <is>
-          <t>Email approval</t>
+          <t>DR test script / DIV test results</t>
         </is>
       </c>
       <c r="G9" s="64" t="inlineStr">
         <is>
-          <t>12/31/2025 &amp; 01/26/2026 – Sadis Alvarenga</t>
+          <t>11/15/2025 – Finance &amp; Accounting Reporting (operator Dunia Gonzalez Collado)</t>
         </is>
       </c>
       <c r="H9" s="64" t="inlineStr">
         <is>
-          <t>Sadis Alvarenga (Financial Analysis &amp; Control manager) replies "Approved." on 12/31/2025 and again on 01/26/2026 to Elizabeth Noda's request to approve the submitted test script.</t>
+          <t>General ledger review script. DIV application in-scope: T24 &amp; ReconXpert. Reconciliations passed; Format / Headers / Content = Yes, "No discrepancies found on the report".</t>
         </is>
       </c>
       <c r="I9" s="64" t="inlineStr">
@@ -13322,7 +13420,7 @@
       </c>
       <c r="J9" s="64" t="inlineStr">
         <is>
-          <t>G, H, J, O</t>
+          <t>B, E, F, I, L, M, O</t>
         </is>
       </c>
       <c r="K9" s="64" t="inlineStr"/>
@@ -13331,47 +13429,47 @@
     <row r="10" ht="34.5" customHeight="1" s="71">
       <c r="A10" s="64" t="inlineStr">
         <is>
-          <t>DMA01</t>
+          <t>BLA06</t>
         </is>
       </c>
       <c r="B10" s="64" t="inlineStr">
         <is>
-          <t>DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
+          <t>BLA06_RE_ Testing enviroment - Financial Analysis Manager Approval - Sadis Alvarenga 01-26-2026.msg</t>
         </is>
       </c>
       <c r="C10" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
+          <t>BSI.IT.6.C7.3-Evidences\02_Business_Line_Approval_Results_Email</t>
         </is>
       </c>
       <c r="D10" s="64" t="inlineStr">
         <is>
-          <t>RE_ Management Attestation – DIV Client Back Office.msg</t>
+          <t>RE_ Testing enviroment.msg</t>
         </is>
       </c>
       <c r="E10" s="64" t="inlineStr">
         <is>
-          <t>DIV Manager Attestation Email_Approvals.zip</t>
+          <t>Business Line Approval Results - Email.zip</t>
         </is>
       </c>
       <c r="F10" s="64" t="inlineStr">
         <is>
-          <t>Email attestation</t>
+          <t>Email approval</t>
         </is>
       </c>
       <c r="G10" s="64" t="inlineStr">
         <is>
-          <t>08/18/2026 – Claudia Romero</t>
+          <t>12/31/2025 &amp; 01/26/2026 – Sadis Alvarenga</t>
         </is>
       </c>
       <c r="H10" s="64" t="inlineStr">
         <is>
-          <t>Claudia Romero (Client Back Office Manager VP) returns the signed Management Attestation – attachment: Data_Integrity_Attestation_Santander-BCiC (002).pdf (signed Claudia Romero).</t>
+          <t>Sadis Alvarenga (Financial Analysis &amp; Control manager) replies "Approved." on 12/31/2025 and again on 01/26/2026 to Elizabeth Noda's request to approve the submitted test script.</t>
         </is>
       </c>
       <c r="I10" s="64" t="inlineStr">
         <is>
-          <t>1822, 1867, 1868, 3299, 1937</t>
+          <t>1917, 1937</t>
         </is>
       </c>
       <c r="J10" s="64" t="inlineStr">
@@ -13385,12 +13483,12 @@
     <row r="11" ht="23" customHeight="1" s="71">
       <c r="A11" s="64" t="inlineStr">
         <is>
-          <t>DMA02</t>
+          <t>DMA01</t>
         </is>
       </c>
       <c r="B11" s="64" t="inlineStr">
         <is>
-          <t>DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg</t>
+          <t>DMA01_RE_ Management Attestation – DIV – Client Back Office - Claudia Romero 08-18-2026.msg</t>
         </is>
       </c>
       <c r="C11" s="64" t="inlineStr">
@@ -13400,7 +13498,7 @@
       </c>
       <c r="D11" s="64" t="inlineStr">
         <is>
-          <t>RE_ Management Attestation – OFAC.msg</t>
+          <t>RE_ Management Attestation – DIV Client Back Office.msg</t>
         </is>
       </c>
       <c r="E11" s="64" t="inlineStr">
@@ -13415,22 +13513,22 @@
       </c>
       <c r="G11" s="64" t="inlineStr">
         <is>
-          <t>08/19/2026 – David Marquez</t>
+          <t>08/18/2026 – Claudia Romero</t>
         </is>
       </c>
       <c r="H11" s="64" t="inlineStr">
         <is>
-          <t>Cesar Vidal request to Department Managers (08/17/2026; DR exercises 11/15/2025 and 02/21/2026; BCiC export attached) and David Marquez (OFAC Manager) reply. Attachment: Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – signed OFAC Manager, VP, BSA/AML-OFAC Compliance, 8/19/2026. Attestation §1: IT DR team facilitates DIV annually; §2: 63 entries / 13 applications, all Y/Y/Y; §3.5: retained in BCMS/BCiC; §3.6: contemporaneous approval going forward.</t>
+          <t>Claudia Romero (Client Back Office Manager VP) returns the signed Management Attestation – attachment: Data_Integrity_Attestation_Santander-BCiC (002).pdf (signed Claudia Romero).</t>
         </is>
       </c>
       <c r="I11" s="64" t="inlineStr">
         <is>
-          <t>1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
+          <t>1822, 1867, 1868, 3299, 1937</t>
         </is>
       </c>
       <c r="J11" s="64" t="inlineStr">
         <is>
-          <t>B, C, G, H, J, L, M, N, O, P</t>
+          <t>G, H, J, O</t>
         </is>
       </c>
       <c r="K11" s="64" t="inlineStr"/>
@@ -13439,12 +13537,12 @@
     <row r="12" ht="34.5" customHeight="1" s="71">
       <c r="A12" s="64" t="inlineStr">
         <is>
-          <t>DMA03</t>
+          <t>DMA02</t>
         </is>
       </c>
       <c r="B12" s="64" t="inlineStr">
         <is>
-          <t>DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
+          <t>DMA02_RE_ Management Attestation – DIV – BSA-AML-OFAC Compliance - David Marquez 08-19-2026.msg</t>
         </is>
       </c>
       <c r="C12" s="64" t="inlineStr">
@@ -13454,7 +13552,7 @@
       </c>
       <c r="D12" s="64" t="inlineStr">
         <is>
-          <t>Management Attestation – DIV Payment &amp; Cash Management.msg</t>
+          <t>RE_ Management Attestation – OFAC.msg</t>
         </is>
       </c>
       <c r="E12" s="64" t="inlineStr">
@@ -13469,22 +13567,22 @@
       </c>
       <c r="G12" s="64" t="inlineStr">
         <is>
-          <t>08/18/2026 – Frank Puentes</t>
+          <t>08/19/2026 – David Marquez</t>
         </is>
       </c>
       <c r="H12" s="64" t="inlineStr">
         <is>
-          <t>Frank Puentes returns the signed attestation – attachment: 4069_001.pdf (scan, signed Executive Director, Payments &amp; Cash Management, 8/18/2026).</t>
+          <t>Cesar Vidal request to Department Managers (08/17/2026; DR exercises 11/15/2025 and 02/21/2026; BCiC export attached) and David Marquez (OFAC Manager) reply. Attachment: Data_Integrity_Attestation_Santander-BCiC (005) - BSA-AML-OFAC Compliance.pdf – signed OFAC Manager, VP, BSA/AML-OFAC Compliance, 8/19/2026. Attestation §1: IT DR team facilitates DIV annually; §2: 63 entries / 13 applications, all Y/Y/Y; §3.5: retained in BCMS/BCiC; §3.6: contemporaneous approval going forward.</t>
         </is>
       </c>
       <c r="I12" s="64" t="inlineStr">
         <is>
-          <t>3301, 1903, 1937</t>
+          <t>1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
         </is>
       </c>
       <c r="J12" s="64" t="inlineStr">
         <is>
-          <t>G, H, J, O</t>
+          <t>B, C, G, H, J, L, M, N, O, P</t>
         </is>
       </c>
       <c r="K12" s="64" t="inlineStr"/>
@@ -13493,12 +13591,12 @@
     <row r="13" ht="34.5" customHeight="1" s="71">
       <c r="A13" s="64" t="inlineStr">
         <is>
-          <t>DMA04</t>
+          <t>DMA03</t>
         </is>
       </c>
       <c r="B13" s="64" t="inlineStr">
         <is>
-          <t>DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
+          <t>DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
         </is>
       </c>
       <c r="C13" s="64" t="inlineStr">
@@ -13508,7 +13606,7 @@
       </c>
       <c r="D13" s="64" t="inlineStr">
         <is>
-          <t>RE_ Management Attestation – DIV Investment Operations.msg</t>
+          <t>Management Attestation – DIV Payment &amp; Cash Management.msg</t>
         </is>
       </c>
       <c r="E13" s="64" t="inlineStr">
@@ -13523,17 +13621,17 @@
       </c>
       <c r="G13" s="64" t="inlineStr">
         <is>
-          <t>08/17/2026 – Michelle Oropesa</t>
+          <t>08/18/2026 – Frank Puentes</t>
         </is>
       </c>
       <c r="H13" s="64" t="inlineStr">
         <is>
-          <t>Michelle Oropesa (Investment Operations Director) returns the signed attestation – attachment: Data_Integrity_Attestation_Santander-BCiC.pdf (signed Investment Operations Director, VP, 8/17/2026).</t>
+          <t>Frank Puentes returns the signed attestation – attachment: 4069_001.pdf (scan, signed Executive Director, Payments &amp; Cash Management, 8/18/2026).</t>
         </is>
       </c>
       <c r="I13" s="64" t="inlineStr">
         <is>
-          <t>4052, 1936, 1937</t>
+          <t>3301, 1903, 1937</t>
         </is>
       </c>
       <c r="J13" s="64" t="inlineStr">
@@ -13547,12 +13645,12 @@
     <row r="14" ht="34.5" customHeight="1" s="71">
       <c r="A14" s="64" t="inlineStr">
         <is>
-          <t>DMA05</t>
+          <t>DMA04</t>
         </is>
       </c>
       <c r="B14" s="64" t="inlineStr">
         <is>
-          <t>DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
+          <t>DMA04_RE_ Management Attestation – DIV – Investment Operations - Michelle Oropesa 08-17-2026.msg</t>
         </is>
       </c>
       <c r="C14" s="64" t="inlineStr">
@@ -13562,7 +13660,7 @@
       </c>
       <c r="D14" s="64" t="inlineStr">
         <is>
-          <t>RE_ Management Attestation – DIV Operations.msg</t>
+          <t>RE_ Management Attestation – DIV Investment Operations.msg</t>
         </is>
       </c>
       <c r="E14" s="64" t="inlineStr">
@@ -13577,17 +13675,17 @@
       </c>
       <c r="G14" s="64" t="inlineStr">
         <is>
-          <t>08/19/2026 – Maria Teresa (Mayte) Del Cerro</t>
+          <t>08/17/2026 – Michelle Oropesa</t>
         </is>
       </c>
       <c r="H14" s="64" t="inlineStr">
         <is>
-          <t>Senior Director of Operations returns the signed attestation – attachments: Data_Integrity_Attestation_Santander-BCiC.pdf (signed Maria Teresa Del Cerro Hontanilla, Director of Operations, 08/19/2026) and the BCiC export (same file as E16b).</t>
+          <t>Michelle Oropesa (Investment Operations Director) returns the signed attestation – attachment: Data_Integrity_Attestation_Santander-BCiC.pdf (signed Investment Operations Director, VP, 8/17/2026).</t>
         </is>
       </c>
       <c r="I14" s="64" t="inlineStr">
         <is>
-          <t>3299, 1903, 1937</t>
+          <t>4052, 1936, 1937</t>
         </is>
       </c>
       <c r="J14" s="64" t="inlineStr">
@@ -13601,12 +13699,12 @@
     <row r="15" ht="34.5" customHeight="1" s="71">
       <c r="A15" s="64" t="inlineStr">
         <is>
-          <t>DMA06</t>
+          <t>DMA05</t>
         </is>
       </c>
       <c r="B15" s="64" t="inlineStr">
         <is>
-          <t>DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg</t>
+          <t>DMA05_RE_ Management Attestation – DIV – Operations (Governance &amp; Static Data, Multi-Family Office) - Maria Teresa Del Cerro 08-19-2026.msg</t>
         </is>
       </c>
       <c r="C15" s="64" t="inlineStr">
@@ -13616,7 +13714,7 @@
       </c>
       <c r="D15" s="64" t="inlineStr">
         <is>
-          <t>RE_ Management Attestation – DIV Trading and Capital Markets.msg</t>
+          <t>RE_ Management Attestation – DIV Operations.msg</t>
         </is>
       </c>
       <c r="E15" s="64" t="inlineStr">
@@ -13631,17 +13729,17 @@
       </c>
       <c r="G15" s="64" t="inlineStr">
         <is>
-          <t>08/18/2026 – Ricardo Garcia-Marques</t>
+          <t>08/19/2026 – Maria Teresa (Mayte) Del Cerro</t>
         </is>
       </c>
       <c r="H15" s="64" t="inlineStr">
         <is>
-          <t>Attestation and approval from Trading &amp; Capital Markets (covers BCiC records approved by Ricardo Garcia) – attachment: Data_Integrity_Attestation_Santander-BCiC_signed.pdf (e-signed MD, Head of Trading &amp; Capital Markets, 08/18/2026 11:45 AM EDT).</t>
+          <t>Senior Director of Operations returns the signed attestation – attachments: Data_Integrity_Attestation_Santander-BCiC.pdf (signed Maria Teresa Del Cerro Hontanilla, Director of Operations, 08/19/2026) and the BCiC export (same file as E16b).</t>
         </is>
       </c>
       <c r="I15" s="64" t="inlineStr">
         <is>
-          <t>1937</t>
+          <t>3299, 1903, 1937</t>
         </is>
       </c>
       <c r="J15" s="64" t="inlineStr">
@@ -13655,12 +13753,12 @@
     <row r="16" ht="23" customHeight="1" s="71">
       <c r="A16" s="64" t="inlineStr">
         <is>
-          <t>DMA07</t>
+          <t>DMA06</t>
         </is>
       </c>
       <c r="B16" s="64" t="inlineStr">
         <is>
-          <t>DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg</t>
+          <t>DMA06_RE_ Management Attestation – DIV – Trading &amp; Capital Markets (AIS, Portfolio Advisory, P&amp;I Tech) - Ricardo Garcia-Marques 08-18-2026.msg</t>
         </is>
       </c>
       <c r="C16" s="64" t="inlineStr">
@@ -13670,7 +13768,7 @@
       </c>
       <c r="D16" s="64" t="inlineStr">
         <is>
-          <t>RE_ Management Attestation – DIV Treasury and Capital Planning.msg</t>
+          <t>RE_ Management Attestation – DIV Trading and Capital Markets.msg</t>
         </is>
       </c>
       <c r="E16" s="64" t="inlineStr">
@@ -13685,12 +13783,12 @@
       </c>
       <c r="G16" s="64" t="inlineStr">
         <is>
-          <t>08/18/2026 – Martha Sullivan</t>
+          <t>08/18/2026 – Ricardo Garcia-Marques</t>
         </is>
       </c>
       <c r="H16" s="64" t="inlineStr">
         <is>
-          <t>Martha Sullivan returns the signed attestation – attachment: Data_Integrity_Attestation_Santander-BCiC.pdf (signed Balance Sheet Manager, Treasury).</t>
+          <t>Attestation and approval from Trading &amp; Capital Markets (covers BCiC records approved by Ricardo Garcia) – attachment: Data_Integrity_Attestation_Santander-BCiC_signed.pdf (e-signed MD, Head of Trading &amp; Capital Markets, 08/18/2026 11:45 AM EDT).</t>
         </is>
       </c>
       <c r="I16" s="64" t="inlineStr">
@@ -13709,12 +13807,12 @@
     <row r="17" ht="23" customHeight="1" s="71">
       <c r="A17" s="64" t="inlineStr">
         <is>
-          <t>DMA08</t>
+          <t>DMA07</t>
         </is>
       </c>
       <c r="B17" s="64" t="inlineStr">
         <is>
-          <t>DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg</t>
+          <t>DMA07_RE_ Management Attestation – DIV – Treasury &amp; Capital Planning - Martha Sullivan 08-18-2026.msg</t>
         </is>
       </c>
       <c r="C17" s="64" t="inlineStr">
@@ -13724,7 +13822,7 @@
       </c>
       <c r="D17" s="64" t="inlineStr">
         <is>
-          <t>RE_ Management Attestation – DIV Solvency and Market Risk.msg</t>
+          <t>RE_ Management Attestation – DIV Treasury and Capital Planning.msg</t>
         </is>
       </c>
       <c r="E17" s="64" t="inlineStr">
@@ -13734,17 +13832,17 @@
       </c>
       <c r="F17" s="64" t="inlineStr">
         <is>
-          <t>Email approval</t>
+          <t>Email attestation</t>
         </is>
       </c>
       <c r="G17" s="64" t="inlineStr">
         <is>
-          <t>08/18/2026 – Ivan Caisapanta</t>
+          <t>08/18/2026 – Martha Sullivan</t>
         </is>
       </c>
       <c r="H17" s="64" t="inlineStr">
         <is>
-          <t>"Hi Elizabeth, You have my approval" – Financial Risk (BCiC Department Manager recorded as Xavier Caisapanta).</t>
+          <t>Martha Sullivan returns the signed attestation – attachment: Data_Integrity_Attestation_Santander-BCiC.pdf (signed Balance Sheet Manager, Treasury).</t>
         </is>
       </c>
       <c r="I17" s="64" t="inlineStr">
@@ -13763,12 +13861,12 @@
     <row r="18" ht="23" customHeight="1" s="71">
       <c r="A18" s="64" t="inlineStr">
         <is>
-          <t>DMA09</t>
+          <t>DMA08</t>
         </is>
       </c>
       <c r="B18" s="64" t="inlineStr">
         <is>
-          <t>DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg</t>
+          <t>DMA08_RE_ Management Attestation – DIV – Solvency &amp; Market Risk (Financial Risk) - Ivan Caisapanta 08-18-2026.msg</t>
         </is>
       </c>
       <c r="C18" s="64" t="inlineStr">
@@ -13778,7 +13876,7 @@
       </c>
       <c r="D18" s="64" t="inlineStr">
         <is>
-          <t>RE_ Management Attestation – DIV General Services.msg</t>
+          <t>RE_ Management Attestation – DIV Solvency and Market Risk.msg</t>
         </is>
       </c>
       <c r="E18" s="64" t="inlineStr">
@@ -13788,17 +13886,17 @@
       </c>
       <c r="F18" s="64" t="inlineStr">
         <is>
-          <t>Email attestation</t>
+          <t>Email approval</t>
         </is>
       </c>
       <c r="G18" s="64" t="inlineStr">
         <is>
-          <t>08/18/2026 – Clara G. De Castro</t>
+          <t>08/18/2026 – Ivan Caisapanta</t>
         </is>
       </c>
       <c r="H18" s="64" t="inlineStr">
         <is>
-          <t>Clara De Castro (Director, General Services &amp; Facilities) returns the signed attestation – attachment: Data_Integrity_Attestation_Santander-BCiC.pdf (signed Clara G. De Castro).</t>
+          <t>"Hi Elizabeth, You have my approval" – Financial Risk (BCiC Department Manager recorded as Xavier Caisapanta).</t>
         </is>
       </c>
       <c r="I18" s="64" t="inlineStr">
@@ -13817,12 +13915,12 @@
     <row r="19" ht="23" customHeight="1" s="71">
       <c r="A19" s="64" t="inlineStr">
         <is>
-          <t>DMA10</t>
+          <t>DMA09</t>
         </is>
       </c>
       <c r="B19" s="64" t="inlineStr">
         <is>
-          <t>DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml</t>
+          <t>DMA09_RE_ Management Attestation – DIV – General Services (Marketing &amp; General Services) - Clara De Castro 08-18-2026.msg</t>
         </is>
       </c>
       <c r="C19" s="64" t="inlineStr">
@@ -13832,7 +13930,7 @@
       </c>
       <c r="D19" s="64" t="inlineStr">
         <is>
-          <t>RE Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises).eml</t>
+          <t>RE_ Management Attestation – DIV General Services.msg</t>
         </is>
       </c>
       <c r="E19" s="64" t="inlineStr">
@@ -13842,17 +13940,17 @@
       </c>
       <c r="F19" s="64" t="inlineStr">
         <is>
-          <t>Email approval</t>
+          <t>Email attestation</t>
         </is>
       </c>
       <c r="G19" s="64" t="inlineStr">
         <is>
-          <t>08/21/2026 – Victoria Fernandez</t>
+          <t>08/18/2026 – Clara G. De Castro</t>
         </is>
       </c>
       <c r="H19" s="64" t="inlineStr">
         <is>
-          <t>"Approved" – Digital Wealth.</t>
+          <t>Clara De Castro (Director, General Services &amp; Facilities) returns the signed attestation – attachment: Data_Integrity_Attestation_Santander-BCiC.pdf (signed Clara G. De Castro).</t>
         </is>
       </c>
       <c r="I19" s="64" t="inlineStr">
@@ -13871,12 +13969,12 @@
     <row r="20" ht="23" customHeight="1" s="71">
       <c r="A20" s="64" t="inlineStr">
         <is>
-          <t>DMA11</t>
+          <t>DMA10</t>
         </is>
       </c>
       <c r="B20" s="64" t="inlineStr">
         <is>
-          <t>DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml</t>
+          <t>DMA10_RE_ Management Attestation – DIV – Digital Wealth - Victoria Fernandez 08-21-2026.eml</t>
         </is>
       </c>
       <c r="C20" s="64" t="inlineStr">
@@ -13886,7 +13984,7 @@
       </c>
       <c r="D20" s="64" t="inlineStr">
         <is>
-          <t>RE Management Attestation – DIV Commercial Middle Office.eml</t>
+          <t>RE Management Attestation – Data Integrity Validation Testing (November 2025 &amp; February 2026 Exercises).eml</t>
         </is>
       </c>
       <c r="E20" s="64" t="inlineStr">
@@ -13901,17 +13999,17 @@
       </c>
       <c r="G20" s="64" t="inlineStr">
         <is>
-          <t>09/09/2026 – Miguel Orozco</t>
+          <t>08/21/2026 – Victoria Fernandez</t>
         </is>
       </c>
       <c r="H20" s="64" t="inlineStr">
         <is>
-          <t>"I approve the integrity validation for the testing performed by the Commercial Middle Office."</t>
+          <t>"Approved" – Digital Wealth.</t>
         </is>
       </c>
       <c r="I20" s="64" t="inlineStr">
         <is>
-          <t>3299, 1937</t>
+          <t>1937</t>
         </is>
       </c>
       <c r="J20" s="64" t="inlineStr">
@@ -13925,12 +14023,12 @@
     <row r="21" ht="23" customHeight="1" s="71">
       <c r="A21" s="64" t="inlineStr">
         <is>
-          <t>DMA12</t>
+          <t>DMA11</t>
         </is>
       </c>
       <c r="B21" s="64" t="inlineStr">
         <is>
-          <t>DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml</t>
+          <t>DMA11_RE_ Management Attestation – DIV – Commercial Middle Office - Miguel Orozco 09-09-2026.eml</t>
         </is>
       </c>
       <c r="C21" s="64" t="inlineStr">
@@ -13940,7 +14038,7 @@
       </c>
       <c r="D21" s="64" t="inlineStr">
         <is>
-          <t>RE Management Attestation – DIV Client Servicing Unit.eml</t>
+          <t>RE Management Attestation – DIV Commercial Middle Office.eml</t>
         </is>
       </c>
       <c r="E21" s="64" t="inlineStr">
@@ -13955,17 +14053,17 @@
       </c>
       <c r="G21" s="64" t="inlineStr">
         <is>
-          <t>09/09/2026 – Liliana Vizhnay</t>
+          <t>09/09/2026 – Miguel Orozco</t>
         </is>
       </c>
       <c r="H21" s="64" t="inlineStr">
         <is>
-          <t>"I approve." – Client Servicing Unit.</t>
+          <t>"I approve the integrity validation for the testing performed by the Commercial Middle Office."</t>
         </is>
       </c>
       <c r="I21" s="64" t="inlineStr">
         <is>
-          <t>1937</t>
+          <t>3299, 1937</t>
         </is>
       </c>
       <c r="J21" s="64" t="inlineStr">
@@ -13979,12 +14077,12 @@
     <row r="22" ht="23" customHeight="1" s="71">
       <c r="A22" s="64" t="inlineStr">
         <is>
-          <t>DMA13</t>
+          <t>DMA12</t>
         </is>
       </c>
       <c r="B22" s="64" t="inlineStr">
         <is>
-          <t>DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml</t>
+          <t>DMA12_RE_ Management Attestation – DIV – Client Servicing Unit - Liliana Vizhnay 09-09-2026.eml</t>
         </is>
       </c>
       <c r="C22" s="64" t="inlineStr">
@@ -13994,7 +14092,7 @@
       </c>
       <c r="D22" s="64" t="inlineStr">
         <is>
-          <t>RE Management Attestation – DIV Unified Communication - Cisco Call Manager.eml</t>
+          <t>RE Management Attestation – DIV Client Servicing Unit.eml</t>
         </is>
       </c>
       <c r="E22" s="64" t="inlineStr">
@@ -14009,22 +14107,22 @@
       </c>
       <c r="G22" s="64" t="inlineStr">
         <is>
-          <t>09/09/2026 – Elizabeth Noda</t>
+          <t>09/09/2026 – Liliana Vizhnay</t>
         </is>
       </c>
       <c r="H22" s="64" t="inlineStr">
         <is>
-          <t>"approve" – Cisco Call Manager (IT). Cisco Call Manager is NOT one of the 10 tested applications – retained for completeness only.</t>
+          <t>"I approve." – Client Servicing Unit.</t>
         </is>
       </c>
       <c r="I22" s="64" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1937</t>
         </is>
       </c>
       <c r="J22" s="64" t="inlineStr">
         <is>
-          <t>Supplemental</t>
+          <t>G, H, J, O</t>
         </is>
       </c>
       <c r="K22" s="64" t="inlineStr"/>
@@ -14033,52 +14131,52 @@
     <row r="23" ht="23" customHeight="1" s="71">
       <c r="A23" s="64" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>DMA13</t>
         </is>
       </c>
       <c r="B23" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
+          <t>DMA13_RE_ Management Attestation – DIV – IT Unified Communication - Cisco Call Manager - Elizabeth Noda 09-09-2026 (out of scope).eml</t>
         </is>
       </c>
       <c r="C23" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
+          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals</t>
         </is>
       </c>
       <c r="D23" s="64" t="inlineStr">
         <is>
-          <t>Applications In Scope for DR Test BSI (13).xlsx</t>
+          <t>RE Management Attestation – DIV Unified Communication - Cisco Call Manager.eml</t>
         </is>
       </c>
       <c r="E23" s="64" t="inlineStr">
         <is>
-          <t>Data Integrity &amp; Email Testing Evidence.zip</t>
+          <t>DIV Manager Attestation Email_Approvals.zip</t>
         </is>
       </c>
       <c r="F23" s="64" t="inlineStr">
         <is>
-          <t>BCiC export</t>
+          <t>Email approval</t>
         </is>
       </c>
       <c r="G23" s="64" t="inlineStr">
         <is>
-          <t>BCiC – Applications In Scope for DR Test BSI</t>
+          <t>09/09/2026 – Elizabeth Noda</t>
         </is>
       </c>
       <c r="H23" s="64" t="inlineStr">
         <is>
-          <t>BCiC export of the BSI DR-scope population (43 applications) with Exercise Date and 2025 DR / Backup-Restore / DIV scope flags.</t>
+          <t>"approve" – Cisco Call Manager (IT). Cisco Call Manager is NOT one of the 10 tested applications – retained for completeness only.</t>
         </is>
       </c>
       <c r="I23" s="64" t="inlineStr">
         <is>
-          <t>1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J23" s="64" t="inlineStr">
         <is>
-          <t>B, C, D, K, L, N</t>
+          <t>Supplemental</t>
         </is>
       </c>
       <c r="K23" s="64" t="inlineStr"/>
@@ -14087,12 +14185,12 @@
     <row r="24" ht="23" customHeight="1" s="71">
       <c r="A24" s="64" t="inlineStr">
         <is>
-          <t>E02</t>
+          <t>E01</t>
         </is>
       </c>
       <c r="B24" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg</t>
+          <t>BSI.IT.6.C7.3_E01_Applications In Scope for DR Test BSI (13).xlsx</t>
         </is>
       </c>
       <c r="C24" s="64" t="inlineStr">
@@ -14102,7 +14200,7 @@
       </c>
       <c r="D24" s="64" t="inlineStr">
         <is>
-          <t>screenshot BCiC apps in scope for DR Testing.jpg</t>
+          <t>Applications In Scope for DR Test BSI (13).xlsx</t>
         </is>
       </c>
       <c r="E24" s="64" t="inlineStr">
@@ -14112,17 +14210,17 @@
       </c>
       <c r="F24" s="64" t="inlineStr">
         <is>
-          <t>BCiC screenshot</t>
+          <t>BCiC export</t>
         </is>
       </c>
       <c r="G24" s="64" t="inlineStr">
         <is>
-          <t>09/10/2026 – Cesar Vidal</t>
+          <t>BCiC – Applications In Scope for DR Test BSI</t>
         </is>
       </c>
       <c r="H24" s="64" t="inlineStr">
         <is>
-          <t>BCiC Applications screen with view 'Applications In Scope for DR Test BSI' selected (1–20 of 43 items).</t>
+          <t>BCiC export of the BSI DR-scope population (43 applications) with Exercise Date and 2025 DR / Backup-Restore / DIV scope flags.</t>
         </is>
       </c>
       <c r="I24" s="64" t="inlineStr">
@@ -14132,7 +14230,7 @@
       </c>
       <c r="J24" s="64" t="inlineStr">
         <is>
-          <t>D, K, N</t>
+          <t>B, C, D, K, L, N</t>
         </is>
       </c>
       <c r="K24" s="64" t="inlineStr"/>
@@ -14141,12 +14239,12 @@
     <row r="25" ht="23" customHeight="1" s="71">
       <c r="A25" s="64" t="inlineStr">
         <is>
-          <t>E03</t>
+          <t>E02</t>
         </is>
       </c>
       <c r="B25" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
+          <t>BSI.IT.6.C7.3_E02_screenshot BCiC apps in scope for DR Testing.jpg</t>
         </is>
       </c>
       <c r="C25" s="64" t="inlineStr">
@@ -14156,7 +14254,7 @@
       </c>
       <c r="D25" s="64" t="inlineStr">
         <is>
-          <t>All Data Integrity Validation Testing_FV.xls</t>
+          <t>screenshot BCiC apps in scope for DR Testing.jpg</t>
         </is>
       </c>
       <c r="E25" s="64" t="inlineStr">
@@ -14166,17 +14264,17 @@
       </c>
       <c r="F25" s="64" t="inlineStr">
         <is>
-          <t>BCiC export</t>
+          <t>BCiC screenshot</t>
         </is>
       </c>
       <c r="G25" s="64" t="inlineStr">
         <is>
-          <t>BCiC – Data Integrity Validation Testing (62 records)</t>
+          <t>09/10/2026 – Cesar Vidal</t>
         </is>
       </c>
       <c r="H25" s="64" t="inlineStr">
         <is>
-          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Y/N Format/Headers/Content, Attestation Date / Provided By. Row numbers quoted are Excel rows.</t>
+          <t>BCiC Applications screen with view 'Applications In Scope for DR Test BSI' selected (1–20 of 43 items).</t>
         </is>
       </c>
       <c r="I25" s="64" t="inlineStr">
@@ -14186,7 +14284,7 @@
       </c>
       <c r="J25" s="64" t="inlineStr">
         <is>
-          <t>B, C, D, E, F, G, H, I, K, L, M, O, P</t>
+          <t>D, K, N</t>
         </is>
       </c>
       <c r="K25" s="64" t="inlineStr"/>
@@ -14195,12 +14293,12 @@
     <row r="26">
       <c r="A26" s="64" t="inlineStr">
         <is>
-          <t>E04</t>
+          <t>E03</t>
         </is>
       </c>
       <c r="B26" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg</t>
+          <t>BSI.IT.6.C7.3_E03_All Data Integrity Validation Testing_FV.xls</t>
         </is>
       </c>
       <c r="C26" s="64" t="inlineStr">
@@ -14210,7 +14308,7 @@
       </c>
       <c r="D26" s="64" t="inlineStr">
         <is>
-          <t>BCiC_Screenshot for Data Integrity Validation report.jpg</t>
+          <t>All Data Integrity Validation Testing_FV.xls</t>
         </is>
       </c>
       <c r="E26" s="64" t="inlineStr">
@@ -14220,17 +14318,17 @@
       </c>
       <c r="F26" s="64" t="inlineStr">
         <is>
-          <t>BCiC screenshot</t>
+          <t>BCiC export</t>
         </is>
       </c>
       <c r="G26" s="64" t="inlineStr">
         <is>
-          <t>09/10/2026 – Cesar Vidal</t>
+          <t>BCiC – Data Integrity Validation Testing (62 records)</t>
         </is>
       </c>
       <c r="H26" s="64" t="inlineStr">
         <is>
-          <t>BCiC 'Data Integrity Validation Testing' screen (1–20 of 66 items) showing tester, validation date, manager, approval date, Y/N results and attestation fields.</t>
+          <t>BCiC DIV export incl. Business Tester, Business Data Validation Date, Department Manager, Department Manager Approval Date, Y/N Format/Headers/Content, Attestation Date / Provided By. Row numbers quoted are Excel rows.</t>
         </is>
       </c>
       <c r="I26" s="64" t="inlineStr">
@@ -14240,7 +14338,7 @@
       </c>
       <c r="J26" s="64" t="inlineStr">
         <is>
-          <t>D, E, F, G, H, K, P</t>
+          <t>B, C, D, E, F, G, H, I, K, L, M, O, P</t>
         </is>
       </c>
       <c r="K26" s="64" t="inlineStr"/>
@@ -14249,12 +14347,12 @@
     <row r="27">
       <c r="A27" s="64" t="inlineStr">
         <is>
-          <t>E05</t>
+          <t>E04</t>
         </is>
       </c>
       <c r="B27" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg</t>
+          <t>BSI.IT.6.C7.3_E04_BCiC_Screenshot for Data Integrity Validation report.jpg</t>
         </is>
       </c>
       <c r="C27" s="64" t="inlineStr">
@@ -14264,7 +14362,7 @@
       </c>
       <c r="D27" s="64" t="inlineStr">
         <is>
-          <t>IT BIA Results Review and preparation for DR .msg</t>
+          <t>BCiC_Screenshot for Data Integrity Validation report.jpg</t>
         </is>
       </c>
       <c r="E27" s="64" t="inlineStr">
@@ -14274,17 +14372,17 @@
       </c>
       <c r="F27" s="64" t="inlineStr">
         <is>
-          <t>Meeting invite</t>
+          <t>BCiC screenshot</t>
         </is>
       </c>
       <c r="G27" s="64" t="inlineStr">
         <is>
-          <t>09/15/2025 – Elizabeth Noda</t>
+          <t>09/10/2026 – Cesar Vidal</t>
         </is>
       </c>
       <c r="H27" s="64" t="inlineStr">
         <is>
-          <t>IT DR meeting invite to review the 2025 BIA results and applications list ahead of the DR exercise (same invite re-sent 09/18/2025 – duplicate E06 removed).</t>
+          <t>BCiC 'Data Integrity Validation Testing' screen (1–20 of 66 items) showing tester, validation date, manager, approval date, Y/N results and attestation fields.</t>
         </is>
       </c>
       <c r="I27" s="64" t="inlineStr">
@@ -14294,7 +14392,7 @@
       </c>
       <c r="J27" s="64" t="inlineStr">
         <is>
-          <t>M, N</t>
+          <t>D, E, F, G, H, K, P</t>
         </is>
       </c>
       <c r="K27" s="64" t="inlineStr"/>
@@ -14303,12 +14401,12 @@
     <row r="28">
       <c r="A28" s="64" t="inlineStr">
         <is>
-          <t>E07</t>
+          <t>E05</t>
         </is>
       </c>
       <c r="B28" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg</t>
+          <t>BSI.IT.6.C7.3_E05_IT BIA Results Review and preparation for DR .msg</t>
         </is>
       </c>
       <c r="C28" s="64" t="inlineStr">
@@ -14318,7 +14416,7 @@
       </c>
       <c r="D28" s="64" t="inlineStr">
         <is>
-          <t>DATA INTERITY FILS FROM 111425.msg</t>
+          <t>IT BIA Results Review and preparation for DR .msg</t>
         </is>
       </c>
       <c r="E28" s="64" t="inlineStr">
@@ -14328,27 +14426,27 @@
       </c>
       <c r="F28" s="64" t="inlineStr">
         <is>
-          <t>Email + report attachments</t>
+          <t>Meeting invite</t>
         </is>
       </c>
       <c r="G28" s="64" t="inlineStr">
         <is>
-          <t>11/15/2025 – Frank Puentes</t>
+          <t>09/15/2025 – Elizabeth Noda</t>
         </is>
       </c>
       <c r="H28" s="64" t="inlineStr">
         <is>
-          <t>Pre-DR (11/14/2025) source reports: Fedlink, OFAC ACH/FED/SWIFT, Payment Monitor, SWIFT Interface Monitor, outgoing Fedwire/SWIFT. Embedded attachments: FEDLINK INCOMING FEDWIRES 111425 0523PM.pdf; FEDLINK OUTGOING FEDWIRES 111425 0523PM.pdf; OFAC ACH 111425 0512PM.pdf; OFAC FED 111425 0511PM.pdf; OFAC SWIFT 111425 0511PM.pdf; OUTGOING FEDWIRE 111425 506PM.xls; OUTGOING SWIFT 111425 509PM.xls; PAYMENT MONITOR INCOMING FEDWIRE 111425 516PM PG1.pdf; PAYMENT MONITOR INCOMING FEDWIRE 111425 516PM PG2.pdf; PAYMENT MONITOR OUTGOING FEDWIRE 111425 516PM PG1.pdf; PAYMENT MONITOR OUTGOING FEDWIRE 111425 516PM PG2.pdf; SWIFT INTERFACE MONITOR 111425 519PM.pdf; SWIFT INTERFACE MONITOR 111425 520PM 2ND SAMPLE.pdf.</t>
+          <t>IT DR meeting invite to review the 2025 BIA results and applications list ahead of the DR exercise (same invite re-sent 09/18/2025 – duplicate E06 removed).</t>
         </is>
       </c>
       <c r="I28" s="64" t="inlineStr">
         <is>
-          <t>3301, 1903, 1936, 1937</t>
+          <t>1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
         </is>
       </c>
       <c r="J28" s="64" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M, N</t>
         </is>
       </c>
       <c r="K28" s="64" t="inlineStr"/>
@@ -14357,12 +14455,12 @@
     <row r="29">
       <c r="A29" s="64" t="inlineStr">
         <is>
-          <t>E08</t>
+          <t>E07</t>
         </is>
       </c>
       <c r="B29" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg</t>
+          <t>BSI.IT.6.C7.3_E07_DATA INTERITY FILS FROM 111425.msg</t>
         </is>
       </c>
       <c r="C29" s="64" t="inlineStr">
@@ -14372,7 +14470,7 @@
       </c>
       <c r="D29" s="64" t="inlineStr">
         <is>
-          <t>FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg</t>
+          <t>DATA INTERITY FILS FROM 111425.msg</t>
         </is>
       </c>
       <c r="E29" s="64" t="inlineStr">
@@ -14392,7 +14490,7 @@
       </c>
       <c r="H29" s="64" t="inlineStr">
         <is>
-          <t>DR test-day (11/15/2025) re-run of the same reports for comparison with 11/14/2025 source. Embedded attachments: FEDLINK INCOMING FEDWIRES 111425 -1115 1148AM.pdf; FEDLINK OUTGOINT TRANSFERS 114125 - 111525 1144AM.pdf; OFAC ACH 111425 - 11152025 1126AM.pdf; OFAC FED 111425 - 111525 1126AM.pdf; OFAC SWIFT 111425 - 111525 1128AM.pdf; OUTGOING FEDWIRE 111525 1025AM.xls; OUTGOING SWIFT 111525 1026AM.xls; PAYMENT MONITOR 111424 - 111525 PG 11156AM.pdf; PAYMENT MONITOR 111425 - 111525 PG 2 1158AM.pdf; PAYMENT MONITOR OUTGOING 111425 - 111525 PG 1 1156AM.pdf; PAYMENT MONITOR OUTGOING 111425 - 111525 PG 2 1156AM.pdf; SWIFT INTERFACE MONITOR INCOMING MT103 111425 - 111525 1152AM.pdf; SWIFT INTERFACE MONITOR INCOMING MT199 111425 -111525 1152AM.pdf.</t>
+          <t>Pre-DR (11/14/2025) source reports: Fedlink, OFAC ACH/FED/SWIFT, Payment Monitor, SWIFT Interface Monitor, outgoing Fedwire/SWIFT. Embedded attachments: FEDLINK INCOMING FEDWIRES 111425 0523PM.pdf; FEDLINK OUTGOING FEDWIRES 111425 0523PM.pdf; OFAC ACH 111425 0512PM.pdf; OFAC FED 111425 0511PM.pdf; OFAC SWIFT 111425 0511PM.pdf; OUTGOING FEDWIRE 111425 506PM.xls; OUTGOING SWIFT 111425 509PM.xls; PAYMENT MONITOR INCOMING FEDWIRE 111425 516PM PG1.pdf; PAYMENT MONITOR INCOMING FEDWIRE 111425 516PM PG2.pdf; PAYMENT MONITOR OUTGOING FEDWIRE 111425 516PM PG1.pdf; PAYMENT MONITOR OUTGOING FEDWIRE 111425 516PM PG2.pdf; SWIFT INTERFACE MONITOR 111425 519PM.pdf; SWIFT INTERFACE MONITOR 111425 520PM 2ND SAMPLE.pdf.</t>
         </is>
       </c>
       <c r="I29" s="64" t="inlineStr">
@@ -14402,7 +14500,7 @@
       </c>
       <c r="J29" s="64" t="inlineStr">
         <is>
-          <t>F, M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="K29" s="64" t="inlineStr"/>
@@ -14411,12 +14509,12 @@
     <row r="30">
       <c r="A30" s="64" t="inlineStr">
         <is>
-          <t>E09</t>
+          <t>E08</t>
         </is>
       </c>
       <c r="B30" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg</t>
+          <t>BSI.IT.6.C7.3_E08_FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg</t>
         </is>
       </c>
       <c r="C30" s="64" t="inlineStr">
@@ -14426,7 +14524,7 @@
       </c>
       <c r="D30" s="64" t="inlineStr">
         <is>
-          <t>RE_ Yearly Backup and restore exercise (Client Back Office)</t>
+          <t>FILES FROM 111525 DR TEST - DATA COMPARISON FROM 111425.msg</t>
         </is>
       </c>
       <c r="E30" s="64" t="inlineStr">
@@ -14436,27 +14534,27 @@
       </c>
       <c r="F30" s="64" t="inlineStr">
         <is>
-          <t>Email approval</t>
+          <t>Email + report attachments</t>
         </is>
       </c>
       <c r="G30" s="64" t="inlineStr">
         <is>
-          <t>03/03/2026 – 05/05/2026 – Claudia Romero</t>
+          <t>11/15/2025 – Frank Puentes</t>
         </is>
       </c>
       <c r="H30" s="64" t="inlineStr">
         <is>
-          <t>Client Back Office test evidence (Mariorly Morales, Ilumel Rodriguez, Rolando Bonilla) and Claudia Romero "Approved." 05/05/2026. Thread maps ACH Express, FedExport, FedImport, Imaging101 to Client Back Office / Claudia Romero.</t>
+          <t>DR test-day (11/15/2025) re-run of the same reports for comparison with 11/14/2025 source. Embedded attachments: FEDLINK INCOMING FEDWIRES 111425 -1115 1148AM.pdf; FEDLINK OUTGOINT TRANSFERS 114125 - 111525 1144AM.pdf; OFAC ACH 111425 - 11152025 1126AM.pdf; OFAC FED 111425 - 111525 1126AM.pdf; OFAC SWIFT 111425 - 111525 1128AM.pdf; OUTGOING FEDWIRE 111525 1025AM.xls; OUTGOING SWIFT 111525 1026AM.xls; PAYMENT MONITOR 111424 - 111525 PG 11156AM.pdf; PAYMENT MONITOR 111425 - 111525 PG 2 1158AM.pdf; PAYMENT MONITOR OUTGOING 111425 - 111525 PG 1 1156AM.pdf; PAYMENT MONITOR OUTGOING 111425 - 111525 PG 2 1156AM.pdf; SWIFT INTERFACE MONITOR INCOMING MT103 111425 - 111525 1152AM.pdf; SWIFT INTERFACE MONITOR INCOMING MT199 111425 -111525 1152AM.pdf.</t>
         </is>
       </c>
       <c r="I30" s="64" t="inlineStr">
         <is>
-          <t>1822, 1867, 1868, 3299, 1937</t>
+          <t>3301, 1903, 1936, 1937</t>
         </is>
       </c>
       <c r="J30" s="64" t="inlineStr">
         <is>
-          <t>E, G, H, J, M, N, O</t>
+          <t>F, M</t>
         </is>
       </c>
       <c r="K30" s="64" t="inlineStr"/>
@@ -14465,12 +14563,12 @@
     <row r="31">
       <c r="A31" s="64" t="inlineStr">
         <is>
-          <t>E10</t>
+          <t>E09</t>
         </is>
       </c>
       <c r="B31" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg</t>
+          <t>BSI.IT.6.C7.3_E09_RE_ Yearly Backup and restore exercise- client back office sign off-ACH,ACH Express, FedExport, FedImport,Imagi.msg</t>
         </is>
       </c>
       <c r="C31" s="64" t="inlineStr">
@@ -14480,7 +14578,7 @@
       </c>
       <c r="D31" s="64" t="inlineStr">
         <is>
-          <t>RE_ Yearly Backup and restore exercise-- re-run (Finance)</t>
+          <t>RE_ Yearly Backup and restore exercise (Client Back Office)</t>
         </is>
       </c>
       <c r="E31" s="64" t="inlineStr">
@@ -14495,22 +14593,22 @@
       </c>
       <c r="G31" s="64" t="inlineStr">
         <is>
-          <t>03/09/2026 – Lina Acuna</t>
+          <t>03/03/2026 – 05/05/2026 – Claudia Romero</t>
         </is>
       </c>
       <c r="H31" s="64" t="inlineStr">
         <is>
-          <t>Finance DIV results chart (Jose Acero) and Lina Acuna "Approved" 03/09/2026 (T24 / ReconXpert backup-restore).</t>
+          <t>Client Back Office test evidence (Mariorly Morales, Ilumel Rodriguez, Rolando Bonilla) and Claudia Romero "Approved." 05/05/2026. Thread maps ACH Express, FedExport, FedImport, Imaging101 to Client Back Office / Claudia Romero.</t>
         </is>
       </c>
       <c r="I31" s="64" t="inlineStr">
         <is>
-          <t>1917, 1937</t>
+          <t>1822, 1867, 1868, 3299, 1937</t>
         </is>
       </c>
       <c r="J31" s="64" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>E, G, H, J, M, N, O</t>
         </is>
       </c>
       <c r="K31" s="64" t="inlineStr"/>
@@ -14519,12 +14617,12 @@
     <row r="32">
       <c r="A32" s="64" t="inlineStr">
         <is>
-          <t>E13</t>
+          <t>E10</t>
         </is>
       </c>
       <c r="B32" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg</t>
+          <t>BSI.IT.6.C7.3_E10_RE_ Yearly Backup and restore exercise-- re-run- Finance approval-T24-ReconXpert.msg</t>
         </is>
       </c>
       <c r="C32" s="64" t="inlineStr">
@@ -14534,7 +14632,7 @@
       </c>
       <c r="D32" s="64" t="inlineStr">
         <is>
-          <t>miasx2 T24 environment(s) miaeod miabed01 refreshed correctly.msg</t>
+          <t>RE_ Yearly Backup and restore exercise-- re-run (Finance)</t>
         </is>
       </c>
       <c r="E32" s="64" t="inlineStr">
@@ -14544,27 +14642,27 @@
       </c>
       <c r="F32" s="64" t="inlineStr">
         <is>
-          <t>System email</t>
+          <t>Email approval</t>
         </is>
       </c>
       <c r="G32" s="64" t="inlineStr">
         <is>
-          <t>11/13/2024 – T24 backup user</t>
+          <t>03/09/2026 – Lina Acuna</t>
         </is>
       </c>
       <c r="H32" s="64" t="inlineStr">
         <is>
-          <t>T24 environment refresh log – prior period (outside review period); supplemental only.</t>
+          <t>Finance DIV results chart (Jose Acero) and Lina Acuna "Approved" 03/09/2026 (T24 / ReconXpert backup-restore).</t>
         </is>
       </c>
       <c r="I32" s="64" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1917, 1937</t>
         </is>
       </c>
       <c r="J32" s="64" t="inlineStr">
         <is>
-          <t>Supplemental</t>
+          <t>M</t>
         </is>
       </c>
       <c r="K32" s="64" t="inlineStr"/>
@@ -14573,12 +14671,12 @@
     <row r="33">
       <c r="A33" s="64" t="inlineStr">
         <is>
-          <t>E16b</t>
+          <t>E13</t>
         </is>
       </c>
       <c r="B33" s="64" t="inlineStr">
         <is>
-          <t>BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
+          <t>BSI.IT.6.C7.3_E13_miasx2 T24 environment(s)  miaeod miabed01 refreshed correctly.msg</t>
         </is>
       </c>
       <c r="C33" s="64" t="inlineStr">
@@ -14588,7 +14686,7 @@
       </c>
       <c r="D33" s="64" t="inlineStr">
         <is>
-          <t>All Data Integrity Validation Testing-BSI 2025-26.xlsx (attachment of DMA05 email)</t>
+          <t>miasx2 T24 environment(s) miaeod miabed01 refreshed correctly.msg</t>
         </is>
       </c>
       <c r="E33" s="64" t="inlineStr">
@@ -14598,52 +14696,88 @@
       </c>
       <c r="F33" s="64" t="inlineStr">
         <is>
-          <t>BCiC export</t>
+          <t>System email</t>
         </is>
       </c>
       <c r="G33" s="64" t="inlineStr">
         <is>
-          <t>08/2026 – BCiC export sent with attestation request</t>
+          <t>11/13/2024 – T24 backup user</t>
         </is>
       </c>
       <c r="H33" s="64" t="inlineStr">
         <is>
-          <t>BCiC DIV export 2025-26 (64 rows; no manager columns) sent to managers with the attestation request and returned by M. T. Del Cerro (DMA05). Row numbers are Excel rows.</t>
+          <t>T24 environment refresh log – prior period (outside review period); supplemental only.</t>
         </is>
       </c>
       <c r="I33" s="64" t="inlineStr">
         <is>
-          <t>1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J33" s="64" t="inlineStr">
         <is>
-          <t>B, D, E, F, I, K, P</t>
+          <t>Supplemental</t>
         </is>
       </c>
       <c r="K33" s="64" t="inlineStr"/>
       <c r="L33" s="82" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="82" t="n"/>
-      <c r="B34" s="82" t="n"/>
-      <c r="C34" s="82" t="n"/>
-      <c r="D34" s="82" t="n"/>
-      <c r="E34" s="82" t="n"/>
-      <c r="F34" s="82" t="n"/>
-      <c r="G34" s="82" t="n"/>
-      <c r="H34" s="82" t="n"/>
-      <c r="I34" s="82" t="n"/>
-      <c r="J34" s="82" t="n"/>
-      <c r="K34" s="82" t="n"/>
+      <c r="A34" s="64" t="inlineStr">
+        <is>
+          <t>E16b</t>
+        </is>
+      </c>
+      <c r="B34" s="64" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3_E16b_All Data Integrity Validation Testing-BSI 2025-26.xlsx</t>
+        </is>
+      </c>
+      <c r="C34" s="64" t="inlineStr">
+        <is>
+          <t>BSI.IT.6.C7.3-Evidences\04_Data_Integrity_and_Email_Testing_Evidence</t>
+        </is>
+      </c>
+      <c r="D34" s="64" t="inlineStr">
+        <is>
+          <t>All Data Integrity Validation Testing-BSI 2025-26.xlsx (attachment of DMA05 email)</t>
+        </is>
+      </c>
+      <c r="E34" s="64" t="inlineStr">
+        <is>
+          <t>Data Integrity &amp; Email Testing Evidence.zip</t>
+        </is>
+      </c>
+      <c r="F34" s="64" t="inlineStr">
+        <is>
+          <t>BCiC export</t>
+        </is>
+      </c>
+      <c r="G34" s="64" t="inlineStr">
+        <is>
+          <t>08/2026 – BCiC export sent with attestation request</t>
+        </is>
+      </c>
+      <c r="H34" s="64" t="inlineStr">
+        <is>
+          <t>BCiC DIV export 2025-26 (64 rows; no manager columns) sent to managers with the attestation request and returned by M. T. Del Cerro (DMA05). Row numbers are Excel rows.</t>
+        </is>
+      </c>
+      <c r="I34" s="64" t="inlineStr">
+        <is>
+          <t>1822, 1867, 1868, 3299, 4052, 3301, 1903, 1917, 1936, 1937</t>
+        </is>
+      </c>
+      <c r="J34" s="64" t="inlineStr">
+        <is>
+          <t>B, D, E, F, I, K, P</t>
+        </is>
+      </c>
+      <c r="K34" s="64" t="inlineStr"/>
       <c r="L34" s="82" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="60" t="inlineStr">
-        <is>
-          <t>Redundant files removed from the repository (one copy of each item retained)</t>
-        </is>
-      </c>
+      <c r="A35" s="82" t="n"/>
       <c r="B35" s="82" t="n"/>
       <c r="C35" s="82" t="n"/>
       <c r="D35" s="82" t="n"/>
@@ -14657,31 +14791,15 @@
       <c r="L35" s="82" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Removed item</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Former location</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Retained ref</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Retained file location</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Reason</t>
-        </is>
-      </c>
+      <c r="A36" s="60" t="inlineStr">
+        <is>
+          <t>Redundant files removed from the repository (one copy of each item retained)</t>
+        </is>
+      </c>
+      <c r="B36" s="82" t="n"/>
+      <c r="C36" s="82" t="n"/>
+      <c r="D36" s="82" t="n"/>
+      <c r="E36" s="82" t="n"/>
       <c r="F36" s="82" t="n"/>
       <c r="G36" s="82" t="n"/>
       <c r="H36" s="82" t="n"/>
@@ -14691,29 +14809,29 @@
       <c r="L36" s="82" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="64" t="inlineStr">
-        <is>
-          <t>MA02</t>
-        </is>
-      </c>
-      <c r="B37" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\01_Management_Attestation_In-Scope_Applications\MA02_RE_ Management Attestation – DIV Testing (Nov 2025 &amp; Feb 2026) – Payments &amp; Cash Management – Frank Puentes 08-18-2026.msg</t>
-        </is>
-      </c>
-      <c r="C37" s="64" t="inlineStr">
-        <is>
-          <t>DMA03</t>
-        </is>
-      </c>
-      <c r="D37" s="64" t="inlineStr">
-        <is>
-          <t>BSI.IT.6.C7.3-Evidences\03_DIV_Manager_Attestation_Email_Approvals\DMA03_RE_ Management Attestation – DIV – Payments &amp; Cash Management - Frank Puentes 08-18-2026.msg</t>
-        </is>
-      </c>
-      <c r="E37" s="64" t="inlineStr">
-        <is>
-          <t>same email message (subject, sent 08/18/2026 14:50, attachment 4069_001.pdf)</t>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Removed item</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Former location</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Retained ref</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Retained file location</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Reason</t>
         </is>
       </c>
       <c r="F37" s="82" t="n"/>
@@ -16327,7 +16445,7 @@
       <c r="L120" s="82" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:K33"/>
+  <autoFilter ref="A2:K34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>